--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2061,13 +2061,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46161.41396914352</v>
+        <v>46161.58063581018</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.71184347222</v>
+        <v>46175.87851013889</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.71185716435</v>
+        <v>46175.87852383102</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2114,13 +2114,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46161.41407934028</v>
+        <v>46161.58074600695</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.71181634259</v>
+        <v>46175.87848300926</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.71184372685</v>
+        <v>46175.87851039352</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2177,13 +2177,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46161.414082407406</v>
+        <v>46161.58074907407</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.711817187504</v>
+        <v>46175.87848385416</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.71184388889</v>
+        <v>46175.87851055556</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2240,13 +2240,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46161.41408527778</v>
+        <v>46161.58075194445</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.71181774305</v>
+        <v>46175.878484409724</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.71184383101</v>
+        <v>46175.878510497685</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2303,13 +2303,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46161.414087997684</v>
+        <v>46161.58075466435</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.71181836806</v>
+        <v>46175.87848503472</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.71184425926</v>
+        <v>46175.878510925926</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2366,13 +2366,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46161.41409119213</v>
+        <v>46161.5807578588</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.711819097225</v>
+        <v>46175.87848576389</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.71184429398</v>
+        <v>46175.87851096065</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2429,11 +2429,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46161.413972951384</v>
+        <v>46161.580639618056</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46161.51805387731</v>
+        <v>46161.684720543984</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2476,11 +2476,11 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46161.41409464121</v>
+        <v>46161.580761307865</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46175.71184089121</v>
+        <v>46175.87850755787</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2539,11 +2539,11 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46161.4140996412</v>
+        <v>46161.580766307874</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46175.71184059027</v>
+        <v>46175.878507256944</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2602,11 +2602,11 @@
         <v>62</v>
       </c>
       <c r="B13" s="9">
-        <v>46161.41410475694</v>
+        <v>46161.580771423614</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46175.7118409838</v>
+        <v>46175.878507650465</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>63</v>
@@ -2665,11 +2665,11 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46161.414109537036</v>
+        <v>46161.5807762037</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46163.01520310185</v>
+        <v>46163.18186976852</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2728,11 +2728,11 @@
         <v>70</v>
       </c>
       <c r="B15" s="9">
-        <v>46161.413977372686</v>
+        <v>46161.58064403935</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46161.57006081019</v>
+        <v>46161.73672747685</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>71</v>
@@ -2775,11 +2775,11 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46161.414116875</v>
+        <v>46161.58078354166</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46169.712868125</v>
+        <v>46169.87953479167</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2838,11 +2838,11 @@
         <v>76</v>
       </c>
       <c r="B17" s="9">
-        <v>46161.414122013884</v>
+        <v>46161.580788680556</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46169.71287873843</v>
+        <v>46169.87954540509</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>77</v>
@@ -2901,11 +2901,11 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46161.41412696759</v>
+        <v>46161.58079363426</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46169.712889965274</v>
+        <v>46169.879556631946</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2964,11 +2964,11 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46161.41413237268</v>
+        <v>46161.58079903935</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46169.712906643515</v>
+        <v>46169.87957331019</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -3027,11 +3027,11 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46161.414137071755</v>
+        <v>46161.58080373843</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46169.71291747685</v>
+        <v>46169.87958414352</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -3090,11 +3090,11 @@
         <v>92</v>
       </c>
       <c r="B21" s="9">
-        <v>46161.414140740744</v>
+        <v>46161.58080740741</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46169.71293371527</v>
+        <v>46169.879600381944</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>93</v>
@@ -3153,11 +3153,11 @@
         <v>95</v>
       </c>
       <c r="B22" s="5">
-        <v>46161.41414407408</v>
+        <v>46161.580810740736</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46169.7129465162</v>
+        <v>46169.87961318287</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>96</v>
@@ -3216,11 +3216,11 @@
         <v>98</v>
       </c>
       <c r="B23" s="9">
-        <v>46161.4139812963</v>
+        <v>46161.58064796297</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46161.571204548614</v>
+        <v>46161.73787121528</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>99</v>
@@ -3263,11 +3263,11 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46161.414148055555</v>
+        <v>46161.58081472223</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.71271201389</v>
+        <v>46169.879378680555</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -3326,11 +3326,11 @@
         <v>106</v>
       </c>
       <c r="B25" s="9">
-        <v>46161.414152349535</v>
+        <v>46161.580819016206</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.71297789352</v>
+        <v>46169.879644560184</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>107</v>
@@ -3385,11 +3385,11 @@
         <v>109</v>
       </c>
       <c r="B26" s="5">
-        <v>46161.41415684028</v>
+        <v>46161.58082350694</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.7130025463</v>
+        <v>46169.87966921296</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>110</v>
@@ -3444,11 +3444,11 @@
         <v>112</v>
       </c>
       <c r="B27" s="9">
-        <v>46161.414161574074</v>
+        <v>46161.58082824074</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46172.01690824074</v>
+        <v>46172.18357490741</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
@@ -3507,11 +3507,11 @@
         <v>115</v>
       </c>
       <c r="B28" s="5">
-        <v>46161.41416587963</v>
+        <v>46161.5808325463</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.713031562496</v>
+        <v>46169.87969822917</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>116</v>
@@ -3566,11 +3566,11 @@
         <v>118</v>
       </c>
       <c r="B29" s="9">
-        <v>46161.41417030092</v>
+        <v>46161.580836967594</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46171.00685518519</v>
+        <v>46171.17352185185</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>119</v>
@@ -3625,11 +3625,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46161.41417498843</v>
+        <v>46161.58084165509</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.71275505787</v>
+        <v>46169.87942172454</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3688,11 +3688,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46161.414179363426</v>
+        <v>46161.58084603009</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46175.00358978009</v>
+        <v>46175.170256446756</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3747,11 +3747,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46161.414183773144</v>
+        <v>46161.580850439816</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.71309979167</v>
+        <v>46169.87976645833</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3806,11 +3806,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46161.41418836806</v>
+        <v>46161.58085503472</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.71311195602</v>
+        <v>46169.879778622686</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3865,11 +3865,11 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46161.41419274306</v>
+        <v>46161.58085940972</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.71276568287</v>
+        <v>46169.87943234954</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3928,11 +3928,11 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46161.41419697917</v>
+        <v>46161.58086364584</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.7131435301</v>
+        <v>46169.879810196755</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3987,11 +3987,11 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46161.41420165509</v>
+        <v>46161.58086832176</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.7131621875</v>
+        <v>46169.879828854166</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -4046,11 +4046,11 @@
         <v>144</v>
       </c>
       <c r="B37" s="9">
-        <v>46161.4142065625</v>
+        <v>46161.58087322916</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.71277699074</v>
+        <v>46169.87944365741</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>145</v>
@@ -4109,11 +4109,11 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46161.41426435186</v>
+        <v>46161.580931018514</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.713187395835</v>
+        <v>46169.8798540625</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>91</v>
@@ -4162,11 +4162,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46161.41426980324</v>
+        <v>46161.58093646991</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.713198495374</v>
+        <v>46169.87986516204</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -4215,11 +4215,11 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46161.41427443287</v>
+        <v>46161.580941099535</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.71278662037</v>
+        <v>46169.87945328704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>153</v>
@@ -4278,11 +4278,11 @@
         <v>157</v>
       </c>
       <c r="B41" s="9">
-        <v>46161.41427865741</v>
+        <v>46161.58094532407</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.713237442134</v>
+        <v>46169.87990410879</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>97</v>
@@ -4331,11 +4331,11 @@
         <v>159</v>
       </c>
       <c r="B42" s="5">
-        <v>46161.41428331019</v>
+        <v>46161.58094997685</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.713248541666</v>
+        <v>46169.87991520834</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>160</v>
@@ -4384,11 +4384,11 @@
         <v>162</v>
       </c>
       <c r="B43" s="9">
-        <v>46161.4142878125</v>
+        <v>46161.58095447917</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.71326314815</v>
+        <v>46169.879929814815</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>163</v>
@@ -4437,11 +4437,11 @@
         <v>166</v>
       </c>
       <c r="B44" s="5">
-        <v>46161.41429076389</v>
+        <v>46161.58095743056</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.712851585646</v>
+        <v>46169.87951825232</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>167</v>
@@ -4500,11 +4500,11 @@
         <v>169</v>
       </c>
       <c r="B45" s="9">
-        <v>46161.41429424769</v>
+        <v>46161.58096091435</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.71330668981</v>
+        <v>46169.87997335648</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>94</v>
@@ -4553,11 +4553,11 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46161.41429832176</v>
+        <v>46161.580964988425</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.713330983795</v>
+        <v>46169.87999765047</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4606,11 +4606,11 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46161.41398572917</v>
+        <v>46161.58065239583</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46161.56942581019</v>
+        <v>46161.73609247685</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4653,11 +4653,11 @@
         <v>177</v>
       </c>
       <c r="B48" s="5">
-        <v>46161.41430311343</v>
+        <v>46161.580969780094</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46171.00413296296</v>
+        <v>46171.17079962963</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4716,11 +4716,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46161.414308402775</v>
+        <v>46161.580975069446</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46161.67789128472</v>
+        <v>46161.844557951394</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4779,11 +4779,11 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46161.414314340276</v>
+        <v>46161.58098100695</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46161.67788876157</v>
+        <v>46161.84455542824</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>87</v>
@@ -4842,11 +4842,11 @@
         <v>188</v>
       </c>
       <c r="B51" s="9">
-        <v>46161.414324502315</v>
+        <v>46161.58099116899</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46161.678096435186</v>
+        <v>46161.84476310185</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>189</v>
@@ -4905,11 +4905,11 @@
         <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46161.41432752315</v>
+        <v>46161.58099418982</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46161.67809940972</v>
+        <v>46161.84476607639</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4956,11 +4956,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="9">
-        <v>46161.47299822917</v>
+        <v>46161.63966489583</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46161.678096805554</v>
+        <v>46161.844763472225</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>192</v>
@@ -5007,11 +5007,11 @@
         <v>197</v>
       </c>
       <c r="B54" s="5">
-        <v>46161.473005949076</v>
+        <v>46161.63967261574</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46161.67809402778</v>
+        <v>46161.84476069444</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>192</v>
@@ -5058,11 +5058,11 @@
         <v>198</v>
       </c>
       <c r="B55" s="9">
-        <v>46161.47301722222</v>
+        <v>46161.63968388889</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46161.678091064816</v>
+        <v>46161.84475773148</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>192</v>
@@ -5109,11 +5109,11 @@
         <v>199</v>
       </c>
       <c r="B56" s="5">
-        <v>46161.47302608796</v>
+        <v>46161.63969275463</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46161.67808804398</v>
+        <v>46161.84475471065</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>192</v>
@@ -5160,11 +5160,11 @@
         <v>200</v>
       </c>
       <c r="B57" s="9">
-        <v>46161.47303854166</v>
+        <v>46161.639705208334</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46161.67808508102</v>
+        <v>46161.84475174769</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>192</v>
@@ -5211,11 +5211,11 @@
         <v>201</v>
       </c>
       <c r="B58" s="5">
-        <v>46161.47304880787</v>
+        <v>46161.639715474535</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46161.67808196759</v>
+        <v>46161.84474863426</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>192</v>
@@ -5262,11 +5262,11 @@
         <v>202</v>
       </c>
       <c r="B59" s="9">
-        <v>46161.47306012732</v>
+        <v>46161.63972679398</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46161.67807836806</v>
+        <v>46161.84474503472</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>192</v>
@@ -5313,11 +5313,11 @@
         <v>203</v>
       </c>
       <c r="B60" s="5">
-        <v>46161.47307637731</v>
+        <v>46161.63974304398</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46161.67807167824</v>
+        <v>46161.84473834491</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>192</v>
@@ -5364,11 +5364,11 @@
         <v>204</v>
       </c>
       <c r="B61" s="9">
-        <v>46161.47308603009</v>
+        <v>46161.63975269676</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.67807086806</v>
+        <v>46161.84473753472</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>192</v>
@@ -5415,11 +5415,11 @@
         <v>205</v>
       </c>
       <c r="B62" s="5">
-        <v>46161.41433151621</v>
+        <v>46161.58099818287</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46161.629804780096</v>
+        <v>46161.79647144676</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>206</v>
@@ -5462,11 +5462,11 @@
         <v>208</v>
       </c>
       <c r="B63" s="9">
-        <v>46161.41433479167</v>
+        <v>46161.58100145833</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.67817583334</v>
+        <v>46161.844842499995</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>209</v>
@@ -5525,11 +5525,11 @@
         <v>213</v>
       </c>
       <c r="B64" s="5">
-        <v>46161.41433947917</v>
+        <v>46161.58100614583</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46161.67825182871</v>
+        <v>46161.84491849537</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>214</v>
@@ -5588,11 +5588,11 @@
         <v>217</v>
       </c>
       <c r="B65" s="9">
-        <v>46161.414349722225</v>
+        <v>46161.58101638889</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46161.6781731713</v>
+        <v>46161.84483983796</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>218</v>
@@ -5651,11 +5651,11 @@
         <v>220</v>
       </c>
       <c r="B66" s="5">
-        <v>46161.41435432871</v>
+        <v>46161.58102099537</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46161.67824836806</v>
+        <v>46161.84491503472</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>221</v>
@@ -5714,11 +5714,11 @@
         <v>223</v>
       </c>
       <c r="B67" s="9">
-        <v>46161.414358055554</v>
+        <v>46161.581024722225</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46161.67816927083</v>
+        <v>46161.8448359375</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>224</v>
@@ -5777,11 +5777,11 @@
         <v>226</v>
       </c>
       <c r="B68" s="5">
-        <v>46161.41436197917</v>
+        <v>46161.58102864583</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46161.67824760417</v>
+        <v>46161.844914270834</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>225</v>
@@ -5840,11 +5840,11 @@
         <v>228</v>
       </c>
       <c r="B69" s="9">
-        <v>46161.41436540509</v>
+        <v>46161.58103207176</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46161.63111915509</v>
+        <v>46161.797785821764</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>229</v>
@@ -5887,11 +5887,11 @@
         <v>231</v>
       </c>
       <c r="B70" s="5">
-        <v>46161.41436790509</v>
+        <v>46161.58103457176</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46161.678511782404</v>
+        <v>46161.845178449075</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>232</v>
@@ -5950,11 +5950,11 @@
         <v>236</v>
       </c>
       <c r="B71" s="9">
-        <v>46161.41437296296</v>
+        <v>46161.58103962963</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46161.67848040509</v>
+        <v>46161.845147071755</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>192</v>
@@ -6003,11 +6003,11 @@
         <v>239</v>
       </c>
       <c r="B72" s="5">
-        <v>46161.415345138885</v>
+        <v>46161.582011805556</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46161.678476817135</v>
+        <v>46161.84514348379</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>192</v>
@@ -6056,11 +6056,11 @@
         <v>241</v>
       </c>
       <c r="B73" s="9">
-        <v>46161.415357164355</v>
+        <v>46161.58202383102</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46161.678473657405</v>
+        <v>46161.845140324076</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>192</v>
@@ -6109,11 +6109,11 @@
         <v>243</v>
       </c>
       <c r="B74" s="5">
-        <v>46161.4159959838</v>
+        <v>46161.582662650464</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46161.67846998843</v>
+        <v>46161.845136655094</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>192</v>
@@ -6162,11 +6162,11 @@
         <v>244</v>
       </c>
       <c r="B75" s="9">
-        <v>46161.416006562504</v>
+        <v>46161.58267322917</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46161.67846685185</v>
+        <v>46161.845133518524</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>192</v>
@@ -6215,11 +6215,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46161.41603467593</v>
+        <v>46161.58270134259</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46161.67846407407</v>
+        <v>46161.84513074074</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>192</v>
@@ -6268,11 +6268,11 @@
         <v>246</v>
       </c>
       <c r="B77" s="9">
-        <v>46161.416047604165</v>
+        <v>46161.58271427083</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46161.67846136574</v>
+        <v>46161.84512803241</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>192</v>
@@ -6321,11 +6321,11 @@
         <v>248</v>
       </c>
       <c r="B78" s="5">
-        <v>46161.41605984954</v>
+        <v>46161.58272651621</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46161.67845740741</v>
+        <v>46161.84512407407</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>192</v>
@@ -6374,11 +6374,11 @@
         <v>249</v>
       </c>
       <c r="B79" s="9">
-        <v>46161.416112962965</v>
+        <v>46161.58277962963</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46161.67845125</v>
+        <v>46161.845117916666</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>192</v>
@@ -6427,11 +6427,11 @@
         <v>251</v>
       </c>
       <c r="B80" s="5">
-        <v>46161.4161237963</v>
+        <v>46161.58279046296</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46161.67845054399</v>
+        <v>46161.84511721064</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>192</v>
@@ -6480,11 +6480,11 @@
         <v>252</v>
       </c>
       <c r="B81" s="9">
-        <v>46161.41437871528</v>
+        <v>46161.58104538194</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46161.67867814815</v>
+        <v>46161.845344814814</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>253</v>
@@ -6543,11 +6543,11 @@
         <v>254</v>
       </c>
       <c r="B82" s="5">
-        <v>46161.414382372684</v>
+        <v>46161.58104903935</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46161.67867253472</v>
+        <v>46161.84533920139</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>192</v>
@@ -6596,11 +6596,11 @@
         <v>257</v>
       </c>
       <c r="B83" s="9">
-        <v>46161.4161674537</v>
+        <v>46161.582834120374</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46161.67866961806</v>
+        <v>46161.84533628472</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>192</v>
@@ -6649,11 +6649,11 @@
         <v>258</v>
       </c>
       <c r="B84" s="5">
-        <v>46161.416197928236</v>
+        <v>46161.58286459491</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46161.67866670139</v>
+        <v>46161.84533336805</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>192</v>
@@ -6702,11 +6702,11 @@
         <v>259</v>
       </c>
       <c r="B85" s="9">
-        <v>46161.41620715278</v>
+        <v>46161.58287381944</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46161.67866399305</v>
+        <v>46161.84533065972</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>192</v>
@@ -6755,11 +6755,11 @@
         <v>260</v>
       </c>
       <c r="B86" s="5">
-        <v>46161.416216990736</v>
+        <v>46161.58288365741</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46161.67866123843</v>
+        <v>46161.84532790509</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>192</v>
@@ -6808,11 +6808,11 @@
         <v>261</v>
       </c>
       <c r="B87" s="9">
-        <v>46161.416225891204</v>
+        <v>46161.58289255787</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46161.67865819445</v>
+        <v>46161.84532486111</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>192</v>
@@ -6861,11 +6861,11 @@
         <v>262</v>
       </c>
       <c r="B88" s="5">
-        <v>46161.41625876157</v>
+        <v>46161.58292542824</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46161.67865545139</v>
+        <v>46161.84532211805</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>192</v>
@@ -6914,11 +6914,11 @@
         <v>263</v>
       </c>
       <c r="B89" s="9">
-        <v>46161.41627030092</v>
+        <v>46161.58293696759</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46161.67865260417</v>
+        <v>46161.84531927083</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>192</v>
@@ -6967,11 +6967,11 @@
         <v>264</v>
       </c>
       <c r="B90" s="5">
-        <v>46161.41628615741</v>
+        <v>46161.58295282407</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46161.67864644676</v>
+        <v>46161.84531311343</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>192</v>
@@ -7020,11 +7020,11 @@
         <v>265</v>
       </c>
       <c r="B91" s="9">
-        <v>46161.41630106482</v>
+        <v>46161.58296773148</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46161.67864576389</v>
+        <v>46161.84531243055</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>192</v>
@@ -7073,11 +7073,11 @@
         <v>266</v>
       </c>
       <c r="B92" s="5">
-        <v>46161.414387094905</v>
+        <v>46161.581053761576</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46161.67885978009</v>
+        <v>46161.84552644676</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>267</v>
@@ -7136,11 +7136,11 @@
         <v>268</v>
       </c>
       <c r="B93" s="9">
-        <v>46161.41439075231</v>
+        <v>46161.58105741898</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46161.678845069444</v>
+        <v>46161.845511736115</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>192</v>
@@ -7189,11 +7189,11 @@
         <v>270</v>
       </c>
       <c r="B94" s="5">
-        <v>46161.41637327547</v>
+        <v>46161.583039942125</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46161.678842141206</v>
+        <v>46161.84550880787</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>192</v>
@@ -7242,11 +7242,11 @@
         <v>271</v>
       </c>
       <c r="B95" s="9">
-        <v>46161.41639048611</v>
+        <v>46161.58305715278</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46161.678838657404</v>
+        <v>46161.845505324076</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>192</v>
@@ -7295,11 +7295,11 @@
         <v>272</v>
       </c>
       <c r="B96" s="5">
-        <v>46161.41641002314</v>
+        <v>46161.583076689814</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46161.678835914354</v>
+        <v>46161.84550258102</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>192</v>
@@ -7348,11 +7348,11 @@
         <v>273</v>
       </c>
       <c r="B97" s="9">
-        <v>46161.41642219907</v>
+        <v>46161.58308886574</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46161.67883261574</v>
+        <v>46161.84549928241</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>192</v>
@@ -7401,11 +7401,11 @@
         <v>274</v>
       </c>
       <c r="B98" s="5">
-        <v>46161.41643353009</v>
+        <v>46161.58310019676</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46161.678828668984</v>
+        <v>46161.84549533565</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>192</v>
@@ -7454,11 +7454,11 @@
         <v>275</v>
       </c>
       <c r="B99" s="9">
-        <v>46161.41644422454</v>
+        <v>46161.5831108912</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46161.67882539352</v>
+        <v>46161.84549206018</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>192</v>
@@ -7507,11 +7507,11 @@
         <v>276</v>
       </c>
       <c r="B100" s="5">
-        <v>46161.416461782406</v>
+        <v>46161.58312844907</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46161.67882221065</v>
+        <v>46161.84548887731</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>192</v>
@@ -7560,11 +7560,11 @@
         <v>277</v>
       </c>
       <c r="B101" s="9">
-        <v>46161.41634108796</v>
+        <v>46161.58300775463</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46161.67881563657</v>
+        <v>46161.84548230324</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>192</v>
@@ -7613,11 +7613,11 @@
         <v>278</v>
       </c>
       <c r="B102" s="5">
-        <v>46161.47283520833</v>
+        <v>46161.639501875004</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46161.6788149537</v>
+        <v>46161.845481620374</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>192</v>
@@ -7666,11 +7666,11 @@
         <v>279</v>
       </c>
       <c r="B103" s="9">
-        <v>46161.414438402775</v>
+        <v>46161.58110506945</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46161.64110194445</v>
+        <v>46161.80776861111</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>206</v>
@@ -7713,11 +7713,11 @@
         <v>281</v>
       </c>
       <c r="B104" s="5">
-        <v>46161.414441863424</v>
+        <v>46161.581108530096</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46176.021446342595</v>
+        <v>46176.18811300926</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>282</v>
@@ -7776,11 +7776,11 @@
         <v>284</v>
       </c>
       <c r="B105" s="9">
-        <v>46161.41444703704</v>
+        <v>46161.58111370371</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46161.67894248843</v>
+        <v>46161.84560915509</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>285</v>
@@ -7839,11 +7839,11 @@
         <v>287</v>
       </c>
       <c r="B106" s="5">
-        <v>46161.4144517824</v>
+        <v>46161.581118449074</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46161.67893978009</v>
+        <v>46161.84560644676</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>288</v>
@@ -7902,11 +7902,11 @@
         <v>290</v>
       </c>
       <c r="B107" s="9">
-        <v>46161.41445644676</v>
+        <v>46161.58112311343</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46161.67893543981</v>
+        <v>46161.84560210648</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>291</v>
@@ -7965,11 +7965,11 @@
         <v>293</v>
       </c>
       <c r="B108" s="5">
-        <v>46161.41446035879</v>
+        <v>46161.58112702546</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46161.667206956015</v>
+        <v>46161.83387362269</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>294</v>
@@ -8012,11 +8012,11 @@
         <v>296</v>
       </c>
       <c r="B109" s="9">
-        <v>46161.41446318287</v>
+        <v>46161.58112984954</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46161.67911563657</v>
+        <v>46161.84578230324</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>297</v>
@@ -8075,11 +8075,11 @@
         <v>299</v>
       </c>
       <c r="B110" s="5">
-        <v>46161.41446888889</v>
+        <v>46161.581135555556</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46161.67911027778</v>
+        <v>46161.84577694444</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>300</v>
@@ -8128,11 +8128,11 @@
         <v>301</v>
       </c>
       <c r="B111" s="9">
-        <v>46161.41651063657</v>
+        <v>46161.58317730324</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46161.67910700232</v>
+        <v>46161.84577366898</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>192</v>
@@ -8181,11 +8181,11 @@
         <v>302</v>
       </c>
       <c r="B112" s="5">
-        <v>46161.416520914354</v>
+        <v>46161.58318758102</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46161.67910421296</v>
+        <v>46161.845770879634</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>192</v>
@@ -8234,11 +8234,11 @@
         <v>303</v>
       </c>
       <c r="B113" s="9">
-        <v>46161.416530925926</v>
+        <v>46161.5831975926</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46161.67910042824</v>
+        <v>46161.84576709491</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>192</v>
@@ -8287,11 +8287,11 @@
         <v>304</v>
       </c>
       <c r="B114" s="5">
-        <v>46161.41653990741</v>
+        <v>46161.58320657407</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46161.67909748842</v>
+        <v>46161.84576415509</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>192</v>
@@ -8340,11 +8340,11 @@
         <v>305</v>
       </c>
       <c r="B115" s="9">
-        <v>46161.41655484954</v>
+        <v>46161.58322151621</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46161.67909415509</v>
+        <v>46161.84576082176</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>192</v>
@@ -8393,11 +8393,11 @@
         <v>306</v>
       </c>
       <c r="B116" s="5">
-        <v>46161.41656050926</v>
+        <v>46161.58322717593</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46161.679083738425</v>
+        <v>46161.84575040509</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>192</v>
@@ -8446,11 +8446,11 @@
         <v>307</v>
       </c>
       <c r="B117" s="9">
-        <v>46161.41657582176</v>
+        <v>46161.58324248843</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46161.67908300926</v>
+        <v>46161.84574967592</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>192</v>
@@ -8499,11 +8499,11 @@
         <v>308</v>
       </c>
       <c r="B118" s="5">
-        <v>46161.41658736111</v>
+        <v>46161.58325402778</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46161.6790822801</v>
+        <v>46161.845748946755</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>192</v>
@@ -8552,11 +8552,11 @@
         <v>309</v>
       </c>
       <c r="B119" s="9">
-        <v>46161.41659625</v>
+        <v>46161.58326291667</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46161.67908155093</v>
+        <v>46161.84574821759</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>192</v>
@@ -8605,11 +8605,11 @@
         <v>310</v>
       </c>
       <c r="B120" s="5">
-        <v>46161.41447261574</v>
+        <v>46161.58113928241</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46161.6793047338</v>
+        <v>46161.845971400464</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>311</v>
@@ -8668,11 +8668,11 @@
         <v>312</v>
       </c>
       <c r="B121" s="9">
-        <v>46161.414476157406</v>
+        <v>46161.58114282407</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46161.67929230324</v>
+        <v>46161.845958969905</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>192</v>
@@ -8721,11 +8721,11 @@
         <v>315</v>
       </c>
       <c r="B122" s="5">
-        <v>46161.41921576389</v>
+        <v>46161.585882430554</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46161.67928945602</v>
+        <v>46161.845956122685</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>192</v>
@@ -8774,11 +8774,11 @@
         <v>317</v>
       </c>
       <c r="B123" s="9">
-        <v>46161.419236319445</v>
+        <v>46161.58590298611</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46161.67928674769</v>
+        <v>46161.84595341435</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>192</v>
@@ -8827,11 +8827,11 @@
         <v>319</v>
       </c>
       <c r="B124" s="5">
-        <v>46161.41925319444</v>
+        <v>46161.585919861114</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46161.67928377315</v>
+        <v>46161.84595043982</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>192</v>
@@ -8880,11 +8880,11 @@
         <v>320</v>
       </c>
       <c r="B125" s="9">
-        <v>46161.419260509254</v>
+        <v>46161.585927175925</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46161.67928041666</v>
+        <v>46161.84594708333</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>192</v>
@@ -8933,11 +8933,11 @@
         <v>321</v>
       </c>
       <c r="B126" s="5">
-        <v>46161.41926643519</v>
+        <v>46161.58593310185</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46161.679277523144</v>
+        <v>46161.845944189816</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>192</v>
@@ -8986,11 +8986,11 @@
         <v>323</v>
       </c>
       <c r="B127" s="9">
-        <v>46161.419270729166</v>
+        <v>46161.58593739584</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46161.67927489583</v>
+        <v>46161.8459415625</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>192</v>
@@ -9039,11 +9039,11 @@
         <v>324</v>
       </c>
       <c r="B128" s="5">
-        <v>46161.419279236114</v>
+        <v>46161.58594590278</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46161.679266990745</v>
+        <v>46161.84593365741</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>192</v>
@@ -9092,11 +9092,11 @@
         <v>325</v>
       </c>
       <c r="B129" s="9">
-        <v>46161.41928962963</v>
+        <v>46161.5859562963</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46161.67926616898</v>
+        <v>46161.84593283565</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>192</v>
@@ -9145,11 +9145,11 @@
         <v>326</v>
       </c>
       <c r="B130" s="5">
-        <v>46161.4195224537</v>
+        <v>46161.58618912037</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46161.679265370374</v>
+        <v>46161.84593203704</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>192</v>
@@ -9198,11 +9198,11 @@
         <v>328</v>
       </c>
       <c r="B131" s="9">
-        <v>46161.414480949075</v>
+        <v>46161.58114761574</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46161.679458240746</v>
+        <v>46161.8461249074</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>329</v>
@@ -9261,11 +9261,11 @@
         <v>330</v>
       </c>
       <c r="B132" s="5">
-        <v>46161.41448450231</v>
+        <v>46161.58115116898</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46161.67944494213</v>
+        <v>46161.8461116088</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>192</v>
@@ -9314,11 +9314,11 @@
         <v>333</v>
       </c>
       <c r="B133" s="9">
-        <v>46161.41937046296</v>
+        <v>46161.58603712963</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46161.67944158565</v>
+        <v>46161.84610825231</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>192</v>
@@ -9367,11 +9367,11 @@
         <v>334</v>
       </c>
       <c r="B134" s="5">
-        <v>46161.41937826389</v>
+        <v>46161.586044930555</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46161.67943881944</v>
+        <v>46161.84610548611</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>192</v>
@@ -9420,11 +9420,11 @@
         <v>336</v>
       </c>
       <c r="B135" s="9">
-        <v>46161.41939224537</v>
+        <v>46161.58605891204</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46161.679435659724</v>
+        <v>46161.84610232639</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>192</v>
@@ -9473,11 +9473,11 @@
         <v>337</v>
       </c>
       <c r="B136" s="5">
-        <v>46161.41940101852</v>
+        <v>46161.58606768519</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46161.679432627316</v>
+        <v>46161.84609929398</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>192</v>
@@ -9526,11 +9526,11 @@
         <v>339</v>
       </c>
       <c r="B137" s="9">
-        <v>46161.41940908565</v>
+        <v>46161.58607575232</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46161.679429745374</v>
+        <v>46161.84609641204</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>192</v>
@@ -9579,11 +9579,11 @@
         <v>340</v>
       </c>
       <c r="B138" s="5">
-        <v>46161.4194221875</v>
+        <v>46161.586088854165</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46161.67942722222</v>
+        <v>46161.84609388889</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>192</v>
@@ -9632,11 +9632,11 @@
         <v>341</v>
       </c>
       <c r="B139" s="9">
-        <v>46161.41942903935</v>
+        <v>46161.58609570602</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46161.679419259264</v>
+        <v>46161.84608592592</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>192</v>
@@ -9685,11 +9685,11 @@
         <v>343</v>
       </c>
       <c r="B140" s="5">
-        <v>46161.41944391203</v>
+        <v>46161.586110578704</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46161.679418541666</v>
+        <v>46161.84608520834</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>192</v>
@@ -9738,11 +9738,11 @@
         <v>344</v>
       </c>
       <c r="B141" s="9">
-        <v>46161.4194558912</v>
+        <v>46161.58612255787</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46161.6794178125</v>
+        <v>46161.84608447917</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>192</v>
@@ -9791,11 +9791,11 @@
         <v>345</v>
       </c>
       <c r="B142" s="5">
-        <v>46161.41448976852</v>
+        <v>46161.58115643519</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46161.679629502316</v>
+        <v>46161.84629616898</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>346</v>
@@ -9854,11 +9854,11 @@
         <v>347</v>
       </c>
       <c r="B143" s="9">
-        <v>46161.41449326389</v>
+        <v>46161.58115993056</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46161.67962244213</v>
+        <v>46161.8462891088</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>300</v>
@@ -9907,11 +9907,11 @@
         <v>350</v>
       </c>
       <c r="B144" s="5">
-        <v>46161.419559745365</v>
+        <v>46161.58622641204</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46161.67961921296</v>
+        <v>46161.84628587963</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>192</v>
@@ -9960,11 +9960,11 @@
         <v>351</v>
       </c>
       <c r="B145" s="9">
-        <v>46161.419569328704</v>
+        <v>46161.586235995375</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46161.679616249996</v>
+        <v>46161.84628291667</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>192</v>
@@ -10013,11 +10013,11 @@
         <v>352</v>
       </c>
       <c r="B146" s="5">
-        <v>46161.419580104164</v>
+        <v>46161.586246770836</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46161.67961337963</v>
+        <v>46161.846280046295</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>192</v>
@@ -10066,11 +10066,11 @@
         <v>354</v>
       </c>
       <c r="B147" s="9">
-        <v>46161.41958976851</v>
+        <v>46161.586256435185</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46161.67961032408</v>
+        <v>46161.84627699074</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>192</v>
@@ -10119,11 +10119,11 @@
         <v>356</v>
       </c>
       <c r="B148" s="5">
-        <v>46161.419599166664</v>
+        <v>46161.586265833335</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46161.67960728009</v>
+        <v>46161.84627394676</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>192</v>
@@ -10172,11 +10172,11 @@
         <v>357</v>
       </c>
       <c r="B149" s="9">
-        <v>46161.41960900463</v>
+        <v>46161.586275671296</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46161.679604467594</v>
+        <v>46161.84627113426</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>192</v>
@@ -10225,11 +10225,11 @@
         <v>358</v>
       </c>
       <c r="B150" s="5">
-        <v>46161.41962519676</v>
+        <v>46161.58629186342</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46161.67960173611</v>
+        <v>46161.846268402776</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>192</v>
@@ -10278,11 +10278,11 @@
         <v>359</v>
       </c>
       <c r="B151" s="9">
-        <v>46161.41964212963</v>
+        <v>46161.58630879629</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46161.67959555556</v>
+        <v>46161.84626222222</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>192</v>
@@ -10331,11 +10331,11 @@
         <v>360</v>
       </c>
       <c r="B152" s="5">
-        <v>46161.41965496528</v>
+        <v>46161.58632163194</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46161.679594953705</v>
+        <v>46161.84626162037</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>192</v>
@@ -10384,11 +10384,11 @@
         <v>361</v>
       </c>
       <c r="B153" s="9">
-        <v>46161.41449802084</v>
+        <v>46161.5811646875</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46161.67977259259</v>
+        <v>46161.84643925926</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>362</v>
@@ -10447,11 +10447,11 @@
         <v>363</v>
       </c>
       <c r="B154" s="5">
-        <v>46161.41450162037</v>
+        <v>46161.58116828704</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46161.67977555556</v>
+        <v>46161.84644222222</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>192</v>
@@ -10498,11 +10498,11 @@
         <v>365</v>
       </c>
       <c r="B155" s="9">
-        <v>46161.47245956019</v>
+        <v>46161.63912622685</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46161.679772627314</v>
+        <v>46161.84643929398</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>192</v>
@@ -10549,11 +10549,11 @@
         <v>366</v>
       </c>
       <c r="B156" s="5">
-        <v>46161.47247070602</v>
+        <v>46161.63913737268</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46161.67976976852</v>
+        <v>46161.84643643518</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>192</v>
@@ -10600,11 +10600,11 @@
         <v>367</v>
       </c>
       <c r="B157" s="9">
-        <v>46161.47248053241</v>
+        <v>46161.63914719908</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46161.67976665509</v>
+        <v>46161.846433321756</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>192</v>
@@ -10651,11 +10651,11 @@
         <v>368</v>
       </c>
       <c r="B158" s="5">
-        <v>46161.4724908912</v>
+        <v>46161.639157557875</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46161.67976347222</v>
+        <v>46161.84643013889</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>192</v>
@@ -10702,11 +10702,11 @@
         <v>369</v>
       </c>
       <c r="B159" s="9">
-        <v>46161.47250552083</v>
+        <v>46161.6391721875</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46161.67975980324</v>
+        <v>46161.84642646991</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>192</v>
@@ -10753,11 +10753,11 @@
         <v>370</v>
       </c>
       <c r="B160" s="5">
-        <v>46161.47252072916</v>
+        <v>46161.639187395835</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46161.679756550926</v>
+        <v>46161.84642321759</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>192</v>
@@ -10804,11 +10804,11 @@
         <v>371</v>
       </c>
       <c r="B161" s="9">
-        <v>46161.47252862269</v>
+        <v>46161.639195289354</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46161.67975347222</v>
+        <v>46161.846420138885</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>192</v>
@@ -10855,11 +10855,11 @@
         <v>372</v>
       </c>
       <c r="B162" s="5">
-        <v>46161.472538842594</v>
+        <v>46161.63920550926</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46161.67974644676</v>
+        <v>46161.846413113424</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>192</v>
@@ -10906,11 +10906,11 @@
         <v>373</v>
       </c>
       <c r="B163" s="9">
-        <v>46161.47254766204</v>
+        <v>46161.63921432871</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46161.67974575231</v>
+        <v>46161.84641241898</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>192</v>
@@ -10957,11 +10957,11 @@
         <v>374</v>
       </c>
       <c r="B164" s="5">
-        <v>46161.414510856484</v>
+        <v>46161.58117752315</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46161.679938368055</v>
+        <v>46161.84660503472</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>375</v>
@@ -11020,11 +11020,11 @@
         <v>377</v>
       </c>
       <c r="B165" s="9">
-        <v>46161.41451471065</v>
+        <v>46161.58118137732</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46161.67991349537</v>
+        <v>46161.84658016203</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>192</v>
@@ -11073,11 +11073,11 @@
         <v>379</v>
       </c>
       <c r="B166" s="5">
-        <v>46161.472587094904</v>
+        <v>46161.639253761576</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46161.679910520834</v>
+        <v>46161.846577187505</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>192</v>
@@ -11126,11 +11126,11 @@
         <v>380</v>
       </c>
       <c r="B167" s="9">
-        <v>46161.47262043982</v>
+        <v>46161.63928710648</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46161.67990751157</v>
+        <v>46161.84657417824</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>192</v>
@@ -11179,11 +11179,11 @@
         <v>381</v>
       </c>
       <c r="B168" s="5">
-        <v>46161.47263069444</v>
+        <v>46161.63929736111</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46161.67990469908</v>
+        <v>46161.84657136574</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>192</v>
@@ -11232,11 +11232,11 @@
         <v>382</v>
       </c>
       <c r="B169" s="9">
-        <v>46161.47264047454</v>
+        <v>46161.6393071412</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46161.67990174769</v>
+        <v>46161.84656841435</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>192</v>
@@ -11285,11 +11285,11 @@
         <v>383</v>
       </c>
       <c r="B170" s="5">
-        <v>46161.47264895833</v>
+        <v>46161.639315625</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46161.679898726856</v>
+        <v>46161.84656539352</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>192</v>
@@ -11338,11 +11338,11 @@
         <v>384</v>
       </c>
       <c r="B171" s="9">
-        <v>46161.472660196756</v>
+        <v>46161.63932686343</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46161.67989608797</v>
+        <v>46161.846562754625</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>192</v>
@@ -11391,11 +11391,11 @@
         <v>385</v>
       </c>
       <c r="B172" s="5">
-        <v>46161.47267041667</v>
+        <v>46161.63933708333</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46161.67989328704</v>
+        <v>46161.8465599537</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>192</v>
@@ -11444,11 +11444,11 @@
         <v>386</v>
       </c>
       <c r="B173" s="9">
-        <v>46161.47268818287</v>
+        <v>46161.63935484954</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46161.6798871412</v>
+        <v>46161.846553807874</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>192</v>
@@ -11497,11 +11497,11 @@
         <v>387</v>
       </c>
       <c r="B174" s="5">
-        <v>46161.47269787037</v>
+        <v>46161.63936453704</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46161.67988646991</v>
+        <v>46161.84655313657</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>192</v>
@@ -11550,11 +11550,11 @@
         <v>388</v>
       </c>
       <c r="B175" s="9">
-        <v>46161.41451859954</v>
+        <v>46161.5811852662</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46161.674260659725</v>
+        <v>46161.84092732639</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>389</v>
@@ -11597,11 +11597,11 @@
         <v>391</v>
       </c>
       <c r="B176" s="5">
-        <v>46161.41452135416</v>
+        <v>46161.581188020835</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46161.68009149306</v>
+        <v>46161.84675815972</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>392</v>
@@ -11660,11 +11660,11 @@
         <v>395</v>
       </c>
       <c r="B177" s="9">
-        <v>46161.41452600695</v>
+        <v>46161.581192673606</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46161.68008268518</v>
+        <v>46161.846749351855</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>192</v>
@@ -11713,11 +11713,11 @@
         <v>397</v>
       </c>
       <c r="B178" s="5">
-        <v>46161.473160416666</v>
+        <v>46161.63982708333</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46161.68007988426</v>
+        <v>46161.84674655093</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>192</v>
@@ -11766,11 +11766,11 @@
         <v>398</v>
       </c>
       <c r="B179" s="9">
-        <v>46161.47316865741</v>
+        <v>46161.63983532407</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46161.68007731481</v>
+        <v>46161.846743981485</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>192</v>
@@ -11819,11 +11819,11 @@
         <v>399</v>
       </c>
       <c r="B180" s="5">
-        <v>46161.4731775463</v>
+        <v>46161.63984421296</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46161.68007476852</v>
+        <v>46161.84674143518</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>192</v>
@@ -11872,11 +11872,11 @@
         <v>400</v>
       </c>
       <c r="B181" s="9">
-        <v>46161.47319211806</v>
+        <v>46161.63985878472</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46161.680071875</v>
+        <v>46161.846738541666</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>192</v>
@@ -11925,11 +11925,11 @@
         <v>401</v>
       </c>
       <c r="B182" s="5">
-        <v>46161.47320113426</v>
+        <v>46161.63986780093</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46161.68006892361</v>
+        <v>46161.84673559028</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>192</v>
@@ -11978,11 +11978,11 @@
         <v>402</v>
       </c>
       <c r="B183" s="9">
-        <v>46161.47320833334</v>
+        <v>46161.639875</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46161.68006622685</v>
+        <v>46161.84673289352</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>192</v>
@@ -12031,11 +12031,11 @@
         <v>403</v>
       </c>
       <c r="B184" s="5">
-        <v>46161.47321675926</v>
+        <v>46161.63988342593</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46161.68005822916</v>
+        <v>46161.84672489583</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>192</v>
@@ -12084,11 +12084,11 @@
         <v>404</v>
       </c>
       <c r="B185" s="9">
-        <v>46161.47322476852</v>
+        <v>46161.63989143519</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46161.68005753472</v>
+        <v>46161.84672420139</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>192</v>
@@ -12137,11 +12137,11 @@
         <v>405</v>
       </c>
       <c r="B186" s="5">
-        <v>46161.47323267361</v>
+        <v>46161.639899340276</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46161.680056736106</v>
+        <v>46161.84672340278</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>192</v>
@@ -12190,11 +12190,11 @@
         <v>406</v>
       </c>
       <c r="B187" s="9">
-        <v>46161.41452984954</v>
+        <v>46161.5811965162</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46161.68023515046</v>
+        <v>46161.84690181713</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>407</v>
@@ -12253,11 +12253,11 @@
         <v>408</v>
       </c>
       <c r="B188" s="5">
-        <v>46161.41453335648</v>
+        <v>46161.58120002315</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46161.68023670139</v>
+        <v>46161.84690336806</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>192</v>
@@ -12306,11 +12306,11 @@
         <v>410</v>
       </c>
       <c r="B189" s="9">
-        <v>46161.47326758102</v>
+        <v>46161.63993424768</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46161.68023371528</v>
+        <v>46161.84690038195</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>192</v>
@@ -12359,11 +12359,11 @@
         <v>411</v>
       </c>
       <c r="B190" s="5">
-        <v>46161.473328113425</v>
+        <v>46161.6399947801</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46161.68023079861</v>
+        <v>46161.84689746528</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>192</v>
@@ -12412,11 +12412,11 @@
         <v>412</v>
       </c>
       <c r="B191" s="9">
-        <v>46161.473337777774</v>
+        <v>46161.640004444445</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46161.68022780093</v>
+        <v>46161.84689446759</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>192</v>
@@ -12465,11 +12465,11 @@
         <v>413</v>
       </c>
       <c r="B192" s="5">
-        <v>46161.47334834491</v>
+        <v>46161.64001501157</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46161.68022471065</v>
+        <v>46161.84689137731</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>192</v>
@@ -12518,11 +12518,11 @@
         <v>414</v>
       </c>
       <c r="B193" s="9">
-        <v>46161.47335716435</v>
+        <v>46161.640023831016</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46161.68022212963</v>
+        <v>46161.846888796295</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>192</v>
@@ -12571,11 +12571,11 @@
         <v>415</v>
       </c>
       <c r="B194" s="5">
-        <v>46161.473371643515</v>
+        <v>46161.640038310186</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46161.68021939815</v>
+        <v>46161.84688606481</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>192</v>
@@ -12624,11 +12624,11 @@
         <v>416</v>
       </c>
       <c r="B195" s="9">
-        <v>46161.47338081019</v>
+        <v>46161.64004747685</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46161.6802158912</v>
+        <v>46161.846882557875</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>192</v>
@@ -12677,11 +12677,11 @@
         <v>417</v>
       </c>
       <c r="B196" s="5">
-        <v>46161.47338982639</v>
+        <v>46161.64005649305</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46161.68021290509</v>
+        <v>46161.84687957176</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>192</v>
@@ -12730,11 +12730,11 @@
         <v>418</v>
       </c>
       <c r="B197" s="9">
-        <v>46161.47339679398</v>
+        <v>46161.64006346065</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46161.68020357639</v>
+        <v>46161.846870243055</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>192</v>
@@ -12783,11 +12783,11 @@
         <v>419</v>
       </c>
       <c r="B198" s="5">
-        <v>46161.41453732639</v>
+        <v>46161.58120399306</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46161.68043979167</v>
+        <v>46161.84710645833</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>420</v>
@@ -12844,11 +12844,11 @@
         <v>421</v>
       </c>
       <c r="B199" s="9">
-        <v>46161.4145408912</v>
+        <v>46161.58120755787</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46161.68041114583</v>
+        <v>46161.847077812505</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>192</v>
@@ -12895,11 +12895,11 @@
         <v>423</v>
       </c>
       <c r="B200" s="5">
-        <v>46161.47345859953</v>
+        <v>46161.6401252662</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46161.6804083912</v>
+        <v>46161.84707505787</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>192</v>
@@ -12946,11 +12946,11 @@
         <v>424</v>
       </c>
       <c r="B201" s="9">
-        <v>46161.47347471065</v>
+        <v>46161.64014137731</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46161.680405810184</v>
+        <v>46161.847072476856</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>192</v>
@@ -12997,11 +12997,11 @@
         <v>425</v>
       </c>
       <c r="B202" s="5">
-        <v>46161.47348627315</v>
+        <v>46161.64015293981</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46161.680402638885</v>
+        <v>46161.84706930556</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>192</v>
@@ -13048,11 +13048,11 @@
         <v>426</v>
       </c>
       <c r="B203" s="9">
-        <v>46161.47350074074</v>
+        <v>46161.64016740741</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46161.680399942124</v>
+        <v>46161.847066608796</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>192</v>
@@ -13099,11 +13099,11 @@
         <v>427</v>
       </c>
       <c r="B204" s="5">
-        <v>46161.47353721065</v>
+        <v>46161.640203877316</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46161.68039736111</v>
+        <v>46161.84706402778</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>192</v>
@@ -13150,11 +13150,11 @@
         <v>428</v>
       </c>
       <c r="B205" s="9">
-        <v>46161.4735484375</v>
+        <v>46161.64021510417</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46161.68039445602</v>
+        <v>46161.84706112268</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>192</v>
@@ -13201,11 +13201,11 @@
         <v>429</v>
       </c>
       <c r="B206" s="5">
-        <v>46161.4735603588</v>
+        <v>46161.64022702546</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46161.68038675926</v>
+        <v>46161.847053425925</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>192</v>
@@ -13252,11 +13252,11 @@
         <v>430</v>
       </c>
       <c r="B207" s="9">
-        <v>46161.473571180555</v>
+        <v>46161.64023784723</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46161.68038609954</v>
+        <v>46161.8470527662</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>192</v>
@@ -13303,11 +13303,11 @@
         <v>431</v>
       </c>
       <c r="B208" s="5">
-        <v>46161.47358644676</v>
+        <v>46161.64025311342</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46161.68038543982</v>
+        <v>46161.84705210648</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>192</v>
@@ -13354,11 +13354,11 @@
         <v>432</v>
       </c>
       <c r="B209" s="9">
-        <v>46161.41454799769</v>
+        <v>46161.58121466435</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46161.6806352662</v>
+        <v>46161.84730193287</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>433</v>
@@ -13417,11 +13417,11 @@
         <v>435</v>
       </c>
       <c r="B210" s="5">
-        <v>46161.414590659726</v>
+        <v>46161.58125732639</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46161.680614247685</v>
+        <v>46161.84728091436</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>192</v>
@@ -13468,11 +13468,11 @@
         <v>436</v>
       </c>
       <c r="B211" s="9">
-        <v>46161.47364123842</v>
+        <v>46161.640307905094</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46161.6806110301</v>
+        <v>46161.84727769676</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>192</v>
@@ -13519,11 +13519,11 @@
         <v>437</v>
       </c>
       <c r="B212" s="5">
-        <v>46161.4736496875</v>
+        <v>46161.64031635417</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46161.680608587965</v>
+        <v>46161.84727525463</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>192</v>
@@ -13570,11 +13570,11 @@
         <v>438</v>
       </c>
       <c r="B213" s="9">
-        <v>46161.473661655094</v>
+        <v>46161.64032832176</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46161.68060581019</v>
+        <v>46161.84727247685</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>192</v>
@@ -13621,11 +13621,11 @@
         <v>439</v>
       </c>
       <c r="B214" s="5">
-        <v>46161.47367131944</v>
+        <v>46161.640337986115</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46161.68060278935</v>
+        <v>46161.84726945602</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>192</v>
@@ -13672,11 +13672,11 @@
         <v>440</v>
       </c>
       <c r="B215" s="9">
-        <v>46161.473691956024</v>
+        <v>46161.64035862268</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46161.680599722225</v>
+        <v>46161.84726638889</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>192</v>
@@ -13723,11 +13723,11 @@
         <v>441</v>
       </c>
       <c r="B216" s="5">
-        <v>46161.47370106481</v>
+        <v>46161.64036773148</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46161.68059693287</v>
+        <v>46161.84726359954</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>192</v>
@@ -13774,11 +13774,11 @@
         <v>442</v>
       </c>
       <c r="B217" s="9">
-        <v>46161.47370990741</v>
+        <v>46161.64037657407</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46161.68059393518</v>
+        <v>46161.84726060185</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>192</v>
@@ -13825,11 +13825,11 @@
         <v>443</v>
       </c>
       <c r="B218" s="5">
-        <v>46161.47371806713</v>
+        <v>46161.64038473379</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46161.68058803241</v>
+        <v>46161.847254699074</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>192</v>
@@ -13876,11 +13876,11 @@
         <v>444</v>
       </c>
       <c r="B219" s="9">
-        <v>46161.47372684028</v>
+        <v>46161.64039350694</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46161.68058739584</v>
+        <v>46161.8472540625</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>192</v>
@@ -13927,11 +13927,11 @@
         <v>445</v>
       </c>
       <c r="B220" s="5">
-        <v>46161.41459615741</v>
+        <v>46161.581262824075</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46161.68134378472</v>
+        <v>46161.84801045139</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>446</v>
@@ -13974,11 +13974,11 @@
         <v>448</v>
       </c>
       <c r="B221" s="9">
-        <v>46161.414599490745</v>
+        <v>46161.58126615741</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46161.680980902776</v>
+        <v>46161.84764756945</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>449</v>
@@ -14037,11 +14037,11 @@
         <v>452</v>
       </c>
       <c r="B222" s="5">
-        <v>46161.41460415509</v>
+        <v>46161.581270821756</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46161.68155587963</v>
+        <v>46161.848222546294</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>453</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46169.87953479167</v>
+        <v>46191.85302043981</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -3448,7 +3448,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46172.18357490741</v>
+        <v>46191.85438790509</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.87942172454</v>
+        <v>46191.85401509259</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46191.85302043981</v>
+        <v>46192.85352256944</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46191.85438790509</v>
+        <v>46192.85867619213</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46191.85401509259</v>
+        <v>46192.86032678241</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="457">
   <si>
     <t>50001555 - "ZITRON COLOMBIA ARIS MINING SEGOVIA"</t>
   </si>
@@ -609,28 +609,34 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214937509347720</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor ot 4332,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214937218721335</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214937509347720</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor ot 4332,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214937218721335</t>
   </si>
   <si>
     <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,Propuesta Fabricación externa  ot 4332,propuesta Corte Laser ot 4332,Propuesta Corte plasma  ot 4332,Propuesta Mecanizado ot 4332,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4332 -  ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 </t>
@@ -2606,7 +2612,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46175.878507650465</v>
+        <v>46196.74087425926</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>63</v>
@@ -4657,7 +4663,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46171.17079962963</v>
+        <v>46196.7401344213</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4720,7 +4726,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46161.844557951394</v>
+        <v>46196.74022112269</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4792,10 +4798,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46223</v>
@@ -4819,7 +4825,7 @@
         <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q50" s="5">
         <v>46223</v>
@@ -4839,7 +4845,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46161.58099116899</v>
@@ -4849,16 +4855,16 @@
         <v>46161.84476310185</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I51" s="9">
         <v>46308</v>
@@ -4879,7 +4885,7 @@
         <v>175</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4902,7 +4908,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B52" s="5">
         <v>46161.58099418982</v>
@@ -4912,16 +4918,16 @@
         <v>46161.84476607639</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="H52" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4937,13 +4943,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4953,7 +4959,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B53" s="9">
         <v>46161.63966489583</v>
@@ -4963,16 +4969,16 @@
         <v>46161.844763472225</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>190</v>
-      </c>
       <c r="H53" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -4988,13 +4994,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5004,7 +5010,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46161.63967261574</v>
@@ -5014,16 +5020,16 @@
         <v>46161.84476069444</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="H54" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5039,13 +5045,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5055,7 +5061,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B55" s="9">
         <v>46161.63968388889</v>
@@ -5065,16 +5071,16 @@
         <v>46161.84475773148</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>190</v>
-      </c>
       <c r="H55" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5090,13 +5096,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5106,7 +5112,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46161.63969275463</v>
@@ -5116,16 +5122,16 @@
         <v>46161.84475471065</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="H56" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5141,13 +5147,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5157,7 +5163,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B57" s="9">
         <v>46161.639705208334</v>
@@ -5167,16 +5173,16 @@
         <v>46161.84475174769</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>190</v>
-      </c>
       <c r="H57" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5192,13 +5198,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5208,7 +5214,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
         <v>46161.639715474535</v>
@@ -5218,16 +5224,16 @@
         <v>46161.84474863426</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="H58" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5243,13 +5249,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5259,7 +5265,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B59" s="9">
         <v>46161.63972679398</v>
@@ -5269,16 +5275,16 @@
         <v>46161.84474503472</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>190</v>
-      </c>
       <c r="H59" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5294,13 +5300,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5310,7 +5316,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B60" s="5">
         <v>46161.63974304398</v>
@@ -5320,16 +5326,16 @@
         <v>46161.84473834491</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="H60" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5345,13 +5351,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5361,7 +5367,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B61" s="9">
         <v>46161.63975269676</v>
@@ -5371,16 +5377,16 @@
         <v>46161.84473753472</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>190</v>
-      </c>
       <c r="H61" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5396,13 +5402,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5412,7 +5418,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B62" s="5">
         <v>46161.58099818287</v>
@@ -5422,7 +5428,7 @@
         <v>46161.79647144676</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5446,7 +5452,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5459,7 +5465,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B63" s="9">
         <v>46161.58100145833</v>
@@ -5469,16 +5475,16 @@
         <v>46161.844842499995</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I63" s="9">
         <v>46239</v>
@@ -5496,13 +5502,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>142</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="9">
         <v>46239</v>
@@ -5522,7 +5528,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B64" s="5">
         <v>46161.58100614583</v>
@@ -5532,7 +5538,7 @@
         <v>46161.84491849537</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5559,13 +5565,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q64" s="5">
         <v>46241</v>
@@ -5585,7 +5591,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B65" s="9">
         <v>46161.58101638889</v>
@@ -5595,16 +5601,16 @@
         <v>46161.84483983796</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I65" s="9">
         <v>46239</v>
@@ -5622,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>150</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="9">
         <v>46239</v>
@@ -5648,7 +5654,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B66" s="5">
         <v>46161.58102099537</v>
@@ -5658,7 +5664,7 @@
         <v>46161.84491503472</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5685,13 +5691,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q66" s="5">
         <v>46241</v>
@@ -5711,7 +5717,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B67" s="9">
         <v>46161.581024722225</v>
@@ -5721,16 +5727,16 @@
         <v>46161.8448359375</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I67" s="9">
         <v>46239</v>
@@ -5748,13 +5754,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>172</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q67" s="9">
         <v>46239</v>
@@ -5774,7 +5780,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B68" s="5">
         <v>46161.58102864583</v>
@@ -5784,7 +5790,7 @@
         <v>46161.844914270834</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5811,13 +5817,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q68" s="5">
         <v>46241</v>
@@ -5837,7 +5843,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B69" s="9">
         <v>46161.58103207176</v>
@@ -5847,7 +5853,7 @@
         <v>46161.797785821764</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5871,7 +5877,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5884,7 +5890,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B70" s="5">
         <v>46161.58103457176</v>
@@ -5894,16 +5900,16 @@
         <v>46161.845178449075</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I70" s="5">
         <v>46245</v>
@@ -5921,13 +5927,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q70" s="5">
         <v>46245</v>
@@ -5947,7 +5953,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46161.58103962963</v>
@@ -5957,16 +5963,16 @@
         <v>46161.845147071755</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I71" s="9">
         <v>46245</v>
@@ -5984,13 +5990,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6000,7 +6006,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46161.582011805556</v>
@@ -6010,16 +6016,16 @@
         <v>46161.84514348379</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I72" s="5">
         <v>46245</v>
@@ -6037,13 +6043,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6053,7 +6059,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B73" s="9">
         <v>46161.58202383102</v>
@@ -6063,16 +6069,16 @@
         <v>46161.845140324076</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I73" s="9">
         <v>46245</v>
@@ -6090,13 +6096,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6106,7 +6112,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46161.582662650464</v>
@@ -6116,16 +6122,16 @@
         <v>46161.845136655094</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I74" s="5">
         <v>46245</v>
@@ -6143,13 +6149,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6159,7 +6165,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B75" s="9">
         <v>46161.58267322917</v>
@@ -6169,16 +6175,16 @@
         <v>46161.845133518524</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I75" s="9">
         <v>46245</v>
@@ -6196,13 +6202,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6212,7 +6218,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46161.58270134259</v>
@@ -6222,16 +6228,16 @@
         <v>46161.84513074074</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I76" s="5">
         <v>46245</v>
@@ -6249,13 +6255,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6265,7 +6271,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B77" s="9">
         <v>46161.58271427083</v>
@@ -6275,16 +6281,16 @@
         <v>46161.84512803241</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I77" s="9">
         <v>46245</v>
@@ -6302,13 +6308,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6318,7 +6324,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46161.58272651621</v>
@@ -6328,16 +6334,16 @@
         <v>46161.84512407407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I78" s="5">
         <v>46245</v>
@@ -6355,13 +6361,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6371,7 +6377,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B79" s="9">
         <v>46161.58277962963</v>
@@ -6381,16 +6387,16 @@
         <v>46161.845117916666</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I79" s="9">
         <v>46245</v>
@@ -6408,13 +6414,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6424,7 +6430,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46161.58279046296</v>
@@ -6434,16 +6440,16 @@
         <v>46161.84511721064</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I80" s="5">
         <v>46245</v>
@@ -6461,13 +6467,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6477,7 +6483,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B81" s="9">
         <v>46161.58104538194</v>
@@ -6487,16 +6493,16 @@
         <v>46161.845344814814</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I81" s="9">
         <v>46254</v>
@@ -6514,13 +6520,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q81" s="9">
         <v>46254</v>
@@ -6540,7 +6546,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46161.58104903935</v>
@@ -6550,16 +6556,16 @@
         <v>46161.84533920139</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I82" s="5">
         <v>46254</v>
@@ -6577,13 +6583,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6593,7 +6599,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B83" s="9">
         <v>46161.582834120374</v>
@@ -6603,16 +6609,16 @@
         <v>46161.84533628472</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I83" s="9">
         <v>46254</v>
@@ -6630,13 +6636,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6646,7 +6652,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B84" s="5">
         <v>46161.58286459491</v>
@@ -6656,16 +6662,16 @@
         <v>46161.84533336805</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I84" s="5">
         <v>46254</v>
@@ -6683,13 +6689,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6699,7 +6705,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B85" s="9">
         <v>46161.58287381944</v>
@@ -6709,16 +6715,16 @@
         <v>46161.84533065972</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I85" s="9">
         <v>46254</v>
@@ -6736,13 +6742,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6752,7 +6758,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B86" s="5">
         <v>46161.58288365741</v>
@@ -6762,16 +6768,16 @@
         <v>46161.84532790509</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I86" s="5">
         <v>46254</v>
@@ -6789,13 +6795,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6805,7 +6811,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B87" s="9">
         <v>46161.58289255787</v>
@@ -6815,16 +6821,16 @@
         <v>46161.84532486111</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I87" s="9">
         <v>46254</v>
@@ -6842,13 +6848,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6858,7 +6864,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B88" s="5">
         <v>46161.58292542824</v>
@@ -6868,16 +6874,16 @@
         <v>46161.84532211805</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I88" s="5">
         <v>46254</v>
@@ -6895,13 +6901,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6911,7 +6917,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B89" s="9">
         <v>46161.58293696759</v>
@@ -6921,16 +6927,16 @@
         <v>46161.84531927083</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I89" s="9">
         <v>46254</v>
@@ -6948,13 +6954,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6964,7 +6970,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B90" s="5">
         <v>46161.58295282407</v>
@@ -6974,16 +6980,16 @@
         <v>46161.84531311343</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I90" s="5">
         <v>46254</v>
@@ -7001,13 +7007,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7017,7 +7023,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B91" s="9">
         <v>46161.58296773148</v>
@@ -7027,16 +7033,16 @@
         <v>46161.84531243055</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I91" s="9">
         <v>46254</v>
@@ -7054,13 +7060,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7070,7 +7076,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B92" s="5">
         <v>46161.581053761576</v>
@@ -7080,7 +7086,7 @@
         <v>46161.84552644676</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7107,13 +7113,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q92" s="5">
         <v>46274</v>
@@ -7133,7 +7139,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B93" s="9">
         <v>46161.58105741898</v>
@@ -7143,7 +7149,7 @@
         <v>46161.845511736115</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7170,13 +7176,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7186,7 +7192,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B94" s="5">
         <v>46161.583039942125</v>
@@ -7196,7 +7202,7 @@
         <v>46161.84550880787</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7223,13 +7229,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7239,7 +7245,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B95" s="9">
         <v>46161.58305715278</v>
@@ -7249,7 +7255,7 @@
         <v>46161.845505324076</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7276,13 +7282,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7292,7 +7298,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B96" s="5">
         <v>46161.583076689814</v>
@@ -7302,7 +7308,7 @@
         <v>46161.84550258102</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7329,13 +7335,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7345,7 +7351,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B97" s="9">
         <v>46161.58308886574</v>
@@ -7355,7 +7361,7 @@
         <v>46161.84549928241</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7382,13 +7388,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7398,7 +7404,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B98" s="5">
         <v>46161.58310019676</v>
@@ -7408,7 +7414,7 @@
         <v>46161.84549533565</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7435,13 +7441,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7451,7 +7457,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B99" s="9">
         <v>46161.5831108912</v>
@@ -7461,7 +7467,7 @@
         <v>46161.84549206018</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7488,13 +7494,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7504,7 +7510,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B100" s="5">
         <v>46161.58312844907</v>
@@ -7514,7 +7520,7 @@
         <v>46161.84548887731</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7541,13 +7547,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7557,7 +7563,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B101" s="9">
         <v>46161.58300775463</v>
@@ -7567,7 +7573,7 @@
         <v>46161.84548230324</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7594,13 +7600,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7610,7 +7616,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B102" s="5">
         <v>46161.639501875004</v>
@@ -7620,7 +7626,7 @@
         <v>46161.845481620374</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7647,13 +7653,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7663,7 +7669,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B103" s="9">
         <v>46161.58110506945</v>
@@ -7673,7 +7679,7 @@
         <v>46161.80776861111</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7697,7 +7703,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7710,7 +7716,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B104" s="5">
         <v>46161.581108530096</v>
@@ -7720,16 +7726,16 @@
         <v>46176.18811300926</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I104" s="5">
         <v>46174</v>
@@ -7747,13 +7753,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>119</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q104" s="5">
         <v>46174</v>
@@ -7773,7 +7779,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B105" s="9">
         <v>46161.58111370371</v>
@@ -7783,16 +7789,16 @@
         <v>46161.84560915509</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I105" s="9">
         <v>46282</v>
@@ -7810,13 +7816,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>110</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q105" s="9">
         <v>46282</v>
@@ -7836,7 +7842,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46161.581118449074</v>
@@ -7846,16 +7852,16 @@
         <v>46161.84560644676</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I106" s="5">
         <v>46301</v>
@@ -7873,13 +7879,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>128</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q106" s="5">
         <v>46301</v>
@@ -7899,7 +7905,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B107" s="9">
         <v>46161.58112311343</v>
@@ -7909,16 +7915,16 @@
         <v>46161.84560210648</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I107" s="9">
         <v>46237</v>
@@ -7936,13 +7942,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>160</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q107" s="9">
         <v>46237</v>
@@ -7962,7 +7968,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B108" s="5">
         <v>46161.58112702546</v>
@@ -7972,7 +7978,7 @@
         <v>46161.83387362269</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>25</v>
@@ -7996,7 +8002,7 @@
         <v>26</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -8009,7 +8015,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B109" s="9">
         <v>46161.58112984954</v>
@@ -8019,7 +8025,7 @@
         <v>46161.84578230324</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8046,13 +8052,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q109" s="9">
         <v>46276</v>
@@ -8072,7 +8078,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B110" s="5">
         <v>46161.581135555556</v>
@@ -8082,7 +8088,7 @@
         <v>46161.84577694444</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8109,13 +8115,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8125,7 +8131,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B111" s="9">
         <v>46161.58317730324</v>
@@ -8135,7 +8141,7 @@
         <v>46161.84577366898</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8162,13 +8168,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8178,7 +8184,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B112" s="5">
         <v>46161.58318758102</v>
@@ -8188,7 +8194,7 @@
         <v>46161.845770879634</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8215,13 +8221,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8231,7 +8237,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B113" s="9">
         <v>46161.5831975926</v>
@@ -8241,7 +8247,7 @@
         <v>46161.84576709491</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8268,13 +8274,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8284,7 +8290,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B114" s="5">
         <v>46161.58320657407</v>
@@ -8294,7 +8300,7 @@
         <v>46161.84576415509</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8321,13 +8327,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8337,7 +8343,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B115" s="9">
         <v>46161.58322151621</v>
@@ -8347,7 +8353,7 @@
         <v>46161.84576082176</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8374,13 +8380,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8390,7 +8396,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B116" s="5">
         <v>46161.58322717593</v>
@@ -8400,7 +8406,7 @@
         <v>46161.84575040509</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8427,13 +8433,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8443,7 +8449,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B117" s="9">
         <v>46161.58324248843</v>
@@ -8453,7 +8459,7 @@
         <v>46161.84574967592</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8480,13 +8486,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8496,7 +8502,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B118" s="5">
         <v>46161.58325402778</v>
@@ -8506,7 +8512,7 @@
         <v>46161.845748946755</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8533,13 +8539,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8549,7 +8555,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B119" s="9">
         <v>46161.58326291667</v>
@@ -8559,7 +8565,7 @@
         <v>46161.84574821759</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8586,13 +8592,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8602,7 +8608,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B120" s="5">
         <v>46161.58113928241</v>
@@ -8612,7 +8618,7 @@
         <v>46161.845971400464</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8639,13 +8645,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q120" s="5">
         <v>46296</v>
@@ -8665,7 +8671,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B121" s="9">
         <v>46161.58114282407</v>
@@ -8675,7 +8681,7 @@
         <v>46161.845958969905</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8702,13 +8708,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8718,7 +8724,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B122" s="5">
         <v>46161.585882430554</v>
@@ -8728,7 +8734,7 @@
         <v>46161.845956122685</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8755,13 +8761,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8771,7 +8777,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B123" s="9">
         <v>46161.58590298611</v>
@@ -8781,7 +8787,7 @@
         <v>46161.84595341435</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8808,13 +8814,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8824,7 +8830,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B124" s="5">
         <v>46161.585919861114</v>
@@ -8834,7 +8840,7 @@
         <v>46161.84595043982</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8861,13 +8867,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8877,7 +8883,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B125" s="9">
         <v>46161.585927175925</v>
@@ -8887,7 +8893,7 @@
         <v>46161.84594708333</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8914,13 +8920,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8930,7 +8936,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B126" s="5">
         <v>46161.58593310185</v>
@@ -8940,7 +8946,7 @@
         <v>46161.845944189816</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8967,13 +8973,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8983,7 +8989,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B127" s="9">
         <v>46161.58593739584</v>
@@ -8993,7 +8999,7 @@
         <v>46161.8459415625</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9020,13 +9026,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9036,7 +9042,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B128" s="5">
         <v>46161.58594590278</v>
@@ -9046,7 +9052,7 @@
         <v>46161.84593365741</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9073,13 +9079,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9089,7 +9095,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B129" s="9">
         <v>46161.5859562963</v>
@@ -9099,7 +9105,7 @@
         <v>46161.84593283565</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9126,13 +9132,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9142,7 +9148,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B130" s="5">
         <v>46161.58618912037</v>
@@ -9152,7 +9158,7 @@
         <v>46161.84593203704</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9179,13 +9185,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9195,7 +9201,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B131" s="9">
         <v>46161.58114761574</v>
@@ -9205,7 +9211,7 @@
         <v>46161.8461249074</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9232,13 +9238,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q131" s="9">
         <v>46300</v>
@@ -9258,7 +9264,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B132" s="5">
         <v>46161.58115116898</v>
@@ -9268,7 +9274,7 @@
         <v>46161.8461116088</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9295,13 +9301,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9311,7 +9317,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B133" s="9">
         <v>46161.58603712963</v>
@@ -9321,7 +9327,7 @@
         <v>46161.84610825231</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9348,13 +9354,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9364,7 +9370,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B134" s="5">
         <v>46161.586044930555</v>
@@ -9374,7 +9380,7 @@
         <v>46161.84610548611</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9401,13 +9407,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9417,7 +9423,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B135" s="9">
         <v>46161.58605891204</v>
@@ -9427,7 +9433,7 @@
         <v>46161.84610232639</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9454,13 +9460,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9470,7 +9476,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B136" s="5">
         <v>46161.58606768519</v>
@@ -9480,7 +9486,7 @@
         <v>46161.84609929398</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9507,13 +9513,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9523,7 +9529,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B137" s="9">
         <v>46161.58607575232</v>
@@ -9533,7 +9539,7 @@
         <v>46161.84609641204</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9560,13 +9566,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9576,7 +9582,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B138" s="5">
         <v>46161.586088854165</v>
@@ -9586,7 +9592,7 @@
         <v>46161.84609388889</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9613,13 +9619,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9629,7 +9635,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B139" s="9">
         <v>46161.58609570602</v>
@@ -9639,7 +9645,7 @@
         <v>46161.84608592592</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9666,13 +9672,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9682,7 +9688,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B140" s="5">
         <v>46161.586110578704</v>
@@ -9692,7 +9698,7 @@
         <v>46161.84608520834</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9719,13 +9725,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9735,7 +9741,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B141" s="9">
         <v>46161.58612255787</v>
@@ -9745,7 +9751,7 @@
         <v>46161.84608447917</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9772,13 +9778,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9788,7 +9794,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B142" s="5">
         <v>46161.58115643519</v>
@@ -9798,7 +9804,7 @@
         <v>46161.84629616898</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9825,13 +9831,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q142" s="5">
         <v>46303</v>
@@ -9851,7 +9857,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B143" s="9">
         <v>46161.58115993056</v>
@@ -9861,7 +9867,7 @@
         <v>46161.8462891088</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9888,13 +9894,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9904,7 +9910,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B144" s="5">
         <v>46161.58622641204</v>
@@ -9914,7 +9920,7 @@
         <v>46161.84628587963</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9941,13 +9947,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9957,7 +9963,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B145" s="9">
         <v>46161.586235995375</v>
@@ -9967,7 +9973,7 @@
         <v>46161.84628291667</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -9994,13 +10000,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10010,7 +10016,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B146" s="5">
         <v>46161.586246770836</v>
@@ -10020,7 +10026,7 @@
         <v>46161.846280046295</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10047,13 +10053,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10063,7 +10069,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B147" s="9">
         <v>46161.586256435185</v>
@@ -10073,7 +10079,7 @@
         <v>46161.84627699074</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10100,13 +10106,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10116,7 +10122,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B148" s="5">
         <v>46161.586265833335</v>
@@ -10126,7 +10132,7 @@
         <v>46161.84627394676</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10153,13 +10159,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10169,7 +10175,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B149" s="9">
         <v>46161.586275671296</v>
@@ -10179,7 +10185,7 @@
         <v>46161.84627113426</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10206,13 +10212,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10222,7 +10228,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B150" s="5">
         <v>46161.58629186342</v>
@@ -10232,7 +10238,7 @@
         <v>46161.846268402776</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10259,13 +10265,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10275,7 +10281,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B151" s="9">
         <v>46161.58630879629</v>
@@ -10285,7 +10291,7 @@
         <v>46161.84626222222</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10312,13 +10318,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10328,7 +10334,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B152" s="5">
         <v>46161.58632163194</v>
@@ -10338,7 +10344,7 @@
         <v>46161.84626162037</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10365,13 +10371,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10381,7 +10387,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B153" s="9">
         <v>46161.5811646875</v>
@@ -10391,7 +10397,7 @@
         <v>46161.84643925926</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10418,13 +10424,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q153" s="9">
         <v>46307</v>
@@ -10444,7 +10450,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B154" s="5">
         <v>46161.58116828704</v>
@@ -10454,7 +10460,7 @@
         <v>46161.84644222222</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10479,13 +10485,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10495,7 +10501,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B155" s="9">
         <v>46161.63912622685</v>
@@ -10505,7 +10511,7 @@
         <v>46161.84643929398</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10530,10 +10536,10 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>26</v>
@@ -10546,7 +10552,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B156" s="5">
         <v>46161.63913737268</v>
@@ -10556,7 +10562,7 @@
         <v>46161.84643643518</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10581,10 +10587,10 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>26</v>
@@ -10597,7 +10603,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B157" s="9">
         <v>46161.63914719908</v>
@@ -10607,7 +10613,7 @@
         <v>46161.846433321756</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10632,10 +10638,10 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>26</v>
@@ -10648,7 +10654,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B158" s="5">
         <v>46161.639157557875</v>
@@ -10658,7 +10664,7 @@
         <v>46161.84643013889</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10683,10 +10689,10 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10699,7 +10705,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B159" s="9">
         <v>46161.6391721875</v>
@@ -10709,7 +10715,7 @@
         <v>46161.84642646991</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10734,10 +10740,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>26</v>
@@ -10750,7 +10756,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B160" s="5">
         <v>46161.639187395835</v>
@@ -10760,7 +10766,7 @@
         <v>46161.84642321759</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10785,10 +10791,10 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>26</v>
@@ -10801,7 +10807,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B161" s="9">
         <v>46161.639195289354</v>
@@ -10811,7 +10817,7 @@
         <v>46161.846420138885</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10836,10 +10842,10 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>26</v>
@@ -10852,7 +10858,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B162" s="5">
         <v>46161.63920550926</v>
@@ -10862,7 +10868,7 @@
         <v>46161.846413113424</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -10887,10 +10893,10 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>26</v>
@@ -10903,7 +10909,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B163" s="9">
         <v>46161.63921432871</v>
@@ -10913,7 +10919,7 @@
         <v>46161.84641241898</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -10938,13 +10944,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10954,7 +10960,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B164" s="5">
         <v>46161.58117752315</v>
@@ -10964,7 +10970,7 @@
         <v>46161.84660503472</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -10991,13 +10997,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q164" s="5">
         <v>46309</v>
@@ -11017,7 +11023,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B165" s="9">
         <v>46161.58118137732</v>
@@ -11027,7 +11033,7 @@
         <v>46161.84658016203</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11054,13 +11060,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11070,7 +11076,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B166" s="5">
         <v>46161.639253761576</v>
@@ -11080,7 +11086,7 @@
         <v>46161.846577187505</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11107,10 +11113,10 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11123,7 +11129,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B167" s="9">
         <v>46161.63928710648</v>
@@ -11133,7 +11139,7 @@
         <v>46161.84657417824</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11160,10 +11166,10 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P167" s="10" t="s">
         <v>26</v>
@@ -11176,7 +11182,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B168" s="5">
         <v>46161.63929736111</v>
@@ -11186,7 +11192,7 @@
         <v>46161.84657136574</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11213,10 +11219,10 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>26</v>
@@ -11229,7 +11235,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B169" s="9">
         <v>46161.6393071412</v>
@@ -11239,7 +11245,7 @@
         <v>46161.84656841435</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11266,10 +11272,10 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11282,7 +11288,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B170" s="5">
         <v>46161.639315625</v>
@@ -11292,7 +11298,7 @@
         <v>46161.84656539352</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11319,10 +11325,10 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11335,7 +11341,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B171" s="9">
         <v>46161.63932686343</v>
@@ -11345,7 +11351,7 @@
         <v>46161.846562754625</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11372,10 +11378,10 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>26</v>
@@ -11388,7 +11394,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B172" s="5">
         <v>46161.63933708333</v>
@@ -11398,7 +11404,7 @@
         <v>46161.8465599537</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11425,10 +11431,10 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>26</v>
@@ -11441,7 +11447,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B173" s="9">
         <v>46161.63935484954</v>
@@ -11451,7 +11457,7 @@
         <v>46161.846553807874</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11478,10 +11484,10 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P173" s="10" t="s">
         <v>26</v>
@@ -11494,7 +11500,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B174" s="5">
         <v>46161.63936453704</v>
@@ -11504,7 +11510,7 @@
         <v>46161.84655313657</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11531,13 +11537,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11547,7 +11553,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B175" s="9">
         <v>46161.5811852662</v>
@@ -11557,7 +11563,7 @@
         <v>46161.84092732639</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>25</v>
@@ -11581,7 +11587,7 @@
         <v>26</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P175" s="10" t="s">
         <v>26</v>
@@ -11594,7 +11600,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B176" s="5">
         <v>46161.581188020835</v>
@@ -11604,16 +11610,16 @@
         <v>46161.84675815972</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I176" s="5">
         <v>46310</v>
@@ -11631,13 +11637,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q176" s="5">
         <v>46310</v>
@@ -11657,7 +11663,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B177" s="9">
         <v>46161.581192673606</v>
@@ -11667,16 +11673,16 @@
         <v>46161.846749351855</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I177" s="9">
         <v>46310</v>
@@ -11694,13 +11700,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11710,7 +11716,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B178" s="5">
         <v>46161.63982708333</v>
@@ -11720,16 +11726,16 @@
         <v>46161.84674655093</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I178" s="5">
         <v>46310</v>
@@ -11747,13 +11753,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11763,7 +11769,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B179" s="9">
         <v>46161.63983532407</v>
@@ -11773,16 +11779,16 @@
         <v>46161.846743981485</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I179" s="9">
         <v>46310</v>
@@ -11800,13 +11806,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11816,7 +11822,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B180" s="5">
         <v>46161.63984421296</v>
@@ -11826,16 +11832,16 @@
         <v>46161.84674143518</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I180" s="5">
         <v>46310</v>
@@ -11853,13 +11859,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11869,7 +11875,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B181" s="9">
         <v>46161.63985878472</v>
@@ -11879,16 +11885,16 @@
         <v>46161.846738541666</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I181" s="9">
         <v>46310</v>
@@ -11906,13 +11912,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11922,7 +11928,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B182" s="5">
         <v>46161.63986780093</v>
@@ -11932,16 +11938,16 @@
         <v>46161.84673559028</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I182" s="5">
         <v>46310</v>
@@ -11959,13 +11965,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -11975,7 +11981,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B183" s="9">
         <v>46161.639875</v>
@@ -11985,16 +11991,16 @@
         <v>46161.84673289352</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I183" s="9">
         <v>46310</v>
@@ -12012,13 +12018,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12028,7 +12034,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B184" s="5">
         <v>46161.63988342593</v>
@@ -12038,16 +12044,16 @@
         <v>46161.84672489583</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I184" s="5">
         <v>46310</v>
@@ -12065,13 +12071,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12081,7 +12087,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B185" s="9">
         <v>46161.63989143519</v>
@@ -12091,16 +12097,16 @@
         <v>46161.84672420139</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I185" s="9">
         <v>46310</v>
@@ -12118,13 +12124,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12134,7 +12140,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B186" s="5">
         <v>46161.639899340276</v>
@@ -12144,16 +12150,16 @@
         <v>46161.84672340278</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I186" s="5">
         <v>46310</v>
@@ -12171,13 +12177,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12187,7 +12193,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B187" s="9">
         <v>46161.5811965162</v>
@@ -12197,7 +12203,7 @@
         <v>46161.84690181713</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12224,13 +12230,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q187" s="9">
         <v>46311</v>
@@ -12250,7 +12256,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B188" s="5">
         <v>46161.58120002315</v>
@@ -12260,7 +12266,7 @@
         <v>46161.84690336806</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12287,13 +12293,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12303,7 +12309,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B189" s="9">
         <v>46161.63993424768</v>
@@ -12313,7 +12319,7 @@
         <v>46161.84690038195</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12340,13 +12346,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12356,7 +12362,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B190" s="5">
         <v>46161.6399947801</v>
@@ -12366,7 +12372,7 @@
         <v>46161.84689746528</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12393,13 +12399,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12409,7 +12415,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B191" s="9">
         <v>46161.640004444445</v>
@@ -12419,7 +12425,7 @@
         <v>46161.84689446759</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12446,13 +12452,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12462,7 +12468,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B192" s="5">
         <v>46161.64001501157</v>
@@ -12472,7 +12478,7 @@
         <v>46161.84689137731</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12499,13 +12505,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12515,7 +12521,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B193" s="9">
         <v>46161.640023831016</v>
@@ -12525,7 +12531,7 @@
         <v>46161.846888796295</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12552,13 +12558,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12568,7 +12574,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B194" s="5">
         <v>46161.640038310186</v>
@@ -12578,7 +12584,7 @@
         <v>46161.84688606481</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12605,13 +12611,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12621,7 +12627,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B195" s="9">
         <v>46161.64004747685</v>
@@ -12631,7 +12637,7 @@
         <v>46161.846882557875</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -12658,13 +12664,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12674,7 +12680,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B196" s="5">
         <v>46161.64005649305</v>
@@ -12684,7 +12690,7 @@
         <v>46161.84687957176</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12711,13 +12717,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12727,7 +12733,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B197" s="9">
         <v>46161.64006346065</v>
@@ -12737,7 +12743,7 @@
         <v>46161.846870243055</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -12764,13 +12770,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12780,7 +12786,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B198" s="5">
         <v>46161.58120399306</v>
@@ -12790,16 +12796,16 @@
         <v>46161.84710645833</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -12815,13 +12821,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q198" s="5">
         <v>46316</v>
@@ -12841,7 +12847,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B199" s="9">
         <v>46161.58120755787</v>
@@ -12851,16 +12857,16 @@
         <v>46161.847077812505</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -12876,13 +12882,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12892,7 +12898,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B200" s="5">
         <v>46161.6401252662</v>
@@ -12902,16 +12908,16 @@
         <v>46161.84707505787</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -12927,13 +12933,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -12943,7 +12949,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B201" s="9">
         <v>46161.64014137731</v>
@@ -12953,16 +12959,16 @@
         <v>46161.847072476856</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -12978,13 +12984,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -12994,7 +13000,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B202" s="5">
         <v>46161.64015293981</v>
@@ -13004,16 +13010,16 @@
         <v>46161.84706930556</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13029,13 +13035,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13045,7 +13051,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B203" s="9">
         <v>46161.64016740741</v>
@@ -13055,16 +13061,16 @@
         <v>46161.847066608796</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -13080,13 +13086,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13096,7 +13102,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B204" s="5">
         <v>46161.640203877316</v>
@@ -13106,16 +13112,16 @@
         <v>46161.84706402778</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13131,13 +13137,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13147,7 +13153,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B205" s="9">
         <v>46161.64021510417</v>
@@ -13157,16 +13163,16 @@
         <v>46161.84706112268</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13182,13 +13188,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13198,7 +13204,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B206" s="5">
         <v>46161.64022702546</v>
@@ -13208,16 +13214,16 @@
         <v>46161.847053425925</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13233,13 +13239,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13249,7 +13255,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B207" s="9">
         <v>46161.64023784723</v>
@@ -13259,16 +13265,16 @@
         <v>46161.8470527662</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13284,13 +13290,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13300,7 +13306,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B208" s="5">
         <v>46161.64025311342</v>
@@ -13310,16 +13316,16 @@
         <v>46161.84705210648</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I208" s="6"/>
       <c r="J208" s="5">
@@ -13335,13 +13341,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13351,7 +13357,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B209" s="9">
         <v>46161.58121466435</v>
@@ -13361,16 +13367,16 @@
         <v>46161.84730193287</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I209" s="9">
         <v>46317</v>
@@ -13388,13 +13394,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Q209" s="9">
         <v>46317</v>
@@ -13414,7 +13420,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B210" s="5">
         <v>46161.58125732639</v>
@@ -13424,16 +13430,16 @@
         <v>46161.84728091436</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13449,13 +13455,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13465,7 +13471,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B211" s="9">
         <v>46161.640307905094</v>
@@ -13475,16 +13481,16 @@
         <v>46161.84727769676</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I211" s="10"/>
       <c r="J211" s="9">
@@ -13500,10 +13506,10 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>26</v>
@@ -13516,7 +13522,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B212" s="5">
         <v>46161.64031635417</v>
@@ -13526,16 +13532,16 @@
         <v>46161.84727525463</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13551,10 +13557,10 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>26</v>
@@ -13567,7 +13573,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B213" s="9">
         <v>46161.64032832176</v>
@@ -13577,16 +13583,16 @@
         <v>46161.84727247685</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I213" s="10"/>
       <c r="J213" s="9">
@@ -13602,10 +13608,10 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>26</v>
@@ -13618,7 +13624,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B214" s="5">
         <v>46161.640337986115</v>
@@ -13628,16 +13634,16 @@
         <v>46161.84726945602</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13653,10 +13659,10 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13669,7 +13675,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B215" s="9">
         <v>46161.64035862268</v>
@@ -13679,16 +13685,16 @@
         <v>46161.84726638889</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I215" s="10"/>
       <c r="J215" s="9">
@@ -13704,10 +13710,10 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13720,7 +13726,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B216" s="5">
         <v>46161.64036773148</v>
@@ -13730,16 +13736,16 @@
         <v>46161.84726359954</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13755,10 +13761,10 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>26</v>
@@ -13771,7 +13777,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B217" s="9">
         <v>46161.64037657407</v>
@@ -13781,16 +13787,16 @@
         <v>46161.84726060185</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I217" s="10"/>
       <c r="J217" s="9">
@@ -13806,10 +13812,10 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>26</v>
@@ -13822,7 +13828,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B218" s="5">
         <v>46161.64038473379</v>
@@ -13832,16 +13838,16 @@
         <v>46161.847254699074</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -13857,10 +13863,10 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>26</v>
@@ -13873,7 +13879,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B219" s="9">
         <v>46161.64039350694</v>
@@ -13883,16 +13889,16 @@
         <v>46161.8472540625</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I219" s="10"/>
       <c r="J219" s="9">
@@ -13908,10 +13914,10 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>26</v>
@@ -13924,7 +13930,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B220" s="5">
         <v>46161.581262824075</v>
@@ -13934,7 +13940,7 @@
         <v>46161.84801045139</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>25</v>
@@ -13958,7 +13964,7 @@
         <v>26</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P220" s="6" t="s">
         <v>26</v>
@@ -13971,7 +13977,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B221" s="9">
         <v>46161.58126615741</v>
@@ -13981,16 +13987,16 @@
         <v>46161.84764756945</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I221" s="9">
         <v>46318</v>
@@ -14008,13 +14014,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Q221" s="9">
         <v>46318</v>
@@ -14034,7 +14040,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B222" s="5">
         <v>46161.581270821756</v>
@@ -14044,7 +14050,7 @@
         <v>46161.848222546294</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
@@ -14071,13 +14077,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Q222" s="5">
         <v>46318</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -783,7 +783,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT2 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214937509401251</t>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2738,7 +2738,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46161.73672747685</v>
+        <v>46197.58860099537</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>71</v>
@@ -2909,9 +2909,11 @@
       <c r="B18" s="5">
         <v>46161.58079363426</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46197.58859138889</v>
+      </c>
       <c r="D18" s="5">
-        <v>46169.879556631946</v>
+        <v>46197.5886116551</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2959,10 +2961,10 @@
         <v>61</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -3517,7 +3519,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.87969822917</v>
+        <v>46197.58860037037</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>116</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="458">
   <si>
     <t>50001555 - "ZITRON COLOMBIA ARIS MINING SEGOVIA"</t>
   </si>
@@ -228,115 +228,135 @@
     <t>cperez@zitron.com</t>
   </si>
   <si>
-    <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
+    <t xml:space="preserve">MOTOR
+        OT 4332 — ZVN 1-10-110/2 -- MOTOR 90 KW, 250 S/M, 2 Polos
+</t>
   </si>
   <si>
     <t>propuesta motor ot 4332,Ingenieria Jefe de proyecto:,Analisis de costeo</t>
   </si>
   <si>
+    <t>1214937151453811</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+    Definición Rodete ZVN 1-10:
+        Alabes s/plano 3073.01
+        Código 300003
+        Calaje y Consumo. hgutierrez@zitron.com por favor tu apoyo.
+</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,propuesta alabes ot 4332,propuesta nucleo rodete ot 4332,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>1214937151453831</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para el pedido 50001555, se tienen 10 ventiladores ZVN 1-10-110/2 para Zitrón Colombia (Airis Marmato):
+Alcance: TOBERA + REJILLA + FAR 100/100 + VENT + FAR 100/100 + TIPO A
+    Plano para fabricación:
+        Ventilador ZVN 1-10-110/2 con motor Weg o similar
+        Alcance Chile: TOBERA + REJILLA + VENT 
+        Alcance Colombia: 2FAR 100/100 + TIPO A
+    Definición Rodete ZVN 1-10:
+        Alabes s/plano 3073.01
+        Código 300003
+    Datos eléctricos motor 
+        MOTOR 90 KW, 250 S/M, 2 Polos
+        Grasera automatica
+    Tratamiento superficial estándar Zitrón:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Ingenieria Jefe de proyecto:,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>1214952151039987</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1214937151453811</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Selección de Rodete:
-        Rodete de placas s/plano 3073.00
-        Alabe s/ plano 3073.01
-        Z8 N600
-        Código 300003
-        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
-</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,propuesta alabes ot 4332,propuesta nucleo rodete ot 4332,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>1214937151453831</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Ingenieria Jefe de proyecto:,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1214952151039987</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
+    <t>1214922603742605</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta motor ot 4332,propuesta alabes ot 4332,propuesta nucleo rodete ot 4332,propuesta Corte Laser ot 4332</t>
+  </si>
+  <si>
+    <t>1214937201122333</t>
+  </si>
+  <si>
+    <t>propuesta motor ot 4332</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor ot 4332</t>
+  </si>
+  <si>
+    <t>1214937218503738</t>
+  </si>
+  <si>
+    <t>propuesta alabes ot 4332</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe ot 4332</t>
+  </si>
+  <si>
+    <t>1214937218503758</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete ot 4332</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4332,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1214952151057781</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser ot 4332</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser ot 4332,Propuesta compras:</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214922603742605</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta motor ot 4332,propuesta alabes ot 4332,propuesta nucleo rodete ot 4332,propuesta Corte Laser ot 4332</t>
-  </si>
-  <si>
-    <t>1214937201122333</t>
-  </si>
-  <si>
-    <t>propuesta motor ot 4332</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor ot 4332</t>
-  </si>
-  <si>
-    <t>1214937218503738</t>
-  </si>
-  <si>
-    <t>propuesta alabes ot 4332</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe ot 4332</t>
-  </si>
-  <si>
-    <t>1214937218503758</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete ot 4332</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4332,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1214952151057781</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser ot 4332</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser ot 4332,Propuesta compras:</t>
   </si>
   <si>
     <t>1214952151057796</t>
@@ -1509,12 +1529,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -2439,7 +2459,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46161.684720543984</v>
+        <v>46197.67728914352</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2484,9 +2504,11 @@
       <c r="B11" s="9">
         <v>46161.580761307865</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="9">
+        <v>46197.67426642361</v>
+      </c>
       <c r="D11" s="9">
-        <v>46175.87850755787</v>
+        <v>46197.674283043976</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2534,25 +2556,27 @@
         <v>33</v>
       </c>
       <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="11" t="s">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" s="5">
         <v>46161.580766307874</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46197.67508163194</v>
+      </c>
       <c r="D12" s="5">
-        <v>46175.878507256944</v>
+        <v>46197.67509547454</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2573,7 +2597,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2585,7 +2609,7 @@
         <v>41</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="5">
         <v>46154</v>
@@ -2593,29 +2617,31 @@
       <c r="R12" s="5">
         <v>46162</v>
       </c>
-      <c r="S12" s="12" t="s">
-        <v>61</v>
+      <c r="S12" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="11" t="s">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="U12" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13" s="9">
         <v>46161.580771423614</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="9">
+        <v>46197.67727987269</v>
+      </c>
       <c r="D13" s="9">
-        <v>46196.74087425926</v>
+        <v>46197.677296249996</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2636,7 +2662,7 @@
         <v>26</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>26</v>
@@ -2656,14 +2682,14 @@
       <c r="R13" s="9">
         <v>46162</v>
       </c>
-      <c r="S13" s="12" t="s">
-        <v>61</v>
+      <c r="S13" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="T13" s="10">
-        <v>0</v>
-      </c>
-      <c r="U13" s="11" t="s">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2675,7 +2701,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46163.18186976852</v>
+        <v>46197.67729836806</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2719,8 +2745,8 @@
       <c r="R14" s="5">
         <v>46162</v>
       </c>
-      <c r="S14" s="12" t="s">
-        <v>61</v>
+      <c r="S14" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="T14" s="6">
         <v>0</v>
@@ -2785,7 +2811,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46192.85352256944</v>
+        <v>46197.67428359954</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2848,7 +2874,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46169.87954540509</v>
+        <v>46197.67510195602</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>77</v>
@@ -2881,7 +2907,7 @@
         <v>71</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P17" s="10" t="s">
         <v>78</v>
@@ -2892,8 +2918,8 @@
       <c r="R17" s="9">
         <v>46167</v>
       </c>
-      <c r="S17" s="12" t="s">
-        <v>61</v>
+      <c r="S17" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
@@ -2913,7 +2939,7 @@
         <v>46197.58859138889</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.5886116551</v>
+        <v>46197.675101863424</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2946,7 +2972,7 @@
         <v>71</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>82</v>
@@ -2957,14 +2983,14 @@
       <c r="R18" s="5">
         <v>46167</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>61</v>
+      <c r="S18" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
       </c>
-      <c r="U18" s="7" t="s">
-        <v>27</v>
+      <c r="U18" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -3026,13 +3052,13 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="12" t="s">
-        <v>69</v>
+      <c r="U19" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B20" s="5">
         <v>46161.58080373843</v>
@@ -3042,7 +3068,7 @@
         <v>46169.87958414352</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3075,7 +3101,7 @@
         <v>87</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -3089,13 +3115,13 @@
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="12" t="s">
-        <v>69</v>
+      <c r="U20" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B21" s="9">
         <v>46161.58080740741</v>
@@ -3105,7 +3131,7 @@
         <v>46169.879600381944</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -3138,7 +3164,7 @@
         <v>87</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q21" s="9">
         <v>46224</v>
@@ -3152,13 +3178,13 @@
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="12" t="s">
-        <v>69</v>
+      <c r="U21" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B22" s="5">
         <v>46161.580810740736</v>
@@ -3168,7 +3194,7 @@
         <v>46169.87961318287</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -3201,7 +3227,7 @@
         <v>87</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q22" s="5">
         <v>46224</v>
@@ -3215,13 +3241,13 @@
       <c r="T22" s="6">
         <v>0</v>
       </c>
-      <c r="U22" s="12" t="s">
-        <v>69</v>
+      <c r="U22" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B23" s="9">
         <v>46161.58064796297</v>
@@ -3231,7 +3257,7 @@
         <v>46161.73787121528</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -3255,7 +3281,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3268,7 +3294,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46161.58081472223</v>
@@ -3278,16 +3304,16 @@
         <v>46169.879378680555</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I24" s="5">
         <v>46168</v>
@@ -3305,13 +3331,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="5">
         <v>46168</v>
@@ -3325,13 +3351,13 @@
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="12" t="s">
-        <v>69</v>
+      <c r="U24" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B25" s="9">
         <v>46161.580819016206</v>
@@ -3341,16 +3367,16 @@
         <v>46169.879644560184</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I25" s="9">
         <v>46168</v>
@@ -3368,13 +3394,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>77</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3384,13 +3410,13 @@
       <c r="T25" s="10">
         <v>0</v>
       </c>
-      <c r="U25" s="12" t="s">
-        <v>69</v>
+      <c r="U25" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B26" s="5">
         <v>46161.58082350694</v>
@@ -3400,16 +3426,16 @@
         <v>46169.87966921296</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I26" s="5">
         <v>46170</v>
@@ -3427,13 +3453,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3443,13 +3469,13 @@
       <c r="T26" s="6">
         <v>0</v>
       </c>
-      <c r="U26" s="12" t="s">
-        <v>69</v>
+      <c r="U26" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B27" s="9">
         <v>46161.58082824074</v>
@@ -3459,16 +3485,16 @@
         <v>46192.85867619213</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I27" s="9">
         <v>46168</v>
@@ -3486,13 +3512,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="9">
         <v>46168</v>
@@ -3500,19 +3526,19 @@
       <c r="R27" s="9">
         <v>46171</v>
       </c>
-      <c r="S27" s="12" t="s">
-        <v>61</v>
+      <c r="S27" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
-      <c r="U27" s="12" t="s">
-        <v>69</v>
+      <c r="U27" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B28" s="5">
         <v>46161.5808325463</v>
@@ -3522,16 +3548,16 @@
         <v>46197.58860037037</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I28" s="5">
         <v>46168</v>
@@ -3549,13 +3575,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>80</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3565,13 +3591,13 @@
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>69</v>
+      <c r="U28" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B29" s="9">
         <v>46161.580836967594</v>
@@ -3581,16 +3607,16 @@
         <v>46171.17352185185</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I29" s="9">
         <v>46170</v>
@@ -3608,13 +3634,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3624,13 +3650,13 @@
       <c r="T29" s="10">
         <v>0</v>
       </c>
-      <c r="U29" s="12" t="s">
-        <v>69</v>
+      <c r="U29" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B30" s="5">
         <v>46161.58084165509</v>
@@ -3640,16 +3666,16 @@
         <v>46192.86032678241</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I30" s="5">
         <v>46156</v>
@@ -3667,13 +3693,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q30" s="5">
         <v>46156</v>
@@ -3687,13 +3713,13 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="12" t="s">
-        <v>69</v>
+      <c r="U30" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B31" s="9">
         <v>46161.58084603009</v>
@@ -3703,16 +3729,16 @@
         <v>46175.170256446756</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I31" s="9">
         <v>46156</v>
@@ -3730,13 +3756,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>74</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3746,13 +3772,13 @@
       <c r="T31" s="10">
         <v>0</v>
       </c>
-      <c r="U31" s="12" t="s">
-        <v>69</v>
+      <c r="U31" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B32" s="5">
         <v>46161.580850439816</v>
@@ -3762,16 +3788,16 @@
         <v>46169.87976645833</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I32" s="5">
         <v>46176</v>
@@ -3789,13 +3815,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3805,13 +3831,13 @@
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="12" t="s">
-        <v>69</v>
+      <c r="U32" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B33" s="9">
         <v>46161.58085503472</v>
@@ -3821,16 +3847,16 @@
         <v>46169.879778622686</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I33" s="9">
         <v>46176</v>
@@ -3848,13 +3874,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3864,13 +3890,13 @@
       <c r="T33" s="10">
         <v>0</v>
       </c>
-      <c r="U33" s="12" t="s">
-        <v>69</v>
+      <c r="U33" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46161.58085940972</v>
@@ -3880,16 +3906,16 @@
         <v>46169.87943234954</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I34" s="5">
         <v>46226</v>
@@ -3907,13 +3933,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q34" s="5">
         <v>46226</v>
@@ -3927,13 +3953,13 @@
       <c r="T34" s="6">
         <v>0</v>
       </c>
-      <c r="U34" s="12" t="s">
-        <v>69</v>
+      <c r="U34" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B35" s="9">
         <v>46161.58086364584</v>
@@ -3943,16 +3969,16 @@
         <v>46169.879810196755</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I35" s="9">
         <v>46226</v>
@@ -3970,13 +3996,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>84</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3986,13 +4012,13 @@
       <c r="T35" s="10">
         <v>0</v>
       </c>
-      <c r="U35" s="12" t="s">
-        <v>69</v>
+      <c r="U35" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="5">
         <v>46161.58086832176</v>
@@ -4002,16 +4028,16 @@
         <v>46169.879828854166</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -4029,13 +4055,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -4045,13 +4071,13 @@
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="12" t="s">
-        <v>69</v>
+      <c r="U36" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="9">
         <v>46161.58087322916</v>
@@ -4061,16 +4087,16 @@
         <v>46169.87944365741</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46226</v>
@@ -4088,10 +4114,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -4108,13 +4134,13 @@
       <c r="T37" s="10">
         <v>0</v>
       </c>
-      <c r="U37" s="12" t="s">
-        <v>69</v>
+      <c r="U37" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5">
         <v>46161.580931018514</v>
@@ -4124,16 +4150,16 @@
         <v>46169.8798540625</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I38" s="5">
         <v>46226</v>
@@ -4151,13 +4177,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4167,7 +4193,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B39" s="9">
         <v>46161.58093646991</v>
@@ -4177,16 +4203,16 @@
         <v>46169.87986516204</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I39" s="9">
         <v>46230</v>
@@ -4204,13 +4230,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4220,7 +4246,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46161.580941099535</v>
@@ -4230,16 +4256,16 @@
         <v>46169.87945328704</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I40" s="5">
         <v>46225</v>
@@ -4257,10 +4283,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -4277,13 +4303,13 @@
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="12" t="s">
-        <v>69</v>
+      <c r="U40" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B41" s="9">
         <v>46161.58094532407</v>
@@ -4293,16 +4319,16 @@
         <v>46169.87990410879</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I41" s="9">
         <v>46225</v>
@@ -4320,13 +4346,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4336,7 +4362,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B42" s="5">
         <v>46161.58094997685</v>
@@ -4346,16 +4372,16 @@
         <v>46169.87991520834</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I42" s="5">
         <v>46234</v>
@@ -4373,13 +4399,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4389,7 +4415,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B43" s="9">
         <v>46161.58095447917</v>
@@ -4399,16 +4425,16 @@
         <v>46169.879929814815</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I43" s="9">
         <v>46265</v>
@@ -4426,10 +4452,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4442,7 +4468,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5">
         <v>46161.58095743056</v>
@@ -4452,16 +4478,16 @@
         <v>46169.87951825232</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I44" s="5">
         <v>46226</v>
@@ -4479,10 +4505,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4499,13 +4525,13 @@
       <c r="T44" s="6">
         <v>0</v>
       </c>
-      <c r="U44" s="12" t="s">
-        <v>69</v>
+      <c r="U44" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="9">
         <v>46161.58096091435</v>
@@ -4515,16 +4541,16 @@
         <v>46169.87997335648</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I45" s="9">
         <v>46226</v>
@@ -4542,13 +4568,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4558,7 +4584,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46161.580964988425</v>
@@ -4568,16 +4594,16 @@
         <v>46169.87999765047</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I46" s="5">
         <v>46230</v>
@@ -4595,13 +4621,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4611,7 +4637,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46161.58065239583</v>
@@ -4621,7 +4647,7 @@
         <v>46161.73609247685</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>25</v>
@@ -4645,7 +4671,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4658,26 +4684,26 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46161.580969780094</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46196.7401344213</v>
+        <v>46197.67729875</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I48" s="5">
         <v>46164</v>
@@ -4695,13 +4721,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="5">
         <v>46164</v>
@@ -4709,8 +4735,8 @@
       <c r="R48" s="5">
         <v>46170</v>
       </c>
-      <c r="S48" s="12" t="s">
-        <v>61</v>
+      <c r="S48" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4721,7 +4747,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46161.580975069446</v>
@@ -4731,16 +4757,16 @@
         <v>46196.74022112269</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I49" s="9">
         <v>46216</v>
@@ -4758,13 +4784,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q49" s="9">
         <v>46216</v>
@@ -4778,13 +4804,13 @@
       <c r="T49" s="10">
         <v>0</v>
       </c>
-      <c r="U49" s="12" t="s">
-        <v>69</v>
+      <c r="U49" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46161.58098100695</v>
@@ -4800,10 +4826,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I50" s="5">
         <v>46223</v>
@@ -4821,13 +4847,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q50" s="5">
         <v>46223</v>
@@ -4841,13 +4867,13 @@
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="12" t="s">
-        <v>69</v>
+      <c r="U50" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46161.58099116899</v>
@@ -4857,16 +4883,16 @@
         <v>46161.84476310185</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I51" s="9">
         <v>46308</v>
@@ -4884,10 +4910,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4904,13 +4930,13 @@
       <c r="T51" s="10">
         <v>0</v>
       </c>
-      <c r="U51" s="12" t="s">
-        <v>69</v>
+      <c r="U51" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B52" s="5">
         <v>46161.58099418982</v>
@@ -4920,16 +4946,16 @@
         <v>46161.84476607639</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4945,13 +4971,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4961,7 +4987,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B53" s="9">
         <v>46161.63966489583</v>
@@ -4971,16 +4997,16 @@
         <v>46161.844763472225</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -4996,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5012,7 +5038,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46161.63967261574</v>
@@ -5022,16 +5048,16 @@
         <v>46161.84476069444</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5047,13 +5073,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5063,7 +5089,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B55" s="9">
         <v>46161.63968388889</v>
@@ -5073,16 +5099,16 @@
         <v>46161.84475773148</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5098,13 +5124,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5114,7 +5140,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B56" s="5">
         <v>46161.63969275463</v>
@@ -5124,16 +5150,16 @@
         <v>46161.84475471065</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5149,13 +5175,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5165,7 +5191,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B57" s="9">
         <v>46161.639705208334</v>
@@ -5175,16 +5201,16 @@
         <v>46161.84475174769</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5200,13 +5226,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5216,7 +5242,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B58" s="5">
         <v>46161.639715474535</v>
@@ -5226,16 +5252,16 @@
         <v>46161.84474863426</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5251,13 +5277,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5267,7 +5293,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B59" s="9">
         <v>46161.63972679398</v>
@@ -5277,16 +5303,16 @@
         <v>46161.84474503472</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5302,13 +5328,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5318,7 +5344,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B60" s="5">
         <v>46161.63974304398</v>
@@ -5328,16 +5354,16 @@
         <v>46161.84473834491</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5353,13 +5379,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5369,7 +5395,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B61" s="9">
         <v>46161.63975269676</v>
@@ -5379,16 +5405,16 @@
         <v>46161.84473753472</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5404,13 +5430,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5420,7 +5446,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B62" s="5">
         <v>46161.58099818287</v>
@@ -5430,7 +5456,7 @@
         <v>46161.79647144676</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5454,7 +5480,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5467,7 +5493,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B63" s="9">
         <v>46161.58100145833</v>
@@ -5477,16 +5503,16 @@
         <v>46161.844842499995</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I63" s="9">
         <v>46239</v>
@@ -5504,13 +5530,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="9">
         <v>46239</v>
@@ -5524,13 +5550,13 @@
       <c r="T63" s="10">
         <v>0</v>
       </c>
-      <c r="U63" s="12" t="s">
-        <v>69</v>
+      <c r="U63" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B64" s="5">
         <v>46161.58100614583</v>
@@ -5540,16 +5566,16 @@
         <v>46161.84491849537</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I64" s="5">
         <v>46241</v>
@@ -5567,13 +5593,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q64" s="5">
         <v>46241</v>
@@ -5587,13 +5613,13 @@
       <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="12" t="s">
-        <v>69</v>
+      <c r="U64" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B65" s="9">
         <v>46161.58101638889</v>
@@ -5603,16 +5629,16 @@
         <v>46161.84483983796</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I65" s="9">
         <v>46239</v>
@@ -5630,13 +5656,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q65" s="9">
         <v>46239</v>
@@ -5650,13 +5676,13 @@
       <c r="T65" s="10">
         <v>0</v>
       </c>
-      <c r="U65" s="12" t="s">
-        <v>69</v>
+      <c r="U65" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B66" s="5">
         <v>46161.58102099537</v>
@@ -5666,16 +5692,16 @@
         <v>46161.84491503472</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I66" s="5">
         <v>46241</v>
@@ -5693,13 +5719,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q66" s="5">
         <v>46241</v>
@@ -5713,13 +5739,13 @@
       <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="U66" s="12" t="s">
-        <v>69</v>
+      <c r="U66" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B67" s="9">
         <v>46161.581024722225</v>
@@ -5729,16 +5755,16 @@
         <v>46161.8448359375</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I67" s="9">
         <v>46239</v>
@@ -5756,13 +5782,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q67" s="9">
         <v>46239</v>
@@ -5776,13 +5802,13 @@
       <c r="T67" s="10">
         <v>0</v>
       </c>
-      <c r="U67" s="12" t="s">
-        <v>69</v>
+      <c r="U67" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B68" s="5">
         <v>46161.58102864583</v>
@@ -5792,16 +5818,16 @@
         <v>46161.844914270834</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I68" s="5">
         <v>46241</v>
@@ -5819,13 +5845,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q68" s="5">
         <v>46241</v>
@@ -5839,13 +5865,13 @@
       <c r="T68" s="6">
         <v>0</v>
       </c>
-      <c r="U68" s="12" t="s">
-        <v>69</v>
+      <c r="U68" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B69" s="9">
         <v>46161.58103207176</v>
@@ -5855,7 +5881,7 @@
         <v>46161.797785821764</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5879,7 +5905,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5892,7 +5918,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
         <v>46161.58103457176</v>
@@ -5902,16 +5928,16 @@
         <v>46161.845178449075</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I70" s="5">
         <v>46245</v>
@@ -5929,13 +5955,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q70" s="5">
         <v>46245</v>
@@ -5949,13 +5975,13 @@
       <c r="T70" s="6">
         <v>0</v>
       </c>
-      <c r="U70" s="12" t="s">
-        <v>69</v>
+      <c r="U70" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="9">
         <v>46161.58103962963</v>
@@ -5965,16 +5991,16 @@
         <v>46161.845147071755</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I71" s="9">
         <v>46245</v>
@@ -5992,13 +6018,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6008,7 +6034,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46161.582011805556</v>
@@ -6018,16 +6044,16 @@
         <v>46161.84514348379</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I72" s="5">
         <v>46245</v>
@@ -6045,13 +6071,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6061,7 +6087,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="9">
         <v>46161.58202383102</v>
@@ -6071,16 +6097,16 @@
         <v>46161.845140324076</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I73" s="9">
         <v>46245</v>
@@ -6098,13 +6124,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6114,7 +6140,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46161.582662650464</v>
@@ -6124,16 +6150,16 @@
         <v>46161.845136655094</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I74" s="5">
         <v>46245</v>
@@ -6151,13 +6177,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6167,7 +6193,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" s="9">
         <v>46161.58267322917</v>
@@ -6177,16 +6203,16 @@
         <v>46161.845133518524</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I75" s="9">
         <v>46245</v>
@@ -6204,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6220,7 +6246,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
         <v>46161.58270134259</v>
@@ -6230,16 +6256,16 @@
         <v>46161.84513074074</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I76" s="5">
         <v>46245</v>
@@ -6257,13 +6283,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6273,7 +6299,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="9">
         <v>46161.58271427083</v>
@@ -6283,16 +6309,16 @@
         <v>46161.84512803241</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I77" s="9">
         <v>46245</v>
@@ -6310,13 +6336,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6326,7 +6352,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46161.58272651621</v>
@@ -6336,16 +6362,16 @@
         <v>46161.84512407407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I78" s="5">
         <v>46245</v>
@@ -6363,13 +6389,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6379,7 +6405,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46161.58277962963</v>
@@ -6389,16 +6415,16 @@
         <v>46161.845117916666</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I79" s="9">
         <v>46245</v>
@@ -6416,13 +6442,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6432,7 +6458,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46161.58279046296</v>
@@ -6442,16 +6468,16 @@
         <v>46161.84511721064</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I80" s="5">
         <v>46245</v>
@@ -6469,13 +6495,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6485,7 +6511,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B81" s="9">
         <v>46161.58104538194</v>
@@ -6495,16 +6521,16 @@
         <v>46161.845344814814</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I81" s="9">
         <v>46254</v>
@@ -6522,13 +6548,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q81" s="9">
         <v>46254</v>
@@ -6542,13 +6568,13 @@
       <c r="T81" s="10">
         <v>0</v>
       </c>
-      <c r="U81" s="12" t="s">
-        <v>69</v>
+      <c r="U81" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B82" s="5">
         <v>46161.58104903935</v>
@@ -6558,16 +6584,16 @@
         <v>46161.84533920139</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I82" s="5">
         <v>46254</v>
@@ -6585,13 +6611,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6601,7 +6627,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B83" s="9">
         <v>46161.582834120374</v>
@@ -6611,16 +6637,16 @@
         <v>46161.84533628472</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I83" s="9">
         <v>46254</v>
@@ -6638,13 +6664,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6654,7 +6680,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46161.58286459491</v>
@@ -6664,16 +6690,16 @@
         <v>46161.84533336805</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I84" s="5">
         <v>46254</v>
@@ -6691,13 +6717,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6707,7 +6733,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B85" s="9">
         <v>46161.58287381944</v>
@@ -6717,16 +6743,16 @@
         <v>46161.84533065972</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I85" s="9">
         <v>46254</v>
@@ -6744,13 +6770,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6760,7 +6786,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B86" s="5">
         <v>46161.58288365741</v>
@@ -6770,16 +6796,16 @@
         <v>46161.84532790509</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I86" s="5">
         <v>46254</v>
@@ -6797,13 +6823,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6813,7 +6839,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B87" s="9">
         <v>46161.58289255787</v>
@@ -6823,16 +6849,16 @@
         <v>46161.84532486111</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I87" s="9">
         <v>46254</v>
@@ -6850,13 +6876,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6866,7 +6892,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B88" s="5">
         <v>46161.58292542824</v>
@@ -6876,16 +6902,16 @@
         <v>46161.84532211805</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I88" s="5">
         <v>46254</v>
@@ -6903,13 +6929,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6919,7 +6945,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B89" s="9">
         <v>46161.58293696759</v>
@@ -6929,16 +6955,16 @@
         <v>46161.84531927083</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I89" s="9">
         <v>46254</v>
@@ -6956,13 +6982,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6972,7 +6998,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B90" s="5">
         <v>46161.58295282407</v>
@@ -6982,16 +7008,16 @@
         <v>46161.84531311343</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I90" s="5">
         <v>46254</v>
@@ -7009,13 +7035,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7025,7 +7051,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B91" s="9">
         <v>46161.58296773148</v>
@@ -7035,16 +7061,16 @@
         <v>46161.84531243055</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I91" s="9">
         <v>46254</v>
@@ -7062,13 +7088,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7078,7 +7104,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B92" s="5">
         <v>46161.581053761576</v>
@@ -7088,16 +7114,16 @@
         <v>46161.84552644676</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -7115,13 +7141,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q92" s="5">
         <v>46274</v>
@@ -7135,13 +7161,13 @@
       <c r="T92" s="6">
         <v>0</v>
       </c>
-      <c r="U92" s="12" t="s">
-        <v>69</v>
+      <c r="U92" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B93" s="9">
         <v>46161.58105741898</v>
@@ -7151,16 +7177,16 @@
         <v>46161.845511736115</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I93" s="9">
         <v>46274</v>
@@ -7178,13 +7204,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7194,7 +7220,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B94" s="5">
         <v>46161.583039942125</v>
@@ -7204,16 +7230,16 @@
         <v>46161.84550880787</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I94" s="5">
         <v>46274</v>
@@ -7231,13 +7257,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7247,7 +7273,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B95" s="9">
         <v>46161.58305715278</v>
@@ -7257,16 +7283,16 @@
         <v>46161.845505324076</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I95" s="9">
         <v>46274</v>
@@ -7284,13 +7310,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7300,7 +7326,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B96" s="5">
         <v>46161.583076689814</v>
@@ -7310,16 +7336,16 @@
         <v>46161.84550258102</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I96" s="5">
         <v>46274</v>
@@ -7337,13 +7363,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7353,7 +7379,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B97" s="9">
         <v>46161.58308886574</v>
@@ -7363,16 +7389,16 @@
         <v>46161.84549928241</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I97" s="9">
         <v>46274</v>
@@ -7390,13 +7416,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7406,7 +7432,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B98" s="5">
         <v>46161.58310019676</v>
@@ -7416,16 +7442,16 @@
         <v>46161.84549533565</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I98" s="5">
         <v>46274</v>
@@ -7443,13 +7469,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7459,7 +7485,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B99" s="9">
         <v>46161.5831108912</v>
@@ -7469,16 +7495,16 @@
         <v>46161.84549206018</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I99" s="9">
         <v>46274</v>
@@ -7496,13 +7522,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7512,7 +7538,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B100" s="5">
         <v>46161.58312844907</v>
@@ -7522,16 +7548,16 @@
         <v>46161.84548887731</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I100" s="5">
         <v>46274</v>
@@ -7549,13 +7575,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7565,7 +7591,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B101" s="9">
         <v>46161.58300775463</v>
@@ -7575,16 +7601,16 @@
         <v>46161.84548230324</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I101" s="9">
         <v>46274</v>
@@ -7602,13 +7628,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7618,7 +7644,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B102" s="5">
         <v>46161.639501875004</v>
@@ -7628,16 +7654,16 @@
         <v>46161.845481620374</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I102" s="5">
         <v>46274</v>
@@ -7655,13 +7681,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7671,7 +7697,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B103" s="9">
         <v>46161.58110506945</v>
@@ -7681,7 +7707,7 @@
         <v>46161.80776861111</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7705,7 +7731,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7718,7 +7744,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B104" s="5">
         <v>46161.581108530096</v>
@@ -7728,16 +7754,16 @@
         <v>46176.18811300926</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I104" s="5">
         <v>46174</v>
@@ -7755,13 +7781,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q104" s="5">
         <v>46174</v>
@@ -7769,19 +7795,19 @@
       <c r="R104" s="5">
         <v>46175</v>
       </c>
-      <c r="S104" s="12" t="s">
-        <v>61</v>
+      <c r="S104" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
-      <c r="U104" s="12" t="s">
-        <v>69</v>
+      <c r="U104" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B105" s="9">
         <v>46161.58111370371</v>
@@ -7791,16 +7817,16 @@
         <v>46161.84560915509</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I105" s="9">
         <v>46282</v>
@@ -7818,13 +7844,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q105" s="9">
         <v>46282</v>
@@ -7838,13 +7864,13 @@
       <c r="T105" s="10">
         <v>0</v>
       </c>
-      <c r="U105" s="12" t="s">
-        <v>69</v>
+      <c r="U105" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B106" s="5">
         <v>46161.581118449074</v>
@@ -7854,16 +7880,16 @@
         <v>46161.84560644676</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I106" s="5">
         <v>46301</v>
@@ -7881,13 +7907,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q106" s="5">
         <v>46301</v>
@@ -7901,13 +7927,13 @@
       <c r="T106" s="6">
         <v>0</v>
       </c>
-      <c r="U106" s="12" t="s">
-        <v>69</v>
+      <c r="U106" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B107" s="9">
         <v>46161.58112311343</v>
@@ -7917,16 +7943,16 @@
         <v>46161.84560210648</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I107" s="9">
         <v>46237</v>
@@ -7944,13 +7970,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q107" s="9">
         <v>46237</v>
@@ -7964,13 +7990,13 @@
       <c r="T107" s="10">
         <v>0</v>
       </c>
-      <c r="U107" s="12" t="s">
-        <v>69</v>
+      <c r="U107" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B108" s="5">
         <v>46161.58112702546</v>
@@ -7980,7 +8006,7 @@
         <v>46161.83387362269</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>25</v>
@@ -8004,7 +8030,7 @@
         <v>26</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -8017,7 +8043,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B109" s="9">
         <v>46161.58112984954</v>
@@ -8027,7 +8053,7 @@
         <v>46161.84578230324</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8054,13 +8080,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q109" s="9">
         <v>46276</v>
@@ -8074,13 +8100,13 @@
       <c r="T109" s="10">
         <v>0</v>
       </c>
-      <c r="U109" s="12" t="s">
-        <v>69</v>
+      <c r="U109" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B110" s="5">
         <v>46161.581135555556</v>
@@ -8090,7 +8116,7 @@
         <v>46161.84577694444</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8117,13 +8143,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8133,7 +8159,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B111" s="9">
         <v>46161.58317730324</v>
@@ -8143,7 +8169,7 @@
         <v>46161.84577366898</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8170,13 +8196,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8186,7 +8212,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B112" s="5">
         <v>46161.58318758102</v>
@@ -8196,7 +8222,7 @@
         <v>46161.845770879634</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8223,13 +8249,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8239,7 +8265,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B113" s="9">
         <v>46161.5831975926</v>
@@ -8249,7 +8275,7 @@
         <v>46161.84576709491</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8276,13 +8302,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8292,7 +8318,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B114" s="5">
         <v>46161.58320657407</v>
@@ -8302,7 +8328,7 @@
         <v>46161.84576415509</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8329,13 +8355,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8345,7 +8371,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B115" s="9">
         <v>46161.58322151621</v>
@@ -8355,7 +8381,7 @@
         <v>46161.84576082176</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8382,13 +8408,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8398,7 +8424,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B116" s="5">
         <v>46161.58322717593</v>
@@ -8408,7 +8434,7 @@
         <v>46161.84575040509</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8435,13 +8461,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8451,7 +8477,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B117" s="9">
         <v>46161.58324248843</v>
@@ -8461,7 +8487,7 @@
         <v>46161.84574967592</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8488,13 +8514,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8504,7 +8530,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B118" s="5">
         <v>46161.58325402778</v>
@@ -8514,7 +8540,7 @@
         <v>46161.845748946755</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8541,13 +8567,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8557,7 +8583,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B119" s="9">
         <v>46161.58326291667</v>
@@ -8567,7 +8593,7 @@
         <v>46161.84574821759</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8594,13 +8620,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8610,7 +8636,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B120" s="5">
         <v>46161.58113928241</v>
@@ -8620,7 +8646,7 @@
         <v>46161.845971400464</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8647,13 +8673,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q120" s="5">
         <v>46296</v>
@@ -8667,13 +8693,13 @@
       <c r="T120" s="6">
         <v>0</v>
       </c>
-      <c r="U120" s="12" t="s">
-        <v>69</v>
+      <c r="U120" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B121" s="9">
         <v>46161.58114282407</v>
@@ -8683,7 +8709,7 @@
         <v>46161.845958969905</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8710,13 +8736,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8726,7 +8752,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B122" s="5">
         <v>46161.585882430554</v>
@@ -8736,7 +8762,7 @@
         <v>46161.845956122685</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8763,13 +8789,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8779,7 +8805,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B123" s="9">
         <v>46161.58590298611</v>
@@ -8789,7 +8815,7 @@
         <v>46161.84595341435</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8816,13 +8842,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8832,7 +8858,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B124" s="5">
         <v>46161.585919861114</v>
@@ -8842,7 +8868,7 @@
         <v>46161.84595043982</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8869,13 +8895,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8885,7 +8911,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B125" s="9">
         <v>46161.585927175925</v>
@@ -8895,7 +8921,7 @@
         <v>46161.84594708333</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8922,13 +8948,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8938,7 +8964,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B126" s="5">
         <v>46161.58593310185</v>
@@ -8948,7 +8974,7 @@
         <v>46161.845944189816</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8975,13 +9001,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8991,7 +9017,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B127" s="9">
         <v>46161.58593739584</v>
@@ -9001,7 +9027,7 @@
         <v>46161.8459415625</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9028,13 +9054,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9044,7 +9070,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B128" s="5">
         <v>46161.58594590278</v>
@@ -9054,7 +9080,7 @@
         <v>46161.84593365741</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9081,13 +9107,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9097,7 +9123,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B129" s="9">
         <v>46161.5859562963</v>
@@ -9107,7 +9133,7 @@
         <v>46161.84593283565</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9134,13 +9160,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9150,7 +9176,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B130" s="5">
         <v>46161.58618912037</v>
@@ -9160,7 +9186,7 @@
         <v>46161.84593203704</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9187,13 +9213,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9203,7 +9229,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B131" s="9">
         <v>46161.58114761574</v>
@@ -9213,7 +9239,7 @@
         <v>46161.8461249074</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9240,13 +9266,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q131" s="9">
         <v>46300</v>
@@ -9260,13 +9286,13 @@
       <c r="T131" s="10">
         <v>0</v>
       </c>
-      <c r="U131" s="12" t="s">
-        <v>69</v>
+      <c r="U131" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B132" s="5">
         <v>46161.58115116898</v>
@@ -9276,7 +9302,7 @@
         <v>46161.8461116088</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9303,13 +9329,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9319,7 +9345,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B133" s="9">
         <v>46161.58603712963</v>
@@ -9329,7 +9355,7 @@
         <v>46161.84610825231</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9356,13 +9382,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9372,7 +9398,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B134" s="5">
         <v>46161.586044930555</v>
@@ -9382,7 +9408,7 @@
         <v>46161.84610548611</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9409,13 +9435,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9425,7 +9451,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B135" s="9">
         <v>46161.58605891204</v>
@@ -9435,7 +9461,7 @@
         <v>46161.84610232639</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9462,13 +9488,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9478,7 +9504,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B136" s="5">
         <v>46161.58606768519</v>
@@ -9488,7 +9514,7 @@
         <v>46161.84609929398</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9515,13 +9541,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9531,7 +9557,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B137" s="9">
         <v>46161.58607575232</v>
@@ -9541,7 +9567,7 @@
         <v>46161.84609641204</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9568,13 +9594,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9584,7 +9610,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B138" s="5">
         <v>46161.586088854165</v>
@@ -9594,7 +9620,7 @@
         <v>46161.84609388889</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9621,13 +9647,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9637,7 +9663,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B139" s="9">
         <v>46161.58609570602</v>
@@ -9647,7 +9673,7 @@
         <v>46161.84608592592</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9674,13 +9700,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9690,7 +9716,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B140" s="5">
         <v>46161.586110578704</v>
@@ -9700,7 +9726,7 @@
         <v>46161.84608520834</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9727,13 +9753,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9743,7 +9769,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B141" s="9">
         <v>46161.58612255787</v>
@@ -9753,7 +9779,7 @@
         <v>46161.84608447917</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9780,13 +9806,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9796,7 +9822,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B142" s="5">
         <v>46161.58115643519</v>
@@ -9806,7 +9832,7 @@
         <v>46161.84629616898</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9833,13 +9859,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q142" s="5">
         <v>46303</v>
@@ -9853,13 +9879,13 @@
       <c r="T142" s="6">
         <v>0</v>
       </c>
-      <c r="U142" s="12" t="s">
-        <v>69</v>
+      <c r="U142" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B143" s="9">
         <v>46161.58115993056</v>
@@ -9869,7 +9895,7 @@
         <v>46161.8462891088</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9896,13 +9922,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9912,7 +9938,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B144" s="5">
         <v>46161.58622641204</v>
@@ -9922,7 +9948,7 @@
         <v>46161.84628587963</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9949,13 +9975,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9965,7 +9991,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B145" s="9">
         <v>46161.586235995375</v>
@@ -9975,7 +10001,7 @@
         <v>46161.84628291667</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10002,13 +10028,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10018,7 +10044,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B146" s="5">
         <v>46161.586246770836</v>
@@ -10028,7 +10054,7 @@
         <v>46161.846280046295</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10055,13 +10081,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10071,7 +10097,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B147" s="9">
         <v>46161.586256435185</v>
@@ -10081,7 +10107,7 @@
         <v>46161.84627699074</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10108,13 +10134,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10124,7 +10150,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B148" s="5">
         <v>46161.586265833335</v>
@@ -10134,7 +10160,7 @@
         <v>46161.84627394676</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10161,13 +10187,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10177,7 +10203,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B149" s="9">
         <v>46161.586275671296</v>
@@ -10187,7 +10213,7 @@
         <v>46161.84627113426</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10214,13 +10240,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10230,7 +10256,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B150" s="5">
         <v>46161.58629186342</v>
@@ -10240,7 +10266,7 @@
         <v>46161.846268402776</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10267,13 +10293,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10283,7 +10309,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B151" s="9">
         <v>46161.58630879629</v>
@@ -10293,7 +10319,7 @@
         <v>46161.84626222222</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10320,13 +10346,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10336,7 +10362,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B152" s="5">
         <v>46161.58632163194</v>
@@ -10346,7 +10372,7 @@
         <v>46161.84626162037</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10373,13 +10399,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10389,7 +10415,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B153" s="9">
         <v>46161.5811646875</v>
@@ -10399,7 +10425,7 @@
         <v>46161.84643925926</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10426,13 +10452,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q153" s="9">
         <v>46307</v>
@@ -10446,13 +10472,13 @@
       <c r="T153" s="10">
         <v>0</v>
       </c>
-      <c r="U153" s="12" t="s">
-        <v>69</v>
+      <c r="U153" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B154" s="5">
         <v>46161.58116828704</v>
@@ -10462,7 +10488,7 @@
         <v>46161.84644222222</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10487,13 +10513,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10503,7 +10529,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B155" s="9">
         <v>46161.63912622685</v>
@@ -10513,7 +10539,7 @@
         <v>46161.84643929398</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10538,10 +10564,10 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>26</v>
@@ -10554,7 +10580,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B156" s="5">
         <v>46161.63913737268</v>
@@ -10564,7 +10590,7 @@
         <v>46161.84643643518</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10589,10 +10615,10 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>26</v>
@@ -10605,7 +10631,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B157" s="9">
         <v>46161.63914719908</v>
@@ -10615,7 +10641,7 @@
         <v>46161.846433321756</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10640,10 +10666,10 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>26</v>
@@ -10656,7 +10682,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B158" s="5">
         <v>46161.639157557875</v>
@@ -10666,7 +10692,7 @@
         <v>46161.84643013889</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10691,10 +10717,10 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10707,7 +10733,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B159" s="9">
         <v>46161.6391721875</v>
@@ -10717,7 +10743,7 @@
         <v>46161.84642646991</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10742,10 +10768,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>26</v>
@@ -10758,7 +10784,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B160" s="5">
         <v>46161.639187395835</v>
@@ -10768,7 +10794,7 @@
         <v>46161.84642321759</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10793,10 +10819,10 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>26</v>
@@ -10809,7 +10835,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B161" s="9">
         <v>46161.639195289354</v>
@@ -10819,7 +10845,7 @@
         <v>46161.846420138885</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10844,10 +10870,10 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>26</v>
@@ -10860,7 +10886,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B162" s="5">
         <v>46161.63920550926</v>
@@ -10870,7 +10896,7 @@
         <v>46161.846413113424</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -10895,10 +10921,10 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>26</v>
@@ -10911,7 +10937,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B163" s="9">
         <v>46161.63921432871</v>
@@ -10921,7 +10947,7 @@
         <v>46161.84641241898</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -10946,13 +10972,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10962,7 +10988,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B164" s="5">
         <v>46161.58117752315</v>
@@ -10972,7 +10998,7 @@
         <v>46161.84660503472</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -10999,13 +11025,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q164" s="5">
         <v>46309</v>
@@ -11019,13 +11045,13 @@
       <c r="T164" s="6">
         <v>0</v>
       </c>
-      <c r="U164" s="12" t="s">
-        <v>69</v>
+      <c r="U164" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B165" s="9">
         <v>46161.58118137732</v>
@@ -11035,7 +11061,7 @@
         <v>46161.84658016203</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11062,13 +11088,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11078,7 +11104,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B166" s="5">
         <v>46161.639253761576</v>
@@ -11088,7 +11114,7 @@
         <v>46161.846577187505</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11115,10 +11141,10 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11131,7 +11157,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B167" s="9">
         <v>46161.63928710648</v>
@@ -11141,7 +11167,7 @@
         <v>46161.84657417824</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11168,10 +11194,10 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P167" s="10" t="s">
         <v>26</v>
@@ -11184,7 +11210,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B168" s="5">
         <v>46161.63929736111</v>
@@ -11194,7 +11220,7 @@
         <v>46161.84657136574</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11221,10 +11247,10 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>26</v>
@@ -11237,7 +11263,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B169" s="9">
         <v>46161.6393071412</v>
@@ -11247,7 +11273,7 @@
         <v>46161.84656841435</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11274,10 +11300,10 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11290,7 +11316,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B170" s="5">
         <v>46161.639315625</v>
@@ -11300,7 +11326,7 @@
         <v>46161.84656539352</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11327,10 +11353,10 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11343,7 +11369,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B171" s="9">
         <v>46161.63932686343</v>
@@ -11353,7 +11379,7 @@
         <v>46161.846562754625</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11380,10 +11406,10 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>26</v>
@@ -11396,7 +11422,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B172" s="5">
         <v>46161.63933708333</v>
@@ -11406,7 +11432,7 @@
         <v>46161.8465599537</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11433,10 +11459,10 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>26</v>
@@ -11449,7 +11475,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B173" s="9">
         <v>46161.63935484954</v>
@@ -11459,7 +11485,7 @@
         <v>46161.846553807874</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11486,10 +11512,10 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P173" s="10" t="s">
         <v>26</v>
@@ -11502,7 +11528,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B174" s="5">
         <v>46161.63936453704</v>
@@ -11512,7 +11538,7 @@
         <v>46161.84655313657</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11539,13 +11565,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11555,7 +11581,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B175" s="9">
         <v>46161.5811852662</v>
@@ -11565,7 +11591,7 @@
         <v>46161.84092732639</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>25</v>
@@ -11589,7 +11615,7 @@
         <v>26</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P175" s="10" t="s">
         <v>26</v>
@@ -11602,7 +11628,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B176" s="5">
         <v>46161.581188020835</v>
@@ -11612,16 +11638,16 @@
         <v>46161.84675815972</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I176" s="5">
         <v>46310</v>
@@ -11639,13 +11665,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q176" s="5">
         <v>46310</v>
@@ -11659,13 +11685,13 @@
       <c r="T176" s="6">
         <v>0</v>
       </c>
-      <c r="U176" s="12" t="s">
-        <v>69</v>
+      <c r="U176" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B177" s="9">
         <v>46161.581192673606</v>
@@ -11675,16 +11701,16 @@
         <v>46161.846749351855</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I177" s="9">
         <v>46310</v>
@@ -11702,13 +11728,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11718,7 +11744,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B178" s="5">
         <v>46161.63982708333</v>
@@ -11728,16 +11754,16 @@
         <v>46161.84674655093</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I178" s="5">
         <v>46310</v>
@@ -11755,13 +11781,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11771,7 +11797,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B179" s="9">
         <v>46161.63983532407</v>
@@ -11781,16 +11807,16 @@
         <v>46161.846743981485</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I179" s="9">
         <v>46310</v>
@@ -11808,13 +11834,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11824,7 +11850,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B180" s="5">
         <v>46161.63984421296</v>
@@ -11834,16 +11860,16 @@
         <v>46161.84674143518</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I180" s="5">
         <v>46310</v>
@@ -11861,13 +11887,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11877,7 +11903,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B181" s="9">
         <v>46161.63985878472</v>
@@ -11887,16 +11913,16 @@
         <v>46161.846738541666</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I181" s="9">
         <v>46310</v>
@@ -11914,13 +11940,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11930,7 +11956,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B182" s="5">
         <v>46161.63986780093</v>
@@ -11940,16 +11966,16 @@
         <v>46161.84673559028</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I182" s="5">
         <v>46310</v>
@@ -11967,13 +11993,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -11983,7 +12009,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B183" s="9">
         <v>46161.639875</v>
@@ -11993,16 +12019,16 @@
         <v>46161.84673289352</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I183" s="9">
         <v>46310</v>
@@ -12020,13 +12046,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12036,7 +12062,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B184" s="5">
         <v>46161.63988342593</v>
@@ -12046,16 +12072,16 @@
         <v>46161.84672489583</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I184" s="5">
         <v>46310</v>
@@ -12073,13 +12099,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12089,7 +12115,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B185" s="9">
         <v>46161.63989143519</v>
@@ -12099,16 +12125,16 @@
         <v>46161.84672420139</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I185" s="9">
         <v>46310</v>
@@ -12126,13 +12152,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12142,7 +12168,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B186" s="5">
         <v>46161.639899340276</v>
@@ -12152,16 +12178,16 @@
         <v>46161.84672340278</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I186" s="5">
         <v>46310</v>
@@ -12179,13 +12205,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12195,7 +12221,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B187" s="9">
         <v>46161.5811965162</v>
@@ -12205,7 +12231,7 @@
         <v>46161.84690181713</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12232,13 +12258,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q187" s="9">
         <v>46311</v>
@@ -12252,13 +12278,13 @@
       <c r="T187" s="10">
         <v>0</v>
       </c>
-      <c r="U187" s="12" t="s">
-        <v>69</v>
+      <c r="U187" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B188" s="5">
         <v>46161.58120002315</v>
@@ -12268,7 +12294,7 @@
         <v>46161.84690336806</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12295,13 +12321,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12311,7 +12337,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B189" s="9">
         <v>46161.63993424768</v>
@@ -12321,7 +12347,7 @@
         <v>46161.84690038195</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12348,13 +12374,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12364,7 +12390,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B190" s="5">
         <v>46161.6399947801</v>
@@ -12374,7 +12400,7 @@
         <v>46161.84689746528</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12401,13 +12427,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12417,7 +12443,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B191" s="9">
         <v>46161.640004444445</v>
@@ -12427,7 +12453,7 @@
         <v>46161.84689446759</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12454,13 +12480,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12470,7 +12496,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B192" s="5">
         <v>46161.64001501157</v>
@@ -12480,7 +12506,7 @@
         <v>46161.84689137731</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12507,13 +12533,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12523,7 +12549,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B193" s="9">
         <v>46161.640023831016</v>
@@ -12533,7 +12559,7 @@
         <v>46161.846888796295</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12560,13 +12586,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12576,7 +12602,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B194" s="5">
         <v>46161.640038310186</v>
@@ -12586,7 +12612,7 @@
         <v>46161.84688606481</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12613,13 +12639,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12629,7 +12655,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B195" s="9">
         <v>46161.64004747685</v>
@@ -12639,7 +12665,7 @@
         <v>46161.846882557875</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -12666,13 +12692,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12682,7 +12708,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B196" s="5">
         <v>46161.64005649305</v>
@@ -12692,7 +12718,7 @@
         <v>46161.84687957176</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12719,13 +12745,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12735,7 +12761,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B197" s="9">
         <v>46161.64006346065</v>
@@ -12745,7 +12771,7 @@
         <v>46161.846870243055</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -12772,13 +12798,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12788,7 +12814,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B198" s="5">
         <v>46161.58120399306</v>
@@ -12798,16 +12824,16 @@
         <v>46161.84710645833</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -12823,13 +12849,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q198" s="5">
         <v>46316</v>
@@ -12843,13 +12869,13 @@
       <c r="T198" s="6">
         <v>0</v>
       </c>
-      <c r="U198" s="12" t="s">
-        <v>69</v>
+      <c r="U198" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B199" s="9">
         <v>46161.58120755787</v>
@@ -12859,16 +12885,16 @@
         <v>46161.847077812505</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -12884,13 +12910,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12900,7 +12926,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B200" s="5">
         <v>46161.6401252662</v>
@@ -12910,16 +12936,16 @@
         <v>46161.84707505787</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -12935,13 +12961,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -12951,7 +12977,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B201" s="9">
         <v>46161.64014137731</v>
@@ -12961,16 +12987,16 @@
         <v>46161.847072476856</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -12986,13 +13012,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13002,7 +13028,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B202" s="5">
         <v>46161.64015293981</v>
@@ -13012,16 +13038,16 @@
         <v>46161.84706930556</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13037,13 +13063,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13053,7 +13079,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B203" s="9">
         <v>46161.64016740741</v>
@@ -13063,16 +13089,16 @@
         <v>46161.847066608796</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -13088,13 +13114,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13104,7 +13130,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B204" s="5">
         <v>46161.640203877316</v>
@@ -13114,16 +13140,16 @@
         <v>46161.84706402778</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13139,13 +13165,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13155,7 +13181,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B205" s="9">
         <v>46161.64021510417</v>
@@ -13165,16 +13191,16 @@
         <v>46161.84706112268</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13190,13 +13216,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13206,7 +13232,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B206" s="5">
         <v>46161.64022702546</v>
@@ -13216,16 +13242,16 @@
         <v>46161.847053425925</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13241,13 +13267,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13257,7 +13283,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B207" s="9">
         <v>46161.64023784723</v>
@@ -13267,16 +13293,16 @@
         <v>46161.8470527662</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13292,13 +13318,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13308,7 +13334,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B208" s="5">
         <v>46161.64025311342</v>
@@ -13318,16 +13344,16 @@
         <v>46161.84705210648</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I208" s="6"/>
       <c r="J208" s="5">
@@ -13343,13 +13369,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13359,7 +13385,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B209" s="9">
         <v>46161.58121466435</v>
@@ -13369,16 +13395,16 @@
         <v>46161.84730193287</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I209" s="9">
         <v>46317</v>
@@ -13396,13 +13422,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q209" s="9">
         <v>46317</v>
@@ -13416,13 +13442,13 @@
       <c r="T209" s="10">
         <v>0</v>
       </c>
-      <c r="U209" s="12" t="s">
-        <v>69</v>
+      <c r="U209" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B210" s="5">
         <v>46161.58125732639</v>
@@ -13432,16 +13458,16 @@
         <v>46161.84728091436</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13457,13 +13483,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13473,7 +13499,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B211" s="9">
         <v>46161.640307905094</v>
@@ -13483,16 +13509,16 @@
         <v>46161.84727769676</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I211" s="10"/>
       <c r="J211" s="9">
@@ -13508,10 +13534,10 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>26</v>
@@ -13524,7 +13550,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B212" s="5">
         <v>46161.64031635417</v>
@@ -13534,16 +13560,16 @@
         <v>46161.84727525463</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13559,10 +13585,10 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>26</v>
@@ -13575,7 +13601,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B213" s="9">
         <v>46161.64032832176</v>
@@ -13585,16 +13611,16 @@
         <v>46161.84727247685</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I213" s="10"/>
       <c r="J213" s="9">
@@ -13610,10 +13636,10 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>26</v>
@@ -13626,7 +13652,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B214" s="5">
         <v>46161.640337986115</v>
@@ -13636,16 +13662,16 @@
         <v>46161.84726945602</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13661,10 +13687,10 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13677,7 +13703,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B215" s="9">
         <v>46161.64035862268</v>
@@ -13687,16 +13713,16 @@
         <v>46161.84726638889</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I215" s="10"/>
       <c r="J215" s="9">
@@ -13712,10 +13738,10 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13728,7 +13754,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B216" s="5">
         <v>46161.64036773148</v>
@@ -13738,16 +13764,16 @@
         <v>46161.84726359954</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13763,10 +13789,10 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>26</v>
@@ -13779,7 +13805,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B217" s="9">
         <v>46161.64037657407</v>
@@ -13789,16 +13815,16 @@
         <v>46161.84726060185</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I217" s="10"/>
       <c r="J217" s="9">
@@ -13814,10 +13840,10 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>26</v>
@@ -13830,7 +13856,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B218" s="5">
         <v>46161.64038473379</v>
@@ -13840,16 +13866,16 @@
         <v>46161.847254699074</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -13865,10 +13891,10 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>26</v>
@@ -13881,7 +13907,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B219" s="9">
         <v>46161.64039350694</v>
@@ -13891,16 +13917,16 @@
         <v>46161.8472540625</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I219" s="10"/>
       <c r="J219" s="9">
@@ -13916,10 +13942,10 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>26</v>
@@ -13932,7 +13958,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B220" s="5">
         <v>46161.581262824075</v>
@@ -13942,7 +13968,7 @@
         <v>46161.84801045139</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>25</v>
@@ -13966,7 +13992,7 @@
         <v>26</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P220" s="6" t="s">
         <v>26</v>
@@ -13979,7 +14005,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B221" s="9">
         <v>46161.58126615741</v>
@@ -13989,16 +14015,16 @@
         <v>46161.84764756945</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="I221" s="9">
         <v>46318</v>
@@ -14016,13 +14042,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q221" s="9">
         <v>46318</v>
@@ -14036,13 +14062,13 @@
       <c r="T221" s="10">
         <v>0</v>
       </c>
-      <c r="U221" s="12" t="s">
-        <v>69</v>
+      <c r="U221" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B222" s="5">
         <v>46161.581270821756</v>
@@ -14052,7 +14078,7 @@
         <v>46161.848222546294</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
@@ -14079,13 +14105,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q222" s="5">
         <v>46318</v>
@@ -14099,8 +14125,8 @@
       <c r="T222" s="6">
         <v>0</v>
       </c>
-      <c r="U222" s="12" t="s">
-        <v>69</v>
+      <c r="U222" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2087,13 +2087,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46161.58063581018</v>
+        <v>46161.41396914352</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87851013889</v>
+        <v>46175.71184347222</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87852383102</v>
+        <v>46175.71185716435</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2140,13 +2140,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46161.58074600695</v>
+        <v>46161.41407934028</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87848300926</v>
+        <v>46175.71181634259</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87851039352</v>
+        <v>46175.71184372685</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2203,13 +2203,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46161.58074907407</v>
+        <v>46161.414082407406</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87848385416</v>
+        <v>46175.711817187504</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87851055556</v>
+        <v>46175.71184388889</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2266,13 +2266,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46161.58075194445</v>
+        <v>46161.41408527778</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.878484409724</v>
+        <v>46175.71181774305</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.878510497685</v>
+        <v>46175.71184383101</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2329,13 +2329,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46161.58075466435</v>
+        <v>46161.414087997684</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.87848503472</v>
+        <v>46175.71181836806</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.878510925926</v>
+        <v>46175.71184425926</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2392,13 +2392,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46161.5807578588</v>
+        <v>46161.41409119213</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87848576389</v>
+        <v>46175.711819097225</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87851096065</v>
+        <v>46175.71184429398</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2455,11 +2455,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46161.580639618056</v>
+        <v>46161.413972951384</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46197.67728914352</v>
+        <v>46197.51062247685</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2502,13 +2502,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46161.580761307865</v>
+        <v>46161.41409464121</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.67426642361</v>
+        <v>46197.507599756944</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.674283043976</v>
+        <v>46197.50761637732</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2567,13 +2567,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46161.580766307874</v>
+        <v>46161.4140996412</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.67508163194</v>
+        <v>46197.50841496528</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.67509547454</v>
+        <v>46197.508428807865</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2632,13 +2632,13 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46161.580771423614</v>
+        <v>46161.41410475694</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.67727987269</v>
+        <v>46197.51061320602</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.677296249996</v>
+        <v>46197.51062958333</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2697,11 +2697,11 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46161.5807762037</v>
+        <v>46161.414109537036</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.67729836806</v>
+        <v>46197.510631701385</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2760,11 +2760,11 @@
         <v>70</v>
       </c>
       <c r="B15" s="9">
-        <v>46161.58064403935</v>
+        <v>46161.413977372686</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46197.58860099537</v>
+        <v>46197.421934328704</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>71</v>
@@ -2807,11 +2807,11 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46161.58078354166</v>
+        <v>46161.414116875</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.67428359954</v>
+        <v>46197.50761693287</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2870,11 +2870,11 @@
         <v>76</v>
       </c>
       <c r="B17" s="9">
-        <v>46161.580788680556</v>
+        <v>46161.414122013884</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46197.67510195602</v>
+        <v>46197.508435289354</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>77</v>
@@ -2933,13 +2933,13 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46161.58079363426</v>
+        <v>46161.41412696759</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.58859138889</v>
+        <v>46197.42192472222</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.675101863424</v>
+        <v>46197.50843519676</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2998,11 +2998,11 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46161.58079903935</v>
+        <v>46161.41413237268</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46169.87957331019</v>
+        <v>46169.712906643515</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -3061,11 +3061,11 @@
         <v>90</v>
       </c>
       <c r="B20" s="5">
-        <v>46161.58080373843</v>
+        <v>46161.414137071755</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46169.87958414352</v>
+        <v>46169.71291747685</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>91</v>
@@ -3124,11 +3124,11 @@
         <v>93</v>
       </c>
       <c r="B21" s="9">
-        <v>46161.58080740741</v>
+        <v>46161.414140740744</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46169.879600381944</v>
+        <v>46169.71293371527</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>94</v>
@@ -3187,11 +3187,11 @@
         <v>96</v>
       </c>
       <c r="B22" s="5">
-        <v>46161.580810740736</v>
+        <v>46161.41414407408</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46169.87961318287</v>
+        <v>46169.7129465162</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>97</v>
@@ -3250,11 +3250,11 @@
         <v>99</v>
       </c>
       <c r="B23" s="9">
-        <v>46161.58064796297</v>
+        <v>46161.4139812963</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46161.73787121528</v>
+        <v>46161.571204548614</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -3297,11 +3297,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46161.58081472223</v>
+        <v>46161.414148055555</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.879378680555</v>
+        <v>46169.71271201389</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3360,11 +3360,11 @@
         <v>107</v>
       </c>
       <c r="B25" s="9">
-        <v>46161.580819016206</v>
+        <v>46161.414152349535</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.879644560184</v>
+        <v>46169.71297789352</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>108</v>
@@ -3419,11 +3419,11 @@
         <v>110</v>
       </c>
       <c r="B26" s="5">
-        <v>46161.58082350694</v>
+        <v>46161.41415684028</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.87966921296</v>
+        <v>46169.7130025463</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>111</v>
@@ -3478,11 +3478,11 @@
         <v>113</v>
       </c>
       <c r="B27" s="9">
-        <v>46161.58082824074</v>
+        <v>46161.414161574074</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46192.85867619213</v>
+        <v>46192.69200952546</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>114</v>
@@ -3541,11 +3541,11 @@
         <v>116</v>
       </c>
       <c r="B28" s="5">
-        <v>46161.5808325463</v>
+        <v>46161.41416587963</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46197.58860037037</v>
+        <v>46197.42193370371</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>117</v>
@@ -3600,11 +3600,11 @@
         <v>119</v>
       </c>
       <c r="B29" s="9">
-        <v>46161.580836967594</v>
+        <v>46161.41417030092</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46171.17352185185</v>
+        <v>46171.00685518519</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>120</v>
@@ -3659,11 +3659,11 @@
         <v>122</v>
       </c>
       <c r="B30" s="5">
-        <v>46161.58084165509</v>
+        <v>46161.41417498843</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46192.86032678241</v>
+        <v>46192.693660115736</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>123</v>
@@ -3722,11 +3722,11 @@
         <v>125</v>
       </c>
       <c r="B31" s="9">
-        <v>46161.58084603009</v>
+        <v>46161.414179363426</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46175.170256446756</v>
+        <v>46175.00358978009</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>126</v>
@@ -3781,11 +3781,11 @@
         <v>128</v>
       </c>
       <c r="B32" s="5">
-        <v>46161.580850439816</v>
+        <v>46161.414183773144</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.87976645833</v>
+        <v>46169.71309979167</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>129</v>
@@ -3840,11 +3840,11 @@
         <v>131</v>
       </c>
       <c r="B33" s="9">
-        <v>46161.58085503472</v>
+        <v>46161.41418836806</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.879778622686</v>
+        <v>46169.71311195602</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>132</v>
@@ -3899,11 +3899,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46161.58085940972</v>
+        <v>46161.41419274306</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.87943234954</v>
+        <v>46169.71276568287</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3962,11 +3962,11 @@
         <v>139</v>
       </c>
       <c r="B35" s="9">
-        <v>46161.58086364584</v>
+        <v>46161.41419697917</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.879810196755</v>
+        <v>46169.7131435301</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>140</v>
@@ -4021,11 +4021,11 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46161.58086832176</v>
+        <v>46161.41420165509</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.879828854166</v>
+        <v>46169.7131621875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -4080,11 +4080,11 @@
         <v>145</v>
       </c>
       <c r="B37" s="9">
-        <v>46161.58087322916</v>
+        <v>46161.4142065625</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.87944365741</v>
+        <v>46169.71277699074</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>146</v>
@@ -4143,11 +4143,11 @@
         <v>148</v>
       </c>
       <c r="B38" s="5">
-        <v>46161.580931018514</v>
+        <v>46161.41426435186</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.8798540625</v>
+        <v>46169.713187395835</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>92</v>
@@ -4196,11 +4196,11 @@
         <v>150</v>
       </c>
       <c r="B39" s="9">
-        <v>46161.58093646991</v>
+        <v>46161.41426980324</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.87986516204</v>
+        <v>46169.713198495374</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>151</v>
@@ -4249,11 +4249,11 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46161.580941099535</v>
+        <v>46161.41427443287</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.87945328704</v>
+        <v>46169.71278662037</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>154</v>
@@ -4312,11 +4312,11 @@
         <v>158</v>
       </c>
       <c r="B41" s="9">
-        <v>46161.58094532407</v>
+        <v>46161.41427865741</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.87990410879</v>
+        <v>46169.713237442134</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>98</v>
@@ -4365,11 +4365,11 @@
         <v>160</v>
       </c>
       <c r="B42" s="5">
-        <v>46161.58094997685</v>
+        <v>46161.41428331019</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.87991520834</v>
+        <v>46169.713248541666</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>161</v>
@@ -4418,11 +4418,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46161.58095447917</v>
+        <v>46161.4142878125</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.879929814815</v>
+        <v>46169.71326314815</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4471,11 +4471,11 @@
         <v>167</v>
       </c>
       <c r="B44" s="5">
-        <v>46161.58095743056</v>
+        <v>46161.41429076389</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.87951825232</v>
+        <v>46169.712851585646</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>168</v>
@@ -4534,11 +4534,11 @@
         <v>170</v>
       </c>
       <c r="B45" s="9">
-        <v>46161.58096091435</v>
+        <v>46161.41429424769</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.87997335648</v>
+        <v>46169.71330668981</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>95</v>
@@ -4587,11 +4587,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46161.580964988425</v>
+        <v>46161.41429832176</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.87999765047</v>
+        <v>46169.713330983795</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4640,11 +4640,11 @@
         <v>175</v>
       </c>
       <c r="B47" s="9">
-        <v>46161.58065239583</v>
+        <v>46161.41398572917</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46161.73609247685</v>
+        <v>46161.56942581019</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>176</v>
@@ -4687,11 +4687,11 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46161.580969780094</v>
+        <v>46161.41430311343</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46197.67729875</v>
+        <v>46197.51063208333</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4750,11 +4750,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46161.580975069446</v>
+        <v>46161.414308402775</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46196.74022112269</v>
+        <v>46196.573554456016</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>184</v>
@@ -4813,11 +4813,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46161.58098100695</v>
+        <v>46161.414314340276</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46161.84455542824</v>
+        <v>46161.67788876157</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>87</v>
@@ -4876,11 +4876,11 @@
         <v>191</v>
       </c>
       <c r="B51" s="9">
-        <v>46161.58099116899</v>
+        <v>46161.414324502315</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46161.84476310185</v>
+        <v>46161.678096435186</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>192</v>
@@ -4939,11 +4939,11 @@
         <v>196</v>
       </c>
       <c r="B52" s="5">
-        <v>46161.58099418982</v>
+        <v>46161.41432752315</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46161.84476607639</v>
+        <v>46161.67809940972</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4990,11 +4990,11 @@
         <v>198</v>
       </c>
       <c r="B53" s="9">
-        <v>46161.63966489583</v>
+        <v>46161.47299822917</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46161.844763472225</v>
+        <v>46161.678096805554</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>195</v>
@@ -5041,11 +5041,11 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46161.63967261574</v>
+        <v>46161.473005949076</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46161.84476069444</v>
+        <v>46161.67809402778</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -5092,11 +5092,11 @@
         <v>201</v>
       </c>
       <c r="B55" s="9">
-        <v>46161.63968388889</v>
+        <v>46161.47301722222</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46161.84475773148</v>
+        <v>46161.678091064816</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>195</v>
@@ -5143,11 +5143,11 @@
         <v>202</v>
       </c>
       <c r="B56" s="5">
-        <v>46161.63969275463</v>
+        <v>46161.47302608796</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46161.84475471065</v>
+        <v>46161.67808804398</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -5194,11 +5194,11 @@
         <v>203</v>
       </c>
       <c r="B57" s="9">
-        <v>46161.639705208334</v>
+        <v>46161.47303854166</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46161.84475174769</v>
+        <v>46161.67808508102</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>195</v>
@@ -5245,11 +5245,11 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46161.639715474535</v>
+        <v>46161.47304880787</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46161.84474863426</v>
+        <v>46161.67808196759</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>195</v>
@@ -5296,11 +5296,11 @@
         <v>205</v>
       </c>
       <c r="B59" s="9">
-        <v>46161.63972679398</v>
+        <v>46161.47306012732</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46161.84474503472</v>
+        <v>46161.67807836806</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>195</v>
@@ -5347,11 +5347,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46161.63974304398</v>
+        <v>46161.47307637731</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46161.84473834491</v>
+        <v>46161.67807167824</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>195</v>
@@ -5398,11 +5398,11 @@
         <v>207</v>
       </c>
       <c r="B61" s="9">
-        <v>46161.63975269676</v>
+        <v>46161.47308603009</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.84473753472</v>
+        <v>46161.67807086806</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>195</v>
@@ -5449,11 +5449,11 @@
         <v>208</v>
       </c>
       <c r="B62" s="5">
-        <v>46161.58099818287</v>
+        <v>46161.41433151621</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46161.79647144676</v>
+        <v>46161.629804780096</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5496,11 +5496,11 @@
         <v>211</v>
       </c>
       <c r="B63" s="9">
-        <v>46161.58100145833</v>
+        <v>46161.41433479167</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.844842499995</v>
+        <v>46161.67817583334</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>212</v>
@@ -5559,11 +5559,11 @@
         <v>216</v>
       </c>
       <c r="B64" s="5">
-        <v>46161.58100614583</v>
+        <v>46161.41433947917</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46161.84491849537</v>
+        <v>46161.67825182871</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>
@@ -5622,11 +5622,11 @@
         <v>220</v>
       </c>
       <c r="B65" s="9">
-        <v>46161.58101638889</v>
+        <v>46161.414349722225</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46161.84483983796</v>
+        <v>46161.6781731713</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>221</v>
@@ -5685,11 +5685,11 @@
         <v>223</v>
       </c>
       <c r="B66" s="5">
-        <v>46161.58102099537</v>
+        <v>46161.41435432871</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46161.84491503472</v>
+        <v>46161.67824836806</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>224</v>
@@ -5748,11 +5748,11 @@
         <v>226</v>
       </c>
       <c r="B67" s="9">
-        <v>46161.581024722225</v>
+        <v>46161.414358055554</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46161.8448359375</v>
+        <v>46161.67816927083</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>227</v>
@@ -5811,11 +5811,11 @@
         <v>229</v>
       </c>
       <c r="B68" s="5">
-        <v>46161.58102864583</v>
+        <v>46161.41436197917</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46161.844914270834</v>
+        <v>46161.67824760417</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5874,11 +5874,11 @@
         <v>231</v>
       </c>
       <c r="B69" s="9">
-        <v>46161.58103207176</v>
+        <v>46161.41436540509</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46161.797785821764</v>
+        <v>46161.63111915509</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>232</v>
@@ -5921,11 +5921,11 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46161.58103457176</v>
+        <v>46161.41436790509</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46161.845178449075</v>
+        <v>46161.678511782404</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>235</v>
@@ -5984,11 +5984,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46161.58103962963</v>
+        <v>46161.41437296296</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46161.845147071755</v>
+        <v>46161.67848040509</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>195</v>
@@ -6037,11 +6037,11 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46161.582011805556</v>
+        <v>46161.415345138885</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46161.84514348379</v>
+        <v>46161.678476817135</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>195</v>
@@ -6090,11 +6090,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46161.58202383102</v>
+        <v>46161.415357164355</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46161.845140324076</v>
+        <v>46161.678473657405</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>195</v>
@@ -6143,11 +6143,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46161.582662650464</v>
+        <v>46161.4159959838</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46161.845136655094</v>
+        <v>46161.67846998843</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>195</v>
@@ -6196,11 +6196,11 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46161.58267322917</v>
+        <v>46161.416006562504</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46161.845133518524</v>
+        <v>46161.67846685185</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>195</v>
@@ -6249,11 +6249,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46161.58270134259</v>
+        <v>46161.41603467593</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46161.84513074074</v>
+        <v>46161.67846407407</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>195</v>
@@ -6302,11 +6302,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46161.58271427083</v>
+        <v>46161.416047604165</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46161.84512803241</v>
+        <v>46161.67846136574</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>195</v>
@@ -6355,11 +6355,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46161.58272651621</v>
+        <v>46161.41605984954</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46161.84512407407</v>
+        <v>46161.67845740741</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>195</v>
@@ -6408,11 +6408,11 @@
         <v>252</v>
       </c>
       <c r="B79" s="9">
-        <v>46161.58277962963</v>
+        <v>46161.416112962965</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46161.845117916666</v>
+        <v>46161.67845125</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>195</v>
@@ -6461,11 +6461,11 @@
         <v>254</v>
       </c>
       <c r="B80" s="5">
-        <v>46161.58279046296</v>
+        <v>46161.4161237963</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46161.84511721064</v>
+        <v>46161.67845054399</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>195</v>
@@ -6514,11 +6514,11 @@
         <v>255</v>
       </c>
       <c r="B81" s="9">
-        <v>46161.58104538194</v>
+        <v>46161.41437871528</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46161.845344814814</v>
+        <v>46161.67867814815</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>256</v>
@@ -6577,11 +6577,11 @@
         <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46161.58104903935</v>
+        <v>46161.414382372684</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46161.84533920139</v>
+        <v>46161.67867253472</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>195</v>
@@ -6630,11 +6630,11 @@
         <v>260</v>
       </c>
       <c r="B83" s="9">
-        <v>46161.582834120374</v>
+        <v>46161.4161674537</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46161.84533628472</v>
+        <v>46161.67866961806</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>195</v>
@@ -6683,11 +6683,11 @@
         <v>261</v>
       </c>
       <c r="B84" s="5">
-        <v>46161.58286459491</v>
+        <v>46161.416197928236</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46161.84533336805</v>
+        <v>46161.67866670139</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>195</v>
@@ -6736,11 +6736,11 @@
         <v>262</v>
       </c>
       <c r="B85" s="9">
-        <v>46161.58287381944</v>
+        <v>46161.41620715278</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46161.84533065972</v>
+        <v>46161.67866399305</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>195</v>
@@ -6789,11 +6789,11 @@
         <v>263</v>
       </c>
       <c r="B86" s="5">
-        <v>46161.58288365741</v>
+        <v>46161.416216990736</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46161.84532790509</v>
+        <v>46161.67866123843</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>195</v>
@@ -6842,11 +6842,11 @@
         <v>264</v>
       </c>
       <c r="B87" s="9">
-        <v>46161.58289255787</v>
+        <v>46161.416225891204</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46161.84532486111</v>
+        <v>46161.67865819445</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>195</v>
@@ -6895,11 +6895,11 @@
         <v>265</v>
       </c>
       <c r="B88" s="5">
-        <v>46161.58292542824</v>
+        <v>46161.41625876157</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46161.84532211805</v>
+        <v>46161.67865545139</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>195</v>
@@ -6948,11 +6948,11 @@
         <v>266</v>
       </c>
       <c r="B89" s="9">
-        <v>46161.58293696759</v>
+        <v>46161.41627030092</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46161.84531927083</v>
+        <v>46161.67865260417</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>195</v>
@@ -7001,11 +7001,11 @@
         <v>267</v>
       </c>
       <c r="B90" s="5">
-        <v>46161.58295282407</v>
+        <v>46161.41628615741</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46161.84531311343</v>
+        <v>46161.67864644676</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>195</v>
@@ -7054,11 +7054,11 @@
         <v>268</v>
       </c>
       <c r="B91" s="9">
-        <v>46161.58296773148</v>
+        <v>46161.41630106482</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46161.84531243055</v>
+        <v>46161.67864576389</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>195</v>
@@ -7107,11 +7107,11 @@
         <v>269</v>
       </c>
       <c r="B92" s="5">
-        <v>46161.581053761576</v>
+        <v>46161.414387094905</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46161.84552644676</v>
+        <v>46161.67885978009</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>270</v>
@@ -7170,11 +7170,11 @@
         <v>271</v>
       </c>
       <c r="B93" s="9">
-        <v>46161.58105741898</v>
+        <v>46161.41439075231</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46161.845511736115</v>
+        <v>46161.678845069444</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>195</v>
@@ -7223,11 +7223,11 @@
         <v>273</v>
       </c>
       <c r="B94" s="5">
-        <v>46161.583039942125</v>
+        <v>46161.41637327547</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46161.84550880787</v>
+        <v>46161.678842141206</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>195</v>
@@ -7276,11 +7276,11 @@
         <v>274</v>
       </c>
       <c r="B95" s="9">
-        <v>46161.58305715278</v>
+        <v>46161.41639048611</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46161.845505324076</v>
+        <v>46161.678838657404</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>195</v>
@@ -7329,11 +7329,11 @@
         <v>275</v>
       </c>
       <c r="B96" s="5">
-        <v>46161.583076689814</v>
+        <v>46161.41641002314</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46161.84550258102</v>
+        <v>46161.678835914354</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>195</v>
@@ -7382,11 +7382,11 @@
         <v>276</v>
       </c>
       <c r="B97" s="9">
-        <v>46161.58308886574</v>
+        <v>46161.41642219907</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46161.84549928241</v>
+        <v>46161.67883261574</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>195</v>
@@ -7435,11 +7435,11 @@
         <v>277</v>
       </c>
       <c r="B98" s="5">
-        <v>46161.58310019676</v>
+        <v>46161.41643353009</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46161.84549533565</v>
+        <v>46161.678828668984</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>195</v>
@@ -7488,11 +7488,11 @@
         <v>278</v>
       </c>
       <c r="B99" s="9">
-        <v>46161.5831108912</v>
+        <v>46161.41644422454</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46161.84549206018</v>
+        <v>46161.67882539352</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>195</v>
@@ -7541,11 +7541,11 @@
         <v>279</v>
       </c>
       <c r="B100" s="5">
-        <v>46161.58312844907</v>
+        <v>46161.416461782406</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46161.84548887731</v>
+        <v>46161.67882221065</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>195</v>
@@ -7594,11 +7594,11 @@
         <v>280</v>
       </c>
       <c r="B101" s="9">
-        <v>46161.58300775463</v>
+        <v>46161.41634108796</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46161.84548230324</v>
+        <v>46161.67881563657</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>195</v>
@@ -7647,11 +7647,11 @@
         <v>281</v>
       </c>
       <c r="B102" s="5">
-        <v>46161.639501875004</v>
+        <v>46161.47283520833</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46161.845481620374</v>
+        <v>46161.6788149537</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>195</v>
@@ -7700,11 +7700,11 @@
         <v>282</v>
       </c>
       <c r="B103" s="9">
-        <v>46161.58110506945</v>
+        <v>46161.414438402775</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46161.80776861111</v>
+        <v>46161.64110194445</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>209</v>
@@ -7747,11 +7747,11 @@
         <v>284</v>
       </c>
       <c r="B104" s="5">
-        <v>46161.581108530096</v>
+        <v>46161.414441863424</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46176.18811300926</v>
+        <v>46176.021446342595</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>285</v>
@@ -7810,11 +7810,11 @@
         <v>287</v>
       </c>
       <c r="B105" s="9">
-        <v>46161.58111370371</v>
+        <v>46161.41444703704</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46161.84560915509</v>
+        <v>46161.67894248843</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>288</v>
@@ -7873,11 +7873,11 @@
         <v>290</v>
       </c>
       <c r="B106" s="5">
-        <v>46161.581118449074</v>
+        <v>46161.4144517824</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46161.84560644676</v>
+        <v>46161.67893978009</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>291</v>
@@ -7936,11 +7936,11 @@
         <v>293</v>
       </c>
       <c r="B107" s="9">
-        <v>46161.58112311343</v>
+        <v>46161.41445644676</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46161.84560210648</v>
+        <v>46161.67893543981</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>294</v>
@@ -7999,11 +7999,11 @@
         <v>296</v>
       </c>
       <c r="B108" s="5">
-        <v>46161.58112702546</v>
+        <v>46161.41446035879</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46161.83387362269</v>
+        <v>46161.667206956015</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>297</v>
@@ -8046,11 +8046,11 @@
         <v>299</v>
       </c>
       <c r="B109" s="9">
-        <v>46161.58112984954</v>
+        <v>46161.41446318287</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46161.84578230324</v>
+        <v>46161.67911563657</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>300</v>
@@ -8109,11 +8109,11 @@
         <v>302</v>
       </c>
       <c r="B110" s="5">
-        <v>46161.581135555556</v>
+        <v>46161.41446888889</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46161.84577694444</v>
+        <v>46161.67911027778</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>303</v>
@@ -8162,11 +8162,11 @@
         <v>304</v>
       </c>
       <c r="B111" s="9">
-        <v>46161.58317730324</v>
+        <v>46161.41651063657</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46161.84577366898</v>
+        <v>46161.67910700232</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>195</v>
@@ -8215,11 +8215,11 @@
         <v>305</v>
       </c>
       <c r="B112" s="5">
-        <v>46161.58318758102</v>
+        <v>46161.416520914354</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46161.845770879634</v>
+        <v>46161.67910421296</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>195</v>
@@ -8268,11 +8268,11 @@
         <v>306</v>
       </c>
       <c r="B113" s="9">
-        <v>46161.5831975926</v>
+        <v>46161.416530925926</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46161.84576709491</v>
+        <v>46161.67910042824</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>195</v>
@@ -8321,11 +8321,11 @@
         <v>307</v>
       </c>
       <c r="B114" s="5">
-        <v>46161.58320657407</v>
+        <v>46161.41653990741</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46161.84576415509</v>
+        <v>46161.67909748842</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>195</v>
@@ -8374,11 +8374,11 @@
         <v>308</v>
       </c>
       <c r="B115" s="9">
-        <v>46161.58322151621</v>
+        <v>46161.41655484954</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46161.84576082176</v>
+        <v>46161.67909415509</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>195</v>
@@ -8427,11 +8427,11 @@
         <v>309</v>
       </c>
       <c r="B116" s="5">
-        <v>46161.58322717593</v>
+        <v>46161.41656050926</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46161.84575040509</v>
+        <v>46161.679083738425</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>195</v>
@@ -8480,11 +8480,11 @@
         <v>310</v>
       </c>
       <c r="B117" s="9">
-        <v>46161.58324248843</v>
+        <v>46161.41657582176</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46161.84574967592</v>
+        <v>46161.67908300926</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>195</v>
@@ -8533,11 +8533,11 @@
         <v>311</v>
       </c>
       <c r="B118" s="5">
-        <v>46161.58325402778</v>
+        <v>46161.41658736111</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46161.845748946755</v>
+        <v>46161.6790822801</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>195</v>
@@ -8586,11 +8586,11 @@
         <v>312</v>
       </c>
       <c r="B119" s="9">
-        <v>46161.58326291667</v>
+        <v>46161.41659625</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46161.84574821759</v>
+        <v>46161.67908155093</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>195</v>
@@ -8639,11 +8639,11 @@
         <v>313</v>
       </c>
       <c r="B120" s="5">
-        <v>46161.58113928241</v>
+        <v>46161.41447261574</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46161.845971400464</v>
+        <v>46161.6793047338</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>314</v>
@@ -8702,11 +8702,11 @@
         <v>315</v>
       </c>
       <c r="B121" s="9">
-        <v>46161.58114282407</v>
+        <v>46161.414476157406</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46161.845958969905</v>
+        <v>46161.67929230324</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>195</v>
@@ -8755,11 +8755,11 @@
         <v>318</v>
       </c>
       <c r="B122" s="5">
-        <v>46161.585882430554</v>
+        <v>46161.41921576389</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46161.845956122685</v>
+        <v>46161.67928945602</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>195</v>
@@ -8808,11 +8808,11 @@
         <v>320</v>
       </c>
       <c r="B123" s="9">
-        <v>46161.58590298611</v>
+        <v>46161.419236319445</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46161.84595341435</v>
+        <v>46161.67928674769</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>195</v>
@@ -8861,11 +8861,11 @@
         <v>322</v>
       </c>
       <c r="B124" s="5">
-        <v>46161.585919861114</v>
+        <v>46161.41925319444</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46161.84595043982</v>
+        <v>46161.67928377315</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>195</v>
@@ -8914,11 +8914,11 @@
         <v>323</v>
       </c>
       <c r="B125" s="9">
-        <v>46161.585927175925</v>
+        <v>46161.419260509254</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46161.84594708333</v>
+        <v>46161.67928041666</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>195</v>
@@ -8967,11 +8967,11 @@
         <v>324</v>
       </c>
       <c r="B126" s="5">
-        <v>46161.58593310185</v>
+        <v>46161.41926643519</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46161.845944189816</v>
+        <v>46161.679277523144</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>195</v>
@@ -9020,11 +9020,11 @@
         <v>326</v>
       </c>
       <c r="B127" s="9">
-        <v>46161.58593739584</v>
+        <v>46161.419270729166</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46161.8459415625</v>
+        <v>46161.67927489583</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>195</v>
@@ -9073,11 +9073,11 @@
         <v>327</v>
       </c>
       <c r="B128" s="5">
-        <v>46161.58594590278</v>
+        <v>46161.419279236114</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46161.84593365741</v>
+        <v>46161.679266990745</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>195</v>
@@ -9126,11 +9126,11 @@
         <v>328</v>
       </c>
       <c r="B129" s="9">
-        <v>46161.5859562963</v>
+        <v>46161.41928962963</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46161.84593283565</v>
+        <v>46161.67926616898</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>195</v>
@@ -9179,11 +9179,11 @@
         <v>329</v>
       </c>
       <c r="B130" s="5">
-        <v>46161.58618912037</v>
+        <v>46161.4195224537</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46161.84593203704</v>
+        <v>46161.679265370374</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>195</v>
@@ -9232,11 +9232,11 @@
         <v>331</v>
       </c>
       <c r="B131" s="9">
-        <v>46161.58114761574</v>
+        <v>46161.414480949075</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46161.8461249074</v>
+        <v>46161.679458240746</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>332</v>
@@ -9295,11 +9295,11 @@
         <v>333</v>
       </c>
       <c r="B132" s="5">
-        <v>46161.58115116898</v>
+        <v>46161.41448450231</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46161.8461116088</v>
+        <v>46161.67944494213</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>195</v>
@@ -9348,11 +9348,11 @@
         <v>336</v>
       </c>
       <c r="B133" s="9">
-        <v>46161.58603712963</v>
+        <v>46161.41937046296</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46161.84610825231</v>
+        <v>46161.67944158565</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>195</v>
@@ -9401,11 +9401,11 @@
         <v>337</v>
       </c>
       <c r="B134" s="5">
-        <v>46161.586044930555</v>
+        <v>46161.41937826389</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46161.84610548611</v>
+        <v>46161.67943881944</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>195</v>
@@ -9454,11 +9454,11 @@
         <v>339</v>
       </c>
       <c r="B135" s="9">
-        <v>46161.58605891204</v>
+        <v>46161.41939224537</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46161.84610232639</v>
+        <v>46161.679435659724</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>195</v>
@@ -9507,11 +9507,11 @@
         <v>340</v>
       </c>
       <c r="B136" s="5">
-        <v>46161.58606768519</v>
+        <v>46161.41940101852</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46161.84609929398</v>
+        <v>46161.679432627316</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>195</v>
@@ -9560,11 +9560,11 @@
         <v>342</v>
       </c>
       <c r="B137" s="9">
-        <v>46161.58607575232</v>
+        <v>46161.41940908565</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46161.84609641204</v>
+        <v>46161.679429745374</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>195</v>
@@ -9613,11 +9613,11 @@
         <v>343</v>
       </c>
       <c r="B138" s="5">
-        <v>46161.586088854165</v>
+        <v>46161.4194221875</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46161.84609388889</v>
+        <v>46161.67942722222</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>195</v>
@@ -9666,11 +9666,11 @@
         <v>344</v>
       </c>
       <c r="B139" s="9">
-        <v>46161.58609570602</v>
+        <v>46161.41942903935</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46161.84608592592</v>
+        <v>46161.679419259264</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>195</v>
@@ -9719,11 +9719,11 @@
         <v>346</v>
       </c>
       <c r="B140" s="5">
-        <v>46161.586110578704</v>
+        <v>46161.41944391203</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46161.84608520834</v>
+        <v>46161.679418541666</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>195</v>
@@ -9772,11 +9772,11 @@
         <v>347</v>
       </c>
       <c r="B141" s="9">
-        <v>46161.58612255787</v>
+        <v>46161.4194558912</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46161.84608447917</v>
+        <v>46161.6794178125</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>195</v>
@@ -9825,11 +9825,11 @@
         <v>348</v>
       </c>
       <c r="B142" s="5">
-        <v>46161.58115643519</v>
+        <v>46161.41448976852</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46161.84629616898</v>
+        <v>46161.679629502316</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>349</v>
@@ -9888,11 +9888,11 @@
         <v>350</v>
       </c>
       <c r="B143" s="9">
-        <v>46161.58115993056</v>
+        <v>46161.41449326389</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46161.8462891088</v>
+        <v>46161.67962244213</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>303</v>
@@ -9941,11 +9941,11 @@
         <v>353</v>
       </c>
       <c r="B144" s="5">
-        <v>46161.58622641204</v>
+        <v>46161.419559745365</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46161.84628587963</v>
+        <v>46161.67961921296</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>195</v>
@@ -9994,11 +9994,11 @@
         <v>354</v>
       </c>
       <c r="B145" s="9">
-        <v>46161.586235995375</v>
+        <v>46161.419569328704</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46161.84628291667</v>
+        <v>46161.679616249996</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>195</v>
@@ -10047,11 +10047,11 @@
         <v>355</v>
       </c>
       <c r="B146" s="5">
-        <v>46161.586246770836</v>
+        <v>46161.419580104164</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46161.846280046295</v>
+        <v>46161.67961337963</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>195</v>
@@ -10100,11 +10100,11 @@
         <v>357</v>
       </c>
       <c r="B147" s="9">
-        <v>46161.586256435185</v>
+        <v>46161.41958976851</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46161.84627699074</v>
+        <v>46161.67961032408</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>195</v>
@@ -10153,11 +10153,11 @@
         <v>359</v>
       </c>
       <c r="B148" s="5">
-        <v>46161.586265833335</v>
+        <v>46161.419599166664</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46161.84627394676</v>
+        <v>46161.67960728009</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>195</v>
@@ -10206,11 +10206,11 @@
         <v>360</v>
       </c>
       <c r="B149" s="9">
-        <v>46161.586275671296</v>
+        <v>46161.41960900463</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46161.84627113426</v>
+        <v>46161.679604467594</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>195</v>
@@ -10259,11 +10259,11 @@
         <v>361</v>
       </c>
       <c r="B150" s="5">
-        <v>46161.58629186342</v>
+        <v>46161.41962519676</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46161.846268402776</v>
+        <v>46161.67960173611</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>195</v>
@@ -10312,11 +10312,11 @@
         <v>362</v>
       </c>
       <c r="B151" s="9">
-        <v>46161.58630879629</v>
+        <v>46161.41964212963</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46161.84626222222</v>
+        <v>46161.67959555556</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>195</v>
@@ -10365,11 +10365,11 @@
         <v>363</v>
       </c>
       <c r="B152" s="5">
-        <v>46161.58632163194</v>
+        <v>46161.41965496528</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46161.84626162037</v>
+        <v>46161.679594953705</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>195</v>
@@ -10418,11 +10418,11 @@
         <v>364</v>
       </c>
       <c r="B153" s="9">
-        <v>46161.5811646875</v>
+        <v>46161.41449802084</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46161.84643925926</v>
+        <v>46161.67977259259</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>365</v>
@@ -10481,11 +10481,11 @@
         <v>366</v>
       </c>
       <c r="B154" s="5">
-        <v>46161.58116828704</v>
+        <v>46161.41450162037</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46161.84644222222</v>
+        <v>46161.67977555556</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>195</v>
@@ -10532,11 +10532,11 @@
         <v>368</v>
       </c>
       <c r="B155" s="9">
-        <v>46161.63912622685</v>
+        <v>46161.47245956019</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46161.84643929398</v>
+        <v>46161.679772627314</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>195</v>
@@ -10583,11 +10583,11 @@
         <v>369</v>
       </c>
       <c r="B156" s="5">
-        <v>46161.63913737268</v>
+        <v>46161.47247070602</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46161.84643643518</v>
+        <v>46161.67976976852</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>195</v>
@@ -10634,11 +10634,11 @@
         <v>370</v>
       </c>
       <c r="B157" s="9">
-        <v>46161.63914719908</v>
+        <v>46161.47248053241</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46161.846433321756</v>
+        <v>46161.67976665509</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>195</v>
@@ -10685,11 +10685,11 @@
         <v>371</v>
       </c>
       <c r="B158" s="5">
-        <v>46161.639157557875</v>
+        <v>46161.4724908912</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46161.84643013889</v>
+        <v>46161.67976347222</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>195</v>
@@ -10736,11 +10736,11 @@
         <v>372</v>
       </c>
       <c r="B159" s="9">
-        <v>46161.6391721875</v>
+        <v>46161.47250552083</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46161.84642646991</v>
+        <v>46161.67975980324</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>195</v>
@@ -10787,11 +10787,11 @@
         <v>373</v>
       </c>
       <c r="B160" s="5">
-        <v>46161.639187395835</v>
+        <v>46161.47252072916</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46161.84642321759</v>
+        <v>46161.679756550926</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>195</v>
@@ -10838,11 +10838,11 @@
         <v>374</v>
       </c>
       <c r="B161" s="9">
-        <v>46161.639195289354</v>
+        <v>46161.47252862269</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46161.846420138885</v>
+        <v>46161.67975347222</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>195</v>
@@ -10889,11 +10889,11 @@
         <v>375</v>
       </c>
       <c r="B162" s="5">
-        <v>46161.63920550926</v>
+        <v>46161.472538842594</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46161.846413113424</v>
+        <v>46161.67974644676</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>195</v>
@@ -10940,11 +10940,11 @@
         <v>376</v>
       </c>
       <c r="B163" s="9">
-        <v>46161.63921432871</v>
+        <v>46161.47254766204</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46161.84641241898</v>
+        <v>46161.67974575231</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>195</v>
@@ -10991,11 +10991,11 @@
         <v>377</v>
       </c>
       <c r="B164" s="5">
-        <v>46161.58117752315</v>
+        <v>46161.414510856484</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46161.84660503472</v>
+        <v>46161.679938368055</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>378</v>
@@ -11054,11 +11054,11 @@
         <v>380</v>
       </c>
       <c r="B165" s="9">
-        <v>46161.58118137732</v>
+        <v>46161.41451471065</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46161.84658016203</v>
+        <v>46161.67991349537</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>195</v>
@@ -11107,11 +11107,11 @@
         <v>382</v>
       </c>
       <c r="B166" s="5">
-        <v>46161.639253761576</v>
+        <v>46161.472587094904</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46161.846577187505</v>
+        <v>46161.679910520834</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>195</v>
@@ -11160,11 +11160,11 @@
         <v>383</v>
       </c>
       <c r="B167" s="9">
-        <v>46161.63928710648</v>
+        <v>46161.47262043982</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46161.84657417824</v>
+        <v>46161.67990751157</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>195</v>
@@ -11213,11 +11213,11 @@
         <v>384</v>
       </c>
       <c r="B168" s="5">
-        <v>46161.63929736111</v>
+        <v>46161.47263069444</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46161.84657136574</v>
+        <v>46161.67990469908</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>195</v>
@@ -11266,11 +11266,11 @@
         <v>385</v>
       </c>
       <c r="B169" s="9">
-        <v>46161.6393071412</v>
+        <v>46161.47264047454</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46161.84656841435</v>
+        <v>46161.67990174769</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>195</v>
@@ -11319,11 +11319,11 @@
         <v>386</v>
       </c>
       <c r="B170" s="5">
-        <v>46161.639315625</v>
+        <v>46161.47264895833</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46161.84656539352</v>
+        <v>46161.679898726856</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>195</v>
@@ -11372,11 +11372,11 @@
         <v>387</v>
       </c>
       <c r="B171" s="9">
-        <v>46161.63932686343</v>
+        <v>46161.472660196756</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46161.846562754625</v>
+        <v>46161.67989608797</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>195</v>
@@ -11425,11 +11425,11 @@
         <v>388</v>
       </c>
       <c r="B172" s="5">
-        <v>46161.63933708333</v>
+        <v>46161.47267041667</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46161.8465599537</v>
+        <v>46161.67989328704</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>195</v>
@@ -11478,11 +11478,11 @@
         <v>389</v>
       </c>
       <c r="B173" s="9">
-        <v>46161.63935484954</v>
+        <v>46161.47268818287</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46161.846553807874</v>
+        <v>46161.6798871412</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>195</v>
@@ -11531,11 +11531,11 @@
         <v>390</v>
       </c>
       <c r="B174" s="5">
-        <v>46161.63936453704</v>
+        <v>46161.47269787037</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46161.84655313657</v>
+        <v>46161.67988646991</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>195</v>
@@ -11584,11 +11584,11 @@
         <v>391</v>
       </c>
       <c r="B175" s="9">
-        <v>46161.5811852662</v>
+        <v>46161.41451859954</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46161.84092732639</v>
+        <v>46161.674260659725</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>392</v>
@@ -11631,11 +11631,11 @@
         <v>394</v>
       </c>
       <c r="B176" s="5">
-        <v>46161.581188020835</v>
+        <v>46161.41452135416</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46161.84675815972</v>
+        <v>46161.68009149306</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>395</v>
@@ -11694,11 +11694,11 @@
         <v>398</v>
       </c>
       <c r="B177" s="9">
-        <v>46161.581192673606</v>
+        <v>46161.41452600695</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46161.846749351855</v>
+        <v>46161.68008268518</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>195</v>
@@ -11747,11 +11747,11 @@
         <v>400</v>
       </c>
       <c r="B178" s="5">
-        <v>46161.63982708333</v>
+        <v>46161.473160416666</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46161.84674655093</v>
+        <v>46161.68007988426</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>195</v>
@@ -11800,11 +11800,11 @@
         <v>401</v>
       </c>
       <c r="B179" s="9">
-        <v>46161.63983532407</v>
+        <v>46161.47316865741</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46161.846743981485</v>
+        <v>46161.68007731481</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>195</v>
@@ -11853,11 +11853,11 @@
         <v>402</v>
       </c>
       <c r="B180" s="5">
-        <v>46161.63984421296</v>
+        <v>46161.4731775463</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46161.84674143518</v>
+        <v>46161.68007476852</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>195</v>
@@ -11906,11 +11906,11 @@
         <v>403</v>
       </c>
       <c r="B181" s="9">
-        <v>46161.63985878472</v>
+        <v>46161.47319211806</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46161.846738541666</v>
+        <v>46161.680071875</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>195</v>
@@ -11959,11 +11959,11 @@
         <v>404</v>
       </c>
       <c r="B182" s="5">
-        <v>46161.63986780093</v>
+        <v>46161.47320113426</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46161.84673559028</v>
+        <v>46161.68006892361</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>195</v>
@@ -12012,11 +12012,11 @@
         <v>405</v>
       </c>
       <c r="B183" s="9">
-        <v>46161.639875</v>
+        <v>46161.47320833334</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46161.84673289352</v>
+        <v>46161.68006622685</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>195</v>
@@ -12065,11 +12065,11 @@
         <v>406</v>
       </c>
       <c r="B184" s="5">
-        <v>46161.63988342593</v>
+        <v>46161.47321675926</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46161.84672489583</v>
+        <v>46161.68005822916</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>195</v>
@@ -12118,11 +12118,11 @@
         <v>407</v>
       </c>
       <c r="B185" s="9">
-        <v>46161.63989143519</v>
+        <v>46161.47322476852</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46161.84672420139</v>
+        <v>46161.68005753472</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>195</v>
@@ -12171,11 +12171,11 @@
         <v>408</v>
       </c>
       <c r="B186" s="5">
-        <v>46161.639899340276</v>
+        <v>46161.47323267361</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46161.84672340278</v>
+        <v>46161.680056736106</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>195</v>
@@ -12224,11 +12224,11 @@
         <v>409</v>
       </c>
       <c r="B187" s="9">
-        <v>46161.5811965162</v>
+        <v>46161.41452984954</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46161.84690181713</v>
+        <v>46161.68023515046</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>410</v>
@@ -12287,11 +12287,11 @@
         <v>411</v>
       </c>
       <c r="B188" s="5">
-        <v>46161.58120002315</v>
+        <v>46161.41453335648</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46161.84690336806</v>
+        <v>46161.68023670139</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>195</v>
@@ -12340,11 +12340,11 @@
         <v>413</v>
       </c>
       <c r="B189" s="9">
-        <v>46161.63993424768</v>
+        <v>46161.47326758102</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46161.84690038195</v>
+        <v>46161.68023371528</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>195</v>
@@ -12393,11 +12393,11 @@
         <v>414</v>
       </c>
       <c r="B190" s="5">
-        <v>46161.6399947801</v>
+        <v>46161.473328113425</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46161.84689746528</v>
+        <v>46161.68023079861</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>195</v>
@@ -12446,11 +12446,11 @@
         <v>415</v>
       </c>
       <c r="B191" s="9">
-        <v>46161.640004444445</v>
+        <v>46161.473337777774</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46161.84689446759</v>
+        <v>46161.68022780093</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>195</v>
@@ -12499,11 +12499,11 @@
         <v>416</v>
       </c>
       <c r="B192" s="5">
-        <v>46161.64001501157</v>
+        <v>46161.47334834491</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46161.84689137731</v>
+        <v>46161.68022471065</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>195</v>
@@ -12552,11 +12552,11 @@
         <v>417</v>
       </c>
       <c r="B193" s="9">
-        <v>46161.640023831016</v>
+        <v>46161.47335716435</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46161.846888796295</v>
+        <v>46161.68022212963</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>195</v>
@@ -12605,11 +12605,11 @@
         <v>418</v>
       </c>
       <c r="B194" s="5">
-        <v>46161.640038310186</v>
+        <v>46161.473371643515</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46161.84688606481</v>
+        <v>46161.68021939815</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>195</v>
@@ -12658,11 +12658,11 @@
         <v>419</v>
       </c>
       <c r="B195" s="9">
-        <v>46161.64004747685</v>
+        <v>46161.47338081019</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46161.846882557875</v>
+        <v>46161.6802158912</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>195</v>
@@ -12711,11 +12711,11 @@
         <v>420</v>
       </c>
       <c r="B196" s="5">
-        <v>46161.64005649305</v>
+        <v>46161.47338982639</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46161.84687957176</v>
+        <v>46161.68021290509</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>195</v>
@@ -12764,11 +12764,11 @@
         <v>421</v>
       </c>
       <c r="B197" s="9">
-        <v>46161.64006346065</v>
+        <v>46161.47339679398</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46161.846870243055</v>
+        <v>46161.68020357639</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>195</v>
@@ -12817,11 +12817,11 @@
         <v>422</v>
       </c>
       <c r="B198" s="5">
-        <v>46161.58120399306</v>
+        <v>46161.41453732639</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46161.84710645833</v>
+        <v>46161.68043979167</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>423</v>
@@ -12878,11 +12878,11 @@
         <v>424</v>
       </c>
       <c r="B199" s="9">
-        <v>46161.58120755787</v>
+        <v>46161.4145408912</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46161.847077812505</v>
+        <v>46161.68041114583</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>195</v>
@@ -12929,11 +12929,11 @@
         <v>426</v>
       </c>
       <c r="B200" s="5">
-        <v>46161.6401252662</v>
+        <v>46161.47345859953</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46161.84707505787</v>
+        <v>46161.6804083912</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>195</v>
@@ -12980,11 +12980,11 @@
         <v>427</v>
       </c>
       <c r="B201" s="9">
-        <v>46161.64014137731</v>
+        <v>46161.47347471065</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46161.847072476856</v>
+        <v>46161.680405810184</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>195</v>
@@ -13031,11 +13031,11 @@
         <v>428</v>
       </c>
       <c r="B202" s="5">
-        <v>46161.64015293981</v>
+        <v>46161.47348627315</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46161.84706930556</v>
+        <v>46161.680402638885</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>195</v>
@@ -13082,11 +13082,11 @@
         <v>429</v>
       </c>
       <c r="B203" s="9">
-        <v>46161.64016740741</v>
+        <v>46161.47350074074</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46161.847066608796</v>
+        <v>46161.680399942124</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>195</v>
@@ -13133,11 +13133,11 @@
         <v>430</v>
       </c>
       <c r="B204" s="5">
-        <v>46161.640203877316</v>
+        <v>46161.47353721065</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46161.84706402778</v>
+        <v>46161.68039736111</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>195</v>
@@ -13184,11 +13184,11 @@
         <v>431</v>
       </c>
       <c r="B205" s="9">
-        <v>46161.64021510417</v>
+        <v>46161.4735484375</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46161.84706112268</v>
+        <v>46161.68039445602</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>195</v>
@@ -13235,11 +13235,11 @@
         <v>432</v>
       </c>
       <c r="B206" s="5">
-        <v>46161.64022702546</v>
+        <v>46161.4735603588</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46161.847053425925</v>
+        <v>46161.68038675926</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>195</v>
@@ -13286,11 +13286,11 @@
         <v>433</v>
       </c>
       <c r="B207" s="9">
-        <v>46161.64023784723</v>
+        <v>46161.473571180555</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46161.8470527662</v>
+        <v>46161.68038609954</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>195</v>
@@ -13337,11 +13337,11 @@
         <v>434</v>
       </c>
       <c r="B208" s="5">
-        <v>46161.64025311342</v>
+        <v>46161.47358644676</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46161.84705210648</v>
+        <v>46161.68038543982</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>195</v>
@@ -13388,11 +13388,11 @@
         <v>435</v>
       </c>
       <c r="B209" s="9">
-        <v>46161.58121466435</v>
+        <v>46161.41454799769</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46161.84730193287</v>
+        <v>46161.6806352662</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>436</v>
@@ -13451,11 +13451,11 @@
         <v>438</v>
       </c>
       <c r="B210" s="5">
-        <v>46161.58125732639</v>
+        <v>46161.414590659726</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46161.84728091436</v>
+        <v>46161.680614247685</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>195</v>
@@ -13502,11 +13502,11 @@
         <v>439</v>
       </c>
       <c r="B211" s="9">
-        <v>46161.640307905094</v>
+        <v>46161.47364123842</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46161.84727769676</v>
+        <v>46161.6806110301</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>195</v>
@@ -13553,11 +13553,11 @@
         <v>440</v>
       </c>
       <c r="B212" s="5">
-        <v>46161.64031635417</v>
+        <v>46161.4736496875</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46161.84727525463</v>
+        <v>46161.680608587965</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>195</v>
@@ -13604,11 +13604,11 @@
         <v>441</v>
       </c>
       <c r="B213" s="9">
-        <v>46161.64032832176</v>
+        <v>46161.473661655094</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46161.84727247685</v>
+        <v>46161.68060581019</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>195</v>
@@ -13655,11 +13655,11 @@
         <v>442</v>
       </c>
       <c r="B214" s="5">
-        <v>46161.640337986115</v>
+        <v>46161.47367131944</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46161.84726945602</v>
+        <v>46161.68060278935</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>195</v>
@@ -13706,11 +13706,11 @@
         <v>443</v>
       </c>
       <c r="B215" s="9">
-        <v>46161.64035862268</v>
+        <v>46161.473691956024</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46161.84726638889</v>
+        <v>46161.680599722225</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>195</v>
@@ -13757,11 +13757,11 @@
         <v>444</v>
       </c>
       <c r="B216" s="5">
-        <v>46161.64036773148</v>
+        <v>46161.47370106481</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46161.84726359954</v>
+        <v>46161.68059693287</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>195</v>
@@ -13808,11 +13808,11 @@
         <v>445</v>
       </c>
       <c r="B217" s="9">
-        <v>46161.64037657407</v>
+        <v>46161.47370990741</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46161.84726060185</v>
+        <v>46161.68059393518</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>195</v>
@@ -13859,11 +13859,11 @@
         <v>446</v>
       </c>
       <c r="B218" s="5">
-        <v>46161.64038473379</v>
+        <v>46161.47371806713</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46161.847254699074</v>
+        <v>46161.68058803241</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>195</v>
@@ -13910,11 +13910,11 @@
         <v>447</v>
       </c>
       <c r="B219" s="9">
-        <v>46161.64039350694</v>
+        <v>46161.47372684028</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46161.8472540625</v>
+        <v>46161.68058739584</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>195</v>
@@ -13961,11 +13961,11 @@
         <v>448</v>
       </c>
       <c r="B220" s="5">
-        <v>46161.581262824075</v>
+        <v>46161.41459615741</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46161.84801045139</v>
+        <v>46161.68134378472</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>449</v>
@@ -14008,11 +14008,11 @@
         <v>451</v>
       </c>
       <c r="B221" s="9">
-        <v>46161.58126615741</v>
+        <v>46161.414599490745</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46161.84764756945</v>
+        <v>46161.680980902776</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>452</v>
@@ -14071,11 +14071,11 @@
         <v>455</v>
       </c>
       <c r="B222" s="5">
-        <v>46161.581270821756</v>
+        <v>46161.41460415509</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46161.848222546294</v>
+        <v>46161.68155587963</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>456</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2087,13 +2087,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46161.41396914352</v>
+        <v>46161.58063581018</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.71184347222</v>
+        <v>46175.87851013889</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.71185716435</v>
+        <v>46175.87852383102</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2140,13 +2140,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46161.41407934028</v>
+        <v>46161.58074600695</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.71181634259</v>
+        <v>46175.87848300926</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.71184372685</v>
+        <v>46175.87851039352</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2203,13 +2203,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46161.414082407406</v>
+        <v>46161.58074907407</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.711817187504</v>
+        <v>46175.87848385416</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.71184388889</v>
+        <v>46175.87851055556</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2266,13 +2266,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46161.41408527778</v>
+        <v>46161.58075194445</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.71181774305</v>
+        <v>46175.878484409724</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.71184383101</v>
+        <v>46175.878510497685</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2329,13 +2329,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46161.414087997684</v>
+        <v>46161.58075466435</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.71181836806</v>
+        <v>46175.87848503472</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.71184425926</v>
+        <v>46175.878510925926</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2392,13 +2392,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46161.41409119213</v>
+        <v>46161.5807578588</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.711819097225</v>
+        <v>46175.87848576389</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.71184429398</v>
+        <v>46175.87851096065</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2455,11 +2455,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46161.413972951384</v>
+        <v>46161.580639618056</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46197.51062247685</v>
+        <v>46197.67728914352</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2502,13 +2502,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46161.41409464121</v>
+        <v>46161.580761307865</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.507599756944</v>
+        <v>46197.67426642361</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.50761637732</v>
+        <v>46197.674283043976</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2567,13 +2567,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46161.4140996412</v>
+        <v>46161.580766307874</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.50841496528</v>
+        <v>46197.67508163194</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.508428807865</v>
+        <v>46197.67509547454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2632,13 +2632,13 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46161.41410475694</v>
+        <v>46161.580771423614</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.51061320602</v>
+        <v>46197.67727987269</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.51062958333</v>
+        <v>46197.677296249996</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2697,11 +2697,11 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46161.414109537036</v>
+        <v>46161.5807762037</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.510631701385</v>
+        <v>46197.67729836806</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2760,11 +2760,11 @@
         <v>70</v>
       </c>
       <c r="B15" s="9">
-        <v>46161.413977372686</v>
+        <v>46161.58064403935</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46197.421934328704</v>
+        <v>46197.58860099537</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>71</v>
@@ -2807,11 +2807,11 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46161.414116875</v>
+        <v>46161.58078354166</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.50761693287</v>
+        <v>46197.67428359954</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2870,11 +2870,11 @@
         <v>76</v>
       </c>
       <c r="B17" s="9">
-        <v>46161.414122013884</v>
+        <v>46161.580788680556</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46197.508435289354</v>
+        <v>46197.67510195602</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>77</v>
@@ -2933,13 +2933,13 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46161.41412696759</v>
+        <v>46161.58079363426</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.42192472222</v>
+        <v>46197.58859138889</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.50843519676</v>
+        <v>46197.675101863424</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2998,11 +2998,11 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46161.41413237268</v>
+        <v>46161.58079903935</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46169.712906643515</v>
+        <v>46169.87957331019</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -3061,11 +3061,11 @@
         <v>90</v>
       </c>
       <c r="B20" s="5">
-        <v>46161.414137071755</v>
+        <v>46161.58080373843</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46169.71291747685</v>
+        <v>46169.87958414352</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>91</v>
@@ -3124,11 +3124,11 @@
         <v>93</v>
       </c>
       <c r="B21" s="9">
-        <v>46161.414140740744</v>
+        <v>46161.58080740741</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46169.71293371527</v>
+        <v>46169.879600381944</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>94</v>
@@ -3187,11 +3187,11 @@
         <v>96</v>
       </c>
       <c r="B22" s="5">
-        <v>46161.41414407408</v>
+        <v>46161.580810740736</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46169.7129465162</v>
+        <v>46169.87961318287</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>97</v>
@@ -3250,11 +3250,11 @@
         <v>99</v>
       </c>
       <c r="B23" s="9">
-        <v>46161.4139812963</v>
+        <v>46161.58064796297</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46161.571204548614</v>
+        <v>46161.73787121528</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -3297,11 +3297,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46161.414148055555</v>
+        <v>46161.58081472223</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.71271201389</v>
+        <v>46169.879378680555</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3360,11 +3360,11 @@
         <v>107</v>
       </c>
       <c r="B25" s="9">
-        <v>46161.414152349535</v>
+        <v>46161.580819016206</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.71297789352</v>
+        <v>46169.879644560184</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>108</v>
@@ -3419,11 +3419,11 @@
         <v>110</v>
       </c>
       <c r="B26" s="5">
-        <v>46161.41415684028</v>
+        <v>46161.58082350694</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.7130025463</v>
+        <v>46169.87966921296</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>111</v>
@@ -3478,11 +3478,11 @@
         <v>113</v>
       </c>
       <c r="B27" s="9">
-        <v>46161.414161574074</v>
+        <v>46161.58082824074</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46192.69200952546</v>
+        <v>46192.85867619213</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>114</v>
@@ -3541,11 +3541,11 @@
         <v>116</v>
       </c>
       <c r="B28" s="5">
-        <v>46161.41416587963</v>
+        <v>46161.5808325463</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46197.42193370371</v>
+        <v>46197.58860037037</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>117</v>
@@ -3600,11 +3600,11 @@
         <v>119</v>
       </c>
       <c r="B29" s="9">
-        <v>46161.41417030092</v>
+        <v>46161.580836967594</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46171.00685518519</v>
+        <v>46171.17352185185</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>120</v>
@@ -3659,11 +3659,11 @@
         <v>122</v>
       </c>
       <c r="B30" s="5">
-        <v>46161.41417498843</v>
+        <v>46161.58084165509</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46192.693660115736</v>
+        <v>46192.86032678241</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>123</v>
@@ -3722,11 +3722,11 @@
         <v>125</v>
       </c>
       <c r="B31" s="9">
-        <v>46161.414179363426</v>
+        <v>46161.58084603009</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46175.00358978009</v>
+        <v>46175.170256446756</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>126</v>
@@ -3781,11 +3781,11 @@
         <v>128</v>
       </c>
       <c r="B32" s="5">
-        <v>46161.414183773144</v>
+        <v>46161.580850439816</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.71309979167</v>
+        <v>46169.87976645833</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>129</v>
@@ -3840,11 +3840,11 @@
         <v>131</v>
       </c>
       <c r="B33" s="9">
-        <v>46161.41418836806</v>
+        <v>46161.58085503472</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.71311195602</v>
+        <v>46169.879778622686</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>132</v>
@@ -3899,11 +3899,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46161.41419274306</v>
+        <v>46161.58085940972</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.71276568287</v>
+        <v>46169.87943234954</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3962,11 +3962,11 @@
         <v>139</v>
       </c>
       <c r="B35" s="9">
-        <v>46161.41419697917</v>
+        <v>46161.58086364584</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.7131435301</v>
+        <v>46169.879810196755</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>140</v>
@@ -4021,11 +4021,11 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46161.41420165509</v>
+        <v>46161.58086832176</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.7131621875</v>
+        <v>46169.879828854166</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -4080,11 +4080,11 @@
         <v>145</v>
       </c>
       <c r="B37" s="9">
-        <v>46161.4142065625</v>
+        <v>46161.58087322916</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.71277699074</v>
+        <v>46169.87944365741</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>146</v>
@@ -4143,11 +4143,11 @@
         <v>148</v>
       </c>
       <c r="B38" s="5">
-        <v>46161.41426435186</v>
+        <v>46161.580931018514</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.713187395835</v>
+        <v>46169.8798540625</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>92</v>
@@ -4196,11 +4196,11 @@
         <v>150</v>
       </c>
       <c r="B39" s="9">
-        <v>46161.41426980324</v>
+        <v>46161.58093646991</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.713198495374</v>
+        <v>46169.87986516204</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>151</v>
@@ -4249,11 +4249,11 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46161.41427443287</v>
+        <v>46161.580941099535</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.71278662037</v>
+        <v>46169.87945328704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>154</v>
@@ -4312,11 +4312,11 @@
         <v>158</v>
       </c>
       <c r="B41" s="9">
-        <v>46161.41427865741</v>
+        <v>46161.58094532407</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.713237442134</v>
+        <v>46169.87990410879</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>98</v>
@@ -4365,11 +4365,11 @@
         <v>160</v>
       </c>
       <c r="B42" s="5">
-        <v>46161.41428331019</v>
+        <v>46161.58094997685</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.713248541666</v>
+        <v>46169.87991520834</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>161</v>
@@ -4418,11 +4418,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46161.4142878125</v>
+        <v>46161.58095447917</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.71326314815</v>
+        <v>46169.879929814815</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4471,11 +4471,11 @@
         <v>167</v>
       </c>
       <c r="B44" s="5">
-        <v>46161.41429076389</v>
+        <v>46161.58095743056</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.712851585646</v>
+        <v>46169.87951825232</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>168</v>
@@ -4534,11 +4534,11 @@
         <v>170</v>
       </c>
       <c r="B45" s="9">
-        <v>46161.41429424769</v>
+        <v>46161.58096091435</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.71330668981</v>
+        <v>46169.87997335648</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>95</v>
@@ -4587,11 +4587,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46161.41429832176</v>
+        <v>46161.580964988425</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.713330983795</v>
+        <v>46169.87999765047</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4640,11 +4640,11 @@
         <v>175</v>
       </c>
       <c r="B47" s="9">
-        <v>46161.41398572917</v>
+        <v>46161.58065239583</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46161.56942581019</v>
+        <v>46197.705037754626</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>176</v>
@@ -4687,11 +4687,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46161.41430311343</v>
-      </c>
-      <c r="C48" s="6"/>
+        <v>46161.580969780094</v>
+      </c>
+      <c r="C48" s="5">
+        <v>46197.70503125</v>
+      </c>
       <c r="D48" s="5">
-        <v>46197.51063208333</v>
+        <v>46197.70504644676</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4739,10 +4741,10 @@
         <v>60</v>
       </c>
       <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="12" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="U48" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4750,11 +4752,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46161.414308402775</v>
+        <v>46161.580975069446</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46196.573554456016</v>
+        <v>46197.70503726852</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>184</v>
@@ -4813,11 +4815,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46161.414314340276</v>
+        <v>46161.58098100695</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46161.67788876157</v>
+        <v>46161.84455542824</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>87</v>
@@ -4876,11 +4878,11 @@
         <v>191</v>
       </c>
       <c r="B51" s="9">
-        <v>46161.414324502315</v>
+        <v>46161.58099116899</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46161.678096435186</v>
+        <v>46161.84476310185</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>192</v>
@@ -4939,11 +4941,11 @@
         <v>196</v>
       </c>
       <c r="B52" s="5">
-        <v>46161.41432752315</v>
+        <v>46161.58099418982</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46161.67809940972</v>
+        <v>46161.84476607639</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4990,11 +4992,11 @@
         <v>198</v>
       </c>
       <c r="B53" s="9">
-        <v>46161.47299822917</v>
+        <v>46161.63966489583</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46161.678096805554</v>
+        <v>46161.844763472225</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>195</v>
@@ -5041,11 +5043,11 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46161.473005949076</v>
+        <v>46161.63967261574</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46161.67809402778</v>
+        <v>46161.84476069444</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -5092,11 +5094,11 @@
         <v>201</v>
       </c>
       <c r="B55" s="9">
-        <v>46161.47301722222</v>
+        <v>46161.63968388889</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46161.678091064816</v>
+        <v>46161.84475773148</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>195</v>
@@ -5143,11 +5145,11 @@
         <v>202</v>
       </c>
       <c r="B56" s="5">
-        <v>46161.47302608796</v>
+        <v>46161.63969275463</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46161.67808804398</v>
+        <v>46161.84475471065</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -5194,11 +5196,11 @@
         <v>203</v>
       </c>
       <c r="B57" s="9">
-        <v>46161.47303854166</v>
+        <v>46161.639705208334</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46161.67808508102</v>
+        <v>46161.84475174769</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>195</v>
@@ -5245,11 +5247,11 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46161.47304880787</v>
+        <v>46161.639715474535</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46161.67808196759</v>
+        <v>46161.84474863426</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>195</v>
@@ -5296,11 +5298,11 @@
         <v>205</v>
       </c>
       <c r="B59" s="9">
-        <v>46161.47306012732</v>
+        <v>46161.63972679398</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46161.67807836806</v>
+        <v>46161.84474503472</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>195</v>
@@ -5347,11 +5349,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46161.47307637731</v>
+        <v>46161.63974304398</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46161.67807167824</v>
+        <v>46161.84473834491</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>195</v>
@@ -5398,11 +5400,11 @@
         <v>207</v>
       </c>
       <c r="B61" s="9">
-        <v>46161.47308603009</v>
+        <v>46161.63975269676</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.67807086806</v>
+        <v>46161.84473753472</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>195</v>
@@ -5449,11 +5451,11 @@
         <v>208</v>
       </c>
       <c r="B62" s="5">
-        <v>46161.41433151621</v>
+        <v>46161.58099818287</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46161.629804780096</v>
+        <v>46161.79647144676</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5496,11 +5498,11 @@
         <v>211</v>
       </c>
       <c r="B63" s="9">
-        <v>46161.41433479167</v>
+        <v>46161.58100145833</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.67817583334</v>
+        <v>46161.844842499995</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>212</v>
@@ -5559,11 +5561,11 @@
         <v>216</v>
       </c>
       <c r="B64" s="5">
-        <v>46161.41433947917</v>
+        <v>46161.58100614583</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46161.67825182871</v>
+        <v>46161.84491849537</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>
@@ -5622,11 +5624,11 @@
         <v>220</v>
       </c>
       <c r="B65" s="9">
-        <v>46161.414349722225</v>
+        <v>46161.58101638889</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46161.6781731713</v>
+        <v>46161.84483983796</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>221</v>
@@ -5685,11 +5687,11 @@
         <v>223</v>
       </c>
       <c r="B66" s="5">
-        <v>46161.41435432871</v>
+        <v>46161.58102099537</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46161.67824836806</v>
+        <v>46161.84491503472</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>224</v>
@@ -5748,11 +5750,11 @@
         <v>226</v>
       </c>
       <c r="B67" s="9">
-        <v>46161.414358055554</v>
+        <v>46161.581024722225</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46161.67816927083</v>
+        <v>46161.8448359375</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>227</v>
@@ -5811,11 +5813,11 @@
         <v>229</v>
       </c>
       <c r="B68" s="5">
-        <v>46161.41436197917</v>
+        <v>46161.58102864583</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46161.67824760417</v>
+        <v>46161.844914270834</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5874,11 +5876,11 @@
         <v>231</v>
       </c>
       <c r="B69" s="9">
-        <v>46161.41436540509</v>
+        <v>46161.58103207176</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46161.63111915509</v>
+        <v>46161.797785821764</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>232</v>
@@ -5921,11 +5923,11 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46161.41436790509</v>
+        <v>46161.58103457176</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46161.678511782404</v>
+        <v>46161.845178449075</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>235</v>
@@ -5984,11 +5986,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46161.41437296296</v>
+        <v>46161.58103962963</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46161.67848040509</v>
+        <v>46161.845147071755</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>195</v>
@@ -6037,11 +6039,11 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46161.415345138885</v>
+        <v>46161.582011805556</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46161.678476817135</v>
+        <v>46161.84514348379</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>195</v>
@@ -6090,11 +6092,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46161.415357164355</v>
+        <v>46161.58202383102</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46161.678473657405</v>
+        <v>46161.845140324076</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>195</v>
@@ -6143,11 +6145,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46161.4159959838</v>
+        <v>46161.582662650464</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46161.67846998843</v>
+        <v>46161.845136655094</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>195</v>
@@ -6196,11 +6198,11 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46161.416006562504</v>
+        <v>46161.58267322917</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46161.67846685185</v>
+        <v>46161.845133518524</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>195</v>
@@ -6249,11 +6251,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46161.41603467593</v>
+        <v>46161.58270134259</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46161.67846407407</v>
+        <v>46161.84513074074</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>195</v>
@@ -6302,11 +6304,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46161.416047604165</v>
+        <v>46161.58271427083</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46161.67846136574</v>
+        <v>46161.84512803241</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>195</v>
@@ -6355,11 +6357,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46161.41605984954</v>
+        <v>46161.58272651621</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46161.67845740741</v>
+        <v>46161.84512407407</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>195</v>
@@ -6408,11 +6410,11 @@
         <v>252</v>
       </c>
       <c r="B79" s="9">
-        <v>46161.416112962965</v>
+        <v>46161.58277962963</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46161.67845125</v>
+        <v>46161.845117916666</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>195</v>
@@ -6461,11 +6463,11 @@
         <v>254</v>
       </c>
       <c r="B80" s="5">
-        <v>46161.4161237963</v>
+        <v>46161.58279046296</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46161.67845054399</v>
+        <v>46161.84511721064</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>195</v>
@@ -6514,11 +6516,11 @@
         <v>255</v>
       </c>
       <c r="B81" s="9">
-        <v>46161.41437871528</v>
+        <v>46161.58104538194</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46161.67867814815</v>
+        <v>46161.845344814814</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>256</v>
@@ -6577,11 +6579,11 @@
         <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46161.414382372684</v>
+        <v>46161.58104903935</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46161.67867253472</v>
+        <v>46161.84533920139</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>195</v>
@@ -6630,11 +6632,11 @@
         <v>260</v>
       </c>
       <c r="B83" s="9">
-        <v>46161.4161674537</v>
+        <v>46161.582834120374</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46161.67866961806</v>
+        <v>46161.84533628472</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>195</v>
@@ -6683,11 +6685,11 @@
         <v>261</v>
       </c>
       <c r="B84" s="5">
-        <v>46161.416197928236</v>
+        <v>46161.58286459491</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46161.67866670139</v>
+        <v>46161.84533336805</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>195</v>
@@ -6736,11 +6738,11 @@
         <v>262</v>
       </c>
       <c r="B85" s="9">
-        <v>46161.41620715278</v>
+        <v>46161.58287381944</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46161.67866399305</v>
+        <v>46161.84533065972</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>195</v>
@@ -6789,11 +6791,11 @@
         <v>263</v>
       </c>
       <c r="B86" s="5">
-        <v>46161.416216990736</v>
+        <v>46161.58288365741</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46161.67866123843</v>
+        <v>46161.84532790509</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>195</v>
@@ -6842,11 +6844,11 @@
         <v>264</v>
       </c>
       <c r="B87" s="9">
-        <v>46161.416225891204</v>
+        <v>46161.58289255787</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46161.67865819445</v>
+        <v>46161.84532486111</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>195</v>
@@ -6895,11 +6897,11 @@
         <v>265</v>
       </c>
       <c r="B88" s="5">
-        <v>46161.41625876157</v>
+        <v>46161.58292542824</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46161.67865545139</v>
+        <v>46161.84532211805</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>195</v>
@@ -6948,11 +6950,11 @@
         <v>266</v>
       </c>
       <c r="B89" s="9">
-        <v>46161.41627030092</v>
+        <v>46161.58293696759</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46161.67865260417</v>
+        <v>46161.84531927083</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>195</v>
@@ -7001,11 +7003,11 @@
         <v>267</v>
       </c>
       <c r="B90" s="5">
-        <v>46161.41628615741</v>
+        <v>46161.58295282407</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46161.67864644676</v>
+        <v>46161.84531311343</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>195</v>
@@ -7054,11 +7056,11 @@
         <v>268</v>
       </c>
       <c r="B91" s="9">
-        <v>46161.41630106482</v>
+        <v>46161.58296773148</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46161.67864576389</v>
+        <v>46161.84531243055</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>195</v>
@@ -7107,11 +7109,11 @@
         <v>269</v>
       </c>
       <c r="B92" s="5">
-        <v>46161.414387094905</v>
+        <v>46161.581053761576</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46161.67885978009</v>
+        <v>46161.84552644676</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>270</v>
@@ -7170,11 +7172,11 @@
         <v>271</v>
       </c>
       <c r="B93" s="9">
-        <v>46161.41439075231</v>
+        <v>46161.58105741898</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46161.678845069444</v>
+        <v>46161.845511736115</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>195</v>
@@ -7223,11 +7225,11 @@
         <v>273</v>
       </c>
       <c r="B94" s="5">
-        <v>46161.41637327547</v>
+        <v>46161.583039942125</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46161.678842141206</v>
+        <v>46161.84550880787</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>195</v>
@@ -7276,11 +7278,11 @@
         <v>274</v>
       </c>
       <c r="B95" s="9">
-        <v>46161.41639048611</v>
+        <v>46161.58305715278</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46161.678838657404</v>
+        <v>46161.845505324076</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>195</v>
@@ -7329,11 +7331,11 @@
         <v>275</v>
       </c>
       <c r="B96" s="5">
-        <v>46161.41641002314</v>
+        <v>46161.583076689814</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46161.678835914354</v>
+        <v>46161.84550258102</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>195</v>
@@ -7382,11 +7384,11 @@
         <v>276</v>
       </c>
       <c r="B97" s="9">
-        <v>46161.41642219907</v>
+        <v>46161.58308886574</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46161.67883261574</v>
+        <v>46161.84549928241</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>195</v>
@@ -7435,11 +7437,11 @@
         <v>277</v>
       </c>
       <c r="B98" s="5">
-        <v>46161.41643353009</v>
+        <v>46161.58310019676</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46161.678828668984</v>
+        <v>46161.84549533565</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>195</v>
@@ -7488,11 +7490,11 @@
         <v>278</v>
       </c>
       <c r="B99" s="9">
-        <v>46161.41644422454</v>
+        <v>46161.5831108912</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46161.67882539352</v>
+        <v>46161.84549206018</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>195</v>
@@ -7541,11 +7543,11 @@
         <v>279</v>
       </c>
       <c r="B100" s="5">
-        <v>46161.416461782406</v>
+        <v>46161.58312844907</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46161.67882221065</v>
+        <v>46161.84548887731</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>195</v>
@@ -7594,11 +7596,11 @@
         <v>280</v>
       </c>
       <c r="B101" s="9">
-        <v>46161.41634108796</v>
+        <v>46161.58300775463</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46161.67881563657</v>
+        <v>46161.84548230324</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>195</v>
@@ -7647,11 +7649,11 @@
         <v>281</v>
       </c>
       <c r="B102" s="5">
-        <v>46161.47283520833</v>
+        <v>46161.639501875004</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46161.6788149537</v>
+        <v>46161.845481620374</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>195</v>
@@ -7700,11 +7702,11 @@
         <v>282</v>
       </c>
       <c r="B103" s="9">
-        <v>46161.414438402775</v>
+        <v>46161.58110506945</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46161.64110194445</v>
+        <v>46161.80776861111</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>209</v>
@@ -7747,11 +7749,11 @@
         <v>284</v>
       </c>
       <c r="B104" s="5">
-        <v>46161.414441863424</v>
+        <v>46161.581108530096</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46176.021446342595</v>
+        <v>46176.18811300926</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>285</v>
@@ -7810,11 +7812,11 @@
         <v>287</v>
       </c>
       <c r="B105" s="9">
-        <v>46161.41444703704</v>
+        <v>46161.58111370371</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46161.67894248843</v>
+        <v>46161.84560915509</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>288</v>
@@ -7873,11 +7875,11 @@
         <v>290</v>
       </c>
       <c r="B106" s="5">
-        <v>46161.4144517824</v>
+        <v>46161.581118449074</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46161.67893978009</v>
+        <v>46161.84560644676</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>291</v>
@@ -7936,11 +7938,11 @@
         <v>293</v>
       </c>
       <c r="B107" s="9">
-        <v>46161.41445644676</v>
+        <v>46161.58112311343</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46161.67893543981</v>
+        <v>46161.84560210648</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>294</v>
@@ -7999,11 +8001,11 @@
         <v>296</v>
       </c>
       <c r="B108" s="5">
-        <v>46161.41446035879</v>
+        <v>46161.58112702546</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46161.667206956015</v>
+        <v>46161.83387362269</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>297</v>
@@ -8046,11 +8048,11 @@
         <v>299</v>
       </c>
       <c r="B109" s="9">
-        <v>46161.41446318287</v>
+        <v>46161.58112984954</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46161.67911563657</v>
+        <v>46161.84578230324</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>300</v>
@@ -8109,11 +8111,11 @@
         <v>302</v>
       </c>
       <c r="B110" s="5">
-        <v>46161.41446888889</v>
+        <v>46161.581135555556</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46161.67911027778</v>
+        <v>46161.84577694444</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>303</v>
@@ -8162,11 +8164,11 @@
         <v>304</v>
       </c>
       <c r="B111" s="9">
-        <v>46161.41651063657</v>
+        <v>46161.58317730324</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46161.67910700232</v>
+        <v>46161.84577366898</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>195</v>
@@ -8215,11 +8217,11 @@
         <v>305</v>
       </c>
       <c r="B112" s="5">
-        <v>46161.416520914354</v>
+        <v>46161.58318758102</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46161.67910421296</v>
+        <v>46161.845770879634</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>195</v>
@@ -8268,11 +8270,11 @@
         <v>306</v>
       </c>
       <c r="B113" s="9">
-        <v>46161.416530925926</v>
+        <v>46161.5831975926</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46161.67910042824</v>
+        <v>46161.84576709491</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>195</v>
@@ -8321,11 +8323,11 @@
         <v>307</v>
       </c>
       <c r="B114" s="5">
-        <v>46161.41653990741</v>
+        <v>46161.58320657407</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46161.67909748842</v>
+        <v>46161.84576415509</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>195</v>
@@ -8374,11 +8376,11 @@
         <v>308</v>
       </c>
       <c r="B115" s="9">
-        <v>46161.41655484954</v>
+        <v>46161.58322151621</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46161.67909415509</v>
+        <v>46161.84576082176</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>195</v>
@@ -8427,11 +8429,11 @@
         <v>309</v>
       </c>
       <c r="B116" s="5">
-        <v>46161.41656050926</v>
+        <v>46161.58322717593</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46161.679083738425</v>
+        <v>46161.84575040509</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>195</v>
@@ -8480,11 +8482,11 @@
         <v>310</v>
       </c>
       <c r="B117" s="9">
-        <v>46161.41657582176</v>
+        <v>46161.58324248843</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46161.67908300926</v>
+        <v>46161.84574967592</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>195</v>
@@ -8533,11 +8535,11 @@
         <v>311</v>
       </c>
       <c r="B118" s="5">
-        <v>46161.41658736111</v>
+        <v>46161.58325402778</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46161.6790822801</v>
+        <v>46161.845748946755</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>195</v>
@@ -8586,11 +8588,11 @@
         <v>312</v>
       </c>
       <c r="B119" s="9">
-        <v>46161.41659625</v>
+        <v>46161.58326291667</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46161.67908155093</v>
+        <v>46161.84574821759</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>195</v>
@@ -8639,11 +8641,11 @@
         <v>313</v>
       </c>
       <c r="B120" s="5">
-        <v>46161.41447261574</v>
+        <v>46161.58113928241</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46161.6793047338</v>
+        <v>46161.845971400464</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>314</v>
@@ -8702,11 +8704,11 @@
         <v>315</v>
       </c>
       <c r="B121" s="9">
-        <v>46161.414476157406</v>
+        <v>46161.58114282407</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46161.67929230324</v>
+        <v>46161.845958969905</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>195</v>
@@ -8755,11 +8757,11 @@
         <v>318</v>
       </c>
       <c r="B122" s="5">
-        <v>46161.41921576389</v>
+        <v>46161.585882430554</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46161.67928945602</v>
+        <v>46161.845956122685</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>195</v>
@@ -8808,11 +8810,11 @@
         <v>320</v>
       </c>
       <c r="B123" s="9">
-        <v>46161.419236319445</v>
+        <v>46161.58590298611</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46161.67928674769</v>
+        <v>46161.84595341435</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>195</v>
@@ -8861,11 +8863,11 @@
         <v>322</v>
       </c>
       <c r="B124" s="5">
-        <v>46161.41925319444</v>
+        <v>46161.585919861114</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46161.67928377315</v>
+        <v>46161.84595043982</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>195</v>
@@ -8914,11 +8916,11 @@
         <v>323</v>
       </c>
       <c r="B125" s="9">
-        <v>46161.419260509254</v>
+        <v>46161.585927175925</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46161.67928041666</v>
+        <v>46161.84594708333</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>195</v>
@@ -8967,11 +8969,11 @@
         <v>324</v>
       </c>
       <c r="B126" s="5">
-        <v>46161.41926643519</v>
+        <v>46161.58593310185</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46161.679277523144</v>
+        <v>46161.845944189816</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>195</v>
@@ -9020,11 +9022,11 @@
         <v>326</v>
       </c>
       <c r="B127" s="9">
-        <v>46161.419270729166</v>
+        <v>46161.58593739584</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46161.67927489583</v>
+        <v>46161.8459415625</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>195</v>
@@ -9073,11 +9075,11 @@
         <v>327</v>
       </c>
       <c r="B128" s="5">
-        <v>46161.419279236114</v>
+        <v>46161.58594590278</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46161.679266990745</v>
+        <v>46161.84593365741</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>195</v>
@@ -9126,11 +9128,11 @@
         <v>328</v>
       </c>
       <c r="B129" s="9">
-        <v>46161.41928962963</v>
+        <v>46161.5859562963</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46161.67926616898</v>
+        <v>46161.84593283565</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>195</v>
@@ -9179,11 +9181,11 @@
         <v>329</v>
       </c>
       <c r="B130" s="5">
-        <v>46161.4195224537</v>
+        <v>46161.58618912037</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46161.679265370374</v>
+        <v>46161.84593203704</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>195</v>
@@ -9232,11 +9234,11 @@
         <v>331</v>
       </c>
       <c r="B131" s="9">
-        <v>46161.414480949075</v>
+        <v>46161.58114761574</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46161.679458240746</v>
+        <v>46161.8461249074</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>332</v>
@@ -9295,11 +9297,11 @@
         <v>333</v>
       </c>
       <c r="B132" s="5">
-        <v>46161.41448450231</v>
+        <v>46161.58115116898</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46161.67944494213</v>
+        <v>46161.8461116088</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>195</v>
@@ -9348,11 +9350,11 @@
         <v>336</v>
       </c>
       <c r="B133" s="9">
-        <v>46161.41937046296</v>
+        <v>46161.58603712963</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46161.67944158565</v>
+        <v>46161.84610825231</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>195</v>
@@ -9401,11 +9403,11 @@
         <v>337</v>
       </c>
       <c r="B134" s="5">
-        <v>46161.41937826389</v>
+        <v>46161.586044930555</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46161.67943881944</v>
+        <v>46161.84610548611</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>195</v>
@@ -9454,11 +9456,11 @@
         <v>339</v>
       </c>
       <c r="B135" s="9">
-        <v>46161.41939224537</v>
+        <v>46161.58605891204</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46161.679435659724</v>
+        <v>46161.84610232639</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>195</v>
@@ -9507,11 +9509,11 @@
         <v>340</v>
       </c>
       <c r="B136" s="5">
-        <v>46161.41940101852</v>
+        <v>46161.58606768519</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46161.679432627316</v>
+        <v>46161.84609929398</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>195</v>
@@ -9560,11 +9562,11 @@
         <v>342</v>
       </c>
       <c r="B137" s="9">
-        <v>46161.41940908565</v>
+        <v>46161.58607575232</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46161.679429745374</v>
+        <v>46161.84609641204</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>195</v>
@@ -9613,11 +9615,11 @@
         <v>343</v>
       </c>
       <c r="B138" s="5">
-        <v>46161.4194221875</v>
+        <v>46161.586088854165</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46161.67942722222</v>
+        <v>46161.84609388889</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>195</v>
@@ -9666,11 +9668,11 @@
         <v>344</v>
       </c>
       <c r="B139" s="9">
-        <v>46161.41942903935</v>
+        <v>46161.58609570602</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46161.679419259264</v>
+        <v>46161.84608592592</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>195</v>
@@ -9719,11 +9721,11 @@
         <v>346</v>
       </c>
       <c r="B140" s="5">
-        <v>46161.41944391203</v>
+        <v>46161.586110578704</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46161.679418541666</v>
+        <v>46161.84608520834</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>195</v>
@@ -9772,11 +9774,11 @@
         <v>347</v>
       </c>
       <c r="B141" s="9">
-        <v>46161.4194558912</v>
+        <v>46161.58612255787</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46161.6794178125</v>
+        <v>46161.84608447917</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>195</v>
@@ -9825,11 +9827,11 @@
         <v>348</v>
       </c>
       <c r="B142" s="5">
-        <v>46161.41448976852</v>
+        <v>46161.58115643519</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46161.679629502316</v>
+        <v>46161.84629616898</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>349</v>
@@ -9888,11 +9890,11 @@
         <v>350</v>
       </c>
       <c r="B143" s="9">
-        <v>46161.41449326389</v>
+        <v>46161.58115993056</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46161.67962244213</v>
+        <v>46161.8462891088</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>303</v>
@@ -9941,11 +9943,11 @@
         <v>353</v>
       </c>
       <c r="B144" s="5">
-        <v>46161.419559745365</v>
+        <v>46161.58622641204</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46161.67961921296</v>
+        <v>46161.84628587963</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>195</v>
@@ -9994,11 +9996,11 @@
         <v>354</v>
       </c>
       <c r="B145" s="9">
-        <v>46161.419569328704</v>
+        <v>46161.586235995375</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46161.679616249996</v>
+        <v>46161.84628291667</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>195</v>
@@ -10047,11 +10049,11 @@
         <v>355</v>
       </c>
       <c r="B146" s="5">
-        <v>46161.419580104164</v>
+        <v>46161.586246770836</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46161.67961337963</v>
+        <v>46161.846280046295</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>195</v>
@@ -10100,11 +10102,11 @@
         <v>357</v>
       </c>
       <c r="B147" s="9">
-        <v>46161.41958976851</v>
+        <v>46161.586256435185</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46161.67961032408</v>
+        <v>46161.84627699074</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>195</v>
@@ -10153,11 +10155,11 @@
         <v>359</v>
       </c>
       <c r="B148" s="5">
-        <v>46161.419599166664</v>
+        <v>46161.586265833335</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46161.67960728009</v>
+        <v>46161.84627394676</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>195</v>
@@ -10206,11 +10208,11 @@
         <v>360</v>
       </c>
       <c r="B149" s="9">
-        <v>46161.41960900463</v>
+        <v>46161.586275671296</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46161.679604467594</v>
+        <v>46161.84627113426</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>195</v>
@@ -10259,11 +10261,11 @@
         <v>361</v>
       </c>
       <c r="B150" s="5">
-        <v>46161.41962519676</v>
+        <v>46161.58629186342</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46161.67960173611</v>
+        <v>46161.846268402776</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>195</v>
@@ -10312,11 +10314,11 @@
         <v>362</v>
       </c>
       <c r="B151" s="9">
-        <v>46161.41964212963</v>
+        <v>46161.58630879629</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46161.67959555556</v>
+        <v>46161.84626222222</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>195</v>
@@ -10365,11 +10367,11 @@
         <v>363</v>
       </c>
       <c r="B152" s="5">
-        <v>46161.41965496528</v>
+        <v>46161.58632163194</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46161.679594953705</v>
+        <v>46161.84626162037</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>195</v>
@@ -10418,11 +10420,11 @@
         <v>364</v>
       </c>
       <c r="B153" s="9">
-        <v>46161.41449802084</v>
+        <v>46161.5811646875</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46161.67977259259</v>
+        <v>46161.84643925926</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>365</v>
@@ -10481,11 +10483,11 @@
         <v>366</v>
       </c>
       <c r="B154" s="5">
-        <v>46161.41450162037</v>
+        <v>46161.58116828704</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46161.67977555556</v>
+        <v>46161.84644222222</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>195</v>
@@ -10532,11 +10534,11 @@
         <v>368</v>
       </c>
       <c r="B155" s="9">
-        <v>46161.47245956019</v>
+        <v>46161.63912622685</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46161.679772627314</v>
+        <v>46161.84643929398</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>195</v>
@@ -10583,11 +10585,11 @@
         <v>369</v>
       </c>
       <c r="B156" s="5">
-        <v>46161.47247070602</v>
+        <v>46161.63913737268</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46161.67976976852</v>
+        <v>46161.84643643518</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>195</v>
@@ -10634,11 +10636,11 @@
         <v>370</v>
       </c>
       <c r="B157" s="9">
-        <v>46161.47248053241</v>
+        <v>46161.63914719908</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46161.67976665509</v>
+        <v>46161.846433321756</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>195</v>
@@ -10685,11 +10687,11 @@
         <v>371</v>
       </c>
       <c r="B158" s="5">
-        <v>46161.4724908912</v>
+        <v>46161.639157557875</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46161.67976347222</v>
+        <v>46161.84643013889</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>195</v>
@@ -10736,11 +10738,11 @@
         <v>372</v>
       </c>
       <c r="B159" s="9">
-        <v>46161.47250552083</v>
+        <v>46161.6391721875</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46161.67975980324</v>
+        <v>46161.84642646991</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>195</v>
@@ -10787,11 +10789,11 @@
         <v>373</v>
       </c>
       <c r="B160" s="5">
-        <v>46161.47252072916</v>
+        <v>46161.639187395835</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46161.679756550926</v>
+        <v>46161.84642321759</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>195</v>
@@ -10838,11 +10840,11 @@
         <v>374</v>
       </c>
       <c r="B161" s="9">
-        <v>46161.47252862269</v>
+        <v>46161.639195289354</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46161.67975347222</v>
+        <v>46161.846420138885</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>195</v>
@@ -10889,11 +10891,11 @@
         <v>375</v>
       </c>
       <c r="B162" s="5">
-        <v>46161.472538842594</v>
+        <v>46161.63920550926</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46161.67974644676</v>
+        <v>46161.846413113424</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>195</v>
@@ -10940,11 +10942,11 @@
         <v>376</v>
       </c>
       <c r="B163" s="9">
-        <v>46161.47254766204</v>
+        <v>46161.63921432871</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46161.67974575231</v>
+        <v>46161.84641241898</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>195</v>
@@ -10991,11 +10993,11 @@
         <v>377</v>
       </c>
       <c r="B164" s="5">
-        <v>46161.414510856484</v>
+        <v>46161.58117752315</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46161.679938368055</v>
+        <v>46161.84660503472</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>378</v>
@@ -11054,11 +11056,11 @@
         <v>380</v>
       </c>
       <c r="B165" s="9">
-        <v>46161.41451471065</v>
+        <v>46161.58118137732</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46161.67991349537</v>
+        <v>46161.84658016203</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>195</v>
@@ -11107,11 +11109,11 @@
         <v>382</v>
       </c>
       <c r="B166" s="5">
-        <v>46161.472587094904</v>
+        <v>46161.639253761576</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46161.679910520834</v>
+        <v>46161.846577187505</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>195</v>
@@ -11160,11 +11162,11 @@
         <v>383</v>
       </c>
       <c r="B167" s="9">
-        <v>46161.47262043982</v>
+        <v>46161.63928710648</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46161.67990751157</v>
+        <v>46161.84657417824</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>195</v>
@@ -11213,11 +11215,11 @@
         <v>384</v>
       </c>
       <c r="B168" s="5">
-        <v>46161.47263069444</v>
+        <v>46161.63929736111</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46161.67990469908</v>
+        <v>46161.84657136574</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>195</v>
@@ -11266,11 +11268,11 @@
         <v>385</v>
       </c>
       <c r="B169" s="9">
-        <v>46161.47264047454</v>
+        <v>46161.6393071412</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46161.67990174769</v>
+        <v>46161.84656841435</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>195</v>
@@ -11319,11 +11321,11 @@
         <v>386</v>
       </c>
       <c r="B170" s="5">
-        <v>46161.47264895833</v>
+        <v>46161.639315625</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46161.679898726856</v>
+        <v>46161.84656539352</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>195</v>
@@ -11372,11 +11374,11 @@
         <v>387</v>
       </c>
       <c r="B171" s="9">
-        <v>46161.472660196756</v>
+        <v>46161.63932686343</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46161.67989608797</v>
+        <v>46161.846562754625</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>195</v>
@@ -11425,11 +11427,11 @@
         <v>388</v>
       </c>
       <c r="B172" s="5">
-        <v>46161.47267041667</v>
+        <v>46161.63933708333</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46161.67989328704</v>
+        <v>46161.8465599537</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>195</v>
@@ -11478,11 +11480,11 @@
         <v>389</v>
       </c>
       <c r="B173" s="9">
-        <v>46161.47268818287</v>
+        <v>46161.63935484954</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46161.6798871412</v>
+        <v>46161.846553807874</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>195</v>
@@ -11531,11 +11533,11 @@
         <v>390</v>
       </c>
       <c r="B174" s="5">
-        <v>46161.47269787037</v>
+        <v>46161.63936453704</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46161.67988646991</v>
+        <v>46161.84655313657</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>195</v>
@@ -11584,11 +11586,11 @@
         <v>391</v>
       </c>
       <c r="B175" s="9">
-        <v>46161.41451859954</v>
+        <v>46161.5811852662</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46161.674260659725</v>
+        <v>46161.84092732639</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>392</v>
@@ -11631,11 +11633,11 @@
         <v>394</v>
       </c>
       <c r="B176" s="5">
-        <v>46161.41452135416</v>
+        <v>46161.581188020835</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46161.68009149306</v>
+        <v>46161.84675815972</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>395</v>
@@ -11694,11 +11696,11 @@
         <v>398</v>
       </c>
       <c r="B177" s="9">
-        <v>46161.41452600695</v>
+        <v>46161.581192673606</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46161.68008268518</v>
+        <v>46161.846749351855</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>195</v>
@@ -11747,11 +11749,11 @@
         <v>400</v>
       </c>
       <c r="B178" s="5">
-        <v>46161.473160416666</v>
+        <v>46161.63982708333</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46161.68007988426</v>
+        <v>46161.84674655093</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>195</v>
@@ -11800,11 +11802,11 @@
         <v>401</v>
       </c>
       <c r="B179" s="9">
-        <v>46161.47316865741</v>
+        <v>46161.63983532407</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46161.68007731481</v>
+        <v>46161.846743981485</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>195</v>
@@ -11853,11 +11855,11 @@
         <v>402</v>
       </c>
       <c r="B180" s="5">
-        <v>46161.4731775463</v>
+        <v>46161.63984421296</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46161.68007476852</v>
+        <v>46161.84674143518</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>195</v>
@@ -11906,11 +11908,11 @@
         <v>403</v>
       </c>
       <c r="B181" s="9">
-        <v>46161.47319211806</v>
+        <v>46161.63985878472</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46161.680071875</v>
+        <v>46161.846738541666</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>195</v>
@@ -11959,11 +11961,11 @@
         <v>404</v>
       </c>
       <c r="B182" s="5">
-        <v>46161.47320113426</v>
+        <v>46161.63986780093</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46161.68006892361</v>
+        <v>46161.84673559028</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>195</v>
@@ -12012,11 +12014,11 @@
         <v>405</v>
       </c>
       <c r="B183" s="9">
-        <v>46161.47320833334</v>
+        <v>46161.639875</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46161.68006622685</v>
+        <v>46161.84673289352</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>195</v>
@@ -12065,11 +12067,11 @@
         <v>406</v>
       </c>
       <c r="B184" s="5">
-        <v>46161.47321675926</v>
+        <v>46161.63988342593</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46161.68005822916</v>
+        <v>46161.84672489583</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>195</v>
@@ -12118,11 +12120,11 @@
         <v>407</v>
       </c>
       <c r="B185" s="9">
-        <v>46161.47322476852</v>
+        <v>46161.63989143519</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46161.68005753472</v>
+        <v>46161.84672420139</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>195</v>
@@ -12171,11 +12173,11 @@
         <v>408</v>
       </c>
       <c r="B186" s="5">
-        <v>46161.47323267361</v>
+        <v>46161.639899340276</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46161.680056736106</v>
+        <v>46161.84672340278</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>195</v>
@@ -12224,11 +12226,11 @@
         <v>409</v>
       </c>
       <c r="B187" s="9">
-        <v>46161.41452984954</v>
+        <v>46161.5811965162</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46161.68023515046</v>
+        <v>46161.84690181713</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>410</v>
@@ -12287,11 +12289,11 @@
         <v>411</v>
       </c>
       <c r="B188" s="5">
-        <v>46161.41453335648</v>
+        <v>46161.58120002315</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46161.68023670139</v>
+        <v>46161.84690336806</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>195</v>
@@ -12340,11 +12342,11 @@
         <v>413</v>
       </c>
       <c r="B189" s="9">
-        <v>46161.47326758102</v>
+        <v>46161.63993424768</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46161.68023371528</v>
+        <v>46161.84690038195</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>195</v>
@@ -12393,11 +12395,11 @@
         <v>414</v>
       </c>
       <c r="B190" s="5">
-        <v>46161.473328113425</v>
+        <v>46161.6399947801</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46161.68023079861</v>
+        <v>46161.84689746528</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>195</v>
@@ -12446,11 +12448,11 @@
         <v>415</v>
       </c>
       <c r="B191" s="9">
-        <v>46161.473337777774</v>
+        <v>46161.640004444445</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46161.68022780093</v>
+        <v>46161.84689446759</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>195</v>
@@ -12499,11 +12501,11 @@
         <v>416</v>
       </c>
       <c r="B192" s="5">
-        <v>46161.47334834491</v>
+        <v>46161.64001501157</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46161.68022471065</v>
+        <v>46161.84689137731</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>195</v>
@@ -12552,11 +12554,11 @@
         <v>417</v>
       </c>
       <c r="B193" s="9">
-        <v>46161.47335716435</v>
+        <v>46161.640023831016</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46161.68022212963</v>
+        <v>46161.846888796295</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>195</v>
@@ -12605,11 +12607,11 @@
         <v>418</v>
       </c>
       <c r="B194" s="5">
-        <v>46161.473371643515</v>
+        <v>46161.640038310186</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46161.68021939815</v>
+        <v>46161.84688606481</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>195</v>
@@ -12658,11 +12660,11 @@
         <v>419</v>
       </c>
       <c r="B195" s="9">
-        <v>46161.47338081019</v>
+        <v>46161.64004747685</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46161.6802158912</v>
+        <v>46161.846882557875</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>195</v>
@@ -12711,11 +12713,11 @@
         <v>420</v>
       </c>
       <c r="B196" s="5">
-        <v>46161.47338982639</v>
+        <v>46161.64005649305</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46161.68021290509</v>
+        <v>46161.84687957176</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>195</v>
@@ -12764,11 +12766,11 @@
         <v>421</v>
       </c>
       <c r="B197" s="9">
-        <v>46161.47339679398</v>
+        <v>46161.64006346065</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46161.68020357639</v>
+        <v>46161.846870243055</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>195</v>
@@ -12817,11 +12819,11 @@
         <v>422</v>
       </c>
       <c r="B198" s="5">
-        <v>46161.41453732639</v>
+        <v>46161.58120399306</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46161.68043979167</v>
+        <v>46161.84710645833</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>423</v>
@@ -12878,11 +12880,11 @@
         <v>424</v>
       </c>
       <c r="B199" s="9">
-        <v>46161.4145408912</v>
+        <v>46161.58120755787</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46161.68041114583</v>
+        <v>46161.847077812505</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>195</v>
@@ -12929,11 +12931,11 @@
         <v>426</v>
       </c>
       <c r="B200" s="5">
-        <v>46161.47345859953</v>
+        <v>46161.6401252662</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46161.6804083912</v>
+        <v>46161.84707505787</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>195</v>
@@ -12980,11 +12982,11 @@
         <v>427</v>
       </c>
       <c r="B201" s="9">
-        <v>46161.47347471065</v>
+        <v>46161.64014137731</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46161.680405810184</v>
+        <v>46161.847072476856</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>195</v>
@@ -13031,11 +13033,11 @@
         <v>428</v>
       </c>
       <c r="B202" s="5">
-        <v>46161.47348627315</v>
+        <v>46161.64015293981</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46161.680402638885</v>
+        <v>46161.84706930556</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>195</v>
@@ -13082,11 +13084,11 @@
         <v>429</v>
       </c>
       <c r="B203" s="9">
-        <v>46161.47350074074</v>
+        <v>46161.64016740741</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46161.680399942124</v>
+        <v>46161.847066608796</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>195</v>
@@ -13133,11 +13135,11 @@
         <v>430</v>
       </c>
       <c r="B204" s="5">
-        <v>46161.47353721065</v>
+        <v>46161.640203877316</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46161.68039736111</v>
+        <v>46161.84706402778</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>195</v>
@@ -13184,11 +13186,11 @@
         <v>431</v>
       </c>
       <c r="B205" s="9">
-        <v>46161.4735484375</v>
+        <v>46161.64021510417</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46161.68039445602</v>
+        <v>46161.84706112268</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>195</v>
@@ -13235,11 +13237,11 @@
         <v>432</v>
       </c>
       <c r="B206" s="5">
-        <v>46161.4735603588</v>
+        <v>46161.64022702546</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46161.68038675926</v>
+        <v>46161.847053425925</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>195</v>
@@ -13286,11 +13288,11 @@
         <v>433</v>
       </c>
       <c r="B207" s="9">
-        <v>46161.473571180555</v>
+        <v>46161.64023784723</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46161.68038609954</v>
+        <v>46161.8470527662</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>195</v>
@@ -13337,11 +13339,11 @@
         <v>434</v>
       </c>
       <c r="B208" s="5">
-        <v>46161.47358644676</v>
+        <v>46161.64025311342</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46161.68038543982</v>
+        <v>46161.84705210648</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>195</v>
@@ -13388,11 +13390,11 @@
         <v>435</v>
       </c>
       <c r="B209" s="9">
-        <v>46161.41454799769</v>
+        <v>46161.58121466435</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46161.6806352662</v>
+        <v>46161.84730193287</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>436</v>
@@ -13451,11 +13453,11 @@
         <v>438</v>
       </c>
       <c r="B210" s="5">
-        <v>46161.414590659726</v>
+        <v>46161.58125732639</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46161.680614247685</v>
+        <v>46161.84728091436</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>195</v>
@@ -13502,11 +13504,11 @@
         <v>439</v>
       </c>
       <c r="B211" s="9">
-        <v>46161.47364123842</v>
+        <v>46161.640307905094</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46161.6806110301</v>
+        <v>46161.84727769676</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>195</v>
@@ -13553,11 +13555,11 @@
         <v>440</v>
       </c>
       <c r="B212" s="5">
-        <v>46161.4736496875</v>
+        <v>46161.64031635417</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46161.680608587965</v>
+        <v>46161.84727525463</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>195</v>
@@ -13604,11 +13606,11 @@
         <v>441</v>
       </c>
       <c r="B213" s="9">
-        <v>46161.473661655094</v>
+        <v>46161.64032832176</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46161.68060581019</v>
+        <v>46161.84727247685</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>195</v>
@@ -13655,11 +13657,11 @@
         <v>442</v>
       </c>
       <c r="B214" s="5">
-        <v>46161.47367131944</v>
+        <v>46161.640337986115</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46161.68060278935</v>
+        <v>46161.84726945602</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>195</v>
@@ -13706,11 +13708,11 @@
         <v>443</v>
       </c>
       <c r="B215" s="9">
-        <v>46161.473691956024</v>
+        <v>46161.64035862268</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46161.680599722225</v>
+        <v>46161.84726638889</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>195</v>
@@ -13757,11 +13759,11 @@
         <v>444</v>
       </c>
       <c r="B216" s="5">
-        <v>46161.47370106481</v>
+        <v>46161.64036773148</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46161.68059693287</v>
+        <v>46161.84726359954</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>195</v>
@@ -13808,11 +13810,11 @@
         <v>445</v>
       </c>
       <c r="B217" s="9">
-        <v>46161.47370990741</v>
+        <v>46161.64037657407</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46161.68059393518</v>
+        <v>46161.84726060185</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>195</v>
@@ -13859,11 +13861,11 @@
         <v>446</v>
       </c>
       <c r="B218" s="5">
-        <v>46161.47371806713</v>
+        <v>46161.64038473379</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46161.68058803241</v>
+        <v>46161.847254699074</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>195</v>
@@ -13910,11 +13912,11 @@
         <v>447</v>
       </c>
       <c r="B219" s="9">
-        <v>46161.47372684028</v>
+        <v>46161.64039350694</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46161.68058739584</v>
+        <v>46161.8472540625</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>195</v>
@@ -13961,11 +13963,11 @@
         <v>448</v>
       </c>
       <c r="B220" s="5">
-        <v>46161.41459615741</v>
+        <v>46161.581262824075</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46161.68134378472</v>
+        <v>46161.84801045139</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>449</v>
@@ -14008,11 +14010,11 @@
         <v>451</v>
       </c>
       <c r="B221" s="9">
-        <v>46161.414599490745</v>
+        <v>46161.58126615741</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46161.680980902776</v>
+        <v>46161.84764756945</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>452</v>
@@ -14071,11 +14073,11 @@
         <v>455</v>
       </c>
       <c r="B222" s="5">
-        <v>46161.41460415509</v>
+        <v>46161.581270821756</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46161.68155587963</v>
+        <v>46161.848222546294</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>456</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46197.70503726852</v>
+        <v>46197.74552802084</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>184</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2087,13 +2087,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46161.58063581018</v>
+        <v>46161.41396914352</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87851013889</v>
+        <v>46175.71184347222</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87852383102</v>
+        <v>46175.71185716435</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2140,13 +2140,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46161.58074600695</v>
+        <v>46161.41407934028</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87848300926</v>
+        <v>46175.71181634259</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87851039352</v>
+        <v>46175.71184372685</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2203,13 +2203,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46161.58074907407</v>
+        <v>46161.414082407406</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87848385416</v>
+        <v>46175.711817187504</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87851055556</v>
+        <v>46175.71184388889</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2266,13 +2266,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46161.58075194445</v>
+        <v>46161.41408527778</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.878484409724</v>
+        <v>46175.71181774305</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.878510497685</v>
+        <v>46175.71184383101</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2329,13 +2329,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46161.58075466435</v>
+        <v>46161.414087997684</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.87848503472</v>
+        <v>46175.71181836806</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.878510925926</v>
+        <v>46175.71184425926</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2392,13 +2392,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46161.5807578588</v>
+        <v>46161.41409119213</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87848576389</v>
+        <v>46175.711819097225</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87851096065</v>
+        <v>46175.71184429398</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2455,11 +2455,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46161.580639618056</v>
+        <v>46161.413972951384</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46197.67728914352</v>
+        <v>46197.51062247685</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2502,13 +2502,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46161.580761307865</v>
+        <v>46161.41409464121</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.67426642361</v>
+        <v>46197.507599756944</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.674283043976</v>
+        <v>46197.50761637732</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2567,13 +2567,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46161.580766307874</v>
+        <v>46161.4140996412</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.67508163194</v>
+        <v>46197.50841496528</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.67509547454</v>
+        <v>46197.508428807865</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2632,13 +2632,13 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46161.580771423614</v>
+        <v>46161.41410475694</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.67727987269</v>
+        <v>46197.51061320602</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.677296249996</v>
+        <v>46197.51062958333</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2697,11 +2697,11 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46161.5807762037</v>
+        <v>46161.414109537036</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.67729836806</v>
+        <v>46197.510631701385</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2760,11 +2760,11 @@
         <v>70</v>
       </c>
       <c r="B15" s="9">
-        <v>46161.58064403935</v>
+        <v>46161.413977372686</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46197.58860099537</v>
+        <v>46197.421934328704</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>71</v>
@@ -2807,11 +2807,11 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46161.58078354166</v>
+        <v>46161.414116875</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.67428359954</v>
+        <v>46197.50761693287</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2870,11 +2870,11 @@
         <v>76</v>
       </c>
       <c r="B17" s="9">
-        <v>46161.580788680556</v>
+        <v>46161.414122013884</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46197.67510195602</v>
+        <v>46197.508435289354</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>77</v>
@@ -2933,13 +2933,13 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46161.58079363426</v>
+        <v>46161.41412696759</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.58859138889</v>
+        <v>46197.42192472222</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.675101863424</v>
+        <v>46197.50843519676</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2998,11 +2998,11 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46161.58079903935</v>
+        <v>46161.41413237268</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46169.87957331019</v>
+        <v>46169.712906643515</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -3061,11 +3061,11 @@
         <v>90</v>
       </c>
       <c r="B20" s="5">
-        <v>46161.58080373843</v>
+        <v>46161.414137071755</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46169.87958414352</v>
+        <v>46169.71291747685</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>91</v>
@@ -3124,11 +3124,11 @@
         <v>93</v>
       </c>
       <c r="B21" s="9">
-        <v>46161.58080740741</v>
+        <v>46161.414140740744</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46169.879600381944</v>
+        <v>46169.71293371527</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>94</v>
@@ -3187,11 +3187,11 @@
         <v>96</v>
       </c>
       <c r="B22" s="5">
-        <v>46161.580810740736</v>
+        <v>46161.41414407408</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46169.87961318287</v>
+        <v>46169.7129465162</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>97</v>
@@ -3250,11 +3250,11 @@
         <v>99</v>
       </c>
       <c r="B23" s="9">
-        <v>46161.58064796297</v>
+        <v>46161.4139812963</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46161.73787121528</v>
+        <v>46161.571204548614</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -3297,11 +3297,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46161.58081472223</v>
+        <v>46161.414148055555</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.879378680555</v>
+        <v>46169.71271201389</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3360,11 +3360,11 @@
         <v>107</v>
       </c>
       <c r="B25" s="9">
-        <v>46161.580819016206</v>
+        <v>46161.414152349535</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.879644560184</v>
+        <v>46169.71297789352</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>108</v>
@@ -3419,11 +3419,11 @@
         <v>110</v>
       </c>
       <c r="B26" s="5">
-        <v>46161.58082350694</v>
+        <v>46161.41415684028</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.87966921296</v>
+        <v>46169.7130025463</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>111</v>
@@ -3478,11 +3478,11 @@
         <v>113</v>
       </c>
       <c r="B27" s="9">
-        <v>46161.58082824074</v>
+        <v>46161.414161574074</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46192.85867619213</v>
+        <v>46192.69200952546</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>114</v>
@@ -3541,11 +3541,11 @@
         <v>116</v>
       </c>
       <c r="B28" s="5">
-        <v>46161.5808325463</v>
+        <v>46161.41416587963</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46197.58860037037</v>
+        <v>46197.42193370371</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>117</v>
@@ -3600,11 +3600,11 @@
         <v>119</v>
       </c>
       <c r="B29" s="9">
-        <v>46161.580836967594</v>
+        <v>46161.41417030092</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46171.17352185185</v>
+        <v>46171.00685518519</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>120</v>
@@ -3659,11 +3659,11 @@
         <v>122</v>
       </c>
       <c r="B30" s="5">
-        <v>46161.58084165509</v>
+        <v>46161.41417498843</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46192.86032678241</v>
+        <v>46192.693660115736</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>123</v>
@@ -3722,11 +3722,11 @@
         <v>125</v>
       </c>
       <c r="B31" s="9">
-        <v>46161.58084603009</v>
+        <v>46161.414179363426</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46175.170256446756</v>
+        <v>46175.00358978009</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>126</v>
@@ -3781,11 +3781,11 @@
         <v>128</v>
       </c>
       <c r="B32" s="5">
-        <v>46161.580850439816</v>
+        <v>46161.414183773144</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.87976645833</v>
+        <v>46169.71309979167</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>129</v>
@@ -3840,11 +3840,11 @@
         <v>131</v>
       </c>
       <c r="B33" s="9">
-        <v>46161.58085503472</v>
+        <v>46161.41418836806</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.879778622686</v>
+        <v>46169.71311195602</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>132</v>
@@ -3899,11 +3899,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46161.58085940972</v>
+        <v>46161.41419274306</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.87943234954</v>
+        <v>46169.71276568287</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3962,11 +3962,11 @@
         <v>139</v>
       </c>
       <c r="B35" s="9">
-        <v>46161.58086364584</v>
+        <v>46161.41419697917</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.879810196755</v>
+        <v>46169.7131435301</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>140</v>
@@ -4021,11 +4021,11 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46161.58086832176</v>
+        <v>46161.41420165509</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.879828854166</v>
+        <v>46169.7131621875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -4080,11 +4080,11 @@
         <v>145</v>
       </c>
       <c r="B37" s="9">
-        <v>46161.58087322916</v>
+        <v>46161.4142065625</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.87944365741</v>
+        <v>46169.71277699074</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>146</v>
@@ -4143,11 +4143,11 @@
         <v>148</v>
       </c>
       <c r="B38" s="5">
-        <v>46161.580931018514</v>
+        <v>46161.41426435186</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.8798540625</v>
+        <v>46169.713187395835</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>92</v>
@@ -4196,11 +4196,11 @@
         <v>150</v>
       </c>
       <c r="B39" s="9">
-        <v>46161.58093646991</v>
+        <v>46161.41426980324</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.87986516204</v>
+        <v>46169.713198495374</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>151</v>
@@ -4249,11 +4249,11 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46161.580941099535</v>
+        <v>46161.41427443287</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.87945328704</v>
+        <v>46169.71278662037</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>154</v>
@@ -4312,11 +4312,11 @@
         <v>158</v>
       </c>
       <c r="B41" s="9">
-        <v>46161.58094532407</v>
+        <v>46161.41427865741</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.87990410879</v>
+        <v>46169.713237442134</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>98</v>
@@ -4365,11 +4365,11 @@
         <v>160</v>
       </c>
       <c r="B42" s="5">
-        <v>46161.58094997685</v>
+        <v>46161.41428331019</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.87991520834</v>
+        <v>46169.713248541666</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>161</v>
@@ -4418,11 +4418,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46161.58095447917</v>
+        <v>46161.4142878125</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.879929814815</v>
+        <v>46169.71326314815</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4471,11 +4471,11 @@
         <v>167</v>
       </c>
       <c r="B44" s="5">
-        <v>46161.58095743056</v>
+        <v>46161.41429076389</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.87951825232</v>
+        <v>46169.712851585646</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>168</v>
@@ -4534,11 +4534,11 @@
         <v>170</v>
       </c>
       <c r="B45" s="9">
-        <v>46161.58096091435</v>
+        <v>46161.41429424769</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.87997335648</v>
+        <v>46169.71330668981</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>95</v>
@@ -4587,11 +4587,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46161.580964988425</v>
+        <v>46161.41429832176</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.87999765047</v>
+        <v>46169.713330983795</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4640,11 +4640,11 @@
         <v>175</v>
       </c>
       <c r="B47" s="9">
-        <v>46161.58065239583</v>
+        <v>46161.41398572917</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46197.705037754626</v>
+        <v>46197.53837108796</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>176</v>
@@ -4687,13 +4687,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46161.580969780094</v>
+        <v>46161.41430311343</v>
       </c>
       <c r="C48" s="5">
-        <v>46197.70503125</v>
+        <v>46197.538364583335</v>
       </c>
       <c r="D48" s="5">
-        <v>46197.70504644676</v>
+        <v>46197.53837978009</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4752,11 +4752,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46161.580975069446</v>
+        <v>46161.414308402775</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46197.74552802084</v>
+        <v>46197.578861354166</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>184</v>
@@ -4815,11 +4815,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46161.58098100695</v>
+        <v>46161.414314340276</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46161.84455542824</v>
+        <v>46161.67788876157</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>87</v>
@@ -4878,11 +4878,11 @@
         <v>191</v>
       </c>
       <c r="B51" s="9">
-        <v>46161.58099116899</v>
+        <v>46161.414324502315</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46161.84476310185</v>
+        <v>46161.678096435186</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>192</v>
@@ -4941,11 +4941,11 @@
         <v>196</v>
       </c>
       <c r="B52" s="5">
-        <v>46161.58099418982</v>
+        <v>46161.41432752315</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46161.84476607639</v>
+        <v>46161.67809940972</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4992,11 +4992,11 @@
         <v>198</v>
       </c>
       <c r="B53" s="9">
-        <v>46161.63966489583</v>
+        <v>46161.47299822917</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46161.844763472225</v>
+        <v>46161.678096805554</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>195</v>
@@ -5043,11 +5043,11 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46161.63967261574</v>
+        <v>46161.473005949076</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46161.84476069444</v>
+        <v>46161.67809402778</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -5094,11 +5094,11 @@
         <v>201</v>
       </c>
       <c r="B55" s="9">
-        <v>46161.63968388889</v>
+        <v>46161.47301722222</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46161.84475773148</v>
+        <v>46161.678091064816</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>195</v>
@@ -5145,11 +5145,11 @@
         <v>202</v>
       </c>
       <c r="B56" s="5">
-        <v>46161.63969275463</v>
+        <v>46161.47302608796</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46161.84475471065</v>
+        <v>46161.67808804398</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -5196,11 +5196,11 @@
         <v>203</v>
       </c>
       <c r="B57" s="9">
-        <v>46161.639705208334</v>
+        <v>46161.47303854166</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46161.84475174769</v>
+        <v>46161.67808508102</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>195</v>
@@ -5247,11 +5247,11 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46161.639715474535</v>
+        <v>46161.47304880787</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46161.84474863426</v>
+        <v>46161.67808196759</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>195</v>
@@ -5298,11 +5298,11 @@
         <v>205</v>
       </c>
       <c r="B59" s="9">
-        <v>46161.63972679398</v>
+        <v>46161.47306012732</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46161.84474503472</v>
+        <v>46161.67807836806</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>195</v>
@@ -5349,11 +5349,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46161.63974304398</v>
+        <v>46161.47307637731</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46161.84473834491</v>
+        <v>46161.67807167824</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>195</v>
@@ -5400,11 +5400,11 @@
         <v>207</v>
       </c>
       <c r="B61" s="9">
-        <v>46161.63975269676</v>
+        <v>46161.47308603009</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.84473753472</v>
+        <v>46161.67807086806</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>195</v>
@@ -5451,11 +5451,11 @@
         <v>208</v>
       </c>
       <c r="B62" s="5">
-        <v>46161.58099818287</v>
+        <v>46161.41433151621</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46161.79647144676</v>
+        <v>46161.629804780096</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5498,11 +5498,11 @@
         <v>211</v>
       </c>
       <c r="B63" s="9">
-        <v>46161.58100145833</v>
+        <v>46161.41433479167</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.844842499995</v>
+        <v>46161.67817583334</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>212</v>
@@ -5561,11 +5561,11 @@
         <v>216</v>
       </c>
       <c r="B64" s="5">
-        <v>46161.58100614583</v>
+        <v>46161.41433947917</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46161.84491849537</v>
+        <v>46161.67825182871</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>
@@ -5624,11 +5624,11 @@
         <v>220</v>
       </c>
       <c r="B65" s="9">
-        <v>46161.58101638889</v>
+        <v>46161.414349722225</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46161.84483983796</v>
+        <v>46161.6781731713</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>221</v>
@@ -5687,11 +5687,11 @@
         <v>223</v>
       </c>
       <c r="B66" s="5">
-        <v>46161.58102099537</v>
+        <v>46161.41435432871</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46161.84491503472</v>
+        <v>46161.67824836806</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>224</v>
@@ -5750,11 +5750,11 @@
         <v>226</v>
       </c>
       <c r="B67" s="9">
-        <v>46161.581024722225</v>
+        <v>46161.414358055554</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46161.8448359375</v>
+        <v>46161.67816927083</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>227</v>
@@ -5813,11 +5813,11 @@
         <v>229</v>
       </c>
       <c r="B68" s="5">
-        <v>46161.58102864583</v>
+        <v>46161.41436197917</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46161.844914270834</v>
+        <v>46161.67824760417</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5876,11 +5876,11 @@
         <v>231</v>
       </c>
       <c r="B69" s="9">
-        <v>46161.58103207176</v>
+        <v>46161.41436540509</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46161.797785821764</v>
+        <v>46161.63111915509</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>232</v>
@@ -5923,11 +5923,11 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46161.58103457176</v>
+        <v>46161.41436790509</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46161.845178449075</v>
+        <v>46161.678511782404</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>235</v>
@@ -5986,11 +5986,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46161.58103962963</v>
+        <v>46161.41437296296</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46161.845147071755</v>
+        <v>46161.67848040509</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>195</v>
@@ -6039,11 +6039,11 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46161.582011805556</v>
+        <v>46161.415345138885</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46161.84514348379</v>
+        <v>46161.678476817135</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>195</v>
@@ -6092,11 +6092,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46161.58202383102</v>
+        <v>46161.415357164355</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46161.845140324076</v>
+        <v>46161.678473657405</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>195</v>
@@ -6145,11 +6145,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46161.582662650464</v>
+        <v>46161.4159959838</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46161.845136655094</v>
+        <v>46161.67846998843</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>195</v>
@@ -6198,11 +6198,11 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46161.58267322917</v>
+        <v>46161.416006562504</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46161.845133518524</v>
+        <v>46161.67846685185</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>195</v>
@@ -6251,11 +6251,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46161.58270134259</v>
+        <v>46161.41603467593</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46161.84513074074</v>
+        <v>46161.67846407407</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>195</v>
@@ -6304,11 +6304,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46161.58271427083</v>
+        <v>46161.416047604165</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46161.84512803241</v>
+        <v>46161.67846136574</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>195</v>
@@ -6357,11 +6357,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46161.58272651621</v>
+        <v>46161.41605984954</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46161.84512407407</v>
+        <v>46161.67845740741</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>195</v>
@@ -6410,11 +6410,11 @@
         <v>252</v>
       </c>
       <c r="B79" s="9">
-        <v>46161.58277962963</v>
+        <v>46161.416112962965</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46161.845117916666</v>
+        <v>46161.67845125</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>195</v>
@@ -6463,11 +6463,11 @@
         <v>254</v>
       </c>
       <c r="B80" s="5">
-        <v>46161.58279046296</v>
+        <v>46161.4161237963</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46161.84511721064</v>
+        <v>46161.67845054399</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>195</v>
@@ -6516,11 +6516,11 @@
         <v>255</v>
       </c>
       <c r="B81" s="9">
-        <v>46161.58104538194</v>
+        <v>46161.41437871528</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46161.845344814814</v>
+        <v>46161.67867814815</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>256</v>
@@ -6579,11 +6579,11 @@
         <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46161.58104903935</v>
+        <v>46161.414382372684</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46161.84533920139</v>
+        <v>46161.67867253472</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>195</v>
@@ -6632,11 +6632,11 @@
         <v>260</v>
       </c>
       <c r="B83" s="9">
-        <v>46161.582834120374</v>
+        <v>46161.4161674537</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46161.84533628472</v>
+        <v>46161.67866961806</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>195</v>
@@ -6685,11 +6685,11 @@
         <v>261</v>
       </c>
       <c r="B84" s="5">
-        <v>46161.58286459491</v>
+        <v>46161.416197928236</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46161.84533336805</v>
+        <v>46161.67866670139</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>195</v>
@@ -6738,11 +6738,11 @@
         <v>262</v>
       </c>
       <c r="B85" s="9">
-        <v>46161.58287381944</v>
+        <v>46161.41620715278</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46161.84533065972</v>
+        <v>46161.67866399305</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>195</v>
@@ -6791,11 +6791,11 @@
         <v>263</v>
       </c>
       <c r="B86" s="5">
-        <v>46161.58288365741</v>
+        <v>46161.416216990736</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46161.84532790509</v>
+        <v>46161.67866123843</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>195</v>
@@ -6844,11 +6844,11 @@
         <v>264</v>
       </c>
       <c r="B87" s="9">
-        <v>46161.58289255787</v>
+        <v>46161.416225891204</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46161.84532486111</v>
+        <v>46161.67865819445</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>195</v>
@@ -6897,11 +6897,11 @@
         <v>265</v>
       </c>
       <c r="B88" s="5">
-        <v>46161.58292542824</v>
+        <v>46161.41625876157</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46161.84532211805</v>
+        <v>46161.67865545139</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>195</v>
@@ -6950,11 +6950,11 @@
         <v>266</v>
       </c>
       <c r="B89" s="9">
-        <v>46161.58293696759</v>
+        <v>46161.41627030092</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46161.84531927083</v>
+        <v>46161.67865260417</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>195</v>
@@ -7003,11 +7003,11 @@
         <v>267</v>
       </c>
       <c r="B90" s="5">
-        <v>46161.58295282407</v>
+        <v>46161.41628615741</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46161.84531311343</v>
+        <v>46161.67864644676</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>195</v>
@@ -7056,11 +7056,11 @@
         <v>268</v>
       </c>
       <c r="B91" s="9">
-        <v>46161.58296773148</v>
+        <v>46161.41630106482</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46161.84531243055</v>
+        <v>46161.67864576389</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>195</v>
@@ -7109,11 +7109,11 @@
         <v>269</v>
       </c>
       <c r="B92" s="5">
-        <v>46161.581053761576</v>
+        <v>46161.414387094905</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46161.84552644676</v>
+        <v>46161.67885978009</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>270</v>
@@ -7172,11 +7172,11 @@
         <v>271</v>
       </c>
       <c r="B93" s="9">
-        <v>46161.58105741898</v>
+        <v>46161.41439075231</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46161.845511736115</v>
+        <v>46161.678845069444</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>195</v>
@@ -7225,11 +7225,11 @@
         <v>273</v>
       </c>
       <c r="B94" s="5">
-        <v>46161.583039942125</v>
+        <v>46161.41637327547</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46161.84550880787</v>
+        <v>46161.678842141206</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>195</v>
@@ -7278,11 +7278,11 @@
         <v>274</v>
       </c>
       <c r="B95" s="9">
-        <v>46161.58305715278</v>
+        <v>46161.41639048611</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46161.845505324076</v>
+        <v>46161.678838657404</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>195</v>
@@ -7331,11 +7331,11 @@
         <v>275</v>
       </c>
       <c r="B96" s="5">
-        <v>46161.583076689814</v>
+        <v>46161.41641002314</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46161.84550258102</v>
+        <v>46161.678835914354</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>195</v>
@@ -7384,11 +7384,11 @@
         <v>276</v>
       </c>
       <c r="B97" s="9">
-        <v>46161.58308886574</v>
+        <v>46161.41642219907</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46161.84549928241</v>
+        <v>46161.67883261574</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>195</v>
@@ -7437,11 +7437,11 @@
         <v>277</v>
       </c>
       <c r="B98" s="5">
-        <v>46161.58310019676</v>
+        <v>46161.41643353009</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46161.84549533565</v>
+        <v>46161.678828668984</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>195</v>
@@ -7490,11 +7490,11 @@
         <v>278</v>
       </c>
       <c r="B99" s="9">
-        <v>46161.5831108912</v>
+        <v>46161.41644422454</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46161.84549206018</v>
+        <v>46161.67882539352</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>195</v>
@@ -7543,11 +7543,11 @@
         <v>279</v>
       </c>
       <c r="B100" s="5">
-        <v>46161.58312844907</v>
+        <v>46161.416461782406</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46161.84548887731</v>
+        <v>46161.67882221065</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>195</v>
@@ -7596,11 +7596,11 @@
         <v>280</v>
       </c>
       <c r="B101" s="9">
-        <v>46161.58300775463</v>
+        <v>46161.41634108796</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46161.84548230324</v>
+        <v>46161.67881563657</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>195</v>
@@ -7649,11 +7649,11 @@
         <v>281</v>
       </c>
       <c r="B102" s="5">
-        <v>46161.639501875004</v>
+        <v>46161.47283520833</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46161.845481620374</v>
+        <v>46161.6788149537</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>195</v>
@@ -7702,11 +7702,11 @@
         <v>282</v>
       </c>
       <c r="B103" s="9">
-        <v>46161.58110506945</v>
+        <v>46161.414438402775</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46161.80776861111</v>
+        <v>46161.64110194445</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>209</v>
@@ -7749,11 +7749,11 @@
         <v>284</v>
       </c>
       <c r="B104" s="5">
-        <v>46161.581108530096</v>
+        <v>46161.414441863424</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46176.18811300926</v>
+        <v>46176.021446342595</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>285</v>
@@ -7812,11 +7812,11 @@
         <v>287</v>
       </c>
       <c r="B105" s="9">
-        <v>46161.58111370371</v>
+        <v>46161.41444703704</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46161.84560915509</v>
+        <v>46161.67894248843</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>288</v>
@@ -7875,11 +7875,11 @@
         <v>290</v>
       </c>
       <c r="B106" s="5">
-        <v>46161.581118449074</v>
+        <v>46161.4144517824</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46161.84560644676</v>
+        <v>46161.67893978009</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>291</v>
@@ -7938,11 +7938,11 @@
         <v>293</v>
       </c>
       <c r="B107" s="9">
-        <v>46161.58112311343</v>
+        <v>46161.41445644676</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46161.84560210648</v>
+        <v>46161.67893543981</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>294</v>
@@ -8001,11 +8001,11 @@
         <v>296</v>
       </c>
       <c r="B108" s="5">
-        <v>46161.58112702546</v>
+        <v>46161.41446035879</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46161.83387362269</v>
+        <v>46161.667206956015</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>297</v>
@@ -8048,11 +8048,11 @@
         <v>299</v>
       </c>
       <c r="B109" s="9">
-        <v>46161.58112984954</v>
+        <v>46161.41446318287</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46161.84578230324</v>
+        <v>46161.67911563657</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>300</v>
@@ -8111,11 +8111,11 @@
         <v>302</v>
       </c>
       <c r="B110" s="5">
-        <v>46161.581135555556</v>
+        <v>46161.41446888889</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46161.84577694444</v>
+        <v>46161.67911027778</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>303</v>
@@ -8164,11 +8164,11 @@
         <v>304</v>
       </c>
       <c r="B111" s="9">
-        <v>46161.58317730324</v>
+        <v>46161.41651063657</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46161.84577366898</v>
+        <v>46161.67910700232</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>195</v>
@@ -8217,11 +8217,11 @@
         <v>305</v>
       </c>
       <c r="B112" s="5">
-        <v>46161.58318758102</v>
+        <v>46161.416520914354</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46161.845770879634</v>
+        <v>46161.67910421296</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>195</v>
@@ -8270,11 +8270,11 @@
         <v>306</v>
       </c>
       <c r="B113" s="9">
-        <v>46161.5831975926</v>
+        <v>46161.416530925926</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46161.84576709491</v>
+        <v>46161.67910042824</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>195</v>
@@ -8323,11 +8323,11 @@
         <v>307</v>
       </c>
       <c r="B114" s="5">
-        <v>46161.58320657407</v>
+        <v>46161.41653990741</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46161.84576415509</v>
+        <v>46161.67909748842</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>195</v>
@@ -8376,11 +8376,11 @@
         <v>308</v>
       </c>
       <c r="B115" s="9">
-        <v>46161.58322151621</v>
+        <v>46161.41655484954</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46161.84576082176</v>
+        <v>46161.67909415509</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>195</v>
@@ -8429,11 +8429,11 @@
         <v>309</v>
       </c>
       <c r="B116" s="5">
-        <v>46161.58322717593</v>
+        <v>46161.41656050926</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46161.84575040509</v>
+        <v>46161.679083738425</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>195</v>
@@ -8482,11 +8482,11 @@
         <v>310</v>
       </c>
       <c r="B117" s="9">
-        <v>46161.58324248843</v>
+        <v>46161.41657582176</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46161.84574967592</v>
+        <v>46161.67908300926</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>195</v>
@@ -8535,11 +8535,11 @@
         <v>311</v>
       </c>
       <c r="B118" s="5">
-        <v>46161.58325402778</v>
+        <v>46161.41658736111</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46161.845748946755</v>
+        <v>46161.6790822801</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>195</v>
@@ -8588,11 +8588,11 @@
         <v>312</v>
       </c>
       <c r="B119" s="9">
-        <v>46161.58326291667</v>
+        <v>46161.41659625</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46161.84574821759</v>
+        <v>46161.67908155093</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>195</v>
@@ -8641,11 +8641,11 @@
         <v>313</v>
       </c>
       <c r="B120" s="5">
-        <v>46161.58113928241</v>
+        <v>46161.41447261574</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46161.845971400464</v>
+        <v>46161.6793047338</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>314</v>
@@ -8704,11 +8704,11 @@
         <v>315</v>
       </c>
       <c r="B121" s="9">
-        <v>46161.58114282407</v>
+        <v>46161.414476157406</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46161.845958969905</v>
+        <v>46161.67929230324</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>195</v>
@@ -8757,11 +8757,11 @@
         <v>318</v>
       </c>
       <c r="B122" s="5">
-        <v>46161.585882430554</v>
+        <v>46161.41921576389</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46161.845956122685</v>
+        <v>46161.67928945602</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>195</v>
@@ -8810,11 +8810,11 @@
         <v>320</v>
       </c>
       <c r="B123" s="9">
-        <v>46161.58590298611</v>
+        <v>46161.419236319445</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46161.84595341435</v>
+        <v>46161.67928674769</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>195</v>
@@ -8863,11 +8863,11 @@
         <v>322</v>
       </c>
       <c r="B124" s="5">
-        <v>46161.585919861114</v>
+        <v>46161.41925319444</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46161.84595043982</v>
+        <v>46161.67928377315</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>195</v>
@@ -8916,11 +8916,11 @@
         <v>323</v>
       </c>
       <c r="B125" s="9">
-        <v>46161.585927175925</v>
+        <v>46161.419260509254</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46161.84594708333</v>
+        <v>46161.67928041666</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>195</v>
@@ -8969,11 +8969,11 @@
         <v>324</v>
       </c>
       <c r="B126" s="5">
-        <v>46161.58593310185</v>
+        <v>46161.41926643519</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46161.845944189816</v>
+        <v>46161.679277523144</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>195</v>
@@ -9022,11 +9022,11 @@
         <v>326</v>
       </c>
       <c r="B127" s="9">
-        <v>46161.58593739584</v>
+        <v>46161.419270729166</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46161.8459415625</v>
+        <v>46161.67927489583</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>195</v>
@@ -9075,11 +9075,11 @@
         <v>327</v>
       </c>
       <c r="B128" s="5">
-        <v>46161.58594590278</v>
+        <v>46161.419279236114</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46161.84593365741</v>
+        <v>46161.679266990745</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>195</v>
@@ -9128,11 +9128,11 @@
         <v>328</v>
       </c>
       <c r="B129" s="9">
-        <v>46161.5859562963</v>
+        <v>46161.41928962963</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46161.84593283565</v>
+        <v>46161.67926616898</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>195</v>
@@ -9181,11 +9181,11 @@
         <v>329</v>
       </c>
       <c r="B130" s="5">
-        <v>46161.58618912037</v>
+        <v>46161.4195224537</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46161.84593203704</v>
+        <v>46161.679265370374</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>195</v>
@@ -9234,11 +9234,11 @@
         <v>331</v>
       </c>
       <c r="B131" s="9">
-        <v>46161.58114761574</v>
+        <v>46161.414480949075</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46161.8461249074</v>
+        <v>46161.679458240746</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>332</v>
@@ -9297,11 +9297,11 @@
         <v>333</v>
       </c>
       <c r="B132" s="5">
-        <v>46161.58115116898</v>
+        <v>46161.41448450231</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46161.8461116088</v>
+        <v>46161.67944494213</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>195</v>
@@ -9350,11 +9350,11 @@
         <v>336</v>
       </c>
       <c r="B133" s="9">
-        <v>46161.58603712963</v>
+        <v>46161.41937046296</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46161.84610825231</v>
+        <v>46161.67944158565</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>195</v>
@@ -9403,11 +9403,11 @@
         <v>337</v>
       </c>
       <c r="B134" s="5">
-        <v>46161.586044930555</v>
+        <v>46161.41937826389</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46161.84610548611</v>
+        <v>46161.67943881944</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>195</v>
@@ -9456,11 +9456,11 @@
         <v>339</v>
       </c>
       <c r="B135" s="9">
-        <v>46161.58605891204</v>
+        <v>46161.41939224537</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46161.84610232639</v>
+        <v>46161.679435659724</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>195</v>
@@ -9509,11 +9509,11 @@
         <v>340</v>
       </c>
       <c r="B136" s="5">
-        <v>46161.58606768519</v>
+        <v>46161.41940101852</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46161.84609929398</v>
+        <v>46161.679432627316</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>195</v>
@@ -9562,11 +9562,11 @@
         <v>342</v>
       </c>
       <c r="B137" s="9">
-        <v>46161.58607575232</v>
+        <v>46161.41940908565</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46161.84609641204</v>
+        <v>46161.679429745374</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>195</v>
@@ -9615,11 +9615,11 @@
         <v>343</v>
       </c>
       <c r="B138" s="5">
-        <v>46161.586088854165</v>
+        <v>46161.4194221875</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46161.84609388889</v>
+        <v>46161.67942722222</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>195</v>
@@ -9668,11 +9668,11 @@
         <v>344</v>
       </c>
       <c r="B139" s="9">
-        <v>46161.58609570602</v>
+        <v>46161.41942903935</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46161.84608592592</v>
+        <v>46161.679419259264</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>195</v>
@@ -9721,11 +9721,11 @@
         <v>346</v>
       </c>
       <c r="B140" s="5">
-        <v>46161.586110578704</v>
+        <v>46161.41944391203</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46161.84608520834</v>
+        <v>46161.679418541666</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>195</v>
@@ -9774,11 +9774,11 @@
         <v>347</v>
       </c>
       <c r="B141" s="9">
-        <v>46161.58612255787</v>
+        <v>46161.4194558912</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46161.84608447917</v>
+        <v>46161.6794178125</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>195</v>
@@ -9827,11 +9827,11 @@
         <v>348</v>
       </c>
       <c r="B142" s="5">
-        <v>46161.58115643519</v>
+        <v>46161.41448976852</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46161.84629616898</v>
+        <v>46161.679629502316</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>349</v>
@@ -9890,11 +9890,11 @@
         <v>350</v>
       </c>
       <c r="B143" s="9">
-        <v>46161.58115993056</v>
+        <v>46161.41449326389</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46161.8462891088</v>
+        <v>46161.67962244213</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>303</v>
@@ -9943,11 +9943,11 @@
         <v>353</v>
       </c>
       <c r="B144" s="5">
-        <v>46161.58622641204</v>
+        <v>46161.419559745365</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46161.84628587963</v>
+        <v>46161.67961921296</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>195</v>
@@ -9996,11 +9996,11 @@
         <v>354</v>
       </c>
       <c r="B145" s="9">
-        <v>46161.586235995375</v>
+        <v>46161.419569328704</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46161.84628291667</v>
+        <v>46161.679616249996</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>195</v>
@@ -10049,11 +10049,11 @@
         <v>355</v>
       </c>
       <c r="B146" s="5">
-        <v>46161.586246770836</v>
+        <v>46161.419580104164</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46161.846280046295</v>
+        <v>46161.67961337963</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>195</v>
@@ -10102,11 +10102,11 @@
         <v>357</v>
       </c>
       <c r="B147" s="9">
-        <v>46161.586256435185</v>
+        <v>46161.41958976851</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46161.84627699074</v>
+        <v>46161.67961032408</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>195</v>
@@ -10155,11 +10155,11 @@
         <v>359</v>
       </c>
       <c r="B148" s="5">
-        <v>46161.586265833335</v>
+        <v>46161.419599166664</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46161.84627394676</v>
+        <v>46161.67960728009</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>195</v>
@@ -10208,11 +10208,11 @@
         <v>360</v>
       </c>
       <c r="B149" s="9">
-        <v>46161.586275671296</v>
+        <v>46161.41960900463</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46161.84627113426</v>
+        <v>46161.679604467594</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>195</v>
@@ -10261,11 +10261,11 @@
         <v>361</v>
       </c>
       <c r="B150" s="5">
-        <v>46161.58629186342</v>
+        <v>46161.41962519676</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46161.846268402776</v>
+        <v>46161.67960173611</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>195</v>
@@ -10314,11 +10314,11 @@
         <v>362</v>
       </c>
       <c r="B151" s="9">
-        <v>46161.58630879629</v>
+        <v>46161.41964212963</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46161.84626222222</v>
+        <v>46161.67959555556</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>195</v>
@@ -10367,11 +10367,11 @@
         <v>363</v>
       </c>
       <c r="B152" s="5">
-        <v>46161.58632163194</v>
+        <v>46161.41965496528</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46161.84626162037</v>
+        <v>46161.679594953705</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>195</v>
@@ -10420,11 +10420,11 @@
         <v>364</v>
       </c>
       <c r="B153" s="9">
-        <v>46161.5811646875</v>
+        <v>46161.41449802084</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46161.84643925926</v>
+        <v>46161.67977259259</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>365</v>
@@ -10483,11 +10483,11 @@
         <v>366</v>
       </c>
       <c r="B154" s="5">
-        <v>46161.58116828704</v>
+        <v>46161.41450162037</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46161.84644222222</v>
+        <v>46161.67977555556</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>195</v>
@@ -10534,11 +10534,11 @@
         <v>368</v>
       </c>
       <c r="B155" s="9">
-        <v>46161.63912622685</v>
+        <v>46161.47245956019</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46161.84643929398</v>
+        <v>46161.679772627314</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>195</v>
@@ -10585,11 +10585,11 @@
         <v>369</v>
       </c>
       <c r="B156" s="5">
-        <v>46161.63913737268</v>
+        <v>46161.47247070602</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46161.84643643518</v>
+        <v>46161.67976976852</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>195</v>
@@ -10636,11 +10636,11 @@
         <v>370</v>
       </c>
       <c r="B157" s="9">
-        <v>46161.63914719908</v>
+        <v>46161.47248053241</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46161.846433321756</v>
+        <v>46161.67976665509</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>195</v>
@@ -10687,11 +10687,11 @@
         <v>371</v>
       </c>
       <c r="B158" s="5">
-        <v>46161.639157557875</v>
+        <v>46161.4724908912</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46161.84643013889</v>
+        <v>46161.67976347222</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>195</v>
@@ -10738,11 +10738,11 @@
         <v>372</v>
       </c>
       <c r="B159" s="9">
-        <v>46161.6391721875</v>
+        <v>46161.47250552083</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46161.84642646991</v>
+        <v>46161.67975980324</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>195</v>
@@ -10789,11 +10789,11 @@
         <v>373</v>
       </c>
       <c r="B160" s="5">
-        <v>46161.639187395835</v>
+        <v>46161.47252072916</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46161.84642321759</v>
+        <v>46161.679756550926</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>195</v>
@@ -10840,11 +10840,11 @@
         <v>374</v>
       </c>
       <c r="B161" s="9">
-        <v>46161.639195289354</v>
+        <v>46161.47252862269</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46161.846420138885</v>
+        <v>46161.67975347222</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>195</v>
@@ -10891,11 +10891,11 @@
         <v>375</v>
       </c>
       <c r="B162" s="5">
-        <v>46161.63920550926</v>
+        <v>46161.472538842594</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46161.846413113424</v>
+        <v>46161.67974644676</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>195</v>
@@ -10942,11 +10942,11 @@
         <v>376</v>
       </c>
       <c r="B163" s="9">
-        <v>46161.63921432871</v>
+        <v>46161.47254766204</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46161.84641241898</v>
+        <v>46161.67974575231</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>195</v>
@@ -10993,11 +10993,11 @@
         <v>377</v>
       </c>
       <c r="B164" s="5">
-        <v>46161.58117752315</v>
+        <v>46161.414510856484</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46161.84660503472</v>
+        <v>46161.679938368055</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>378</v>
@@ -11056,11 +11056,11 @@
         <v>380</v>
       </c>
       <c r="B165" s="9">
-        <v>46161.58118137732</v>
+        <v>46161.41451471065</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46161.84658016203</v>
+        <v>46161.67991349537</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>195</v>
@@ -11109,11 +11109,11 @@
         <v>382</v>
       </c>
       <c r="B166" s="5">
-        <v>46161.639253761576</v>
+        <v>46161.472587094904</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46161.846577187505</v>
+        <v>46161.679910520834</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>195</v>
@@ -11162,11 +11162,11 @@
         <v>383</v>
       </c>
       <c r="B167" s="9">
-        <v>46161.63928710648</v>
+        <v>46161.47262043982</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46161.84657417824</v>
+        <v>46161.67990751157</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>195</v>
@@ -11215,11 +11215,11 @@
         <v>384</v>
       </c>
       <c r="B168" s="5">
-        <v>46161.63929736111</v>
+        <v>46161.47263069444</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46161.84657136574</v>
+        <v>46161.67990469908</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>195</v>
@@ -11268,11 +11268,11 @@
         <v>385</v>
       </c>
       <c r="B169" s="9">
-        <v>46161.6393071412</v>
+        <v>46161.47264047454</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46161.84656841435</v>
+        <v>46161.67990174769</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>195</v>
@@ -11321,11 +11321,11 @@
         <v>386</v>
       </c>
       <c r="B170" s="5">
-        <v>46161.639315625</v>
+        <v>46161.47264895833</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46161.84656539352</v>
+        <v>46161.679898726856</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>195</v>
@@ -11374,11 +11374,11 @@
         <v>387</v>
       </c>
       <c r="B171" s="9">
-        <v>46161.63932686343</v>
+        <v>46161.472660196756</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46161.846562754625</v>
+        <v>46161.67989608797</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>195</v>
@@ -11427,11 +11427,11 @@
         <v>388</v>
       </c>
       <c r="B172" s="5">
-        <v>46161.63933708333</v>
+        <v>46161.47267041667</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46161.8465599537</v>
+        <v>46161.67989328704</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>195</v>
@@ -11480,11 +11480,11 @@
         <v>389</v>
       </c>
       <c r="B173" s="9">
-        <v>46161.63935484954</v>
+        <v>46161.47268818287</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46161.846553807874</v>
+        <v>46161.6798871412</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>195</v>
@@ -11533,11 +11533,11 @@
         <v>390</v>
       </c>
       <c r="B174" s="5">
-        <v>46161.63936453704</v>
+        <v>46161.47269787037</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46161.84655313657</v>
+        <v>46161.67988646991</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>195</v>
@@ -11586,11 +11586,11 @@
         <v>391</v>
       </c>
       <c r="B175" s="9">
-        <v>46161.5811852662</v>
+        <v>46161.41451859954</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46161.84092732639</v>
+        <v>46161.674260659725</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>392</v>
@@ -11633,11 +11633,11 @@
         <v>394</v>
       </c>
       <c r="B176" s="5">
-        <v>46161.581188020835</v>
+        <v>46161.41452135416</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46161.84675815972</v>
+        <v>46161.68009149306</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>395</v>
@@ -11696,11 +11696,11 @@
         <v>398</v>
       </c>
       <c r="B177" s="9">
-        <v>46161.581192673606</v>
+        <v>46161.41452600695</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46161.846749351855</v>
+        <v>46161.68008268518</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>195</v>
@@ -11749,11 +11749,11 @@
         <v>400</v>
       </c>
       <c r="B178" s="5">
-        <v>46161.63982708333</v>
+        <v>46161.473160416666</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46161.84674655093</v>
+        <v>46161.68007988426</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>195</v>
@@ -11802,11 +11802,11 @@
         <v>401</v>
       </c>
       <c r="B179" s="9">
-        <v>46161.63983532407</v>
+        <v>46161.47316865741</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46161.846743981485</v>
+        <v>46161.68007731481</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>195</v>
@@ -11855,11 +11855,11 @@
         <v>402</v>
       </c>
       <c r="B180" s="5">
-        <v>46161.63984421296</v>
+        <v>46161.4731775463</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46161.84674143518</v>
+        <v>46161.68007476852</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>195</v>
@@ -11908,11 +11908,11 @@
         <v>403</v>
       </c>
       <c r="B181" s="9">
-        <v>46161.63985878472</v>
+        <v>46161.47319211806</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46161.846738541666</v>
+        <v>46161.680071875</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>195</v>
@@ -11961,11 +11961,11 @@
         <v>404</v>
       </c>
       <c r="B182" s="5">
-        <v>46161.63986780093</v>
+        <v>46161.47320113426</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46161.84673559028</v>
+        <v>46161.68006892361</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>195</v>
@@ -12014,11 +12014,11 @@
         <v>405</v>
       </c>
       <c r="B183" s="9">
-        <v>46161.639875</v>
+        <v>46161.47320833334</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46161.84673289352</v>
+        <v>46161.68006622685</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>195</v>
@@ -12067,11 +12067,11 @@
         <v>406</v>
       </c>
       <c r="B184" s="5">
-        <v>46161.63988342593</v>
+        <v>46161.47321675926</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46161.84672489583</v>
+        <v>46161.68005822916</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>195</v>
@@ -12120,11 +12120,11 @@
         <v>407</v>
       </c>
       <c r="B185" s="9">
-        <v>46161.63989143519</v>
+        <v>46161.47322476852</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46161.84672420139</v>
+        <v>46161.68005753472</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>195</v>
@@ -12173,11 +12173,11 @@
         <v>408</v>
       </c>
       <c r="B186" s="5">
-        <v>46161.639899340276</v>
+        <v>46161.47323267361</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46161.84672340278</v>
+        <v>46161.680056736106</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>195</v>
@@ -12226,11 +12226,11 @@
         <v>409</v>
       </c>
       <c r="B187" s="9">
-        <v>46161.5811965162</v>
+        <v>46161.41452984954</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46161.84690181713</v>
+        <v>46161.68023515046</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>410</v>
@@ -12289,11 +12289,11 @@
         <v>411</v>
       </c>
       <c r="B188" s="5">
-        <v>46161.58120002315</v>
+        <v>46161.41453335648</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46161.84690336806</v>
+        <v>46161.68023670139</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>195</v>
@@ -12342,11 +12342,11 @@
         <v>413</v>
       </c>
       <c r="B189" s="9">
-        <v>46161.63993424768</v>
+        <v>46161.47326758102</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46161.84690038195</v>
+        <v>46161.68023371528</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>195</v>
@@ -12395,11 +12395,11 @@
         <v>414</v>
       </c>
       <c r="B190" s="5">
-        <v>46161.6399947801</v>
+        <v>46161.473328113425</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46161.84689746528</v>
+        <v>46161.68023079861</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>195</v>
@@ -12448,11 +12448,11 @@
         <v>415</v>
       </c>
       <c r="B191" s="9">
-        <v>46161.640004444445</v>
+        <v>46161.473337777774</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46161.84689446759</v>
+        <v>46161.68022780093</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>195</v>
@@ -12501,11 +12501,11 @@
         <v>416</v>
       </c>
       <c r="B192" s="5">
-        <v>46161.64001501157</v>
+        <v>46161.47334834491</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46161.84689137731</v>
+        <v>46161.68022471065</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>195</v>
@@ -12554,11 +12554,11 @@
         <v>417</v>
       </c>
       <c r="B193" s="9">
-        <v>46161.640023831016</v>
+        <v>46161.47335716435</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46161.846888796295</v>
+        <v>46161.68022212963</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>195</v>
@@ -12607,11 +12607,11 @@
         <v>418</v>
       </c>
       <c r="B194" s="5">
-        <v>46161.640038310186</v>
+        <v>46161.473371643515</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46161.84688606481</v>
+        <v>46161.68021939815</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>195</v>
@@ -12660,11 +12660,11 @@
         <v>419</v>
       </c>
       <c r="B195" s="9">
-        <v>46161.64004747685</v>
+        <v>46161.47338081019</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46161.846882557875</v>
+        <v>46161.6802158912</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>195</v>
@@ -12713,11 +12713,11 @@
         <v>420</v>
       </c>
       <c r="B196" s="5">
-        <v>46161.64005649305</v>
+        <v>46161.47338982639</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46161.84687957176</v>
+        <v>46161.68021290509</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>195</v>
@@ -12766,11 +12766,11 @@
         <v>421</v>
       </c>
       <c r="B197" s="9">
-        <v>46161.64006346065</v>
+        <v>46161.47339679398</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46161.846870243055</v>
+        <v>46161.68020357639</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>195</v>
@@ -12819,11 +12819,11 @@
         <v>422</v>
       </c>
       <c r="B198" s="5">
-        <v>46161.58120399306</v>
+        <v>46161.41453732639</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46161.84710645833</v>
+        <v>46161.68043979167</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>423</v>
@@ -12880,11 +12880,11 @@
         <v>424</v>
       </c>
       <c r="B199" s="9">
-        <v>46161.58120755787</v>
+        <v>46161.4145408912</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46161.847077812505</v>
+        <v>46161.68041114583</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>195</v>
@@ -12931,11 +12931,11 @@
         <v>426</v>
       </c>
       <c r="B200" s="5">
-        <v>46161.6401252662</v>
+        <v>46161.47345859953</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46161.84707505787</v>
+        <v>46161.6804083912</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>195</v>
@@ -12982,11 +12982,11 @@
         <v>427</v>
       </c>
       <c r="B201" s="9">
-        <v>46161.64014137731</v>
+        <v>46161.47347471065</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46161.847072476856</v>
+        <v>46161.680405810184</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>195</v>
@@ -13033,11 +13033,11 @@
         <v>428</v>
       </c>
       <c r="B202" s="5">
-        <v>46161.64015293981</v>
+        <v>46161.47348627315</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46161.84706930556</v>
+        <v>46161.680402638885</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>195</v>
@@ -13084,11 +13084,11 @@
         <v>429</v>
       </c>
       <c r="B203" s="9">
-        <v>46161.64016740741</v>
+        <v>46161.47350074074</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46161.847066608796</v>
+        <v>46161.680399942124</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>195</v>
@@ -13135,11 +13135,11 @@
         <v>430</v>
       </c>
       <c r="B204" s="5">
-        <v>46161.640203877316</v>
+        <v>46161.47353721065</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46161.84706402778</v>
+        <v>46161.68039736111</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>195</v>
@@ -13186,11 +13186,11 @@
         <v>431</v>
       </c>
       <c r="B205" s="9">
-        <v>46161.64021510417</v>
+        <v>46161.4735484375</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46161.84706112268</v>
+        <v>46161.68039445602</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>195</v>
@@ -13237,11 +13237,11 @@
         <v>432</v>
       </c>
       <c r="B206" s="5">
-        <v>46161.64022702546</v>
+        <v>46161.4735603588</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46161.847053425925</v>
+        <v>46161.68038675926</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>195</v>
@@ -13288,11 +13288,11 @@
         <v>433</v>
       </c>
       <c r="B207" s="9">
-        <v>46161.64023784723</v>
+        <v>46161.473571180555</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46161.8470527662</v>
+        <v>46161.68038609954</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>195</v>
@@ -13339,11 +13339,11 @@
         <v>434</v>
       </c>
       <c r="B208" s="5">
-        <v>46161.64025311342</v>
+        <v>46161.47358644676</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46161.84705210648</v>
+        <v>46161.68038543982</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>195</v>
@@ -13390,11 +13390,11 @@
         <v>435</v>
       </c>
       <c r="B209" s="9">
-        <v>46161.58121466435</v>
+        <v>46161.41454799769</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46161.84730193287</v>
+        <v>46161.6806352662</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>436</v>
@@ -13453,11 +13453,11 @@
         <v>438</v>
       </c>
       <c r="B210" s="5">
-        <v>46161.58125732639</v>
+        <v>46161.414590659726</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46161.84728091436</v>
+        <v>46161.680614247685</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>195</v>
@@ -13504,11 +13504,11 @@
         <v>439</v>
       </c>
       <c r="B211" s="9">
-        <v>46161.640307905094</v>
+        <v>46161.47364123842</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46161.84727769676</v>
+        <v>46161.6806110301</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>195</v>
@@ -13555,11 +13555,11 @@
         <v>440</v>
       </c>
       <c r="B212" s="5">
-        <v>46161.64031635417</v>
+        <v>46161.4736496875</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46161.84727525463</v>
+        <v>46161.680608587965</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>195</v>
@@ -13606,11 +13606,11 @@
         <v>441</v>
       </c>
       <c r="B213" s="9">
-        <v>46161.64032832176</v>
+        <v>46161.473661655094</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46161.84727247685</v>
+        <v>46161.68060581019</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>195</v>
@@ -13657,11 +13657,11 @@
         <v>442</v>
       </c>
       <c r="B214" s="5">
-        <v>46161.640337986115</v>
+        <v>46161.47367131944</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46161.84726945602</v>
+        <v>46161.68060278935</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>195</v>
@@ -13708,11 +13708,11 @@
         <v>443</v>
       </c>
       <c r="B215" s="9">
-        <v>46161.64035862268</v>
+        <v>46161.473691956024</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46161.84726638889</v>
+        <v>46161.680599722225</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>195</v>
@@ -13759,11 +13759,11 @@
         <v>444</v>
       </c>
       <c r="B216" s="5">
-        <v>46161.64036773148</v>
+        <v>46161.47370106481</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46161.84726359954</v>
+        <v>46161.68059693287</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>195</v>
@@ -13810,11 +13810,11 @@
         <v>445</v>
       </c>
       <c r="B217" s="9">
-        <v>46161.64037657407</v>
+        <v>46161.47370990741</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46161.84726060185</v>
+        <v>46161.68059393518</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>195</v>
@@ -13861,11 +13861,11 @@
         <v>446</v>
       </c>
       <c r="B218" s="5">
-        <v>46161.64038473379</v>
+        <v>46161.47371806713</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46161.847254699074</v>
+        <v>46161.68058803241</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>195</v>
@@ -13912,11 +13912,11 @@
         <v>447</v>
       </c>
       <c r="B219" s="9">
-        <v>46161.64039350694</v>
+        <v>46161.47372684028</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46161.8472540625</v>
+        <v>46161.68058739584</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>195</v>
@@ -13963,11 +13963,11 @@
         <v>448</v>
       </c>
       <c r="B220" s="5">
-        <v>46161.581262824075</v>
+        <v>46161.41459615741</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46161.84801045139</v>
+        <v>46161.68134378472</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>449</v>
@@ -14010,11 +14010,11 @@
         <v>451</v>
       </c>
       <c r="B221" s="9">
-        <v>46161.58126615741</v>
+        <v>46161.414599490745</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46161.84764756945</v>
+        <v>46161.680980902776</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>452</v>
@@ -14073,11 +14073,11 @@
         <v>455</v>
       </c>
       <c r="B222" s="5">
-        <v>46161.581270821756</v>
+        <v>46161.41460415509</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46161.848222546294</v>
+        <v>46161.68155587963</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>456</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2087,13 +2087,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46161.41396914352</v>
+        <v>46161.58063581018</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.71184347222</v>
+        <v>46175.87851013889</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.71185716435</v>
+        <v>46175.87852383102</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2140,13 +2140,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46161.41407934028</v>
+        <v>46161.58074600695</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.71181634259</v>
+        <v>46175.87848300926</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.71184372685</v>
+        <v>46175.87851039352</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2203,13 +2203,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46161.414082407406</v>
+        <v>46161.58074907407</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.711817187504</v>
+        <v>46175.87848385416</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.71184388889</v>
+        <v>46175.87851055556</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2266,13 +2266,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46161.41408527778</v>
+        <v>46161.58075194445</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.71181774305</v>
+        <v>46175.878484409724</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.71184383101</v>
+        <v>46175.878510497685</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2329,13 +2329,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46161.414087997684</v>
+        <v>46161.58075466435</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.71181836806</v>
+        <v>46175.87848503472</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.71184425926</v>
+        <v>46175.878510925926</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2392,13 +2392,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46161.41409119213</v>
+        <v>46161.5807578588</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.711819097225</v>
+        <v>46175.87848576389</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.71184429398</v>
+        <v>46175.87851096065</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2455,11 +2455,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46161.413972951384</v>
+        <v>46161.580639618056</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46197.51062247685</v>
+        <v>46197.67728914352</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2502,13 +2502,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46161.41409464121</v>
+        <v>46161.580761307865</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.507599756944</v>
+        <v>46197.67426642361</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.50761637732</v>
+        <v>46197.674283043976</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2567,13 +2567,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46161.4140996412</v>
+        <v>46161.580766307874</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.50841496528</v>
+        <v>46197.67508163194</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.508428807865</v>
+        <v>46197.67509547454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2632,13 +2632,13 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46161.41410475694</v>
+        <v>46161.580771423614</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.51061320602</v>
+        <v>46197.67727987269</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.51062958333</v>
+        <v>46197.677296249996</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2697,11 +2697,11 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46161.414109537036</v>
+        <v>46161.5807762037</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.510631701385</v>
+        <v>46197.67729836806</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2760,11 +2760,11 @@
         <v>70</v>
       </c>
       <c r="B15" s="9">
-        <v>46161.413977372686</v>
+        <v>46161.58064403935</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46197.421934328704</v>
+        <v>46197.58860099537</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>71</v>
@@ -2807,11 +2807,11 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46161.414116875</v>
+        <v>46161.58078354166</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.50761693287</v>
+        <v>46197.67428359954</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2870,11 +2870,11 @@
         <v>76</v>
       </c>
       <c r="B17" s="9">
-        <v>46161.414122013884</v>
+        <v>46161.580788680556</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46197.508435289354</v>
+        <v>46197.67510195602</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>77</v>
@@ -2933,13 +2933,13 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46161.41412696759</v>
+        <v>46161.58079363426</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.42192472222</v>
+        <v>46197.58859138889</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.50843519676</v>
+        <v>46197.675101863424</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2998,11 +2998,11 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46161.41413237268</v>
+        <v>46161.58079903935</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46169.712906643515</v>
+        <v>46169.87957331019</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -3061,11 +3061,11 @@
         <v>90</v>
       </c>
       <c r="B20" s="5">
-        <v>46161.414137071755</v>
+        <v>46161.58080373843</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46169.71291747685</v>
+        <v>46169.87958414352</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>91</v>
@@ -3124,11 +3124,11 @@
         <v>93</v>
       </c>
       <c r="B21" s="9">
-        <v>46161.414140740744</v>
+        <v>46161.58080740741</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46169.71293371527</v>
+        <v>46169.879600381944</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>94</v>
@@ -3187,11 +3187,11 @@
         <v>96</v>
       </c>
       <c r="B22" s="5">
-        <v>46161.41414407408</v>
+        <v>46161.580810740736</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46169.7129465162</v>
+        <v>46169.87961318287</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>97</v>
@@ -3250,11 +3250,11 @@
         <v>99</v>
       </c>
       <c r="B23" s="9">
-        <v>46161.4139812963</v>
+        <v>46161.58064796297</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46161.571204548614</v>
+        <v>46161.73787121528</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -3297,11 +3297,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46161.414148055555</v>
+        <v>46161.58081472223</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.71271201389</v>
+        <v>46169.879378680555</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3360,11 +3360,11 @@
         <v>107</v>
       </c>
       <c r="B25" s="9">
-        <v>46161.414152349535</v>
+        <v>46161.580819016206</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.71297789352</v>
+        <v>46169.879644560184</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>108</v>
@@ -3419,11 +3419,11 @@
         <v>110</v>
       </c>
       <c r="B26" s="5">
-        <v>46161.41415684028</v>
+        <v>46161.58082350694</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.7130025463</v>
+        <v>46169.87966921296</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>111</v>
@@ -3478,11 +3478,11 @@
         <v>113</v>
       </c>
       <c r="B27" s="9">
-        <v>46161.414161574074</v>
+        <v>46161.58082824074</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46192.69200952546</v>
+        <v>46192.85867619213</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>114</v>
@@ -3541,11 +3541,11 @@
         <v>116</v>
       </c>
       <c r="B28" s="5">
-        <v>46161.41416587963</v>
+        <v>46161.5808325463</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46197.42193370371</v>
+        <v>46197.58860037037</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>117</v>
@@ -3600,11 +3600,11 @@
         <v>119</v>
       </c>
       <c r="B29" s="9">
-        <v>46161.41417030092</v>
+        <v>46161.580836967594</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46171.00685518519</v>
+        <v>46171.17352185185</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>120</v>
@@ -3659,11 +3659,11 @@
         <v>122</v>
       </c>
       <c r="B30" s="5">
-        <v>46161.41417498843</v>
+        <v>46161.58084165509</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46192.693660115736</v>
+        <v>46192.86032678241</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>123</v>
@@ -3722,11 +3722,11 @@
         <v>125</v>
       </c>
       <c r="B31" s="9">
-        <v>46161.414179363426</v>
+        <v>46161.58084603009</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46175.00358978009</v>
+        <v>46175.170256446756</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>126</v>
@@ -3781,11 +3781,11 @@
         <v>128</v>
       </c>
       <c r="B32" s="5">
-        <v>46161.414183773144</v>
+        <v>46161.580850439816</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.71309979167</v>
+        <v>46169.87976645833</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>129</v>
@@ -3840,11 +3840,11 @@
         <v>131</v>
       </c>
       <c r="B33" s="9">
-        <v>46161.41418836806</v>
+        <v>46161.58085503472</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.71311195602</v>
+        <v>46169.879778622686</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>132</v>
@@ -3899,11 +3899,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46161.41419274306</v>
+        <v>46161.58085940972</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.71276568287</v>
+        <v>46169.87943234954</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3962,11 +3962,11 @@
         <v>139</v>
       </c>
       <c r="B35" s="9">
-        <v>46161.41419697917</v>
+        <v>46161.58086364584</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.7131435301</v>
+        <v>46169.879810196755</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>140</v>
@@ -4021,11 +4021,11 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46161.41420165509</v>
+        <v>46161.58086832176</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.7131621875</v>
+        <v>46169.879828854166</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -4080,11 +4080,11 @@
         <v>145</v>
       </c>
       <c r="B37" s="9">
-        <v>46161.4142065625</v>
+        <v>46161.58087322916</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.71277699074</v>
+        <v>46169.87944365741</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>146</v>
@@ -4143,11 +4143,11 @@
         <v>148</v>
       </c>
       <c r="B38" s="5">
-        <v>46161.41426435186</v>
+        <v>46161.580931018514</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.713187395835</v>
+        <v>46169.8798540625</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>92</v>
@@ -4196,11 +4196,11 @@
         <v>150</v>
       </c>
       <c r="B39" s="9">
-        <v>46161.41426980324</v>
+        <v>46161.58093646991</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.713198495374</v>
+        <v>46169.87986516204</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>151</v>
@@ -4249,11 +4249,11 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46161.41427443287</v>
+        <v>46161.580941099535</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.71278662037</v>
+        <v>46169.87945328704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>154</v>
@@ -4312,11 +4312,11 @@
         <v>158</v>
       </c>
       <c r="B41" s="9">
-        <v>46161.41427865741</v>
+        <v>46161.58094532407</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.713237442134</v>
+        <v>46169.87990410879</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>98</v>
@@ -4365,11 +4365,11 @@
         <v>160</v>
       </c>
       <c r="B42" s="5">
-        <v>46161.41428331019</v>
+        <v>46161.58094997685</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.713248541666</v>
+        <v>46169.87991520834</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>161</v>
@@ -4418,11 +4418,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46161.4142878125</v>
+        <v>46161.58095447917</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.71326314815</v>
+        <v>46169.879929814815</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4471,11 +4471,11 @@
         <v>167</v>
       </c>
       <c r="B44" s="5">
-        <v>46161.41429076389</v>
+        <v>46161.58095743056</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.712851585646</v>
+        <v>46169.87951825232</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>168</v>
@@ -4534,11 +4534,11 @@
         <v>170</v>
       </c>
       <c r="B45" s="9">
-        <v>46161.41429424769</v>
+        <v>46161.58096091435</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.71330668981</v>
+        <v>46169.87997335648</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>95</v>
@@ -4587,11 +4587,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46161.41429832176</v>
+        <v>46161.580964988425</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.713330983795</v>
+        <v>46169.87999765047</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4640,11 +4640,11 @@
         <v>175</v>
       </c>
       <c r="B47" s="9">
-        <v>46161.41398572917</v>
+        <v>46161.58065239583</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46197.53837108796</v>
+        <v>46197.705037754626</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>176</v>
@@ -4687,13 +4687,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46161.41430311343</v>
+        <v>46161.580969780094</v>
       </c>
       <c r="C48" s="5">
-        <v>46197.538364583335</v>
+        <v>46197.70503125</v>
       </c>
       <c r="D48" s="5">
-        <v>46197.53837978009</v>
+        <v>46197.70504644676</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4752,11 +4752,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46161.414308402775</v>
+        <v>46161.580975069446</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46197.578861354166</v>
+        <v>46197.74552802084</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>184</v>
@@ -4815,11 +4815,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46161.414314340276</v>
+        <v>46161.58098100695</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46161.67788876157</v>
+        <v>46161.84455542824</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>87</v>
@@ -4878,11 +4878,11 @@
         <v>191</v>
       </c>
       <c r="B51" s="9">
-        <v>46161.414324502315</v>
+        <v>46161.58099116899</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46161.678096435186</v>
+        <v>46161.84476310185</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>192</v>
@@ -4941,11 +4941,11 @@
         <v>196</v>
       </c>
       <c r="B52" s="5">
-        <v>46161.41432752315</v>
+        <v>46161.58099418982</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46161.67809940972</v>
+        <v>46161.84476607639</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4992,11 +4992,11 @@
         <v>198</v>
       </c>
       <c r="B53" s="9">
-        <v>46161.47299822917</v>
+        <v>46161.63966489583</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46161.678096805554</v>
+        <v>46161.844763472225</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>195</v>
@@ -5043,11 +5043,11 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46161.473005949076</v>
+        <v>46161.63967261574</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46161.67809402778</v>
+        <v>46161.84476069444</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -5094,11 +5094,11 @@
         <v>201</v>
       </c>
       <c r="B55" s="9">
-        <v>46161.47301722222</v>
+        <v>46161.63968388889</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46161.678091064816</v>
+        <v>46161.84475773148</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>195</v>
@@ -5145,11 +5145,11 @@
         <v>202</v>
       </c>
       <c r="B56" s="5">
-        <v>46161.47302608796</v>
+        <v>46161.63969275463</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46161.67808804398</v>
+        <v>46161.84475471065</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -5196,11 +5196,11 @@
         <v>203</v>
       </c>
       <c r="B57" s="9">
-        <v>46161.47303854166</v>
+        <v>46161.639705208334</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46161.67808508102</v>
+        <v>46161.84475174769</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>195</v>
@@ -5247,11 +5247,11 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46161.47304880787</v>
+        <v>46161.639715474535</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46161.67808196759</v>
+        <v>46161.84474863426</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>195</v>
@@ -5298,11 +5298,11 @@
         <v>205</v>
       </c>
       <c r="B59" s="9">
-        <v>46161.47306012732</v>
+        <v>46161.63972679398</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46161.67807836806</v>
+        <v>46161.84474503472</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>195</v>
@@ -5349,11 +5349,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46161.47307637731</v>
+        <v>46161.63974304398</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46161.67807167824</v>
+        <v>46161.84473834491</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>195</v>
@@ -5400,11 +5400,11 @@
         <v>207</v>
       </c>
       <c r="B61" s="9">
-        <v>46161.47308603009</v>
+        <v>46161.63975269676</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.67807086806</v>
+        <v>46161.84473753472</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>195</v>
@@ -5451,11 +5451,11 @@
         <v>208</v>
       </c>
       <c r="B62" s="5">
-        <v>46161.41433151621</v>
+        <v>46161.58099818287</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46161.629804780096</v>
+        <v>46161.79647144676</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5498,11 +5498,11 @@
         <v>211</v>
       </c>
       <c r="B63" s="9">
-        <v>46161.41433479167</v>
+        <v>46161.58100145833</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.67817583334</v>
+        <v>46161.844842499995</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>212</v>
@@ -5561,11 +5561,11 @@
         <v>216</v>
       </c>
       <c r="B64" s="5">
-        <v>46161.41433947917</v>
+        <v>46161.58100614583</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46161.67825182871</v>
+        <v>46161.84491849537</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>
@@ -5624,11 +5624,11 @@
         <v>220</v>
       </c>
       <c r="B65" s="9">
-        <v>46161.414349722225</v>
+        <v>46161.58101638889</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46161.6781731713</v>
+        <v>46161.84483983796</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>221</v>
@@ -5687,11 +5687,11 @@
         <v>223</v>
       </c>
       <c r="B66" s="5">
-        <v>46161.41435432871</v>
+        <v>46161.58102099537</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46161.67824836806</v>
+        <v>46161.84491503472</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>224</v>
@@ -5750,11 +5750,11 @@
         <v>226</v>
       </c>
       <c r="B67" s="9">
-        <v>46161.414358055554</v>
+        <v>46161.581024722225</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46161.67816927083</v>
+        <v>46161.8448359375</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>227</v>
@@ -5813,11 +5813,11 @@
         <v>229</v>
       </c>
       <c r="B68" s="5">
-        <v>46161.41436197917</v>
+        <v>46161.58102864583</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46161.67824760417</v>
+        <v>46161.844914270834</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5876,11 +5876,11 @@
         <v>231</v>
       </c>
       <c r="B69" s="9">
-        <v>46161.41436540509</v>
+        <v>46161.58103207176</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46161.63111915509</v>
+        <v>46161.797785821764</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>232</v>
@@ -5923,11 +5923,11 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46161.41436790509</v>
+        <v>46161.58103457176</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46161.678511782404</v>
+        <v>46161.845178449075</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>235</v>
@@ -5986,11 +5986,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46161.41437296296</v>
+        <v>46161.58103962963</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46161.67848040509</v>
+        <v>46161.845147071755</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>195</v>
@@ -6039,11 +6039,11 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46161.415345138885</v>
+        <v>46161.582011805556</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46161.678476817135</v>
+        <v>46161.84514348379</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>195</v>
@@ -6092,11 +6092,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46161.415357164355</v>
+        <v>46161.58202383102</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46161.678473657405</v>
+        <v>46161.845140324076</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>195</v>
@@ -6145,11 +6145,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46161.4159959838</v>
+        <v>46161.582662650464</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46161.67846998843</v>
+        <v>46161.845136655094</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>195</v>
@@ -6198,11 +6198,11 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46161.416006562504</v>
+        <v>46161.58267322917</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46161.67846685185</v>
+        <v>46161.845133518524</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>195</v>
@@ -6251,11 +6251,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46161.41603467593</v>
+        <v>46161.58270134259</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46161.67846407407</v>
+        <v>46161.84513074074</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>195</v>
@@ -6304,11 +6304,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46161.416047604165</v>
+        <v>46161.58271427083</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46161.67846136574</v>
+        <v>46161.84512803241</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>195</v>
@@ -6357,11 +6357,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46161.41605984954</v>
+        <v>46161.58272651621</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46161.67845740741</v>
+        <v>46161.84512407407</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>195</v>
@@ -6410,11 +6410,11 @@
         <v>252</v>
       </c>
       <c r="B79" s="9">
-        <v>46161.416112962965</v>
+        <v>46161.58277962963</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46161.67845125</v>
+        <v>46161.845117916666</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>195</v>
@@ -6463,11 +6463,11 @@
         <v>254</v>
       </c>
       <c r="B80" s="5">
-        <v>46161.4161237963</v>
+        <v>46161.58279046296</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46161.67845054399</v>
+        <v>46161.84511721064</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>195</v>
@@ -6516,11 +6516,11 @@
         <v>255</v>
       </c>
       <c r="B81" s="9">
-        <v>46161.41437871528</v>
+        <v>46161.58104538194</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46161.67867814815</v>
+        <v>46161.845344814814</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>256</v>
@@ -6579,11 +6579,11 @@
         <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46161.414382372684</v>
+        <v>46161.58104903935</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46161.67867253472</v>
+        <v>46161.84533920139</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>195</v>
@@ -6632,11 +6632,11 @@
         <v>260</v>
       </c>
       <c r="B83" s="9">
-        <v>46161.4161674537</v>
+        <v>46161.582834120374</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46161.67866961806</v>
+        <v>46161.84533628472</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>195</v>
@@ -6685,11 +6685,11 @@
         <v>261</v>
       </c>
       <c r="B84" s="5">
-        <v>46161.416197928236</v>
+        <v>46161.58286459491</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46161.67866670139</v>
+        <v>46161.84533336805</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>195</v>
@@ -6738,11 +6738,11 @@
         <v>262</v>
       </c>
       <c r="B85" s="9">
-        <v>46161.41620715278</v>
+        <v>46161.58287381944</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46161.67866399305</v>
+        <v>46161.84533065972</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>195</v>
@@ -6791,11 +6791,11 @@
         <v>263</v>
       </c>
       <c r="B86" s="5">
-        <v>46161.416216990736</v>
+        <v>46161.58288365741</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46161.67866123843</v>
+        <v>46161.84532790509</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>195</v>
@@ -6844,11 +6844,11 @@
         <v>264</v>
       </c>
       <c r="B87" s="9">
-        <v>46161.416225891204</v>
+        <v>46161.58289255787</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46161.67865819445</v>
+        <v>46161.84532486111</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>195</v>
@@ -6897,11 +6897,11 @@
         <v>265</v>
       </c>
       <c r="B88" s="5">
-        <v>46161.41625876157</v>
+        <v>46161.58292542824</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46161.67865545139</v>
+        <v>46161.84532211805</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>195</v>
@@ -6950,11 +6950,11 @@
         <v>266</v>
       </c>
       <c r="B89" s="9">
-        <v>46161.41627030092</v>
+        <v>46161.58293696759</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46161.67865260417</v>
+        <v>46161.84531927083</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>195</v>
@@ -7003,11 +7003,11 @@
         <v>267</v>
       </c>
       <c r="B90" s="5">
-        <v>46161.41628615741</v>
+        <v>46161.58295282407</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46161.67864644676</v>
+        <v>46161.84531311343</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>195</v>
@@ -7056,11 +7056,11 @@
         <v>268</v>
       </c>
       <c r="B91" s="9">
-        <v>46161.41630106482</v>
+        <v>46161.58296773148</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46161.67864576389</v>
+        <v>46161.84531243055</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>195</v>
@@ -7109,11 +7109,11 @@
         <v>269</v>
       </c>
       <c r="B92" s="5">
-        <v>46161.414387094905</v>
+        <v>46161.581053761576</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46161.67885978009</v>
+        <v>46161.84552644676</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>270</v>
@@ -7172,11 +7172,11 @@
         <v>271</v>
       </c>
       <c r="B93" s="9">
-        <v>46161.41439075231</v>
+        <v>46161.58105741898</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46161.678845069444</v>
+        <v>46161.845511736115</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>195</v>
@@ -7225,11 +7225,11 @@
         <v>273</v>
       </c>
       <c r="B94" s="5">
-        <v>46161.41637327547</v>
+        <v>46161.583039942125</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46161.678842141206</v>
+        <v>46161.84550880787</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>195</v>
@@ -7278,11 +7278,11 @@
         <v>274</v>
       </c>
       <c r="B95" s="9">
-        <v>46161.41639048611</v>
+        <v>46161.58305715278</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46161.678838657404</v>
+        <v>46161.845505324076</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>195</v>
@@ -7331,11 +7331,11 @@
         <v>275</v>
       </c>
       <c r="B96" s="5">
-        <v>46161.41641002314</v>
+        <v>46161.583076689814</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46161.678835914354</v>
+        <v>46161.84550258102</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>195</v>
@@ -7384,11 +7384,11 @@
         <v>276</v>
       </c>
       <c r="B97" s="9">
-        <v>46161.41642219907</v>
+        <v>46161.58308886574</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46161.67883261574</v>
+        <v>46161.84549928241</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>195</v>
@@ -7437,11 +7437,11 @@
         <v>277</v>
       </c>
       <c r="B98" s="5">
-        <v>46161.41643353009</v>
+        <v>46161.58310019676</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46161.678828668984</v>
+        <v>46161.84549533565</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>195</v>
@@ -7490,11 +7490,11 @@
         <v>278</v>
       </c>
       <c r="B99" s="9">
-        <v>46161.41644422454</v>
+        <v>46161.5831108912</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46161.67882539352</v>
+        <v>46161.84549206018</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>195</v>
@@ -7543,11 +7543,11 @@
         <v>279</v>
       </c>
       <c r="B100" s="5">
-        <v>46161.416461782406</v>
+        <v>46161.58312844907</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46161.67882221065</v>
+        <v>46161.84548887731</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>195</v>
@@ -7596,11 +7596,11 @@
         <v>280</v>
       </c>
       <c r="B101" s="9">
-        <v>46161.41634108796</v>
+        <v>46161.58300775463</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46161.67881563657</v>
+        <v>46161.84548230324</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>195</v>
@@ -7649,11 +7649,11 @@
         <v>281</v>
       </c>
       <c r="B102" s="5">
-        <v>46161.47283520833</v>
+        <v>46161.639501875004</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46161.6788149537</v>
+        <v>46161.845481620374</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>195</v>
@@ -7702,11 +7702,11 @@
         <v>282</v>
       </c>
       <c r="B103" s="9">
-        <v>46161.414438402775</v>
+        <v>46161.58110506945</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46161.64110194445</v>
+        <v>46161.80776861111</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>209</v>
@@ -7749,11 +7749,11 @@
         <v>284</v>
       </c>
       <c r="B104" s="5">
-        <v>46161.414441863424</v>
+        <v>46161.581108530096</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46176.021446342595</v>
+        <v>46176.18811300926</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>285</v>
@@ -7812,11 +7812,11 @@
         <v>287</v>
       </c>
       <c r="B105" s="9">
-        <v>46161.41444703704</v>
+        <v>46161.58111370371</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46161.67894248843</v>
+        <v>46161.84560915509</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>288</v>
@@ -7875,11 +7875,11 @@
         <v>290</v>
       </c>
       <c r="B106" s="5">
-        <v>46161.4144517824</v>
+        <v>46161.581118449074</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46161.67893978009</v>
+        <v>46161.84560644676</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>291</v>
@@ -7938,11 +7938,11 @@
         <v>293</v>
       </c>
       <c r="B107" s="9">
-        <v>46161.41445644676</v>
+        <v>46161.58112311343</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46161.67893543981</v>
+        <v>46161.84560210648</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>294</v>
@@ -8001,11 +8001,11 @@
         <v>296</v>
       </c>
       <c r="B108" s="5">
-        <v>46161.41446035879</v>
+        <v>46161.58112702546</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46161.667206956015</v>
+        <v>46161.83387362269</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>297</v>
@@ -8048,11 +8048,11 @@
         <v>299</v>
       </c>
       <c r="B109" s="9">
-        <v>46161.41446318287</v>
+        <v>46161.58112984954</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46161.67911563657</v>
+        <v>46161.84578230324</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>300</v>
@@ -8111,11 +8111,11 @@
         <v>302</v>
       </c>
       <c r="B110" s="5">
-        <v>46161.41446888889</v>
+        <v>46161.581135555556</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46161.67911027778</v>
+        <v>46161.84577694444</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>303</v>
@@ -8164,11 +8164,11 @@
         <v>304</v>
       </c>
       <c r="B111" s="9">
-        <v>46161.41651063657</v>
+        <v>46161.58317730324</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46161.67910700232</v>
+        <v>46161.84577366898</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>195</v>
@@ -8217,11 +8217,11 @@
         <v>305</v>
       </c>
       <c r="B112" s="5">
-        <v>46161.416520914354</v>
+        <v>46161.58318758102</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46161.67910421296</v>
+        <v>46161.845770879634</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>195</v>
@@ -8270,11 +8270,11 @@
         <v>306</v>
       </c>
       <c r="B113" s="9">
-        <v>46161.416530925926</v>
+        <v>46161.5831975926</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46161.67910042824</v>
+        <v>46161.84576709491</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>195</v>
@@ -8323,11 +8323,11 @@
         <v>307</v>
       </c>
       <c r="B114" s="5">
-        <v>46161.41653990741</v>
+        <v>46161.58320657407</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46161.67909748842</v>
+        <v>46161.84576415509</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>195</v>
@@ -8376,11 +8376,11 @@
         <v>308</v>
       </c>
       <c r="B115" s="9">
-        <v>46161.41655484954</v>
+        <v>46161.58322151621</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46161.67909415509</v>
+        <v>46161.84576082176</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>195</v>
@@ -8429,11 +8429,11 @@
         <v>309</v>
       </c>
       <c r="B116" s="5">
-        <v>46161.41656050926</v>
+        <v>46161.58322717593</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46161.679083738425</v>
+        <v>46161.84575040509</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>195</v>
@@ -8482,11 +8482,11 @@
         <v>310</v>
       </c>
       <c r="B117" s="9">
-        <v>46161.41657582176</v>
+        <v>46161.58324248843</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46161.67908300926</v>
+        <v>46161.84574967592</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>195</v>
@@ -8535,11 +8535,11 @@
         <v>311</v>
       </c>
       <c r="B118" s="5">
-        <v>46161.41658736111</v>
+        <v>46161.58325402778</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46161.6790822801</v>
+        <v>46161.845748946755</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>195</v>
@@ -8588,11 +8588,11 @@
         <v>312</v>
       </c>
       <c r="B119" s="9">
-        <v>46161.41659625</v>
+        <v>46161.58326291667</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46161.67908155093</v>
+        <v>46161.84574821759</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>195</v>
@@ -8641,11 +8641,11 @@
         <v>313</v>
       </c>
       <c r="B120" s="5">
-        <v>46161.41447261574</v>
+        <v>46161.58113928241</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46161.6793047338</v>
+        <v>46161.845971400464</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>314</v>
@@ -8704,11 +8704,11 @@
         <v>315</v>
       </c>
       <c r="B121" s="9">
-        <v>46161.414476157406</v>
+        <v>46161.58114282407</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46161.67929230324</v>
+        <v>46161.845958969905</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>195</v>
@@ -8757,11 +8757,11 @@
         <v>318</v>
       </c>
       <c r="B122" s="5">
-        <v>46161.41921576389</v>
+        <v>46161.585882430554</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46161.67928945602</v>
+        <v>46161.845956122685</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>195</v>
@@ -8810,11 +8810,11 @@
         <v>320</v>
       </c>
       <c r="B123" s="9">
-        <v>46161.419236319445</v>
+        <v>46161.58590298611</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46161.67928674769</v>
+        <v>46161.84595341435</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>195</v>
@@ -8863,11 +8863,11 @@
         <v>322</v>
       </c>
       <c r="B124" s="5">
-        <v>46161.41925319444</v>
+        <v>46161.585919861114</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46161.67928377315</v>
+        <v>46161.84595043982</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>195</v>
@@ -8916,11 +8916,11 @@
         <v>323</v>
       </c>
       <c r="B125" s="9">
-        <v>46161.419260509254</v>
+        <v>46161.585927175925</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46161.67928041666</v>
+        <v>46161.84594708333</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>195</v>
@@ -8969,11 +8969,11 @@
         <v>324</v>
       </c>
       <c r="B126" s="5">
-        <v>46161.41926643519</v>
+        <v>46161.58593310185</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46161.679277523144</v>
+        <v>46161.845944189816</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>195</v>
@@ -9022,11 +9022,11 @@
         <v>326</v>
       </c>
       <c r="B127" s="9">
-        <v>46161.419270729166</v>
+        <v>46161.58593739584</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46161.67927489583</v>
+        <v>46161.8459415625</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>195</v>
@@ -9075,11 +9075,11 @@
         <v>327</v>
       </c>
       <c r="B128" s="5">
-        <v>46161.419279236114</v>
+        <v>46161.58594590278</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46161.679266990745</v>
+        <v>46161.84593365741</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>195</v>
@@ -9128,11 +9128,11 @@
         <v>328</v>
       </c>
       <c r="B129" s="9">
-        <v>46161.41928962963</v>
+        <v>46161.5859562963</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46161.67926616898</v>
+        <v>46161.84593283565</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>195</v>
@@ -9181,11 +9181,11 @@
         <v>329</v>
       </c>
       <c r="B130" s="5">
-        <v>46161.4195224537</v>
+        <v>46161.58618912037</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46161.679265370374</v>
+        <v>46161.84593203704</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>195</v>
@@ -9234,11 +9234,11 @@
         <v>331</v>
       </c>
       <c r="B131" s="9">
-        <v>46161.414480949075</v>
+        <v>46161.58114761574</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46161.679458240746</v>
+        <v>46161.8461249074</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>332</v>
@@ -9297,11 +9297,11 @@
         <v>333</v>
       </c>
       <c r="B132" s="5">
-        <v>46161.41448450231</v>
+        <v>46161.58115116898</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46161.67944494213</v>
+        <v>46161.8461116088</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>195</v>
@@ -9350,11 +9350,11 @@
         <v>336</v>
       </c>
       <c r="B133" s="9">
-        <v>46161.41937046296</v>
+        <v>46161.58603712963</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46161.67944158565</v>
+        <v>46161.84610825231</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>195</v>
@@ -9403,11 +9403,11 @@
         <v>337</v>
       </c>
       <c r="B134" s="5">
-        <v>46161.41937826389</v>
+        <v>46161.586044930555</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46161.67943881944</v>
+        <v>46161.84610548611</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>195</v>
@@ -9456,11 +9456,11 @@
         <v>339</v>
       </c>
       <c r="B135" s="9">
-        <v>46161.41939224537</v>
+        <v>46161.58605891204</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46161.679435659724</v>
+        <v>46161.84610232639</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>195</v>
@@ -9509,11 +9509,11 @@
         <v>340</v>
       </c>
       <c r="B136" s="5">
-        <v>46161.41940101852</v>
+        <v>46161.58606768519</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46161.679432627316</v>
+        <v>46161.84609929398</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>195</v>
@@ -9562,11 +9562,11 @@
         <v>342</v>
       </c>
       <c r="B137" s="9">
-        <v>46161.41940908565</v>
+        <v>46161.58607575232</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46161.679429745374</v>
+        <v>46161.84609641204</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>195</v>
@@ -9615,11 +9615,11 @@
         <v>343</v>
       </c>
       <c r="B138" s="5">
-        <v>46161.4194221875</v>
+        <v>46161.586088854165</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46161.67942722222</v>
+        <v>46161.84609388889</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>195</v>
@@ -9668,11 +9668,11 @@
         <v>344</v>
       </c>
       <c r="B139" s="9">
-        <v>46161.41942903935</v>
+        <v>46161.58609570602</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46161.679419259264</v>
+        <v>46161.84608592592</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>195</v>
@@ -9721,11 +9721,11 @@
         <v>346</v>
       </c>
       <c r="B140" s="5">
-        <v>46161.41944391203</v>
+        <v>46161.586110578704</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46161.679418541666</v>
+        <v>46161.84608520834</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>195</v>
@@ -9774,11 +9774,11 @@
         <v>347</v>
       </c>
       <c r="B141" s="9">
-        <v>46161.4194558912</v>
+        <v>46161.58612255787</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46161.6794178125</v>
+        <v>46161.84608447917</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>195</v>
@@ -9827,11 +9827,11 @@
         <v>348</v>
       </c>
       <c r="B142" s="5">
-        <v>46161.41448976852</v>
+        <v>46161.58115643519</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46161.679629502316</v>
+        <v>46161.84629616898</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>349</v>
@@ -9890,11 +9890,11 @@
         <v>350</v>
       </c>
       <c r="B143" s="9">
-        <v>46161.41449326389</v>
+        <v>46161.58115993056</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46161.67962244213</v>
+        <v>46161.8462891088</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>303</v>
@@ -9943,11 +9943,11 @@
         <v>353</v>
       </c>
       <c r="B144" s="5">
-        <v>46161.419559745365</v>
+        <v>46161.58622641204</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46161.67961921296</v>
+        <v>46161.84628587963</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>195</v>
@@ -9996,11 +9996,11 @@
         <v>354</v>
       </c>
       <c r="B145" s="9">
-        <v>46161.419569328704</v>
+        <v>46161.586235995375</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46161.679616249996</v>
+        <v>46161.84628291667</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>195</v>
@@ -10049,11 +10049,11 @@
         <v>355</v>
       </c>
       <c r="B146" s="5">
-        <v>46161.419580104164</v>
+        <v>46161.586246770836</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46161.67961337963</v>
+        <v>46161.846280046295</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>195</v>
@@ -10102,11 +10102,11 @@
         <v>357</v>
       </c>
       <c r="B147" s="9">
-        <v>46161.41958976851</v>
+        <v>46161.586256435185</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46161.67961032408</v>
+        <v>46161.84627699074</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>195</v>
@@ -10155,11 +10155,11 @@
         <v>359</v>
       </c>
       <c r="B148" s="5">
-        <v>46161.419599166664</v>
+        <v>46161.586265833335</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46161.67960728009</v>
+        <v>46161.84627394676</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>195</v>
@@ -10208,11 +10208,11 @@
         <v>360</v>
       </c>
       <c r="B149" s="9">
-        <v>46161.41960900463</v>
+        <v>46161.586275671296</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46161.679604467594</v>
+        <v>46161.84627113426</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>195</v>
@@ -10261,11 +10261,11 @@
         <v>361</v>
       </c>
       <c r="B150" s="5">
-        <v>46161.41962519676</v>
+        <v>46161.58629186342</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46161.67960173611</v>
+        <v>46161.846268402776</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>195</v>
@@ -10314,11 +10314,11 @@
         <v>362</v>
       </c>
       <c r="B151" s="9">
-        <v>46161.41964212963</v>
+        <v>46161.58630879629</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46161.67959555556</v>
+        <v>46161.84626222222</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>195</v>
@@ -10367,11 +10367,11 @@
         <v>363</v>
       </c>
       <c r="B152" s="5">
-        <v>46161.41965496528</v>
+        <v>46161.58632163194</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46161.679594953705</v>
+        <v>46161.84626162037</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>195</v>
@@ -10420,11 +10420,11 @@
         <v>364</v>
       </c>
       <c r="B153" s="9">
-        <v>46161.41449802084</v>
+        <v>46161.5811646875</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46161.67977259259</v>
+        <v>46161.84643925926</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>365</v>
@@ -10483,11 +10483,11 @@
         <v>366</v>
       </c>
       <c r="B154" s="5">
-        <v>46161.41450162037</v>
+        <v>46161.58116828704</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46161.67977555556</v>
+        <v>46161.84644222222</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>195</v>
@@ -10534,11 +10534,11 @@
         <v>368</v>
       </c>
       <c r="B155" s="9">
-        <v>46161.47245956019</v>
+        <v>46161.63912622685</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46161.679772627314</v>
+        <v>46161.84643929398</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>195</v>
@@ -10585,11 +10585,11 @@
         <v>369</v>
       </c>
       <c r="B156" s="5">
-        <v>46161.47247070602</v>
+        <v>46161.63913737268</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46161.67976976852</v>
+        <v>46161.84643643518</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>195</v>
@@ -10636,11 +10636,11 @@
         <v>370</v>
       </c>
       <c r="B157" s="9">
-        <v>46161.47248053241</v>
+        <v>46161.63914719908</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46161.67976665509</v>
+        <v>46161.846433321756</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>195</v>
@@ -10687,11 +10687,11 @@
         <v>371</v>
       </c>
       <c r="B158" s="5">
-        <v>46161.4724908912</v>
+        <v>46161.639157557875</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46161.67976347222</v>
+        <v>46161.84643013889</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>195</v>
@@ -10738,11 +10738,11 @@
         <v>372</v>
       </c>
       <c r="B159" s="9">
-        <v>46161.47250552083</v>
+        <v>46161.6391721875</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46161.67975980324</v>
+        <v>46161.84642646991</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>195</v>
@@ -10789,11 +10789,11 @@
         <v>373</v>
       </c>
       <c r="B160" s="5">
-        <v>46161.47252072916</v>
+        <v>46161.639187395835</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46161.679756550926</v>
+        <v>46161.84642321759</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>195</v>
@@ -10840,11 +10840,11 @@
         <v>374</v>
       </c>
       <c r="B161" s="9">
-        <v>46161.47252862269</v>
+        <v>46161.639195289354</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46161.67975347222</v>
+        <v>46161.846420138885</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>195</v>
@@ -10891,11 +10891,11 @@
         <v>375</v>
       </c>
       <c r="B162" s="5">
-        <v>46161.472538842594</v>
+        <v>46161.63920550926</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46161.67974644676</v>
+        <v>46161.846413113424</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>195</v>
@@ -10942,11 +10942,11 @@
         <v>376</v>
       </c>
       <c r="B163" s="9">
-        <v>46161.47254766204</v>
+        <v>46161.63921432871</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46161.67974575231</v>
+        <v>46161.84641241898</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>195</v>
@@ -10993,11 +10993,11 @@
         <v>377</v>
       </c>
       <c r="B164" s="5">
-        <v>46161.414510856484</v>
+        <v>46161.58117752315</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46161.679938368055</v>
+        <v>46161.84660503472</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>378</v>
@@ -11056,11 +11056,11 @@
         <v>380</v>
       </c>
       <c r="B165" s="9">
-        <v>46161.41451471065</v>
+        <v>46161.58118137732</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46161.67991349537</v>
+        <v>46161.84658016203</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>195</v>
@@ -11109,11 +11109,11 @@
         <v>382</v>
       </c>
       <c r="B166" s="5">
-        <v>46161.472587094904</v>
+        <v>46161.639253761576</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46161.679910520834</v>
+        <v>46161.846577187505</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>195</v>
@@ -11162,11 +11162,11 @@
         <v>383</v>
       </c>
       <c r="B167" s="9">
-        <v>46161.47262043982</v>
+        <v>46161.63928710648</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46161.67990751157</v>
+        <v>46161.84657417824</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>195</v>
@@ -11215,11 +11215,11 @@
         <v>384</v>
       </c>
       <c r="B168" s="5">
-        <v>46161.47263069444</v>
+        <v>46161.63929736111</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46161.67990469908</v>
+        <v>46161.84657136574</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>195</v>
@@ -11268,11 +11268,11 @@
         <v>385</v>
       </c>
       <c r="B169" s="9">
-        <v>46161.47264047454</v>
+        <v>46161.6393071412</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46161.67990174769</v>
+        <v>46161.84656841435</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>195</v>
@@ -11321,11 +11321,11 @@
         <v>386</v>
       </c>
       <c r="B170" s="5">
-        <v>46161.47264895833</v>
+        <v>46161.639315625</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46161.679898726856</v>
+        <v>46161.84656539352</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>195</v>
@@ -11374,11 +11374,11 @@
         <v>387</v>
       </c>
       <c r="B171" s="9">
-        <v>46161.472660196756</v>
+        <v>46161.63932686343</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46161.67989608797</v>
+        <v>46161.846562754625</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>195</v>
@@ -11427,11 +11427,11 @@
         <v>388</v>
       </c>
       <c r="B172" s="5">
-        <v>46161.47267041667</v>
+        <v>46161.63933708333</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46161.67989328704</v>
+        <v>46161.8465599537</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>195</v>
@@ -11480,11 +11480,11 @@
         <v>389</v>
       </c>
       <c r="B173" s="9">
-        <v>46161.47268818287</v>
+        <v>46161.63935484954</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46161.6798871412</v>
+        <v>46161.846553807874</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>195</v>
@@ -11533,11 +11533,11 @@
         <v>390</v>
       </c>
       <c r="B174" s="5">
-        <v>46161.47269787037</v>
+        <v>46161.63936453704</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46161.67988646991</v>
+        <v>46161.84655313657</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>195</v>
@@ -11586,11 +11586,11 @@
         <v>391</v>
       </c>
       <c r="B175" s="9">
-        <v>46161.41451859954</v>
+        <v>46161.5811852662</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46161.674260659725</v>
+        <v>46161.84092732639</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>392</v>
@@ -11633,11 +11633,11 @@
         <v>394</v>
       </c>
       <c r="B176" s="5">
-        <v>46161.41452135416</v>
+        <v>46161.581188020835</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46161.68009149306</v>
+        <v>46161.84675815972</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>395</v>
@@ -11696,11 +11696,11 @@
         <v>398</v>
       </c>
       <c r="B177" s="9">
-        <v>46161.41452600695</v>
+        <v>46161.581192673606</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46161.68008268518</v>
+        <v>46161.846749351855</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>195</v>
@@ -11749,11 +11749,11 @@
         <v>400</v>
       </c>
       <c r="B178" s="5">
-        <v>46161.473160416666</v>
+        <v>46161.63982708333</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46161.68007988426</v>
+        <v>46161.84674655093</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>195</v>
@@ -11802,11 +11802,11 @@
         <v>401</v>
       </c>
       <c r="B179" s="9">
-        <v>46161.47316865741</v>
+        <v>46161.63983532407</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46161.68007731481</v>
+        <v>46161.846743981485</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>195</v>
@@ -11855,11 +11855,11 @@
         <v>402</v>
       </c>
       <c r="B180" s="5">
-        <v>46161.4731775463</v>
+        <v>46161.63984421296</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46161.68007476852</v>
+        <v>46161.84674143518</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>195</v>
@@ -11908,11 +11908,11 @@
         <v>403</v>
       </c>
       <c r="B181" s="9">
-        <v>46161.47319211806</v>
+        <v>46161.63985878472</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46161.680071875</v>
+        <v>46161.846738541666</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>195</v>
@@ -11961,11 +11961,11 @@
         <v>404</v>
       </c>
       <c r="B182" s="5">
-        <v>46161.47320113426</v>
+        <v>46161.63986780093</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46161.68006892361</v>
+        <v>46161.84673559028</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>195</v>
@@ -12014,11 +12014,11 @@
         <v>405</v>
       </c>
       <c r="B183" s="9">
-        <v>46161.47320833334</v>
+        <v>46161.639875</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46161.68006622685</v>
+        <v>46161.84673289352</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>195</v>
@@ -12067,11 +12067,11 @@
         <v>406</v>
       </c>
       <c r="B184" s="5">
-        <v>46161.47321675926</v>
+        <v>46161.63988342593</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46161.68005822916</v>
+        <v>46161.84672489583</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>195</v>
@@ -12120,11 +12120,11 @@
         <v>407</v>
       </c>
       <c r="B185" s="9">
-        <v>46161.47322476852</v>
+        <v>46161.63989143519</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46161.68005753472</v>
+        <v>46161.84672420139</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>195</v>
@@ -12173,11 +12173,11 @@
         <v>408</v>
       </c>
       <c r="B186" s="5">
-        <v>46161.47323267361</v>
+        <v>46161.639899340276</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46161.680056736106</v>
+        <v>46161.84672340278</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>195</v>
@@ -12226,11 +12226,11 @@
         <v>409</v>
       </c>
       <c r="B187" s="9">
-        <v>46161.41452984954</v>
+        <v>46161.5811965162</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46161.68023515046</v>
+        <v>46161.84690181713</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>410</v>
@@ -12289,11 +12289,11 @@
         <v>411</v>
       </c>
       <c r="B188" s="5">
-        <v>46161.41453335648</v>
+        <v>46161.58120002315</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46161.68023670139</v>
+        <v>46161.84690336806</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>195</v>
@@ -12342,11 +12342,11 @@
         <v>413</v>
       </c>
       <c r="B189" s="9">
-        <v>46161.47326758102</v>
+        <v>46161.63993424768</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46161.68023371528</v>
+        <v>46161.84690038195</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>195</v>
@@ -12395,11 +12395,11 @@
         <v>414</v>
       </c>
       <c r="B190" s="5">
-        <v>46161.473328113425</v>
+        <v>46161.6399947801</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46161.68023079861</v>
+        <v>46161.84689746528</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>195</v>
@@ -12448,11 +12448,11 @@
         <v>415</v>
       </c>
       <c r="B191" s="9">
-        <v>46161.473337777774</v>
+        <v>46161.640004444445</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46161.68022780093</v>
+        <v>46161.84689446759</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>195</v>
@@ -12501,11 +12501,11 @@
         <v>416</v>
       </c>
       <c r="B192" s="5">
-        <v>46161.47334834491</v>
+        <v>46161.64001501157</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46161.68022471065</v>
+        <v>46161.84689137731</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>195</v>
@@ -12554,11 +12554,11 @@
         <v>417</v>
       </c>
       <c r="B193" s="9">
-        <v>46161.47335716435</v>
+        <v>46161.640023831016</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46161.68022212963</v>
+        <v>46161.846888796295</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>195</v>
@@ -12607,11 +12607,11 @@
         <v>418</v>
       </c>
       <c r="B194" s="5">
-        <v>46161.473371643515</v>
+        <v>46161.640038310186</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46161.68021939815</v>
+        <v>46161.84688606481</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>195</v>
@@ -12660,11 +12660,11 @@
         <v>419</v>
       </c>
       <c r="B195" s="9">
-        <v>46161.47338081019</v>
+        <v>46161.64004747685</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46161.6802158912</v>
+        <v>46161.846882557875</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>195</v>
@@ -12713,11 +12713,11 @@
         <v>420</v>
       </c>
       <c r="B196" s="5">
-        <v>46161.47338982639</v>
+        <v>46161.64005649305</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46161.68021290509</v>
+        <v>46161.84687957176</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>195</v>
@@ -12766,11 +12766,11 @@
         <v>421</v>
       </c>
       <c r="B197" s="9">
-        <v>46161.47339679398</v>
+        <v>46161.64006346065</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46161.68020357639</v>
+        <v>46161.846870243055</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>195</v>
@@ -12819,11 +12819,11 @@
         <v>422</v>
       </c>
       <c r="B198" s="5">
-        <v>46161.41453732639</v>
+        <v>46161.58120399306</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46161.68043979167</v>
+        <v>46161.84710645833</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>423</v>
@@ -12880,11 +12880,11 @@
         <v>424</v>
       </c>
       <c r="B199" s="9">
-        <v>46161.4145408912</v>
+        <v>46161.58120755787</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46161.68041114583</v>
+        <v>46161.847077812505</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>195</v>
@@ -12931,11 +12931,11 @@
         <v>426</v>
       </c>
       <c r="B200" s="5">
-        <v>46161.47345859953</v>
+        <v>46161.6401252662</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46161.6804083912</v>
+        <v>46161.84707505787</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>195</v>
@@ -12982,11 +12982,11 @@
         <v>427</v>
       </c>
       <c r="B201" s="9">
-        <v>46161.47347471065</v>
+        <v>46161.64014137731</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46161.680405810184</v>
+        <v>46161.847072476856</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>195</v>
@@ -13033,11 +13033,11 @@
         <v>428</v>
       </c>
       <c r="B202" s="5">
-        <v>46161.47348627315</v>
+        <v>46161.64015293981</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46161.680402638885</v>
+        <v>46161.84706930556</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>195</v>
@@ -13084,11 +13084,11 @@
         <v>429</v>
       </c>
       <c r="B203" s="9">
-        <v>46161.47350074074</v>
+        <v>46161.64016740741</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46161.680399942124</v>
+        <v>46161.847066608796</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>195</v>
@@ -13135,11 +13135,11 @@
         <v>430</v>
       </c>
       <c r="B204" s="5">
-        <v>46161.47353721065</v>
+        <v>46161.640203877316</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46161.68039736111</v>
+        <v>46161.84706402778</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>195</v>
@@ -13186,11 +13186,11 @@
         <v>431</v>
       </c>
       <c r="B205" s="9">
-        <v>46161.4735484375</v>
+        <v>46161.64021510417</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46161.68039445602</v>
+        <v>46161.84706112268</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>195</v>
@@ -13237,11 +13237,11 @@
         <v>432</v>
       </c>
       <c r="B206" s="5">
-        <v>46161.4735603588</v>
+        <v>46161.64022702546</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46161.68038675926</v>
+        <v>46161.847053425925</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>195</v>
@@ -13288,11 +13288,11 @@
         <v>433</v>
       </c>
       <c r="B207" s="9">
-        <v>46161.473571180555</v>
+        <v>46161.64023784723</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46161.68038609954</v>
+        <v>46161.8470527662</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>195</v>
@@ -13339,11 +13339,11 @@
         <v>434</v>
       </c>
       <c r="B208" s="5">
-        <v>46161.47358644676</v>
+        <v>46161.64025311342</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46161.68038543982</v>
+        <v>46161.84705210648</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>195</v>
@@ -13390,11 +13390,11 @@
         <v>435</v>
       </c>
       <c r="B209" s="9">
-        <v>46161.41454799769</v>
+        <v>46161.58121466435</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46161.6806352662</v>
+        <v>46161.84730193287</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>436</v>
@@ -13453,11 +13453,11 @@
         <v>438</v>
       </c>
       <c r="B210" s="5">
-        <v>46161.414590659726</v>
+        <v>46161.58125732639</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46161.680614247685</v>
+        <v>46161.84728091436</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>195</v>
@@ -13504,11 +13504,11 @@
         <v>439</v>
       </c>
       <c r="B211" s="9">
-        <v>46161.47364123842</v>
+        <v>46161.640307905094</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46161.6806110301</v>
+        <v>46161.84727769676</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>195</v>
@@ -13555,11 +13555,11 @@
         <v>440</v>
       </c>
       <c r="B212" s="5">
-        <v>46161.4736496875</v>
+        <v>46161.64031635417</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46161.680608587965</v>
+        <v>46161.84727525463</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>195</v>
@@ -13606,11 +13606,11 @@
         <v>441</v>
       </c>
       <c r="B213" s="9">
-        <v>46161.473661655094</v>
+        <v>46161.64032832176</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46161.68060581019</v>
+        <v>46161.84727247685</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>195</v>
@@ -13657,11 +13657,11 @@
         <v>442</v>
       </c>
       <c r="B214" s="5">
-        <v>46161.47367131944</v>
+        <v>46161.640337986115</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46161.68060278935</v>
+        <v>46161.84726945602</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>195</v>
@@ -13708,11 +13708,11 @@
         <v>443</v>
       </c>
       <c r="B215" s="9">
-        <v>46161.473691956024</v>
+        <v>46161.64035862268</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46161.680599722225</v>
+        <v>46161.84726638889</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>195</v>
@@ -13759,11 +13759,11 @@
         <v>444</v>
       </c>
       <c r="B216" s="5">
-        <v>46161.47370106481</v>
+        <v>46161.64036773148</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46161.68059693287</v>
+        <v>46161.84726359954</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>195</v>
@@ -13810,11 +13810,11 @@
         <v>445</v>
       </c>
       <c r="B217" s="9">
-        <v>46161.47370990741</v>
+        <v>46161.64037657407</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46161.68059393518</v>
+        <v>46161.84726060185</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>195</v>
@@ -13861,11 +13861,11 @@
         <v>446</v>
       </c>
       <c r="B218" s="5">
-        <v>46161.47371806713</v>
+        <v>46161.64038473379</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46161.68058803241</v>
+        <v>46161.847254699074</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>195</v>
@@ -13912,11 +13912,11 @@
         <v>447</v>
       </c>
       <c r="B219" s="9">
-        <v>46161.47372684028</v>
+        <v>46161.64039350694</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46161.68058739584</v>
+        <v>46161.8472540625</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>195</v>
@@ -13963,11 +13963,11 @@
         <v>448</v>
       </c>
       <c r="B220" s="5">
-        <v>46161.41459615741</v>
+        <v>46161.581262824075</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46161.68134378472</v>
+        <v>46161.84801045139</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>449</v>
@@ -14010,11 +14010,11 @@
         <v>451</v>
       </c>
       <c r="B221" s="9">
-        <v>46161.414599490745</v>
+        <v>46161.58126615741</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46161.680980902776</v>
+        <v>46161.84764756945</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>452</v>
@@ -14073,11 +14073,11 @@
         <v>455</v>
       </c>
       <c r="B222" s="5">
-        <v>46161.41460415509</v>
+        <v>46161.581270821756</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46161.68155587963</v>
+        <v>46161.848222546294</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>456</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46198.80555135416</v>
+        <v>46204.900667615744</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2923,9 +2923,11 @@
       <c r="B18" s="5">
         <v>46161.58079903935</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46204.90066085648</v>
+      </c>
       <c r="D18" s="5">
-        <v>46198.80753384259</v>
+        <v>46204.90095260416</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2973,10 +2975,10 @@
         <v>33</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="11" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -2986,9 +2988,11 @@
       <c r="B19" s="9">
         <v>46161.58080373843</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9">
+        <v>46204.90101555556</v>
+      </c>
       <c r="D19" s="9">
-        <v>46198.80753430555</v>
+        <v>46204.90139665509</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>85</v>
@@ -3036,10 +3040,10 @@
         <v>33</v>
       </c>
       <c r="T19" s="10">
-        <v>0</v>
-      </c>
-      <c r="U19" s="11" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -3049,9 +3053,11 @@
       <c r="B20" s="5">
         <v>46161.58080740741</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5">
+        <v>46204.90180252315</v>
+      </c>
       <c r="D20" s="5">
-        <v>46198.80753359954</v>
+        <v>46204.9022046875</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -3099,10 +3105,10 @@
         <v>33</v>
       </c>
       <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="11" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -3112,9 +3118,11 @@
       <c r="B21" s="9">
         <v>46161.580810740736</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9">
+        <v>46204.90175329861</v>
+      </c>
       <c r="D21" s="9">
-        <v>46198.807534085645</v>
+        <v>46204.90176861111</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -3162,10 +3170,10 @@
         <v>33</v>
       </c>
       <c r="T21" s="10">
-        <v>0</v>
-      </c>
-      <c r="U21" s="11" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -3893,7 +3901,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.879810196755</v>
+        <v>46204.90066701389</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -4074,7 +4082,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.8798540625</v>
+        <v>46204.90102186342</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>86</v>
@@ -4243,7 +4251,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.87990410879</v>
+        <v>46204.90175859953</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>92</v>
@@ -4465,7 +4473,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.87997335648</v>
+        <v>46204.90180835648</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>89</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2069,13 +2069,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46161.58063581018</v>
+        <v>46161.41396914352</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87851013889</v>
+        <v>46175.71184347222</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87852383102</v>
+        <v>46175.71185716435</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2122,13 +2122,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46161.58074600695</v>
+        <v>46161.41407934028</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87848300926</v>
+        <v>46175.71181634259</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87851039352</v>
+        <v>46175.71184372685</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2185,13 +2185,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46161.58074907407</v>
+        <v>46161.414082407406</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87848385416</v>
+        <v>46175.711817187504</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87851055556</v>
+        <v>46175.71184388889</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2248,13 +2248,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46161.58075194445</v>
+        <v>46161.41408527778</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.878484409724</v>
+        <v>46175.71181774305</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.878510497685</v>
+        <v>46175.71184383101</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2311,13 +2311,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46161.58075466435</v>
+        <v>46161.414087997684</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.87848503472</v>
+        <v>46175.71181836806</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.878510925926</v>
+        <v>46175.71184425926</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2374,13 +2374,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46161.5807578588</v>
+        <v>46161.41409119213</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87848576389</v>
+        <v>46175.711819097225</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87851096065</v>
+        <v>46175.71184429398</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2437,11 +2437,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46161.580639618056</v>
+        <v>46161.413972951384</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46198.80657155093</v>
+        <v>46198.63990488426</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2486,13 +2486,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46161.580761307865</v>
+        <v>46161.41409464121</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.67426642361</v>
+        <v>46197.507599756944</v>
       </c>
       <c r="D11" s="9">
-        <v>46198.80656200231</v>
+        <v>46198.63989533565</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2551,13 +2551,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46161.580766307874</v>
+        <v>46161.4140996412</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.67508163194</v>
+        <v>46197.50841496528</v>
       </c>
       <c r="D12" s="5">
-        <v>46198.80656201389</v>
+        <v>46198.63989534722</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2616,13 +2616,13 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46161.580771423614</v>
+        <v>46161.41410475694</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.67727987269</v>
+        <v>46197.51061320602</v>
       </c>
       <c r="D13" s="9">
-        <v>46198.80656199074</v>
+        <v>46198.63989532407</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2681,11 +2681,11 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46161.58064403935</v>
+        <v>46161.413977372686</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46204.900667615744</v>
+        <v>46204.73400094907</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2728,13 +2728,13 @@
         <v>68</v>
       </c>
       <c r="B15" s="9">
-        <v>46161.58078354166</v>
+        <v>46161.414116875</v>
       </c>
       <c r="C15" s="9">
-        <v>46198.80554483796</v>
+        <v>46198.638878171296</v>
       </c>
       <c r="D15" s="9">
-        <v>46198.8073902662</v>
+        <v>46198.640723599536</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>69</v>
@@ -2793,11 +2793,11 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46161.580788680556</v>
+        <v>46161.414122013884</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.67510195602</v>
+        <v>46197.508435289354</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2856,13 +2856,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46161.58079363426</v>
+        <v>46161.41412696759</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.58859138889</v>
+        <v>46197.42192472222</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.675101863424</v>
+        <v>46197.50843519676</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2921,13 +2921,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46161.58079903935</v>
+        <v>46161.41413237268</v>
       </c>
       <c r="C18" s="5">
-        <v>46204.90066085648</v>
+        <v>46204.73399418981</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.90095260416</v>
+        <v>46204.7342859375</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2986,13 +2986,13 @@
         <v>84</v>
       </c>
       <c r="B19" s="9">
-        <v>46161.58080373843</v>
+        <v>46161.414137071755</v>
       </c>
       <c r="C19" s="9">
-        <v>46204.90101555556</v>
+        <v>46204.73434888889</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.90139665509</v>
+        <v>46204.73472998843</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>85</v>
@@ -3051,13 +3051,13 @@
         <v>87</v>
       </c>
       <c r="B20" s="5">
-        <v>46161.58080740741</v>
+        <v>46161.414140740744</v>
       </c>
       <c r="C20" s="5">
-        <v>46204.90180252315</v>
+        <v>46204.73513585648</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.9022046875</v>
+        <v>46204.73553802083</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -3116,13 +3116,13 @@
         <v>90</v>
       </c>
       <c r="B21" s="9">
-        <v>46161.580810740736</v>
+        <v>46161.41414407408</v>
       </c>
       <c r="C21" s="9">
-        <v>46204.90175329861</v>
+        <v>46204.73508663195</v>
       </c>
       <c r="D21" s="9">
-        <v>46204.90176861111</v>
+        <v>46204.73510194445</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -3181,11 +3181,11 @@
         <v>93</v>
       </c>
       <c r="B22" s="5">
-        <v>46161.58064796297</v>
+        <v>46161.4139812963</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46161.73787121528</v>
+        <v>46161.571204548614</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -3228,11 +3228,11 @@
         <v>96</v>
       </c>
       <c r="B23" s="9">
-        <v>46161.58081472223</v>
+        <v>46161.414148055555</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.879378680555</v>
+        <v>46169.71271201389</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>97</v>
@@ -3291,11 +3291,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46161.580819016206</v>
+        <v>46161.414152349535</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.879644560184</v>
+        <v>46169.71297789352</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3350,11 +3350,11 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46161.58082350694</v>
+        <v>46161.41415684028</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.87966921296</v>
+        <v>46169.7130025463</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3409,11 +3409,11 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46161.58082824074</v>
+        <v>46161.414161574074</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46192.85867619213</v>
+        <v>46192.69200952546</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3472,11 +3472,11 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46161.5808325463</v>
+        <v>46161.41416587963</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.58860037037</v>
+        <v>46197.42193370371</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3531,11 +3531,11 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46161.580836967594</v>
+        <v>46161.41417030092</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46171.17352185185</v>
+        <v>46171.00685518519</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3590,11 +3590,11 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46161.58084165509</v>
+        <v>46161.41417498843</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46198.805784641205</v>
+        <v>46198.63911797454</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3653,13 +3653,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46161.58084603009</v>
+        <v>46161.414179363426</v>
       </c>
       <c r="C30" s="5">
-        <v>46198.805726481485</v>
+        <v>46198.639059814814</v>
       </c>
       <c r="D30" s="5">
-        <v>46198.80572795139</v>
+        <v>46198.63906128472</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3714,11 +3714,11 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46161.580850439816</v>
+        <v>46161.414183773144</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46198.80573190972</v>
+        <v>46198.63906524306</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3773,13 +3773,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46161.58085503472</v>
+        <v>46161.41418836806</v>
       </c>
       <c r="C32" s="5">
-        <v>46198.80577472222</v>
+        <v>46198.639108055555</v>
       </c>
       <c r="D32" s="5">
-        <v>46198.80577622685</v>
+        <v>46198.63910956019</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3834,11 +3834,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46161.58085940972</v>
+        <v>46161.41419274306</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.87943234954</v>
+        <v>46169.71276568287</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>130</v>
@@ -3897,11 +3897,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46161.58086364584</v>
+        <v>46161.41419697917</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46204.90066701389</v>
+        <v>46204.73400034722</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3956,11 +3956,11 @@
         <v>137</v>
       </c>
       <c r="B35" s="9">
-        <v>46161.58086832176</v>
+        <v>46161.41420165509</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.879828854166</v>
+        <v>46169.7131621875</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -4015,11 +4015,11 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46161.58087322916</v>
+        <v>46161.4142065625</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.87944365741</v>
+        <v>46169.71277699074</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -4078,11 +4078,11 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46161.580931018514</v>
+        <v>46161.41426435186</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46204.90102186342</v>
+        <v>46204.734355196764</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>86</v>
@@ -4131,11 +4131,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46161.58093646991</v>
+        <v>46161.41426980324</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.87986516204</v>
+        <v>46169.713198495374</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -4184,11 +4184,11 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46161.580941099535</v>
+        <v>46161.41427443287</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.87945328704</v>
+        <v>46169.71278662037</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -4247,11 +4247,11 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46161.58094532407</v>
+        <v>46161.41427865741</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46204.90175859953</v>
+        <v>46204.735091932875</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>92</v>
@@ -4300,11 +4300,11 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46161.58094997685</v>
+        <v>46161.41428331019</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.87991520834</v>
+        <v>46169.713248541666</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4353,11 +4353,11 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46161.58095447917</v>
+        <v>46161.4142878125</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.879929814815</v>
+        <v>46169.71326314815</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4406,11 +4406,11 @@
         <v>162</v>
       </c>
       <c r="B43" s="9">
-        <v>46161.58095743056</v>
+        <v>46161.41429076389</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.87951825232</v>
+        <v>46169.712851585646</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>163</v>
@@ -4469,11 +4469,11 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46161.58096091435</v>
+        <v>46161.41429424769</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46204.90180835648</v>
+        <v>46204.73514168982</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>89</v>
@@ -4522,11 +4522,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46161.580964988425</v>
+        <v>46161.41429832176</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.87999765047</v>
+        <v>46169.713330983795</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>168</v>
@@ -4575,11 +4575,11 @@
         <v>170</v>
       </c>
       <c r="B46" s="5">
-        <v>46161.58065239583</v>
+        <v>46161.41398572917</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46198.80746668982</v>
+        <v>46198.640800023146</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4624,13 +4624,13 @@
         <v>173</v>
       </c>
       <c r="B47" s="9">
-        <v>46161.580969780094</v>
+        <v>46161.41430311343</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.70503125</v>
+        <v>46197.538364583335</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.70504644676</v>
+        <v>46197.53837978009</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>174</v>
@@ -4689,13 +4689,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46161.580975069446</v>
+        <v>46161.414308402775</v>
       </c>
       <c r="C48" s="5">
-        <v>46198.8074493287</v>
+        <v>46198.64078266204</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.80746766204</v>
+        <v>46198.640800995374</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4754,13 +4754,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46161.58098100695</v>
+        <v>46161.414314340276</v>
       </c>
       <c r="C49" s="9">
-        <v>46198.80749446759</v>
+        <v>46198.640827800926</v>
       </c>
       <c r="D49" s="9">
-        <v>46198.807511481486</v>
+        <v>46198.640844814814</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>82</v>
@@ -4819,11 +4819,11 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46161.58099116899</v>
+        <v>46161.414324502315</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46161.84476310185</v>
+        <v>46161.678096435186</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4882,11 +4882,11 @@
         <v>191</v>
       </c>
       <c r="B51" s="9">
-        <v>46161.58099418982</v>
+        <v>46161.41432752315</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46161.84476607639</v>
+        <v>46161.67809940972</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4933,11 +4933,11 @@
         <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46161.63966489583</v>
+        <v>46161.47299822917</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46161.844763472225</v>
+        <v>46161.678096805554</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4984,11 +4984,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="9">
-        <v>46161.63967261574</v>
+        <v>46161.473005949076</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46161.84476069444</v>
+        <v>46161.67809402778</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -5035,11 +5035,11 @@
         <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46161.63968388889</v>
+        <v>46161.47301722222</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46161.84475773148</v>
+        <v>46161.678091064816</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5086,11 +5086,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="9">
-        <v>46161.63969275463</v>
+        <v>46161.47302608796</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46161.84475471065</v>
+        <v>46161.67808804398</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>190</v>
@@ -5137,11 +5137,11 @@
         <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46161.639705208334</v>
+        <v>46161.47303854166</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46161.84475174769</v>
+        <v>46161.67808508102</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>190</v>
@@ -5188,11 +5188,11 @@
         <v>199</v>
       </c>
       <c r="B57" s="9">
-        <v>46161.639715474535</v>
+        <v>46161.47304880787</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46161.84474863426</v>
+        <v>46161.67808196759</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>190</v>
@@ -5239,11 +5239,11 @@
         <v>200</v>
       </c>
       <c r="B58" s="5">
-        <v>46161.63972679398</v>
+        <v>46161.47306012732</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46161.84474503472</v>
+        <v>46161.67807836806</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>190</v>
@@ -5290,11 +5290,11 @@
         <v>201</v>
       </c>
       <c r="B59" s="9">
-        <v>46161.63974304398</v>
+        <v>46161.47307637731</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46161.84473834491</v>
+        <v>46161.67807167824</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>190</v>
@@ -5341,11 +5341,11 @@
         <v>202</v>
       </c>
       <c r="B60" s="5">
-        <v>46161.63975269676</v>
+        <v>46161.47308603009</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46161.84473753472</v>
+        <v>46161.67807086806</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>190</v>
@@ -5392,11 +5392,11 @@
         <v>203</v>
       </c>
       <c r="B61" s="9">
-        <v>46161.58099818287</v>
+        <v>46161.41433151621</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.79647144676</v>
+        <v>46161.629804780096</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>204</v>
@@ -5439,11 +5439,11 @@
         <v>206</v>
       </c>
       <c r="B62" s="5">
-        <v>46161.58100145833</v>
+        <v>46161.41433479167</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46161.844842499995</v>
+        <v>46161.67817583334</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>207</v>
@@ -5502,11 +5502,11 @@
         <v>211</v>
       </c>
       <c r="B63" s="9">
-        <v>46161.58100614583</v>
+        <v>46161.41433947917</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.84491849537</v>
+        <v>46161.67825182871</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>212</v>
@@ -5565,11 +5565,11 @@
         <v>215</v>
       </c>
       <c r="B64" s="5">
-        <v>46161.58101638889</v>
+        <v>46161.414349722225</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46161.84483983796</v>
+        <v>46161.6781731713</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5628,11 +5628,11 @@
         <v>218</v>
       </c>
       <c r="B65" s="9">
-        <v>46161.58102099537</v>
+        <v>46161.41435432871</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46161.84491503472</v>
+        <v>46161.67824836806</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>219</v>
@@ -5691,11 +5691,11 @@
         <v>221</v>
       </c>
       <c r="B66" s="5">
-        <v>46161.581024722225</v>
+        <v>46161.414358055554</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46161.8448359375</v>
+        <v>46161.67816927083</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>222</v>
@@ -5754,11 +5754,11 @@
         <v>224</v>
       </c>
       <c r="B67" s="9">
-        <v>46161.58102864583</v>
+        <v>46161.41436197917</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46161.844914270834</v>
+        <v>46161.67824760417</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>223</v>
@@ -5817,11 +5817,11 @@
         <v>226</v>
       </c>
       <c r="B68" s="5">
-        <v>46161.58103207176</v>
+        <v>46161.41436540509</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46161.797785821764</v>
+        <v>46161.63111915509</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5864,11 +5864,11 @@
         <v>229</v>
       </c>
       <c r="B69" s="9">
-        <v>46161.58103457176</v>
+        <v>46161.41436790509</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46161.845178449075</v>
+        <v>46161.678511782404</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>230</v>
@@ -5927,11 +5927,11 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46161.58103962963</v>
+        <v>46161.41437296296</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46161.845147071755</v>
+        <v>46161.67848040509</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>190</v>
@@ -5980,11 +5980,11 @@
         <v>237</v>
       </c>
       <c r="B71" s="9">
-        <v>46161.582011805556</v>
+        <v>46161.415345138885</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46161.84514348379</v>
+        <v>46161.678476817135</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>190</v>
@@ -6033,11 +6033,11 @@
         <v>239</v>
       </c>
       <c r="B72" s="5">
-        <v>46161.58202383102</v>
+        <v>46161.415357164355</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46161.845140324076</v>
+        <v>46161.678473657405</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -6086,11 +6086,11 @@
         <v>241</v>
       </c>
       <c r="B73" s="9">
-        <v>46161.582662650464</v>
+        <v>46161.4159959838</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46161.845136655094</v>
+        <v>46161.67846998843</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>190</v>
@@ -6139,11 +6139,11 @@
         <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46161.58267322917</v>
+        <v>46161.416006562504</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46161.845133518524</v>
+        <v>46161.67846685185</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -6192,11 +6192,11 @@
         <v>243</v>
       </c>
       <c r="B75" s="9">
-        <v>46161.58270134259</v>
+        <v>46161.41603467593</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46161.84513074074</v>
+        <v>46161.67846407407</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -6245,11 +6245,11 @@
         <v>244</v>
       </c>
       <c r="B76" s="5">
-        <v>46161.58271427083</v>
+        <v>46161.416047604165</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46161.84512803241</v>
+        <v>46161.67846136574</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>190</v>
@@ -6298,11 +6298,11 @@
         <v>246</v>
       </c>
       <c r="B77" s="9">
-        <v>46161.58272651621</v>
+        <v>46161.41605984954</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46161.84512407407</v>
+        <v>46161.67845740741</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>190</v>
@@ -6351,11 +6351,11 @@
         <v>247</v>
       </c>
       <c r="B78" s="5">
-        <v>46161.58277962963</v>
+        <v>46161.416112962965</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46161.845117916666</v>
+        <v>46161.67845125</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>190</v>
@@ -6404,11 +6404,11 @@
         <v>249</v>
       </c>
       <c r="B79" s="9">
-        <v>46161.58279046296</v>
+        <v>46161.4161237963</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46161.84511721064</v>
+        <v>46161.67845054399</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>190</v>
@@ -6457,11 +6457,11 @@
         <v>250</v>
       </c>
       <c r="B80" s="5">
-        <v>46161.58104538194</v>
+        <v>46161.41437871528</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46161.845344814814</v>
+        <v>46161.67867814815</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>251</v>
@@ -6520,11 +6520,11 @@
         <v>252</v>
       </c>
       <c r="B81" s="9">
-        <v>46161.58104903935</v>
+        <v>46161.414382372684</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46198.80752025463</v>
+        <v>46198.64085358796</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>190</v>
@@ -6573,11 +6573,11 @@
         <v>255</v>
       </c>
       <c r="B82" s="5">
-        <v>46161.582834120374</v>
+        <v>46161.4161674537</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46161.84533628472</v>
+        <v>46161.67866961806</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>190</v>
@@ -6626,11 +6626,11 @@
         <v>256</v>
       </c>
       <c r="B83" s="9">
-        <v>46161.58286459491</v>
+        <v>46161.416197928236</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46161.84533336805</v>
+        <v>46161.67866670139</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>190</v>
@@ -6679,11 +6679,11 @@
         <v>257</v>
       </c>
       <c r="B84" s="5">
-        <v>46161.58287381944</v>
+        <v>46161.41620715278</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46161.84533065972</v>
+        <v>46161.67866399305</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>190</v>
@@ -6732,11 +6732,11 @@
         <v>258</v>
       </c>
       <c r="B85" s="9">
-        <v>46161.58288365741</v>
+        <v>46161.416216990736</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46161.84532790509</v>
+        <v>46161.67866123843</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>190</v>
@@ -6785,11 +6785,11 @@
         <v>259</v>
       </c>
       <c r="B86" s="5">
-        <v>46161.58289255787</v>
+        <v>46161.416225891204</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46161.84532486111</v>
+        <v>46161.67865819445</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>190</v>
@@ -6838,11 +6838,11 @@
         <v>260</v>
       </c>
       <c r="B87" s="9">
-        <v>46161.58292542824</v>
+        <v>46161.41625876157</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46161.84532211805</v>
+        <v>46161.67865545139</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>190</v>
@@ -6891,11 +6891,11 @@
         <v>261</v>
       </c>
       <c r="B88" s="5">
-        <v>46161.58293696759</v>
+        <v>46161.41627030092</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46161.84531927083</v>
+        <v>46161.67865260417</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>190</v>
@@ -6944,11 +6944,11 @@
         <v>262</v>
       </c>
       <c r="B89" s="9">
-        <v>46161.58295282407</v>
+        <v>46161.41628615741</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46161.84531311343</v>
+        <v>46161.67864644676</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>190</v>
@@ -6997,11 +6997,11 @@
         <v>263</v>
       </c>
       <c r="B90" s="5">
-        <v>46161.58296773148</v>
+        <v>46161.41630106482</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46161.84531243055</v>
+        <v>46161.67864576389</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>190</v>
@@ -7050,11 +7050,11 @@
         <v>264</v>
       </c>
       <c r="B91" s="9">
-        <v>46161.581053761576</v>
+        <v>46161.414387094905</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46161.84552644676</v>
+        <v>46161.67885978009</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>265</v>
@@ -7113,11 +7113,11 @@
         <v>266</v>
       </c>
       <c r="B92" s="5">
-        <v>46161.58105741898</v>
+        <v>46161.41439075231</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46198.80752082176</v>
+        <v>46198.64085415509</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>190</v>
@@ -7166,11 +7166,11 @@
         <v>268</v>
       </c>
       <c r="B93" s="9">
-        <v>46161.583039942125</v>
+        <v>46161.41637327547</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46161.84550880787</v>
+        <v>46161.678842141206</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>190</v>
@@ -7219,11 +7219,11 @@
         <v>269</v>
       </c>
       <c r="B94" s="5">
-        <v>46161.58305715278</v>
+        <v>46161.41639048611</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46161.845505324076</v>
+        <v>46161.678838657404</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>190</v>
@@ -7272,11 +7272,11 @@
         <v>270</v>
       </c>
       <c r="B95" s="9">
-        <v>46161.583076689814</v>
+        <v>46161.41641002314</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46161.84550258102</v>
+        <v>46161.678835914354</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>190</v>
@@ -7325,11 +7325,11 @@
         <v>271</v>
       </c>
       <c r="B96" s="5">
-        <v>46161.58308886574</v>
+        <v>46161.41642219907</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46161.84549928241</v>
+        <v>46161.67883261574</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>190</v>
@@ -7378,11 +7378,11 @@
         <v>272</v>
       </c>
       <c r="B97" s="9">
-        <v>46161.58310019676</v>
+        <v>46161.41643353009</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46161.84549533565</v>
+        <v>46161.678828668984</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>190</v>
@@ -7431,11 +7431,11 @@
         <v>273</v>
       </c>
       <c r="B98" s="5">
-        <v>46161.5831108912</v>
+        <v>46161.41644422454</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46161.84549206018</v>
+        <v>46161.67882539352</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>190</v>
@@ -7484,11 +7484,11 @@
         <v>274</v>
       </c>
       <c r="B99" s="9">
-        <v>46161.58312844907</v>
+        <v>46161.416461782406</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46161.84548887731</v>
+        <v>46161.67882221065</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>190</v>
@@ -7537,11 +7537,11 @@
         <v>275</v>
       </c>
       <c r="B100" s="5">
-        <v>46161.58300775463</v>
+        <v>46161.41634108796</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46161.84548230324</v>
+        <v>46161.67881563657</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>190</v>
@@ -7590,11 +7590,11 @@
         <v>276</v>
       </c>
       <c r="B101" s="9">
-        <v>46161.639501875004</v>
+        <v>46161.47283520833</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46161.845481620374</v>
+        <v>46161.6788149537</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>190</v>
@@ -7643,11 +7643,11 @@
         <v>277</v>
       </c>
       <c r="B102" s="5">
-        <v>46161.58110506945</v>
+        <v>46161.414438402775</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46161.80776861111</v>
+        <v>46161.64110194445</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>204</v>
@@ -7690,11 +7690,11 @@
         <v>279</v>
       </c>
       <c r="B103" s="9">
-        <v>46161.581108530096</v>
+        <v>46161.414441863424</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46176.18811300926</v>
+        <v>46176.021446342595</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>280</v>
@@ -7753,11 +7753,11 @@
         <v>282</v>
       </c>
       <c r="B104" s="5">
-        <v>46161.58111370371</v>
+        <v>46161.41444703704</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46161.84560915509</v>
+        <v>46161.67894248843</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>283</v>
@@ -7816,11 +7816,11 @@
         <v>285</v>
       </c>
       <c r="B105" s="9">
-        <v>46161.581118449074</v>
+        <v>46161.4144517824</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46161.84560644676</v>
+        <v>46161.67893978009</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>286</v>
@@ -7879,11 +7879,11 @@
         <v>288</v>
       </c>
       <c r="B106" s="5">
-        <v>46161.58112311343</v>
+        <v>46161.41445644676</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46161.84560210648</v>
+        <v>46161.67893543981</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>289</v>
@@ -7942,11 +7942,11 @@
         <v>291</v>
       </c>
       <c r="B107" s="9">
-        <v>46161.58112702546</v>
+        <v>46161.41446035879</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46161.83387362269</v>
+        <v>46161.667206956015</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>292</v>
@@ -7989,11 +7989,11 @@
         <v>294</v>
       </c>
       <c r="B108" s="5">
-        <v>46161.58112984954</v>
+        <v>46161.41446318287</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46161.84578230324</v>
+        <v>46161.67911563657</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>295</v>
@@ -8052,11 +8052,11 @@
         <v>297</v>
       </c>
       <c r="B109" s="9">
-        <v>46161.581135555556</v>
+        <v>46161.41446888889</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46161.84577694444</v>
+        <v>46161.67911027778</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>298</v>
@@ -8105,11 +8105,11 @@
         <v>299</v>
       </c>
       <c r="B110" s="5">
-        <v>46161.58317730324</v>
+        <v>46161.41651063657</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46161.84577366898</v>
+        <v>46161.67910700232</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -8158,11 +8158,11 @@
         <v>300</v>
       </c>
       <c r="B111" s="9">
-        <v>46161.58318758102</v>
+        <v>46161.416520914354</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46161.845770879634</v>
+        <v>46161.67910421296</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>190</v>
@@ -8211,11 +8211,11 @@
         <v>301</v>
       </c>
       <c r="B112" s="5">
-        <v>46161.5831975926</v>
+        <v>46161.416530925926</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46161.84576709491</v>
+        <v>46161.67910042824</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>190</v>
@@ -8264,11 +8264,11 @@
         <v>302</v>
       </c>
       <c r="B113" s="9">
-        <v>46161.58320657407</v>
+        <v>46161.41653990741</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46161.84576415509</v>
+        <v>46161.67909748842</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>190</v>
@@ -8317,11 +8317,11 @@
         <v>303</v>
       </c>
       <c r="B114" s="5">
-        <v>46161.58322151621</v>
+        <v>46161.41655484954</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46161.84576082176</v>
+        <v>46161.67909415509</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>190</v>
@@ -8370,11 +8370,11 @@
         <v>304</v>
       </c>
       <c r="B115" s="9">
-        <v>46161.58322717593</v>
+        <v>46161.41656050926</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46161.84575040509</v>
+        <v>46161.679083738425</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>190</v>
@@ -8423,11 +8423,11 @@
         <v>305</v>
       </c>
       <c r="B116" s="5">
-        <v>46161.58324248843</v>
+        <v>46161.41657582176</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46161.84574967592</v>
+        <v>46161.67908300926</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8476,11 +8476,11 @@
         <v>306</v>
       </c>
       <c r="B117" s="9">
-        <v>46161.58325402778</v>
+        <v>46161.41658736111</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46161.845748946755</v>
+        <v>46161.6790822801</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8529,11 +8529,11 @@
         <v>307</v>
       </c>
       <c r="B118" s="5">
-        <v>46161.58326291667</v>
+        <v>46161.41659625</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46161.84574821759</v>
+        <v>46161.67908155093</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8582,11 +8582,11 @@
         <v>308</v>
       </c>
       <c r="B119" s="9">
-        <v>46161.58113928241</v>
+        <v>46161.41447261574</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46161.845971400464</v>
+        <v>46161.6793047338</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>309</v>
@@ -8645,11 +8645,11 @@
         <v>310</v>
       </c>
       <c r="B120" s="5">
-        <v>46161.58114282407</v>
+        <v>46161.414476157406</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46198.807521180555</v>
+        <v>46198.640854513884</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8698,11 +8698,11 @@
         <v>313</v>
       </c>
       <c r="B121" s="9">
-        <v>46161.585882430554</v>
+        <v>46161.41921576389</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46198.807499965274</v>
+        <v>46198.64083329861</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>190</v>
@@ -8751,11 +8751,11 @@
         <v>315</v>
       </c>
       <c r="B122" s="5">
-        <v>46161.58590298611</v>
+        <v>46161.419236319445</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46198.80750063657</v>
+        <v>46198.64083396991</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8804,11 +8804,11 @@
         <v>317</v>
       </c>
       <c r="B123" s="9">
-        <v>46161.585919861114</v>
+        <v>46161.41925319444</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46198.80750122685</v>
+        <v>46198.64083456018</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>190</v>
@@ -8857,11 +8857,11 @@
         <v>318</v>
       </c>
       <c r="B124" s="5">
-        <v>46161.585927175925</v>
+        <v>46161.419260509254</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46198.807501793985</v>
+        <v>46198.64083512731</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>190</v>
@@ -8910,11 +8910,11 @@
         <v>319</v>
       </c>
       <c r="B125" s="9">
-        <v>46161.58593310185</v>
+        <v>46161.41926643519</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46198.807502384254</v>
+        <v>46198.6408357176</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>190</v>
@@ -8963,11 +8963,11 @@
         <v>321</v>
       </c>
       <c r="B126" s="5">
-        <v>46161.58593739584</v>
+        <v>46161.419270729166</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46198.807502951386</v>
+        <v>46198.64083628472</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -9016,11 +9016,11 @@
         <v>322</v>
       </c>
       <c r="B127" s="9">
-        <v>46161.58594590278</v>
+        <v>46161.419279236114</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46198.80750380787</v>
+        <v>46198.6408371412</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>190</v>
@@ -9069,11 +9069,11 @@
         <v>323</v>
       </c>
       <c r="B128" s="5">
-        <v>46161.5859562963</v>
+        <v>46161.41928962963</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46198.80750443287</v>
+        <v>46198.6408377662</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -9122,11 +9122,11 @@
         <v>324</v>
       </c>
       <c r="B129" s="9">
-        <v>46161.58618912037</v>
+        <v>46161.4195224537</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46198.80750512732</v>
+        <v>46198.64083846065</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>190</v>
@@ -9175,11 +9175,11 @@
         <v>326</v>
       </c>
       <c r="B130" s="5">
-        <v>46161.58114761574</v>
+        <v>46161.414480949075</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46161.8461249074</v>
+        <v>46161.679458240746</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>327</v>
@@ -9238,11 +9238,11 @@
         <v>328</v>
       </c>
       <c r="B131" s="9">
-        <v>46161.58115116898</v>
+        <v>46161.41448450231</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46198.807510914354</v>
+        <v>46198.64084424768</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9291,11 +9291,11 @@
         <v>331</v>
       </c>
       <c r="B132" s="5">
-        <v>46161.58603712963</v>
+        <v>46161.41937046296</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46198.80750575232</v>
+        <v>46198.64083908565</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9344,11 +9344,11 @@
         <v>332</v>
       </c>
       <c r="B133" s="9">
-        <v>46161.586044930555</v>
+        <v>46161.41937826389</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46198.8075062037</v>
+        <v>46198.64083953704</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>190</v>
@@ -9397,11 +9397,11 @@
         <v>334</v>
       </c>
       <c r="B134" s="5">
-        <v>46161.58605891204</v>
+        <v>46161.41939224537</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46198.807506666664</v>
+        <v>46198.64084</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9450,11 +9450,11 @@
         <v>335</v>
       </c>
       <c r="B135" s="9">
-        <v>46161.58606768519</v>
+        <v>46161.41940101852</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46198.8075071412</v>
+        <v>46198.64084047454</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>190</v>
@@ -9503,11 +9503,11 @@
         <v>337</v>
       </c>
       <c r="B136" s="5">
-        <v>46161.58607575232</v>
+        <v>46161.41940908565</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46198.807507708334</v>
+        <v>46198.64084104166</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>190</v>
@@ -9556,11 +9556,11 @@
         <v>338</v>
       </c>
       <c r="B137" s="9">
-        <v>46161.586088854165</v>
+        <v>46161.4194221875</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46198.80750815972</v>
+        <v>46198.640841493056</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>190</v>
@@ -9609,11 +9609,11 @@
         <v>339</v>
       </c>
       <c r="B138" s="5">
-        <v>46161.58609570602</v>
+        <v>46161.41942903935</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46198.80750863426</v>
+        <v>46198.64084196759</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>190</v>
@@ -9662,11 +9662,11 @@
         <v>341</v>
       </c>
       <c r="B139" s="9">
-        <v>46161.586110578704</v>
+        <v>46161.41944391203</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46198.807509085644</v>
+        <v>46198.64084241899</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>190</v>
@@ -9715,11 +9715,11 @@
         <v>342</v>
       </c>
       <c r="B140" s="5">
-        <v>46161.58612255787</v>
+        <v>46161.4194558912</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46198.80750956018</v>
+        <v>46198.64084289352</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>190</v>
@@ -9768,11 +9768,11 @@
         <v>343</v>
       </c>
       <c r="B141" s="9">
-        <v>46161.58115643519</v>
+        <v>46161.41448976852</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46161.84629616898</v>
+        <v>46161.679629502316</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>344</v>
@@ -9831,11 +9831,11 @@
         <v>345</v>
       </c>
       <c r="B142" s="5">
-        <v>46161.58115993056</v>
+        <v>46161.41449326389</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46198.807521759256</v>
+        <v>46198.64085509259</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>298</v>
@@ -9884,11 +9884,11 @@
         <v>348</v>
       </c>
       <c r="B143" s="9">
-        <v>46161.58622641204</v>
+        <v>46161.419559745365</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46198.80750998843</v>
+        <v>46198.64084332176</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>190</v>
@@ -9937,11 +9937,11 @@
         <v>349</v>
       </c>
       <c r="B144" s="5">
-        <v>46161.586235995375</v>
+        <v>46161.419569328704</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46198.807510416664</v>
+        <v>46198.64084375</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -9990,11 +9990,11 @@
         <v>350</v>
       </c>
       <c r="B145" s="9">
-        <v>46161.586246770836</v>
+        <v>46161.419580104164</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46161.846280046295</v>
+        <v>46161.67961337963</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>190</v>
@@ -10043,11 +10043,11 @@
         <v>352</v>
       </c>
       <c r="B146" s="5">
-        <v>46161.586256435185</v>
+        <v>46161.41958976851</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46161.84627699074</v>
+        <v>46161.67961032408</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -10096,11 +10096,11 @@
         <v>354</v>
       </c>
       <c r="B147" s="9">
-        <v>46161.586265833335</v>
+        <v>46161.419599166664</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46161.84627394676</v>
+        <v>46161.67960728009</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>190</v>
@@ -10149,11 +10149,11 @@
         <v>355</v>
       </c>
       <c r="B148" s="5">
-        <v>46161.586275671296</v>
+        <v>46161.41960900463</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46161.84627113426</v>
+        <v>46161.679604467594</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>190</v>
@@ -10202,11 +10202,11 @@
         <v>356</v>
       </c>
       <c r="B149" s="9">
-        <v>46161.58629186342</v>
+        <v>46161.41962519676</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46161.846268402776</v>
+        <v>46161.67960173611</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>190</v>
@@ -10255,11 +10255,11 @@
         <v>357</v>
       </c>
       <c r="B150" s="5">
-        <v>46161.58630879629</v>
+        <v>46161.41964212963</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46161.84626222222</v>
+        <v>46161.67959555556</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>190</v>
@@ -10308,11 +10308,11 @@
         <v>358</v>
       </c>
       <c r="B151" s="9">
-        <v>46161.58632163194</v>
+        <v>46161.41965496528</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46161.84626162037</v>
+        <v>46161.679594953705</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>190</v>
@@ -10361,11 +10361,11 @@
         <v>359</v>
       </c>
       <c r="B152" s="5">
-        <v>46161.5811646875</v>
+        <v>46161.41449802084</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46161.84643925926</v>
+        <v>46161.67977259259</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>360</v>
@@ -10424,11 +10424,11 @@
         <v>361</v>
       </c>
       <c r="B153" s="9">
-        <v>46161.58116828704</v>
+        <v>46161.41450162037</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46161.84644222222</v>
+        <v>46161.67977555556</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>190</v>
@@ -10475,11 +10475,11 @@
         <v>363</v>
       </c>
       <c r="B154" s="5">
-        <v>46161.63912622685</v>
+        <v>46161.47245956019</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46161.84643929398</v>
+        <v>46161.679772627314</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>190</v>
@@ -10526,11 +10526,11 @@
         <v>364</v>
       </c>
       <c r="B155" s="9">
-        <v>46161.63913737268</v>
+        <v>46161.47247070602</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46161.84643643518</v>
+        <v>46161.67976976852</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>190</v>
@@ -10577,11 +10577,11 @@
         <v>365</v>
       </c>
       <c r="B156" s="5">
-        <v>46161.63914719908</v>
+        <v>46161.47248053241</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46161.846433321756</v>
+        <v>46161.67976665509</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>190</v>
@@ -10628,11 +10628,11 @@
         <v>366</v>
       </c>
       <c r="B157" s="9">
-        <v>46161.639157557875</v>
+        <v>46161.4724908912</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46161.84643013889</v>
+        <v>46161.67976347222</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>190</v>
@@ -10679,11 +10679,11 @@
         <v>367</v>
       </c>
       <c r="B158" s="5">
-        <v>46161.6391721875</v>
+        <v>46161.47250552083</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46161.84642646991</v>
+        <v>46161.67975980324</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>190</v>
@@ -10730,11 +10730,11 @@
         <v>368</v>
       </c>
       <c r="B159" s="9">
-        <v>46161.639187395835</v>
+        <v>46161.47252072916</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46161.84642321759</v>
+        <v>46161.679756550926</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>190</v>
@@ -10781,11 +10781,11 @@
         <v>369</v>
       </c>
       <c r="B160" s="5">
-        <v>46161.639195289354</v>
+        <v>46161.47252862269</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46161.846420138885</v>
+        <v>46161.67975347222</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>190</v>
@@ -10832,11 +10832,11 @@
         <v>370</v>
       </c>
       <c r="B161" s="9">
-        <v>46161.63920550926</v>
+        <v>46161.472538842594</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46161.846413113424</v>
+        <v>46161.67974644676</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>190</v>
@@ -10883,11 +10883,11 @@
         <v>371</v>
       </c>
       <c r="B162" s="5">
-        <v>46161.63921432871</v>
+        <v>46161.47254766204</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46161.84641241898</v>
+        <v>46161.67974575231</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>190</v>
@@ -10934,11 +10934,11 @@
         <v>372</v>
       </c>
       <c r="B163" s="9">
-        <v>46161.58117752315</v>
+        <v>46161.414510856484</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46161.84660503472</v>
+        <v>46161.679938368055</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>373</v>
@@ -10997,11 +10997,11 @@
         <v>375</v>
       </c>
       <c r="B164" s="5">
-        <v>46161.58118137732</v>
+        <v>46161.41451471065</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46161.84658016203</v>
+        <v>46161.67991349537</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>190</v>
@@ -11050,11 +11050,11 @@
         <v>377</v>
       </c>
       <c r="B165" s="9">
-        <v>46161.639253761576</v>
+        <v>46161.472587094904</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46161.846577187505</v>
+        <v>46161.679910520834</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>190</v>
@@ -11103,11 +11103,11 @@
         <v>378</v>
       </c>
       <c r="B166" s="5">
-        <v>46161.63928710648</v>
+        <v>46161.47262043982</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46161.84657417824</v>
+        <v>46161.67990751157</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>190</v>
@@ -11156,11 +11156,11 @@
         <v>379</v>
       </c>
       <c r="B167" s="9">
-        <v>46161.63929736111</v>
+        <v>46161.47263069444</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46161.84657136574</v>
+        <v>46161.67990469908</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>190</v>
@@ -11209,11 +11209,11 @@
         <v>380</v>
       </c>
       <c r="B168" s="5">
-        <v>46161.6393071412</v>
+        <v>46161.47264047454</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46161.84656841435</v>
+        <v>46161.67990174769</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>190</v>
@@ -11262,11 +11262,11 @@
         <v>381</v>
       </c>
       <c r="B169" s="9">
-        <v>46161.639315625</v>
+        <v>46161.47264895833</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46161.84656539352</v>
+        <v>46161.679898726856</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>190</v>
@@ -11315,11 +11315,11 @@
         <v>382</v>
       </c>
       <c r="B170" s="5">
-        <v>46161.63932686343</v>
+        <v>46161.472660196756</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46161.846562754625</v>
+        <v>46161.67989608797</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>190</v>
@@ -11368,11 +11368,11 @@
         <v>383</v>
       </c>
       <c r="B171" s="9">
-        <v>46161.63933708333</v>
+        <v>46161.47267041667</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46161.8465599537</v>
+        <v>46161.67989328704</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>190</v>
@@ -11421,11 +11421,11 @@
         <v>384</v>
       </c>
       <c r="B172" s="5">
-        <v>46161.63935484954</v>
+        <v>46161.47268818287</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46161.846553807874</v>
+        <v>46161.6798871412</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>190</v>
@@ -11474,11 +11474,11 @@
         <v>385</v>
       </c>
       <c r="B173" s="9">
-        <v>46161.63936453704</v>
+        <v>46161.47269787037</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46161.84655313657</v>
+        <v>46161.67988646991</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>190</v>
@@ -11527,11 +11527,11 @@
         <v>386</v>
       </c>
       <c r="B174" s="5">
-        <v>46161.5811852662</v>
+        <v>46161.41451859954</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46161.84092732639</v>
+        <v>46161.674260659725</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>387</v>
@@ -11574,11 +11574,11 @@
         <v>389</v>
       </c>
       <c r="B175" s="9">
-        <v>46161.581188020835</v>
+        <v>46161.41452135416</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46161.84675815972</v>
+        <v>46161.68009149306</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>390</v>
@@ -11637,11 +11637,11 @@
         <v>393</v>
       </c>
       <c r="B176" s="5">
-        <v>46161.581192673606</v>
+        <v>46161.41452600695</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46161.846749351855</v>
+        <v>46161.68008268518</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>190</v>
@@ -11690,11 +11690,11 @@
         <v>395</v>
       </c>
       <c r="B177" s="9">
-        <v>46161.63982708333</v>
+        <v>46161.473160416666</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46161.84674655093</v>
+        <v>46161.68007988426</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>190</v>
@@ -11743,11 +11743,11 @@
         <v>396</v>
       </c>
       <c r="B178" s="5">
-        <v>46161.63983532407</v>
+        <v>46161.47316865741</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46161.846743981485</v>
+        <v>46161.68007731481</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>190</v>
@@ -11796,11 +11796,11 @@
         <v>397</v>
       </c>
       <c r="B179" s="9">
-        <v>46161.63984421296</v>
+        <v>46161.4731775463</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46161.84674143518</v>
+        <v>46161.68007476852</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>190</v>
@@ -11849,11 +11849,11 @@
         <v>398</v>
       </c>
       <c r="B180" s="5">
-        <v>46161.63985878472</v>
+        <v>46161.47319211806</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46161.846738541666</v>
+        <v>46161.680071875</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>190</v>
@@ -11902,11 +11902,11 @@
         <v>399</v>
       </c>
       <c r="B181" s="9">
-        <v>46161.63986780093</v>
+        <v>46161.47320113426</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46161.84673559028</v>
+        <v>46161.68006892361</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>190</v>
@@ -11955,11 +11955,11 @@
         <v>400</v>
       </c>
       <c r="B182" s="5">
-        <v>46161.639875</v>
+        <v>46161.47320833334</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46161.84673289352</v>
+        <v>46161.68006622685</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>190</v>
@@ -12008,11 +12008,11 @@
         <v>401</v>
       </c>
       <c r="B183" s="9">
-        <v>46161.63988342593</v>
+        <v>46161.47321675926</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46161.84672489583</v>
+        <v>46161.68005822916</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>190</v>
@@ -12061,11 +12061,11 @@
         <v>402</v>
       </c>
       <c r="B184" s="5">
-        <v>46161.63989143519</v>
+        <v>46161.47322476852</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46161.84672420139</v>
+        <v>46161.68005753472</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>190</v>
@@ -12114,11 +12114,11 @@
         <v>403</v>
       </c>
       <c r="B185" s="9">
-        <v>46161.639899340276</v>
+        <v>46161.47323267361</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46161.84672340278</v>
+        <v>46161.680056736106</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>190</v>
@@ -12167,11 +12167,11 @@
         <v>404</v>
       </c>
       <c r="B186" s="5">
-        <v>46161.5811965162</v>
+        <v>46161.41452984954</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46161.84690181713</v>
+        <v>46161.68023515046</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>405</v>
@@ -12230,11 +12230,11 @@
         <v>406</v>
       </c>
       <c r="B187" s="9">
-        <v>46161.58120002315</v>
+        <v>46161.41453335648</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46161.84690336806</v>
+        <v>46161.68023670139</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>190</v>
@@ -12283,11 +12283,11 @@
         <v>408</v>
       </c>
       <c r="B188" s="5">
-        <v>46161.63993424768</v>
+        <v>46161.47326758102</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46161.84690038195</v>
+        <v>46161.68023371528</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>190</v>
@@ -12336,11 +12336,11 @@
         <v>409</v>
       </c>
       <c r="B189" s="9">
-        <v>46161.6399947801</v>
+        <v>46161.473328113425</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46161.84689746528</v>
+        <v>46161.68023079861</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>190</v>
@@ -12389,11 +12389,11 @@
         <v>410</v>
       </c>
       <c r="B190" s="5">
-        <v>46161.640004444445</v>
+        <v>46161.473337777774</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46161.84689446759</v>
+        <v>46161.68022780093</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>190</v>
@@ -12442,11 +12442,11 @@
         <v>411</v>
       </c>
       <c r="B191" s="9">
-        <v>46161.64001501157</v>
+        <v>46161.47334834491</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46161.84689137731</v>
+        <v>46161.68022471065</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>190</v>
@@ -12495,11 +12495,11 @@
         <v>412</v>
       </c>
       <c r="B192" s="5">
-        <v>46161.640023831016</v>
+        <v>46161.47335716435</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46161.846888796295</v>
+        <v>46161.68022212963</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>190</v>
@@ -12548,11 +12548,11 @@
         <v>413</v>
       </c>
       <c r="B193" s="9">
-        <v>46161.640038310186</v>
+        <v>46161.473371643515</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46161.84688606481</v>
+        <v>46161.68021939815</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>190</v>
@@ -12601,11 +12601,11 @@
         <v>414</v>
       </c>
       <c r="B194" s="5">
-        <v>46161.64004747685</v>
+        <v>46161.47338081019</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46161.846882557875</v>
+        <v>46161.6802158912</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>190</v>
@@ -12654,11 +12654,11 @@
         <v>415</v>
       </c>
       <c r="B195" s="9">
-        <v>46161.64005649305</v>
+        <v>46161.47338982639</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46161.84687957176</v>
+        <v>46161.68021290509</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>190</v>
@@ -12707,11 +12707,11 @@
         <v>416</v>
       </c>
       <c r="B196" s="5">
-        <v>46161.64006346065</v>
+        <v>46161.47339679398</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46161.846870243055</v>
+        <v>46161.68020357639</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>190</v>
@@ -12760,11 +12760,11 @@
         <v>417</v>
       </c>
       <c r="B197" s="9">
-        <v>46161.58120399306</v>
+        <v>46161.41453732639</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46161.84710645833</v>
+        <v>46161.68043979167</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>418</v>
@@ -12821,11 +12821,11 @@
         <v>419</v>
       </c>
       <c r="B198" s="5">
-        <v>46161.58120755787</v>
+        <v>46161.4145408912</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46161.847077812505</v>
+        <v>46161.68041114583</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>190</v>
@@ -12872,11 +12872,11 @@
         <v>421</v>
       </c>
       <c r="B199" s="9">
-        <v>46161.6401252662</v>
+        <v>46161.47345859953</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46161.84707505787</v>
+        <v>46161.6804083912</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>190</v>
@@ -12923,11 +12923,11 @@
         <v>422</v>
       </c>
       <c r="B200" s="5">
-        <v>46161.64014137731</v>
+        <v>46161.47347471065</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46161.847072476856</v>
+        <v>46161.680405810184</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>190</v>
@@ -12974,11 +12974,11 @@
         <v>423</v>
       </c>
       <c r="B201" s="9">
-        <v>46161.64015293981</v>
+        <v>46161.47348627315</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46161.84706930556</v>
+        <v>46161.680402638885</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>190</v>
@@ -13025,11 +13025,11 @@
         <v>424</v>
       </c>
       <c r="B202" s="5">
-        <v>46161.64016740741</v>
+        <v>46161.47350074074</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46161.847066608796</v>
+        <v>46161.680399942124</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>190</v>
@@ -13076,11 +13076,11 @@
         <v>425</v>
       </c>
       <c r="B203" s="9">
-        <v>46161.640203877316</v>
+        <v>46161.47353721065</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46161.84706402778</v>
+        <v>46161.68039736111</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>190</v>
@@ -13127,11 +13127,11 @@
         <v>426</v>
       </c>
       <c r="B204" s="5">
-        <v>46161.64021510417</v>
+        <v>46161.4735484375</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46161.84706112268</v>
+        <v>46161.68039445602</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>190</v>
@@ -13178,11 +13178,11 @@
         <v>427</v>
       </c>
       <c r="B205" s="9">
-        <v>46161.64022702546</v>
+        <v>46161.4735603588</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46161.847053425925</v>
+        <v>46161.68038675926</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>190</v>
@@ -13229,11 +13229,11 @@
         <v>428</v>
       </c>
       <c r="B206" s="5">
-        <v>46161.64023784723</v>
+        <v>46161.473571180555</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46161.8470527662</v>
+        <v>46161.68038609954</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>190</v>
@@ -13280,11 +13280,11 @@
         <v>429</v>
       </c>
       <c r="B207" s="9">
-        <v>46161.64025311342</v>
+        <v>46161.47358644676</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46161.84705210648</v>
+        <v>46161.68038543982</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>190</v>
@@ -13331,11 +13331,11 @@
         <v>430</v>
       </c>
       <c r="B208" s="5">
-        <v>46161.58121466435</v>
+        <v>46161.41454799769</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46161.84730193287</v>
+        <v>46161.6806352662</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>431</v>
@@ -13394,11 +13394,11 @@
         <v>433</v>
       </c>
       <c r="B209" s="9">
-        <v>46161.58125732639</v>
+        <v>46161.414590659726</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46161.84728091436</v>
+        <v>46161.680614247685</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>190</v>
@@ -13445,11 +13445,11 @@
         <v>434</v>
       </c>
       <c r="B210" s="5">
-        <v>46161.640307905094</v>
+        <v>46161.47364123842</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46161.84727769676</v>
+        <v>46161.6806110301</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>190</v>
@@ -13496,11 +13496,11 @@
         <v>435</v>
       </c>
       <c r="B211" s="9">
-        <v>46161.64031635417</v>
+        <v>46161.4736496875</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46161.84727525463</v>
+        <v>46161.680608587965</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>190</v>
@@ -13547,11 +13547,11 @@
         <v>436</v>
       </c>
       <c r="B212" s="5">
-        <v>46161.64032832176</v>
+        <v>46161.473661655094</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46161.84727247685</v>
+        <v>46161.68060581019</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>190</v>
@@ -13598,11 +13598,11 @@
         <v>437</v>
       </c>
       <c r="B213" s="9">
-        <v>46161.640337986115</v>
+        <v>46161.47367131944</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46161.84726945602</v>
+        <v>46161.68060278935</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>190</v>
@@ -13649,11 +13649,11 @@
         <v>438</v>
       </c>
       <c r="B214" s="5">
-        <v>46161.64035862268</v>
+        <v>46161.473691956024</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46161.84726638889</v>
+        <v>46161.680599722225</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>190</v>
@@ -13700,11 +13700,11 @@
         <v>439</v>
       </c>
       <c r="B215" s="9">
-        <v>46161.64036773148</v>
+        <v>46161.47370106481</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46161.84726359954</v>
+        <v>46161.68059693287</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>190</v>
@@ -13751,11 +13751,11 @@
         <v>440</v>
       </c>
       <c r="B216" s="5">
-        <v>46161.64037657407</v>
+        <v>46161.47370990741</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46161.84726060185</v>
+        <v>46161.68059393518</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>190</v>
@@ -13802,11 +13802,11 @@
         <v>441</v>
       </c>
       <c r="B217" s="9">
-        <v>46161.64038473379</v>
+        <v>46161.47371806713</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46161.847254699074</v>
+        <v>46161.68058803241</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>190</v>
@@ -13853,11 +13853,11 @@
         <v>442</v>
       </c>
       <c r="B218" s="5">
-        <v>46161.64039350694</v>
+        <v>46161.47372684028</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46161.8472540625</v>
+        <v>46161.68058739584</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>190</v>
@@ -13904,11 +13904,11 @@
         <v>443</v>
       </c>
       <c r="B219" s="9">
-        <v>46161.581262824075</v>
+        <v>46161.41459615741</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46161.84801045139</v>
+        <v>46161.68134378472</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>444</v>
@@ -13951,11 +13951,11 @@
         <v>446</v>
       </c>
       <c r="B220" s="5">
-        <v>46161.58126615741</v>
+        <v>46161.414599490745</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46161.84764756945</v>
+        <v>46161.680980902776</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>447</v>
@@ -14014,11 +14014,11 @@
         <v>450</v>
       </c>
       <c r="B221" s="9">
-        <v>46161.581270821756</v>
+        <v>46161.41460415509</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46198.80656221065</v>
+        <v>46198.63989554398</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>451</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2069,13 +2069,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46161.41396914352</v>
+        <v>46161.58063581018</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.71184347222</v>
+        <v>46175.87851013889</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.71185716435</v>
+        <v>46175.87852383102</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2122,13 +2122,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46161.41407934028</v>
+        <v>46161.58074600695</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.71181634259</v>
+        <v>46175.87848300926</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.71184372685</v>
+        <v>46175.87851039352</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2185,13 +2185,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46161.414082407406</v>
+        <v>46161.58074907407</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.711817187504</v>
+        <v>46175.87848385416</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.71184388889</v>
+        <v>46175.87851055556</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2248,13 +2248,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46161.41408527778</v>
+        <v>46161.58075194445</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.71181774305</v>
+        <v>46175.878484409724</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.71184383101</v>
+        <v>46175.878510497685</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2311,13 +2311,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46161.414087997684</v>
+        <v>46161.58075466435</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.71181836806</v>
+        <v>46175.87848503472</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.71184425926</v>
+        <v>46175.878510925926</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2374,13 +2374,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46161.41409119213</v>
+        <v>46161.5807578588</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.711819097225</v>
+        <v>46175.87848576389</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.71184429398</v>
+        <v>46175.87851096065</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2437,11 +2437,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46161.413972951384</v>
+        <v>46161.580639618056</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46198.63990488426</v>
+        <v>46198.80657155093</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2486,13 +2486,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46161.41409464121</v>
+        <v>46161.580761307865</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.507599756944</v>
+        <v>46197.67426642361</v>
       </c>
       <c r="D11" s="9">
-        <v>46198.63989533565</v>
+        <v>46198.80656200231</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2551,13 +2551,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46161.4140996412</v>
+        <v>46161.580766307874</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.50841496528</v>
+        <v>46197.67508163194</v>
       </c>
       <c r="D12" s="5">
-        <v>46198.63989534722</v>
+        <v>46198.80656201389</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2616,13 +2616,13 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46161.41410475694</v>
+        <v>46161.580771423614</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.51061320602</v>
+        <v>46197.67727987269</v>
       </c>
       <c r="D13" s="9">
-        <v>46198.63989532407</v>
+        <v>46198.80656199074</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2681,11 +2681,11 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46161.413977372686</v>
+        <v>46161.58064403935</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46204.73400094907</v>
+        <v>46204.900667615744</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2728,13 +2728,13 @@
         <v>68</v>
       </c>
       <c r="B15" s="9">
-        <v>46161.414116875</v>
+        <v>46161.58078354166</v>
       </c>
       <c r="C15" s="9">
-        <v>46198.638878171296</v>
+        <v>46198.80554483796</v>
       </c>
       <c r="D15" s="9">
-        <v>46198.640723599536</v>
+        <v>46198.8073902662</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>69</v>
@@ -2793,11 +2793,11 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46161.414122013884</v>
+        <v>46161.580788680556</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.508435289354</v>
+        <v>46197.67510195602</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2856,13 +2856,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46161.41412696759</v>
+        <v>46161.58079363426</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.42192472222</v>
+        <v>46197.58859138889</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.50843519676</v>
+        <v>46197.675101863424</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2921,13 +2921,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46161.41413237268</v>
+        <v>46161.58079903935</v>
       </c>
       <c r="C18" s="5">
-        <v>46204.73399418981</v>
+        <v>46204.90066085648</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.7342859375</v>
+        <v>46204.90095260416</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2986,13 +2986,13 @@
         <v>84</v>
       </c>
       <c r="B19" s="9">
-        <v>46161.414137071755</v>
+        <v>46161.58080373843</v>
       </c>
       <c r="C19" s="9">
-        <v>46204.73434888889</v>
+        <v>46204.90101555556</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.73472998843</v>
+        <v>46204.90139665509</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>85</v>
@@ -3051,13 +3051,13 @@
         <v>87</v>
       </c>
       <c r="B20" s="5">
-        <v>46161.414140740744</v>
+        <v>46161.58080740741</v>
       </c>
       <c r="C20" s="5">
-        <v>46204.73513585648</v>
+        <v>46204.90180252315</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.73553802083</v>
+        <v>46204.9022046875</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -3116,13 +3116,13 @@
         <v>90</v>
       </c>
       <c r="B21" s="9">
-        <v>46161.41414407408</v>
+        <v>46161.580810740736</v>
       </c>
       <c r="C21" s="9">
-        <v>46204.73508663195</v>
+        <v>46204.90175329861</v>
       </c>
       <c r="D21" s="9">
-        <v>46204.73510194445</v>
+        <v>46204.90176861111</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -3181,11 +3181,11 @@
         <v>93</v>
       </c>
       <c r="B22" s="5">
-        <v>46161.4139812963</v>
+        <v>46161.58064796297</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46161.571204548614</v>
+        <v>46161.73787121528</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -3228,11 +3228,11 @@
         <v>96</v>
       </c>
       <c r="B23" s="9">
-        <v>46161.414148055555</v>
+        <v>46161.58081472223</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.71271201389</v>
+        <v>46169.879378680555</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>97</v>
@@ -3291,11 +3291,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46161.414152349535</v>
+        <v>46161.580819016206</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.71297789352</v>
+        <v>46169.879644560184</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3350,11 +3350,11 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46161.41415684028</v>
+        <v>46161.58082350694</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.7130025463</v>
+        <v>46169.87966921296</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3409,11 +3409,11 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46161.414161574074</v>
+        <v>46161.58082824074</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46192.69200952546</v>
+        <v>46192.85867619213</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3472,11 +3472,11 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46161.41416587963</v>
+        <v>46161.5808325463</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.42193370371</v>
+        <v>46197.58860037037</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3531,11 +3531,11 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46161.41417030092</v>
+        <v>46161.580836967594</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46171.00685518519</v>
+        <v>46171.17352185185</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3590,11 +3590,11 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46161.41417498843</v>
+        <v>46161.58084165509</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46198.63911797454</v>
+        <v>46198.805784641205</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3653,13 +3653,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46161.414179363426</v>
+        <v>46161.58084603009</v>
       </c>
       <c r="C30" s="5">
-        <v>46198.639059814814</v>
+        <v>46198.805726481485</v>
       </c>
       <c r="D30" s="5">
-        <v>46198.63906128472</v>
+        <v>46198.80572795139</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3714,11 +3714,11 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46161.414183773144</v>
+        <v>46161.580850439816</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46198.63906524306</v>
+        <v>46198.80573190972</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3773,13 +3773,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46161.41418836806</v>
+        <v>46161.58085503472</v>
       </c>
       <c r="C32" s="5">
-        <v>46198.639108055555</v>
+        <v>46198.80577472222</v>
       </c>
       <c r="D32" s="5">
-        <v>46198.63910956019</v>
+        <v>46198.80577622685</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3834,11 +3834,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46161.41419274306</v>
+        <v>46161.58085940972</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.71276568287</v>
+        <v>46205.61009494213</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>130</v>
@@ -3897,11 +3897,13 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46161.41419697917</v>
-      </c>
-      <c r="C34" s="6"/>
+        <v>46161.58086364584</v>
+      </c>
+      <c r="C34" s="5">
+        <v>46205.610087141205</v>
+      </c>
       <c r="D34" s="5">
-        <v>46204.73400034722</v>
+        <v>46205.61008960648</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3956,11 +3958,11 @@
         <v>137</v>
       </c>
       <c r="B35" s="9">
-        <v>46161.41420165509</v>
+        <v>46161.58086832176</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.7131621875</v>
+        <v>46205.61009606482</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -4015,11 +4017,11 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46161.4142065625</v>
+        <v>46161.58087322916</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.71277699074</v>
+        <v>46205.61025262732</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -4078,11 +4080,13 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46161.41426435186</v>
-      </c>
-      <c r="C37" s="10"/>
+        <v>46161.580931018514</v>
+      </c>
+      <c r="C37" s="9">
+        <v>46205.610246435186</v>
+      </c>
       <c r="D37" s="9">
-        <v>46204.734355196764</v>
+        <v>46205.610248032404</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>86</v>
@@ -4131,11 +4135,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46161.41426980324</v>
+        <v>46161.58093646991</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.713198495374</v>
+        <v>46205.610401655096</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -4184,11 +4188,11 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46161.41427443287</v>
+        <v>46161.580941099535</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.71278662037</v>
+        <v>46169.87945328704</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -4247,11 +4251,11 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46161.41427865741</v>
+        <v>46161.58094532407</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46204.735091932875</v>
+        <v>46204.90175859953</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>92</v>
@@ -4300,11 +4304,11 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46161.41428331019</v>
+        <v>46161.58094997685</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.713248541666</v>
+        <v>46169.87991520834</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4353,11 +4357,11 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46161.4142878125</v>
+        <v>46161.58095447917</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.71326314815</v>
+        <v>46169.879929814815</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4406,11 +4410,11 @@
         <v>162</v>
       </c>
       <c r="B43" s="9">
-        <v>46161.41429076389</v>
+        <v>46161.58095743056</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.712851585646</v>
+        <v>46169.87951825232</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>163</v>
@@ -4469,11 +4473,11 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46161.41429424769</v>
+        <v>46161.58096091435</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46204.73514168982</v>
+        <v>46205.61062071759</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>89</v>
@@ -4522,11 +4526,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46161.41429832176</v>
+        <v>46161.580964988425</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.713330983795</v>
+        <v>46169.87999765047</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>168</v>
@@ -4575,11 +4579,11 @@
         <v>170</v>
       </c>
       <c r="B46" s="5">
-        <v>46161.41398572917</v>
+        <v>46161.58065239583</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46198.640800023146</v>
+        <v>46198.80746668982</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4624,13 +4628,13 @@
         <v>173</v>
       </c>
       <c r="B47" s="9">
-        <v>46161.41430311343</v>
+        <v>46161.580969780094</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.538364583335</v>
+        <v>46197.70503125</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.53837978009</v>
+        <v>46197.70504644676</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>174</v>
@@ -4689,13 +4693,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46161.414308402775</v>
+        <v>46161.580975069446</v>
       </c>
       <c r="C48" s="5">
-        <v>46198.64078266204</v>
+        <v>46198.8074493287</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.640800995374</v>
+        <v>46198.80746766204</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4754,13 +4758,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46161.414314340276</v>
+        <v>46161.58098100695</v>
       </c>
       <c r="C49" s="9">
-        <v>46198.640827800926</v>
+        <v>46198.80749446759</v>
       </c>
       <c r="D49" s="9">
-        <v>46198.640844814814</v>
+        <v>46198.807511481486</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>82</v>
@@ -4819,11 +4823,11 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46161.414324502315</v>
+        <v>46161.58099116899</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46161.678096435186</v>
+        <v>46161.84476310185</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4882,11 +4886,11 @@
         <v>191</v>
       </c>
       <c r="B51" s="9">
-        <v>46161.41432752315</v>
+        <v>46161.58099418982</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46161.67809940972</v>
+        <v>46161.84476607639</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4933,11 +4937,11 @@
         <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46161.47299822917</v>
+        <v>46161.63966489583</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46161.678096805554</v>
+        <v>46161.844763472225</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4984,11 +4988,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="9">
-        <v>46161.473005949076</v>
+        <v>46161.63967261574</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46161.67809402778</v>
+        <v>46161.84476069444</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -5035,11 +5039,11 @@
         <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46161.47301722222</v>
+        <v>46161.63968388889</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46161.678091064816</v>
+        <v>46161.84475773148</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5086,11 +5090,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="9">
-        <v>46161.47302608796</v>
+        <v>46161.63969275463</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46161.67808804398</v>
+        <v>46161.84475471065</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>190</v>
@@ -5137,11 +5141,11 @@
         <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46161.47303854166</v>
+        <v>46161.639705208334</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46161.67808508102</v>
+        <v>46161.84475174769</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>190</v>
@@ -5188,11 +5192,11 @@
         <v>199</v>
       </c>
       <c r="B57" s="9">
-        <v>46161.47304880787</v>
+        <v>46161.639715474535</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46161.67808196759</v>
+        <v>46161.84474863426</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>190</v>
@@ -5239,11 +5243,11 @@
         <v>200</v>
       </c>
       <c r="B58" s="5">
-        <v>46161.47306012732</v>
+        <v>46161.63972679398</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46161.67807836806</v>
+        <v>46161.84474503472</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>190</v>
@@ -5290,11 +5294,11 @@
         <v>201</v>
       </c>
       <c r="B59" s="9">
-        <v>46161.47307637731</v>
+        <v>46161.63974304398</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46161.67807167824</v>
+        <v>46161.84473834491</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>190</v>
@@ -5341,11 +5345,11 @@
         <v>202</v>
       </c>
       <c r="B60" s="5">
-        <v>46161.47308603009</v>
+        <v>46161.63975269676</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46161.67807086806</v>
+        <v>46161.84473753472</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>190</v>
@@ -5392,11 +5396,11 @@
         <v>203</v>
       </c>
       <c r="B61" s="9">
-        <v>46161.41433151621</v>
+        <v>46161.58099818287</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.629804780096</v>
+        <v>46161.79647144676</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>204</v>
@@ -5439,11 +5443,11 @@
         <v>206</v>
       </c>
       <c r="B62" s="5">
-        <v>46161.41433479167</v>
+        <v>46161.58100145833</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46161.67817583334</v>
+        <v>46161.844842499995</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>207</v>
@@ -5502,11 +5506,11 @@
         <v>211</v>
       </c>
       <c r="B63" s="9">
-        <v>46161.41433947917</v>
+        <v>46161.58100614583</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.67825182871</v>
+        <v>46161.84491849537</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>212</v>
@@ -5565,11 +5569,11 @@
         <v>215</v>
       </c>
       <c r="B64" s="5">
-        <v>46161.414349722225</v>
+        <v>46161.58101638889</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46161.6781731713</v>
+        <v>46161.84483983796</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5628,11 +5632,11 @@
         <v>218</v>
       </c>
       <c r="B65" s="9">
-        <v>46161.41435432871</v>
+        <v>46161.58102099537</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46161.67824836806</v>
+        <v>46161.84491503472</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>219</v>
@@ -5691,11 +5695,11 @@
         <v>221</v>
       </c>
       <c r="B66" s="5">
-        <v>46161.414358055554</v>
+        <v>46161.581024722225</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46161.67816927083</v>
+        <v>46161.8448359375</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>222</v>
@@ -5754,11 +5758,11 @@
         <v>224</v>
       </c>
       <c r="B67" s="9">
-        <v>46161.41436197917</v>
+        <v>46161.58102864583</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46161.67824760417</v>
+        <v>46161.844914270834</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>223</v>
@@ -5817,11 +5821,11 @@
         <v>226</v>
       </c>
       <c r="B68" s="5">
-        <v>46161.41436540509</v>
+        <v>46161.58103207176</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46161.63111915509</v>
+        <v>46161.797785821764</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5864,11 +5868,11 @@
         <v>229</v>
       </c>
       <c r="B69" s="9">
-        <v>46161.41436790509</v>
+        <v>46161.58103457176</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46161.678511782404</v>
+        <v>46161.845178449075</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>230</v>
@@ -5927,11 +5931,11 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46161.41437296296</v>
+        <v>46161.58103962963</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46161.67848040509</v>
+        <v>46161.845147071755</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>190</v>
@@ -5980,11 +5984,11 @@
         <v>237</v>
       </c>
       <c r="B71" s="9">
-        <v>46161.415345138885</v>
+        <v>46161.582011805556</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46161.678476817135</v>
+        <v>46161.84514348379</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>190</v>
@@ -6033,11 +6037,11 @@
         <v>239</v>
       </c>
       <c r="B72" s="5">
-        <v>46161.415357164355</v>
+        <v>46161.58202383102</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46161.678473657405</v>
+        <v>46161.845140324076</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -6086,11 +6090,11 @@
         <v>241</v>
       </c>
       <c r="B73" s="9">
-        <v>46161.4159959838</v>
+        <v>46161.582662650464</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46161.67846998843</v>
+        <v>46161.845136655094</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>190</v>
@@ -6139,11 +6143,11 @@
         <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46161.416006562504</v>
+        <v>46161.58267322917</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46161.67846685185</v>
+        <v>46161.845133518524</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -6192,11 +6196,11 @@
         <v>243</v>
       </c>
       <c r="B75" s="9">
-        <v>46161.41603467593</v>
+        <v>46161.58270134259</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46161.67846407407</v>
+        <v>46161.84513074074</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -6245,11 +6249,11 @@
         <v>244</v>
       </c>
       <c r="B76" s="5">
-        <v>46161.416047604165</v>
+        <v>46161.58271427083</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46161.67846136574</v>
+        <v>46161.84512803241</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>190</v>
@@ -6298,11 +6302,11 @@
         <v>246</v>
       </c>
       <c r="B77" s="9">
-        <v>46161.41605984954</v>
+        <v>46161.58272651621</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46161.67845740741</v>
+        <v>46161.84512407407</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>190</v>
@@ -6351,11 +6355,11 @@
         <v>247</v>
       </c>
       <c r="B78" s="5">
-        <v>46161.416112962965</v>
+        <v>46161.58277962963</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46161.67845125</v>
+        <v>46161.845117916666</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>190</v>
@@ -6404,11 +6408,11 @@
         <v>249</v>
       </c>
       <c r="B79" s="9">
-        <v>46161.4161237963</v>
+        <v>46161.58279046296</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46161.67845054399</v>
+        <v>46161.84511721064</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>190</v>
@@ -6457,11 +6461,11 @@
         <v>250</v>
       </c>
       <c r="B80" s="5">
-        <v>46161.41437871528</v>
+        <v>46161.58104538194</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46161.67867814815</v>
+        <v>46161.845344814814</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>251</v>
@@ -6520,11 +6524,11 @@
         <v>252</v>
       </c>
       <c r="B81" s="9">
-        <v>46161.414382372684</v>
+        <v>46161.58104903935</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46198.64085358796</v>
+        <v>46198.80752025463</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>190</v>
@@ -6573,11 +6577,11 @@
         <v>255</v>
       </c>
       <c r="B82" s="5">
-        <v>46161.4161674537</v>
+        <v>46161.582834120374</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46161.67866961806</v>
+        <v>46161.84533628472</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>190</v>
@@ -6626,11 +6630,11 @@
         <v>256</v>
       </c>
       <c r="B83" s="9">
-        <v>46161.416197928236</v>
+        <v>46161.58286459491</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46161.67866670139</v>
+        <v>46161.84533336805</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>190</v>
@@ -6679,11 +6683,11 @@
         <v>257</v>
       </c>
       <c r="B84" s="5">
-        <v>46161.41620715278</v>
+        <v>46161.58287381944</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46161.67866399305</v>
+        <v>46161.84533065972</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>190</v>
@@ -6732,11 +6736,11 @@
         <v>258</v>
       </c>
       <c r="B85" s="9">
-        <v>46161.416216990736</v>
+        <v>46161.58288365741</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46161.67866123843</v>
+        <v>46161.84532790509</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>190</v>
@@ -6785,11 +6789,11 @@
         <v>259</v>
       </c>
       <c r="B86" s="5">
-        <v>46161.416225891204</v>
+        <v>46161.58289255787</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46161.67865819445</v>
+        <v>46161.84532486111</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>190</v>
@@ -6838,11 +6842,11 @@
         <v>260</v>
       </c>
       <c r="B87" s="9">
-        <v>46161.41625876157</v>
+        <v>46161.58292542824</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46161.67865545139</v>
+        <v>46161.84532211805</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>190</v>
@@ -6891,11 +6895,11 @@
         <v>261</v>
       </c>
       <c r="B88" s="5">
-        <v>46161.41627030092</v>
+        <v>46161.58293696759</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46161.67865260417</v>
+        <v>46161.84531927083</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>190</v>
@@ -6944,11 +6948,11 @@
         <v>262</v>
       </c>
       <c r="B89" s="9">
-        <v>46161.41628615741</v>
+        <v>46161.58295282407</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46161.67864644676</v>
+        <v>46161.84531311343</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>190</v>
@@ -6997,11 +7001,11 @@
         <v>263</v>
       </c>
       <c r="B90" s="5">
-        <v>46161.41630106482</v>
+        <v>46161.58296773148</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46161.67864576389</v>
+        <v>46161.84531243055</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>190</v>
@@ -7050,11 +7054,11 @@
         <v>264</v>
       </c>
       <c r="B91" s="9">
-        <v>46161.414387094905</v>
+        <v>46161.581053761576</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46161.67885978009</v>
+        <v>46161.84552644676</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>265</v>
@@ -7113,11 +7117,11 @@
         <v>266</v>
       </c>
       <c r="B92" s="5">
-        <v>46161.41439075231</v>
+        <v>46161.58105741898</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46198.64085415509</v>
+        <v>46198.80752082176</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>190</v>
@@ -7166,11 +7170,11 @@
         <v>268</v>
       </c>
       <c r="B93" s="9">
-        <v>46161.41637327547</v>
+        <v>46161.583039942125</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46161.678842141206</v>
+        <v>46161.84550880787</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>190</v>
@@ -7219,11 +7223,11 @@
         <v>269</v>
       </c>
       <c r="B94" s="5">
-        <v>46161.41639048611</v>
+        <v>46161.58305715278</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46161.678838657404</v>
+        <v>46161.845505324076</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>190</v>
@@ -7272,11 +7276,11 @@
         <v>270</v>
       </c>
       <c r="B95" s="9">
-        <v>46161.41641002314</v>
+        <v>46161.583076689814</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46161.678835914354</v>
+        <v>46161.84550258102</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>190</v>
@@ -7325,11 +7329,11 @@
         <v>271</v>
       </c>
       <c r="B96" s="5">
-        <v>46161.41642219907</v>
+        <v>46161.58308886574</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46161.67883261574</v>
+        <v>46161.84549928241</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>190</v>
@@ -7378,11 +7382,11 @@
         <v>272</v>
       </c>
       <c r="B97" s="9">
-        <v>46161.41643353009</v>
+        <v>46161.58310019676</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46161.678828668984</v>
+        <v>46161.84549533565</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>190</v>
@@ -7431,11 +7435,11 @@
         <v>273</v>
       </c>
       <c r="B98" s="5">
-        <v>46161.41644422454</v>
+        <v>46161.5831108912</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46161.67882539352</v>
+        <v>46161.84549206018</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>190</v>
@@ -7484,11 +7488,11 @@
         <v>274</v>
       </c>
       <c r="B99" s="9">
-        <v>46161.416461782406</v>
+        <v>46161.58312844907</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46161.67882221065</v>
+        <v>46161.84548887731</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>190</v>
@@ -7537,11 +7541,11 @@
         <v>275</v>
       </c>
       <c r="B100" s="5">
-        <v>46161.41634108796</v>
+        <v>46161.58300775463</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46161.67881563657</v>
+        <v>46161.84548230324</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>190</v>
@@ -7590,11 +7594,11 @@
         <v>276</v>
       </c>
       <c r="B101" s="9">
-        <v>46161.47283520833</v>
+        <v>46161.639501875004</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46161.6788149537</v>
+        <v>46161.845481620374</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>190</v>
@@ -7643,11 +7647,11 @@
         <v>277</v>
       </c>
       <c r="B102" s="5">
-        <v>46161.414438402775</v>
+        <v>46161.58110506945</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46161.64110194445</v>
+        <v>46161.80776861111</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>204</v>
@@ -7690,11 +7694,11 @@
         <v>279</v>
       </c>
       <c r="B103" s="9">
-        <v>46161.414441863424</v>
+        <v>46161.581108530096</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46176.021446342595</v>
+        <v>46176.18811300926</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>280</v>
@@ -7753,11 +7757,11 @@
         <v>282</v>
       </c>
       <c r="B104" s="5">
-        <v>46161.41444703704</v>
+        <v>46161.58111370371</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46161.67894248843</v>
+        <v>46161.84560915509</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>283</v>
@@ -7816,11 +7820,11 @@
         <v>285</v>
       </c>
       <c r="B105" s="9">
-        <v>46161.4144517824</v>
+        <v>46161.581118449074</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46161.67893978009</v>
+        <v>46161.84560644676</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>286</v>
@@ -7879,11 +7883,11 @@
         <v>288</v>
       </c>
       <c r="B106" s="5">
-        <v>46161.41445644676</v>
+        <v>46161.58112311343</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46161.67893543981</v>
+        <v>46161.84560210648</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>289</v>
@@ -7942,11 +7946,11 @@
         <v>291</v>
       </c>
       <c r="B107" s="9">
-        <v>46161.41446035879</v>
+        <v>46161.58112702546</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46161.667206956015</v>
+        <v>46161.83387362269</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>292</v>
@@ -7989,11 +7993,11 @@
         <v>294</v>
       </c>
       <c r="B108" s="5">
-        <v>46161.41446318287</v>
+        <v>46161.58112984954</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46161.67911563657</v>
+        <v>46161.84578230324</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>295</v>
@@ -8052,11 +8056,11 @@
         <v>297</v>
       </c>
       <c r="B109" s="9">
-        <v>46161.41446888889</v>
+        <v>46161.581135555556</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46161.67911027778</v>
+        <v>46161.84577694444</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>298</v>
@@ -8105,11 +8109,11 @@
         <v>299</v>
       </c>
       <c r="B110" s="5">
-        <v>46161.41651063657</v>
+        <v>46161.58317730324</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46161.67910700232</v>
+        <v>46161.84577366898</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -8158,11 +8162,11 @@
         <v>300</v>
       </c>
       <c r="B111" s="9">
-        <v>46161.416520914354</v>
+        <v>46161.58318758102</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46161.67910421296</v>
+        <v>46161.845770879634</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>190</v>
@@ -8211,11 +8215,11 @@
         <v>301</v>
       </c>
       <c r="B112" s="5">
-        <v>46161.416530925926</v>
+        <v>46161.5831975926</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46161.67910042824</v>
+        <v>46161.84576709491</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>190</v>
@@ -8264,11 +8268,11 @@
         <v>302</v>
       </c>
       <c r="B113" s="9">
-        <v>46161.41653990741</v>
+        <v>46161.58320657407</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46161.67909748842</v>
+        <v>46161.84576415509</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>190</v>
@@ -8317,11 +8321,11 @@
         <v>303</v>
       </c>
       <c r="B114" s="5">
-        <v>46161.41655484954</v>
+        <v>46161.58322151621</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46161.67909415509</v>
+        <v>46161.84576082176</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>190</v>
@@ -8370,11 +8374,11 @@
         <v>304</v>
       </c>
       <c r="B115" s="9">
-        <v>46161.41656050926</v>
+        <v>46161.58322717593</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46161.679083738425</v>
+        <v>46161.84575040509</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>190</v>
@@ -8423,11 +8427,11 @@
         <v>305</v>
       </c>
       <c r="B116" s="5">
-        <v>46161.41657582176</v>
+        <v>46161.58324248843</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46161.67908300926</v>
+        <v>46161.84574967592</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8476,11 +8480,11 @@
         <v>306</v>
       </c>
       <c r="B117" s="9">
-        <v>46161.41658736111</v>
+        <v>46161.58325402778</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46161.6790822801</v>
+        <v>46161.845748946755</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8529,11 +8533,11 @@
         <v>307</v>
       </c>
       <c r="B118" s="5">
-        <v>46161.41659625</v>
+        <v>46161.58326291667</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46161.67908155093</v>
+        <v>46161.84574821759</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8582,11 +8586,11 @@
         <v>308</v>
       </c>
       <c r="B119" s="9">
-        <v>46161.41447261574</v>
+        <v>46161.58113928241</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46161.6793047338</v>
+        <v>46161.845971400464</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>309</v>
@@ -8645,11 +8649,11 @@
         <v>310</v>
       </c>
       <c r="B120" s="5">
-        <v>46161.414476157406</v>
+        <v>46161.58114282407</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46198.640854513884</v>
+        <v>46198.807521180555</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8698,11 +8702,11 @@
         <v>313</v>
       </c>
       <c r="B121" s="9">
-        <v>46161.41921576389</v>
+        <v>46161.585882430554</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46198.64083329861</v>
+        <v>46198.807499965274</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>190</v>
@@ -8751,11 +8755,11 @@
         <v>315</v>
       </c>
       <c r="B122" s="5">
-        <v>46161.419236319445</v>
+        <v>46161.58590298611</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46198.64083396991</v>
+        <v>46198.80750063657</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8804,11 +8808,11 @@
         <v>317</v>
       </c>
       <c r="B123" s="9">
-        <v>46161.41925319444</v>
+        <v>46161.585919861114</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46198.64083456018</v>
+        <v>46198.80750122685</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>190</v>
@@ -8857,11 +8861,11 @@
         <v>318</v>
       </c>
       <c r="B124" s="5">
-        <v>46161.419260509254</v>
+        <v>46161.585927175925</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46198.64083512731</v>
+        <v>46198.807501793985</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>190</v>
@@ -8910,11 +8914,11 @@
         <v>319</v>
       </c>
       <c r="B125" s="9">
-        <v>46161.41926643519</v>
+        <v>46161.58593310185</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46198.6408357176</v>
+        <v>46198.807502384254</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>190</v>
@@ -8963,11 +8967,11 @@
         <v>321</v>
       </c>
       <c r="B126" s="5">
-        <v>46161.419270729166</v>
+        <v>46161.58593739584</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46198.64083628472</v>
+        <v>46198.807502951386</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -9016,11 +9020,11 @@
         <v>322</v>
       </c>
       <c r="B127" s="9">
-        <v>46161.419279236114</v>
+        <v>46161.58594590278</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46198.6408371412</v>
+        <v>46198.80750380787</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>190</v>
@@ -9069,11 +9073,11 @@
         <v>323</v>
       </c>
       <c r="B128" s="5">
-        <v>46161.41928962963</v>
+        <v>46161.5859562963</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46198.6408377662</v>
+        <v>46198.80750443287</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -9122,11 +9126,11 @@
         <v>324</v>
       </c>
       <c r="B129" s="9">
-        <v>46161.4195224537</v>
+        <v>46161.58618912037</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46198.64083846065</v>
+        <v>46198.80750512732</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>190</v>
@@ -9175,11 +9179,11 @@
         <v>326</v>
       </c>
       <c r="B130" s="5">
-        <v>46161.414480949075</v>
+        <v>46161.58114761574</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46161.679458240746</v>
+        <v>46161.8461249074</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>327</v>
@@ -9238,11 +9242,11 @@
         <v>328</v>
       </c>
       <c r="B131" s="9">
-        <v>46161.41448450231</v>
+        <v>46161.58115116898</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46198.64084424768</v>
+        <v>46198.807510914354</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9291,11 +9295,11 @@
         <v>331</v>
       </c>
       <c r="B132" s="5">
-        <v>46161.41937046296</v>
+        <v>46161.58603712963</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46198.64083908565</v>
+        <v>46198.80750575232</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9344,11 +9348,11 @@
         <v>332</v>
       </c>
       <c r="B133" s="9">
-        <v>46161.41937826389</v>
+        <v>46161.586044930555</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46198.64083953704</v>
+        <v>46198.8075062037</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>190</v>
@@ -9397,11 +9401,11 @@
         <v>334</v>
       </c>
       <c r="B134" s="5">
-        <v>46161.41939224537</v>
+        <v>46161.58605891204</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46198.64084</v>
+        <v>46198.807506666664</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9450,11 +9454,11 @@
         <v>335</v>
       </c>
       <c r="B135" s="9">
-        <v>46161.41940101852</v>
+        <v>46161.58606768519</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46198.64084047454</v>
+        <v>46198.8075071412</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>190</v>
@@ -9503,11 +9507,11 @@
         <v>337</v>
       </c>
       <c r="B136" s="5">
-        <v>46161.41940908565</v>
+        <v>46161.58607575232</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46198.64084104166</v>
+        <v>46198.807507708334</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>190</v>
@@ -9556,11 +9560,11 @@
         <v>338</v>
       </c>
       <c r="B137" s="9">
-        <v>46161.4194221875</v>
+        <v>46161.586088854165</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46198.640841493056</v>
+        <v>46198.80750815972</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>190</v>
@@ -9609,11 +9613,11 @@
         <v>339</v>
       </c>
       <c r="B138" s="5">
-        <v>46161.41942903935</v>
+        <v>46161.58609570602</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46198.64084196759</v>
+        <v>46198.80750863426</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>190</v>
@@ -9662,11 +9666,11 @@
         <v>341</v>
       </c>
       <c r="B139" s="9">
-        <v>46161.41944391203</v>
+        <v>46161.586110578704</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46198.64084241899</v>
+        <v>46198.807509085644</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>190</v>
@@ -9715,11 +9719,11 @@
         <v>342</v>
       </c>
       <c r="B140" s="5">
-        <v>46161.4194558912</v>
+        <v>46161.58612255787</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46198.64084289352</v>
+        <v>46198.80750956018</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>190</v>
@@ -9768,11 +9772,11 @@
         <v>343</v>
       </c>
       <c r="B141" s="9">
-        <v>46161.41448976852</v>
+        <v>46161.58115643519</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46161.679629502316</v>
+        <v>46161.84629616898</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>344</v>
@@ -9831,11 +9835,11 @@
         <v>345</v>
       </c>
       <c r="B142" s="5">
-        <v>46161.41449326389</v>
+        <v>46161.58115993056</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46198.64085509259</v>
+        <v>46198.807521759256</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>298</v>
@@ -9884,11 +9888,11 @@
         <v>348</v>
       </c>
       <c r="B143" s="9">
-        <v>46161.419559745365</v>
+        <v>46161.58622641204</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46198.64084332176</v>
+        <v>46198.80750998843</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>190</v>
@@ -9937,11 +9941,11 @@
         <v>349</v>
       </c>
       <c r="B144" s="5">
-        <v>46161.419569328704</v>
+        <v>46161.586235995375</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46198.64084375</v>
+        <v>46198.807510416664</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -9990,11 +9994,11 @@
         <v>350</v>
       </c>
       <c r="B145" s="9">
-        <v>46161.419580104164</v>
+        <v>46161.586246770836</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46161.67961337963</v>
+        <v>46161.846280046295</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>190</v>
@@ -10043,11 +10047,11 @@
         <v>352</v>
       </c>
       <c r="B146" s="5">
-        <v>46161.41958976851</v>
+        <v>46161.586256435185</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46161.67961032408</v>
+        <v>46161.84627699074</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -10096,11 +10100,11 @@
         <v>354</v>
       </c>
       <c r="B147" s="9">
-        <v>46161.419599166664</v>
+        <v>46161.586265833335</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46161.67960728009</v>
+        <v>46161.84627394676</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>190</v>
@@ -10149,11 +10153,11 @@
         <v>355</v>
       </c>
       <c r="B148" s="5">
-        <v>46161.41960900463</v>
+        <v>46161.586275671296</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46161.679604467594</v>
+        <v>46161.84627113426</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>190</v>
@@ -10202,11 +10206,11 @@
         <v>356</v>
       </c>
       <c r="B149" s="9">
-        <v>46161.41962519676</v>
+        <v>46161.58629186342</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46161.67960173611</v>
+        <v>46161.846268402776</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>190</v>
@@ -10255,11 +10259,11 @@
         <v>357</v>
       </c>
       <c r="B150" s="5">
-        <v>46161.41964212963</v>
+        <v>46161.58630879629</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46161.67959555556</v>
+        <v>46161.84626222222</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>190</v>
@@ -10308,11 +10312,11 @@
         <v>358</v>
       </c>
       <c r="B151" s="9">
-        <v>46161.41965496528</v>
+        <v>46161.58632163194</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46161.679594953705</v>
+        <v>46161.84626162037</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>190</v>
@@ -10361,11 +10365,11 @@
         <v>359</v>
       </c>
       <c r="B152" s="5">
-        <v>46161.41449802084</v>
+        <v>46161.5811646875</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46161.67977259259</v>
+        <v>46161.84643925926</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>360</v>
@@ -10424,11 +10428,11 @@
         <v>361</v>
       </c>
       <c r="B153" s="9">
-        <v>46161.41450162037</v>
+        <v>46161.58116828704</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46161.67977555556</v>
+        <v>46161.84644222222</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>190</v>
@@ -10475,11 +10479,11 @@
         <v>363</v>
       </c>
       <c r="B154" s="5">
-        <v>46161.47245956019</v>
+        <v>46161.63912622685</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46161.679772627314</v>
+        <v>46161.84643929398</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>190</v>
@@ -10526,11 +10530,11 @@
         <v>364</v>
       </c>
       <c r="B155" s="9">
-        <v>46161.47247070602</v>
+        <v>46161.63913737268</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46161.67976976852</v>
+        <v>46161.84643643518</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>190</v>
@@ -10577,11 +10581,11 @@
         <v>365</v>
       </c>
       <c r="B156" s="5">
-        <v>46161.47248053241</v>
+        <v>46161.63914719908</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46161.67976665509</v>
+        <v>46161.846433321756</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>190</v>
@@ -10628,11 +10632,11 @@
         <v>366</v>
       </c>
       <c r="B157" s="9">
-        <v>46161.4724908912</v>
+        <v>46161.639157557875</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46161.67976347222</v>
+        <v>46161.84643013889</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>190</v>
@@ -10679,11 +10683,11 @@
         <v>367</v>
       </c>
       <c r="B158" s="5">
-        <v>46161.47250552083</v>
+        <v>46161.6391721875</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46161.67975980324</v>
+        <v>46161.84642646991</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>190</v>
@@ -10730,11 +10734,11 @@
         <v>368</v>
       </c>
       <c r="B159" s="9">
-        <v>46161.47252072916</v>
+        <v>46161.639187395835</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46161.679756550926</v>
+        <v>46161.84642321759</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>190</v>
@@ -10781,11 +10785,11 @@
         <v>369</v>
       </c>
       <c r="B160" s="5">
-        <v>46161.47252862269</v>
+        <v>46161.639195289354</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46161.67975347222</v>
+        <v>46161.846420138885</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>190</v>
@@ -10832,11 +10836,11 @@
         <v>370</v>
       </c>
       <c r="B161" s="9">
-        <v>46161.472538842594</v>
+        <v>46161.63920550926</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46161.67974644676</v>
+        <v>46161.846413113424</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>190</v>
@@ -10883,11 +10887,11 @@
         <v>371</v>
       </c>
       <c r="B162" s="5">
-        <v>46161.47254766204</v>
+        <v>46161.63921432871</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46161.67974575231</v>
+        <v>46161.84641241898</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>190</v>
@@ -10934,11 +10938,11 @@
         <v>372</v>
       </c>
       <c r="B163" s="9">
-        <v>46161.414510856484</v>
+        <v>46161.58117752315</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46161.679938368055</v>
+        <v>46161.84660503472</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>373</v>
@@ -10997,11 +11001,11 @@
         <v>375</v>
       </c>
       <c r="B164" s="5">
-        <v>46161.41451471065</v>
+        <v>46161.58118137732</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46161.67991349537</v>
+        <v>46161.84658016203</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>190</v>
@@ -11050,11 +11054,11 @@
         <v>377</v>
       </c>
       <c r="B165" s="9">
-        <v>46161.472587094904</v>
+        <v>46161.639253761576</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46161.679910520834</v>
+        <v>46161.846577187505</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>190</v>
@@ -11103,11 +11107,11 @@
         <v>378</v>
       </c>
       <c r="B166" s="5">
-        <v>46161.47262043982</v>
+        <v>46161.63928710648</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46161.67990751157</v>
+        <v>46161.84657417824</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>190</v>
@@ -11156,11 +11160,11 @@
         <v>379</v>
       </c>
       <c r="B167" s="9">
-        <v>46161.47263069444</v>
+        <v>46161.63929736111</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46161.67990469908</v>
+        <v>46161.84657136574</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>190</v>
@@ -11209,11 +11213,11 @@
         <v>380</v>
       </c>
       <c r="B168" s="5">
-        <v>46161.47264047454</v>
+        <v>46161.6393071412</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46161.67990174769</v>
+        <v>46161.84656841435</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>190</v>
@@ -11262,11 +11266,11 @@
         <v>381</v>
       </c>
       <c r="B169" s="9">
-        <v>46161.47264895833</v>
+        <v>46161.639315625</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46161.679898726856</v>
+        <v>46161.84656539352</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>190</v>
@@ -11315,11 +11319,11 @@
         <v>382</v>
       </c>
       <c r="B170" s="5">
-        <v>46161.472660196756</v>
+        <v>46161.63932686343</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46161.67989608797</v>
+        <v>46161.846562754625</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>190</v>
@@ -11368,11 +11372,11 @@
         <v>383</v>
       </c>
       <c r="B171" s="9">
-        <v>46161.47267041667</v>
+        <v>46161.63933708333</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46161.67989328704</v>
+        <v>46161.8465599537</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>190</v>
@@ -11421,11 +11425,11 @@
         <v>384</v>
       </c>
       <c r="B172" s="5">
-        <v>46161.47268818287</v>
+        <v>46161.63935484954</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46161.6798871412</v>
+        <v>46161.846553807874</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>190</v>
@@ -11474,11 +11478,11 @@
         <v>385</v>
       </c>
       <c r="B173" s="9">
-        <v>46161.47269787037</v>
+        <v>46161.63936453704</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46161.67988646991</v>
+        <v>46161.84655313657</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>190</v>
@@ -11527,11 +11531,11 @@
         <v>386</v>
       </c>
       <c r="B174" s="5">
-        <v>46161.41451859954</v>
+        <v>46161.5811852662</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46161.674260659725</v>
+        <v>46161.84092732639</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>387</v>
@@ -11574,11 +11578,11 @@
         <v>389</v>
       </c>
       <c r="B175" s="9">
-        <v>46161.41452135416</v>
+        <v>46161.581188020835</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46161.68009149306</v>
+        <v>46161.84675815972</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>390</v>
@@ -11637,11 +11641,11 @@
         <v>393</v>
       </c>
       <c r="B176" s="5">
-        <v>46161.41452600695</v>
+        <v>46161.581192673606</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46161.68008268518</v>
+        <v>46161.846749351855</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>190</v>
@@ -11690,11 +11694,11 @@
         <v>395</v>
       </c>
       <c r="B177" s="9">
-        <v>46161.473160416666</v>
+        <v>46161.63982708333</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46161.68007988426</v>
+        <v>46161.84674655093</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>190</v>
@@ -11743,11 +11747,11 @@
         <v>396</v>
       </c>
       <c r="B178" s="5">
-        <v>46161.47316865741</v>
+        <v>46161.63983532407</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46161.68007731481</v>
+        <v>46161.846743981485</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>190</v>
@@ -11796,11 +11800,11 @@
         <v>397</v>
       </c>
       <c r="B179" s="9">
-        <v>46161.4731775463</v>
+        <v>46161.63984421296</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46161.68007476852</v>
+        <v>46161.84674143518</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>190</v>
@@ -11849,11 +11853,11 @@
         <v>398</v>
       </c>
       <c r="B180" s="5">
-        <v>46161.47319211806</v>
+        <v>46161.63985878472</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46161.680071875</v>
+        <v>46161.846738541666</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>190</v>
@@ -11902,11 +11906,11 @@
         <v>399</v>
       </c>
       <c r="B181" s="9">
-        <v>46161.47320113426</v>
+        <v>46161.63986780093</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46161.68006892361</v>
+        <v>46161.84673559028</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>190</v>
@@ -11955,11 +11959,11 @@
         <v>400</v>
       </c>
       <c r="B182" s="5">
-        <v>46161.47320833334</v>
+        <v>46161.639875</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46161.68006622685</v>
+        <v>46161.84673289352</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>190</v>
@@ -12008,11 +12012,11 @@
         <v>401</v>
       </c>
       <c r="B183" s="9">
-        <v>46161.47321675926</v>
+        <v>46161.63988342593</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46161.68005822916</v>
+        <v>46161.84672489583</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>190</v>
@@ -12061,11 +12065,11 @@
         <v>402</v>
       </c>
       <c r="B184" s="5">
-        <v>46161.47322476852</v>
+        <v>46161.63989143519</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46161.68005753472</v>
+        <v>46161.84672420139</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>190</v>
@@ -12114,11 +12118,11 @@
         <v>403</v>
       </c>
       <c r="B185" s="9">
-        <v>46161.47323267361</v>
+        <v>46161.639899340276</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46161.680056736106</v>
+        <v>46161.84672340278</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>190</v>
@@ -12167,11 +12171,11 @@
         <v>404</v>
       </c>
       <c r="B186" s="5">
-        <v>46161.41452984954</v>
+        <v>46161.5811965162</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46161.68023515046</v>
+        <v>46161.84690181713</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>405</v>
@@ -12230,11 +12234,11 @@
         <v>406</v>
       </c>
       <c r="B187" s="9">
-        <v>46161.41453335648</v>
+        <v>46161.58120002315</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46161.68023670139</v>
+        <v>46161.84690336806</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>190</v>
@@ -12283,11 +12287,11 @@
         <v>408</v>
       </c>
       <c r="B188" s="5">
-        <v>46161.47326758102</v>
+        <v>46161.63993424768</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46161.68023371528</v>
+        <v>46161.84690038195</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>190</v>
@@ -12336,11 +12340,11 @@
         <v>409</v>
       </c>
       <c r="B189" s="9">
-        <v>46161.473328113425</v>
+        <v>46161.6399947801</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46161.68023079861</v>
+        <v>46161.84689746528</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>190</v>
@@ -12389,11 +12393,11 @@
         <v>410</v>
       </c>
       <c r="B190" s="5">
-        <v>46161.473337777774</v>
+        <v>46161.640004444445</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46161.68022780093</v>
+        <v>46161.84689446759</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>190</v>
@@ -12442,11 +12446,11 @@
         <v>411</v>
       </c>
       <c r="B191" s="9">
-        <v>46161.47334834491</v>
+        <v>46161.64001501157</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46161.68022471065</v>
+        <v>46161.84689137731</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>190</v>
@@ -12495,11 +12499,11 @@
         <v>412</v>
       </c>
       <c r="B192" s="5">
-        <v>46161.47335716435</v>
+        <v>46161.640023831016</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46161.68022212963</v>
+        <v>46161.846888796295</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>190</v>
@@ -12548,11 +12552,11 @@
         <v>413</v>
       </c>
       <c r="B193" s="9">
-        <v>46161.473371643515</v>
+        <v>46161.640038310186</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46161.68021939815</v>
+        <v>46161.84688606481</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>190</v>
@@ -12601,11 +12605,11 @@
         <v>414</v>
       </c>
       <c r="B194" s="5">
-        <v>46161.47338081019</v>
+        <v>46161.64004747685</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46161.6802158912</v>
+        <v>46161.846882557875</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>190</v>
@@ -12654,11 +12658,11 @@
         <v>415</v>
       </c>
       <c r="B195" s="9">
-        <v>46161.47338982639</v>
+        <v>46161.64005649305</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46161.68021290509</v>
+        <v>46161.84687957176</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>190</v>
@@ -12707,11 +12711,11 @@
         <v>416</v>
       </c>
       <c r="B196" s="5">
-        <v>46161.47339679398</v>
+        <v>46161.64006346065</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46161.68020357639</v>
+        <v>46161.846870243055</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>190</v>
@@ -12760,11 +12764,11 @@
         <v>417</v>
       </c>
       <c r="B197" s="9">
-        <v>46161.41453732639</v>
+        <v>46161.58120399306</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46161.68043979167</v>
+        <v>46161.84710645833</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>418</v>
@@ -12821,11 +12825,11 @@
         <v>419</v>
       </c>
       <c r="B198" s="5">
-        <v>46161.4145408912</v>
+        <v>46161.58120755787</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46161.68041114583</v>
+        <v>46161.847077812505</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>190</v>
@@ -12872,11 +12876,11 @@
         <v>421</v>
       </c>
       <c r="B199" s="9">
-        <v>46161.47345859953</v>
+        <v>46161.6401252662</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46161.6804083912</v>
+        <v>46161.84707505787</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>190</v>
@@ -12923,11 +12927,11 @@
         <v>422</v>
       </c>
       <c r="B200" s="5">
-        <v>46161.47347471065</v>
+        <v>46161.64014137731</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46161.680405810184</v>
+        <v>46161.847072476856</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>190</v>
@@ -12974,11 +12978,11 @@
         <v>423</v>
       </c>
       <c r="B201" s="9">
-        <v>46161.47348627315</v>
+        <v>46161.64015293981</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46161.680402638885</v>
+        <v>46161.84706930556</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>190</v>
@@ -13025,11 +13029,11 @@
         <v>424</v>
       </c>
       <c r="B202" s="5">
-        <v>46161.47350074074</v>
+        <v>46161.64016740741</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46161.680399942124</v>
+        <v>46161.847066608796</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>190</v>
@@ -13076,11 +13080,11 @@
         <v>425</v>
       </c>
       <c r="B203" s="9">
-        <v>46161.47353721065</v>
+        <v>46161.640203877316</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46161.68039736111</v>
+        <v>46161.84706402778</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>190</v>
@@ -13127,11 +13131,11 @@
         <v>426</v>
       </c>
       <c r="B204" s="5">
-        <v>46161.4735484375</v>
+        <v>46161.64021510417</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46161.68039445602</v>
+        <v>46161.84706112268</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>190</v>
@@ -13178,11 +13182,11 @@
         <v>427</v>
       </c>
       <c r="B205" s="9">
-        <v>46161.4735603588</v>
+        <v>46161.64022702546</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46161.68038675926</v>
+        <v>46161.847053425925</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>190</v>
@@ -13229,11 +13233,11 @@
         <v>428</v>
       </c>
       <c r="B206" s="5">
-        <v>46161.473571180555</v>
+        <v>46161.64023784723</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46161.68038609954</v>
+        <v>46161.8470527662</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>190</v>
@@ -13280,11 +13284,11 @@
         <v>429</v>
       </c>
       <c r="B207" s="9">
-        <v>46161.47358644676</v>
+        <v>46161.64025311342</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46161.68038543982</v>
+        <v>46161.84705210648</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>190</v>
@@ -13331,11 +13335,11 @@
         <v>430</v>
       </c>
       <c r="B208" s="5">
-        <v>46161.41454799769</v>
+        <v>46161.58121466435</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46161.6806352662</v>
+        <v>46161.84730193287</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>431</v>
@@ -13394,11 +13398,11 @@
         <v>433</v>
       </c>
       <c r="B209" s="9">
-        <v>46161.414590659726</v>
+        <v>46161.58125732639</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46161.680614247685</v>
+        <v>46161.84728091436</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>190</v>
@@ -13445,11 +13449,11 @@
         <v>434</v>
       </c>
       <c r="B210" s="5">
-        <v>46161.47364123842</v>
+        <v>46161.640307905094</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46161.6806110301</v>
+        <v>46161.84727769676</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>190</v>
@@ -13496,11 +13500,11 @@
         <v>435</v>
       </c>
       <c r="B211" s="9">
-        <v>46161.4736496875</v>
+        <v>46161.64031635417</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46161.680608587965</v>
+        <v>46161.84727525463</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>190</v>
@@ -13547,11 +13551,11 @@
         <v>436</v>
       </c>
       <c r="B212" s="5">
-        <v>46161.473661655094</v>
+        <v>46161.64032832176</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46161.68060581019</v>
+        <v>46161.84727247685</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>190</v>
@@ -13598,11 +13602,11 @@
         <v>437</v>
       </c>
       <c r="B213" s="9">
-        <v>46161.47367131944</v>
+        <v>46161.640337986115</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46161.68060278935</v>
+        <v>46161.84726945602</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>190</v>
@@ -13649,11 +13653,11 @@
         <v>438</v>
       </c>
       <c r="B214" s="5">
-        <v>46161.473691956024</v>
+        <v>46161.64035862268</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46161.680599722225</v>
+        <v>46161.84726638889</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>190</v>
@@ -13700,11 +13704,11 @@
         <v>439</v>
       </c>
       <c r="B215" s="9">
-        <v>46161.47370106481</v>
+        <v>46161.64036773148</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46161.68059693287</v>
+        <v>46161.84726359954</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>190</v>
@@ -13751,11 +13755,11 @@
         <v>440</v>
       </c>
       <c r="B216" s="5">
-        <v>46161.47370990741</v>
+        <v>46161.64037657407</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46161.68059393518</v>
+        <v>46161.84726060185</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>190</v>
@@ -13802,11 +13806,11 @@
         <v>441</v>
       </c>
       <c r="B217" s="9">
-        <v>46161.47371806713</v>
+        <v>46161.64038473379</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46161.68058803241</v>
+        <v>46161.847254699074</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>190</v>
@@ -13853,11 +13857,11 @@
         <v>442</v>
       </c>
       <c r="B218" s="5">
-        <v>46161.47372684028</v>
+        <v>46161.64039350694</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46161.68058739584</v>
+        <v>46161.8472540625</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>190</v>
@@ -13904,11 +13908,11 @@
         <v>443</v>
       </c>
       <c r="B219" s="9">
-        <v>46161.41459615741</v>
+        <v>46161.581262824075</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46161.68134378472</v>
+        <v>46161.84801045139</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>444</v>
@@ -13951,11 +13955,11 @@
         <v>446</v>
       </c>
       <c r="B220" s="5">
-        <v>46161.414599490745</v>
+        <v>46161.58126615741</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46161.680980902776</v>
+        <v>46161.84764756945</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>447</v>
@@ -14014,11 +14018,11 @@
         <v>450</v>
       </c>
       <c r="B221" s="9">
-        <v>46161.41460415509</v>
+        <v>46161.581270821756</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46198.63989554398</v>
+        <v>46198.80656221065</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>451</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -2927,7 +2927,7 @@
         <v>46204.90066085648</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.90095260416</v>
+        <v>46206.560436921296</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2992,7 +2992,7 @@
         <v>46204.90101555556</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.90139665509</v>
+        <v>46206.560617662035</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>85</v>
@@ -3057,7 +3057,7 @@
         <v>46204.90180252315</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.9022046875</v>
+        <v>46206.56075704861</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -3122,7 +3122,7 @@
         <v>46204.90175329861</v>
       </c>
       <c r="D21" s="9">
-        <v>46204.90176861111</v>
+        <v>46206.560877592594</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="452">
   <si>
     <t>50001555 - "ZITRON COLOMBIA ARIS MINING SEGOVIA"</t>
   </si>
@@ -392,16 +392,16 @@
     <t>Generación OC Alabe ot 4332,Fabricación Alabe ot 4332</t>
   </si>
   <si>
+    <t>1214937218513477</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe ot 4332</t>
+  </si>
+  <si>
+    <t>Alabe ot 4332,Fabricación Alabe ot 4332</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214937218513477</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe ot 4332</t>
-  </si>
-  <si>
-    <t>Alabe ot 4332,Fabricación Alabe ot 4332</t>
   </si>
   <si>
     <t>1214937218513495</t>
@@ -2683,9 +2683,11 @@
       <c r="B14" s="5">
         <v>46161.58064403935</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46209.56505414352</v>
+      </c>
       <c r="D14" s="5">
-        <v>46204.900667615744</v>
+        <v>46209.56506746528</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2720,8 +2722,12 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -2795,9 +2801,11 @@
       <c r="B16" s="5">
         <v>46161.580788680556</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="5">
+        <v>46209.56503421297</v>
+      </c>
       <c r="D16" s="5">
-        <v>46197.67510195602</v>
+        <v>46209.565114375</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2845,10 +2853,10 @@
         <v>60</v>
       </c>
       <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="11" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -3185,7 +3193,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46161.73787121528</v>
+        <v>46209.56573239583</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -3230,9 +3238,11 @@
       <c r="B23" s="9">
         <v>46161.58081472223</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9">
+        <v>46209.565500937504</v>
+      </c>
       <c r="D23" s="9">
-        <v>46169.879378680555</v>
+        <v>46209.56551446759</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>97</v>
@@ -3280,25 +3290,27 @@
         <v>33</v>
       </c>
       <c r="T23" s="10">
-        <v>0</v>
-      </c>
-      <c r="U23" s="12" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46161.580819016206</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46209.56543814814</v>
+      </c>
       <c r="D24" s="5">
-        <v>46169.879644560184</v>
+        <v>46209.56543981482</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3331,7 +3343,7 @@
         <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3342,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3352,9 +3364,11 @@
       <c r="B25" s="9">
         <v>46161.58082350694</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46209.56548716435</v>
+      </c>
       <c r="D25" s="9">
-        <v>46169.87966921296</v>
+        <v>46209.565488576394</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3387,7 +3401,7 @@
         <v>97</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>107</v>
@@ -3401,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3411,9 +3425,11 @@
       <c r="B26" s="5">
         <v>46161.58082824074</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46209.56571918981</v>
+      </c>
       <c r="D26" s="5">
-        <v>46192.85867619213</v>
+        <v>46209.56600694444</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3461,10 +3477,10 @@
         <v>60</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="12" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3474,9 +3490,11 @@
       <c r="B27" s="9">
         <v>46161.5808325463</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9">
+        <v>46209.56565701389</v>
+      </c>
       <c r="D27" s="9">
-        <v>46197.58860037037</v>
+        <v>46209.56565858796</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3523,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3533,9 +3551,11 @@
       <c r="B28" s="5">
         <v>46161.580836967594</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46209.565705243054</v>
+      </c>
       <c r="D28" s="5">
-        <v>46171.17352185185</v>
+        <v>46209.56570685185</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3582,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3645,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3706,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3765,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3826,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3889,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3950,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -4009,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -4072,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4243,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4465,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4878,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5498,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5561,7 +5581,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5624,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5687,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5750,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5813,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5923,7 +5943,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -6516,7 +6536,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -7109,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7698,7 +7718,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46176.18811300926</v>
+        <v>46209.56572255787</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>280</v>
@@ -7748,8 +7768,8 @@
       <c r="T103" s="10">
         <v>0</v>
       </c>
-      <c r="U103" s="12" t="s">
-        <v>101</v>
+      <c r="U103" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7761,7 +7781,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46161.84560915509</v>
+        <v>46209.56550644676</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>283</v>
@@ -7811,8 +7831,8 @@
       <c r="T104" s="6">
         <v>0</v>
       </c>
-      <c r="U104" s="12" t="s">
-        <v>101</v>
+      <c r="U104" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7875,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -7938,7 +7958,7 @@
         <v>0</v>
       </c>
       <c r="U106" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -8048,7 +8068,7 @@
         <v>0</v>
       </c>
       <c r="U108" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -8641,7 +8661,7 @@
         <v>0</v>
       </c>
       <c r="U119" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -9234,7 +9254,7 @@
         <v>0</v>
       </c>
       <c r="U130" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -9827,7 +9847,7 @@
         <v>0</v>
       </c>
       <c r="U141" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
@@ -10420,7 +10440,7 @@
         <v>0</v>
       </c>
       <c r="U152" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
@@ -10993,7 +11013,7 @@
         <v>0</v>
       </c>
       <c r="U163" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
@@ -11633,7 +11653,7 @@
         <v>0</v>
       </c>
       <c r="U175" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
@@ -12226,7 +12246,7 @@
         <v>0</v>
       </c>
       <c r="U186" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
@@ -12817,7 +12837,7 @@
         <v>0</v>
       </c>
       <c r="U197" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
@@ -13390,7 +13410,7 @@
         <v>0</v>
       </c>
       <c r="U208" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
@@ -14010,7 +14030,7 @@
         <v>0</v>
       </c>
       <c r="U220" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
@@ -14073,7 +14093,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -4210,9 +4210,11 @@
       <c r="B39" s="9">
         <v>46161.580941099535</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46209.62287337963</v>
+      </c>
       <c r="D39" s="9">
-        <v>46169.87945328704</v>
+        <v>46209.62288859954</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -4260,10 +4262,10 @@
         <v>33</v>
       </c>
       <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="12" t="s">
-        <v>104</v>
+        <v>1</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4273,9 +4275,11 @@
       <c r="B40" s="5">
         <v>46161.58094532407</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46209.6227827199</v>
+      </c>
       <c r="D40" s="5">
-        <v>46204.90175859953</v>
+        <v>46209.622784444444</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>92</v>
@@ -4326,9 +4330,11 @@
       <c r="B41" s="9">
         <v>46161.58094997685</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="9">
+        <v>46209.62282931713</v>
+      </c>
       <c r="D41" s="9">
-        <v>46169.87991520834</v>
+        <v>46209.62283091435</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4381,7 +4387,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.879929814815</v>
+        <v>46209.62284077547</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -7907,7 +7913,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46161.84560210648</v>
+        <v>46209.62284840278</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>289</v>
@@ -7957,8 +7963,8 @@
       <c r="T106" s="6">
         <v>0</v>
       </c>
-      <c r="U106" s="12" t="s">
-        <v>104</v>
+      <c r="U106" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -3982,7 +3982,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46205.61009606482</v>
+        <v>46209.80471142361</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -4039,9 +4039,11 @@
       <c r="B36" s="5">
         <v>46161.58087322916</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46209.804941608796</v>
+      </c>
       <c r="D36" s="5">
-        <v>46205.61025262732</v>
+        <v>46209.804952569444</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -4089,10 +4091,10 @@
         <v>33</v>
       </c>
       <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="12" t="s">
-        <v>104</v>
+        <v>1</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4157,9 +4159,11 @@
       <c r="B38" s="5">
         <v>46161.58093646991</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46209.804927233796</v>
+      </c>
       <c r="D38" s="5">
-        <v>46205.610401655096</v>
+        <v>46209.809419513884</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -4438,9 +4442,11 @@
       <c r="B43" s="9">
         <v>46161.58095743056</v>
       </c>
-      <c r="C43" s="10"/>
+      <c r="C43" s="9">
+        <v>46209.81258817129</v>
+      </c>
       <c r="D43" s="9">
-        <v>46169.87951825232</v>
+        <v>46209.81259914352</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>163</v>
@@ -4488,10 +4494,10 @@
         <v>33</v>
       </c>
       <c r="T43" s="10">
-        <v>0</v>
-      </c>
-      <c r="U43" s="12" t="s">
-        <v>104</v>
+        <v>1</v>
+      </c>
+      <c r="U43" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4501,9 +4507,11 @@
       <c r="B44" s="5">
         <v>46161.58096091435</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46209.81220123843</v>
+      </c>
       <c r="D44" s="5">
-        <v>46205.61062071759</v>
+        <v>46209.81220270833</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>89</v>
@@ -4554,9 +4562,11 @@
       <c r="B45" s="9">
         <v>46161.580964988425</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46209.812571435185</v>
+      </c>
       <c r="D45" s="9">
-        <v>46169.87999765047</v>
+        <v>46209.81257327546</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>168</v>
@@ -5599,7 +5609,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46161.84483983796</v>
+        <v>46209.804944710646</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5649,8 +5659,8 @@
       <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="12" t="s">
-        <v>104</v>
+      <c r="U64" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5725,7 +5735,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46161.8448359375</v>
+        <v>46209.81259190972</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>222</v>
@@ -5775,8 +5785,8 @@
       <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="U66" s="12" t="s">
-        <v>104</v>
+      <c r="U66" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -4617,9 +4617,11 @@
       <c r="B46" s="5">
         <v>46161.58065239583</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46210.52868532407</v>
+      </c>
       <c r="D46" s="5">
-        <v>46198.80746668982</v>
+        <v>46210.52870142361</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4654,9 +4656,11 @@
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="11" t="s">
-        <v>49</v>
+      <c r="T46" s="6">
+        <v>1</v>
+      </c>
+      <c r="U46" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46209.56573239583</v>
+        <v>46211.83005701389</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -3856,9 +3856,11 @@
       <c r="B33" s="9">
         <v>46161.58085940972</v>
       </c>
-      <c r="C33" s="10"/>
+      <c r="C33" s="9">
+        <v>46211.830044375005</v>
+      </c>
       <c r="D33" s="9">
-        <v>46205.61009494213</v>
+        <v>46211.830060266206</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>130</v>
@@ -3906,10 +3908,10 @@
         <v>33</v>
       </c>
       <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="12" t="s">
-        <v>104</v>
+        <v>1</v>
+      </c>
+      <c r="U33" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3980,9 +3982,11 @@
       <c r="B35" s="9">
         <v>46161.58086832176</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="9">
+        <v>46211.83002739583</v>
+      </c>
       <c r="D35" s="9">
-        <v>46209.80471142361</v>
+        <v>46211.83003016203</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -5487,7 +5491,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46161.844842499995</v>
+        <v>46211.830047766205</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>207</v>
@@ -5537,8 +5541,8 @@
       <c r="T62" s="6">
         <v>0</v>
       </c>
-      <c r="U62" s="12" t="s">
-        <v>104</v>
+      <c r="U62" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="453">
   <si>
     <t>50001555 - "ZITRON COLOMBIA ARIS MINING SEGOVIA"</t>
   </si>
@@ -633,6 +633,9 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214937218721335</t>
@@ -4743,7 +4746,7 @@
         <v>46198.8074493287</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.80746766204</v>
+        <v>46213.18419743056</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4787,8 +4790,8 @@
       <c r="R48" s="5">
         <v>46220</v>
       </c>
-      <c r="S48" s="7" t="s">
-        <v>33</v>
+      <c r="S48" s="11" t="s">
+        <v>182</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4799,7 +4802,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46161.58098100695</v>
@@ -4817,10 +4820,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I49" s="9">
         <v>46223</v>
@@ -4844,7 +4847,7 @@
         <v>179</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q49" s="9">
         <v>46223</v>
@@ -4864,7 +4867,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46161.58099116899</v>
@@ -4874,16 +4877,16 @@
         <v>46161.84476310185</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I50" s="5">
         <v>46308</v>
@@ -4904,7 +4907,7 @@
         <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4927,7 +4930,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B51" s="9">
         <v>46161.58099418982</v>
@@ -4937,16 +4940,16 @@
         <v>46161.84476607639</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4962,13 +4965,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4978,7 +4981,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46161.63966489583</v>
@@ -4988,16 +4991,16 @@
         <v>46161.844763472225</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -5013,13 +5016,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5029,7 +5032,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46161.63967261574</v>
@@ -5039,16 +5042,16 @@
         <v>46161.84476069444</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5064,13 +5067,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5080,7 +5083,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46161.63968388889</v>
@@ -5090,16 +5093,16 @@
         <v>46161.84475773148</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5115,13 +5118,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5131,7 +5134,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B55" s="9">
         <v>46161.63969275463</v>
@@ -5141,16 +5144,16 @@
         <v>46161.84475471065</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5166,13 +5169,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5182,7 +5185,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46161.639705208334</v>
@@ -5192,16 +5195,16 @@
         <v>46161.84475174769</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5217,13 +5220,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5233,7 +5236,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B57" s="9">
         <v>46161.639715474535</v>
@@ -5243,16 +5246,16 @@
         <v>46161.84474863426</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5268,13 +5271,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5284,7 +5287,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46161.63972679398</v>
@@ -5294,16 +5297,16 @@
         <v>46161.84474503472</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5319,13 +5322,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5335,7 +5338,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B59" s="9">
         <v>46161.63974304398</v>
@@ -5345,16 +5348,16 @@
         <v>46161.84473834491</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5370,13 +5373,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5386,7 +5389,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46161.63975269676</v>
@@ -5396,16 +5399,16 @@
         <v>46161.84473753472</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5421,13 +5424,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5437,7 +5440,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46161.58099818287</v>
@@ -5447,7 +5450,7 @@
         <v>46161.79647144676</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5471,7 +5474,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5484,7 +5487,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B62" s="5">
         <v>46161.58100145833</v>
@@ -5494,16 +5497,16 @@
         <v>46211.830047766205</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46239</v>
@@ -5521,13 +5524,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q62" s="5">
         <v>46239</v>
@@ -5547,7 +5550,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B63" s="9">
         <v>46161.58100614583</v>
@@ -5557,7 +5560,7 @@
         <v>46161.84491849537</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5584,13 +5587,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="9">
         <v>46241</v>
@@ -5610,7 +5613,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B64" s="5">
         <v>46161.58101638889</v>
@@ -5620,16 +5623,16 @@
         <v>46209.804944710646</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46239</v>
@@ -5647,13 +5650,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q64" s="5">
         <v>46239</v>
@@ -5673,7 +5676,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B65" s="9">
         <v>46161.58102099537</v>
@@ -5683,7 +5686,7 @@
         <v>46161.84491503472</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5710,13 +5713,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="9">
         <v>46241</v>
@@ -5736,7 +5739,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B66" s="5">
         <v>46161.581024722225</v>
@@ -5746,16 +5749,16 @@
         <v>46209.81259190972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46239</v>
@@ -5773,13 +5776,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>168</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q66" s="5">
         <v>46239</v>
@@ -5799,7 +5802,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B67" s="9">
         <v>46161.58102864583</v>
@@ -5809,7 +5812,7 @@
         <v>46161.844914270834</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5836,13 +5839,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q67" s="9">
         <v>46241</v>
@@ -5862,7 +5865,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B68" s="5">
         <v>46161.58103207176</v>
@@ -5872,7 +5875,7 @@
         <v>46161.797785821764</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5896,7 +5899,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5909,7 +5912,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B69" s="9">
         <v>46161.58103457176</v>
@@ -5919,16 +5922,16 @@
         <v>46161.845178449075</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I69" s="9">
         <v>46245</v>
@@ -5946,13 +5949,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q69" s="9">
         <v>46245</v>
@@ -5972,7 +5975,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46161.58103962963</v>
@@ -5982,16 +5985,16 @@
         <v>46161.845147071755</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I70" s="5">
         <v>46245</v>
@@ -6009,13 +6012,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6025,7 +6028,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46161.582011805556</v>
@@ -6035,16 +6038,16 @@
         <v>46161.84514348379</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I71" s="9">
         <v>46245</v>
@@ -6062,13 +6065,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6078,7 +6081,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46161.58202383102</v>
@@ -6088,16 +6091,16 @@
         <v>46161.845140324076</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I72" s="5">
         <v>46245</v>
@@ -6115,13 +6118,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6131,7 +6134,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B73" s="9">
         <v>46161.582662650464</v>
@@ -6141,16 +6144,16 @@
         <v>46161.845136655094</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I73" s="9">
         <v>46245</v>
@@ -6168,13 +6171,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6184,7 +6187,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46161.58267322917</v>
@@ -6194,16 +6197,16 @@
         <v>46161.845133518524</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I74" s="5">
         <v>46245</v>
@@ -6221,13 +6224,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6237,7 +6240,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46161.58270134259</v>
@@ -6247,16 +6250,16 @@
         <v>46161.84513074074</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I75" s="9">
         <v>46245</v>
@@ -6274,13 +6277,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6290,7 +6293,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46161.58271427083</v>
@@ -6300,16 +6303,16 @@
         <v>46161.84512803241</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I76" s="5">
         <v>46245</v>
@@ -6327,13 +6330,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6343,7 +6346,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46161.58272651621</v>
@@ -6353,16 +6356,16 @@
         <v>46161.84512407407</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I77" s="9">
         <v>46245</v>
@@ -6380,13 +6383,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6396,7 +6399,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
         <v>46161.58277962963</v>
@@ -6406,16 +6409,16 @@
         <v>46161.845117916666</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I78" s="5">
         <v>46245</v>
@@ -6433,13 +6436,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6449,7 +6452,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B79" s="9">
         <v>46161.58279046296</v>
@@ -6459,16 +6462,16 @@
         <v>46161.84511721064</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I79" s="9">
         <v>46245</v>
@@ -6486,13 +6489,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6502,7 +6505,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5">
         <v>46161.58104538194</v>
@@ -6512,16 +6515,16 @@
         <v>46161.845344814814</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I80" s="5">
         <v>46254</v>
@@ -6539,13 +6542,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q80" s="5">
         <v>46254</v>
@@ -6565,7 +6568,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B81" s="9">
         <v>46161.58104903935</v>
@@ -6575,16 +6578,16 @@
         <v>46198.80752025463</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I81" s="9">
         <v>46254</v>
@@ -6602,13 +6605,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6618,7 +6621,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46161.582834120374</v>
@@ -6628,16 +6631,16 @@
         <v>46161.84533628472</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I82" s="5">
         <v>46254</v>
@@ -6655,13 +6658,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6671,7 +6674,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B83" s="9">
         <v>46161.58286459491</v>
@@ -6681,16 +6684,16 @@
         <v>46161.84533336805</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I83" s="9">
         <v>46254</v>
@@ -6708,13 +6711,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6724,7 +6727,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B84" s="5">
         <v>46161.58287381944</v>
@@ -6734,16 +6737,16 @@
         <v>46161.84533065972</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I84" s="5">
         <v>46254</v>
@@ -6761,13 +6764,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6777,7 +6780,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B85" s="9">
         <v>46161.58288365741</v>
@@ -6787,16 +6790,16 @@
         <v>46161.84532790509</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I85" s="9">
         <v>46254</v>
@@ -6814,13 +6817,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6830,7 +6833,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B86" s="5">
         <v>46161.58289255787</v>
@@ -6840,16 +6843,16 @@
         <v>46161.84532486111</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I86" s="5">
         <v>46254</v>
@@ -6867,13 +6870,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6883,7 +6886,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B87" s="9">
         <v>46161.58292542824</v>
@@ -6893,16 +6896,16 @@
         <v>46161.84532211805</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I87" s="9">
         <v>46254</v>
@@ -6920,13 +6923,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6936,7 +6939,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B88" s="5">
         <v>46161.58293696759</v>
@@ -6946,16 +6949,16 @@
         <v>46161.84531927083</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I88" s="5">
         <v>46254</v>
@@ -6973,13 +6976,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6989,7 +6992,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B89" s="9">
         <v>46161.58295282407</v>
@@ -6999,16 +7002,16 @@
         <v>46161.84531311343</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I89" s="9">
         <v>46254</v>
@@ -7026,13 +7029,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7042,7 +7045,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B90" s="5">
         <v>46161.58296773148</v>
@@ -7052,16 +7055,16 @@
         <v>46161.84531243055</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I90" s="5">
         <v>46254</v>
@@ -7079,13 +7082,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7095,7 +7098,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B91" s="9">
         <v>46161.581053761576</v>
@@ -7105,7 +7108,7 @@
         <v>46161.84552644676</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7132,13 +7135,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q91" s="9">
         <v>46274</v>
@@ -7158,7 +7161,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B92" s="5">
         <v>46161.58105741898</v>
@@ -7168,7 +7171,7 @@
         <v>46198.80752082176</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7195,13 +7198,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7211,7 +7214,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B93" s="9">
         <v>46161.583039942125</v>
@@ -7221,7 +7224,7 @@
         <v>46161.84550880787</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7248,13 +7251,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7264,7 +7267,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B94" s="5">
         <v>46161.58305715278</v>
@@ -7274,7 +7277,7 @@
         <v>46161.845505324076</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7301,13 +7304,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7317,7 +7320,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B95" s="9">
         <v>46161.583076689814</v>
@@ -7327,7 +7330,7 @@
         <v>46161.84550258102</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7354,13 +7357,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7370,7 +7373,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B96" s="5">
         <v>46161.58308886574</v>
@@ -7380,7 +7383,7 @@
         <v>46161.84549928241</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7407,13 +7410,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7423,7 +7426,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B97" s="9">
         <v>46161.58310019676</v>
@@ -7433,7 +7436,7 @@
         <v>46161.84549533565</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7460,13 +7463,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7476,7 +7479,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B98" s="5">
         <v>46161.5831108912</v>
@@ -7486,7 +7489,7 @@
         <v>46161.84549206018</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7513,13 +7516,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7529,7 +7532,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B99" s="9">
         <v>46161.58312844907</v>
@@ -7539,7 +7542,7 @@
         <v>46161.84548887731</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7566,13 +7569,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7582,7 +7585,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B100" s="5">
         <v>46161.58300775463</v>
@@ -7592,7 +7595,7 @@
         <v>46161.84548230324</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7619,13 +7622,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7635,7 +7638,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B101" s="9">
         <v>46161.639501875004</v>
@@ -7645,7 +7648,7 @@
         <v>46161.845481620374</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7672,13 +7675,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7688,7 +7691,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B102" s="5">
         <v>46161.58110506945</v>
@@ -7698,7 +7701,7 @@
         <v>46161.80776861111</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7722,7 +7725,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7735,7 +7738,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B103" s="9">
         <v>46161.581108530096</v>
@@ -7745,16 +7748,16 @@
         <v>46209.56572255787</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I103" s="9">
         <v>46174</v>
@@ -7772,13 +7775,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>115</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q103" s="9">
         <v>46174</v>
@@ -7798,7 +7801,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B104" s="5">
         <v>46161.58111370371</v>
@@ -7808,16 +7811,16 @@
         <v>46209.56550644676</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I104" s="5">
         <v>46282</v>
@@ -7835,13 +7838,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>106</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q104" s="5">
         <v>46282</v>
@@ -7861,7 +7864,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B105" s="9">
         <v>46161.581118449074</v>
@@ -7871,16 +7874,16 @@
         <v>46161.84560644676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I105" s="9">
         <v>46301</v>
@@ -7898,13 +7901,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>124</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q105" s="9">
         <v>46301</v>
@@ -7924,7 +7927,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46161.58112311343</v>
@@ -7934,16 +7937,16 @@
         <v>46209.62284840278</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I106" s="5">
         <v>46237</v>
@@ -7961,13 +7964,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>156</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q106" s="5">
         <v>46237</v>
@@ -7987,7 +7990,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B107" s="9">
         <v>46161.58112702546</v>
@@ -7997,7 +8000,7 @@
         <v>46161.83387362269</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -8021,7 +8024,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -8034,7 +8037,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B108" s="5">
         <v>46161.58112984954</v>
@@ -8044,7 +8047,7 @@
         <v>46161.84578230324</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8071,13 +8074,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q108" s="5">
         <v>46276</v>
@@ -8097,7 +8100,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B109" s="9">
         <v>46161.581135555556</v>
@@ -8107,7 +8110,7 @@
         <v>46161.84577694444</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8134,13 +8137,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8150,7 +8153,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B110" s="5">
         <v>46161.58317730324</v>
@@ -8160,7 +8163,7 @@
         <v>46161.84577366898</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8187,13 +8190,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8203,7 +8206,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B111" s="9">
         <v>46161.58318758102</v>
@@ -8213,7 +8216,7 @@
         <v>46161.845770879634</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8240,13 +8243,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8256,7 +8259,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B112" s="5">
         <v>46161.5831975926</v>
@@ -8266,7 +8269,7 @@
         <v>46161.84576709491</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8293,13 +8296,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8309,7 +8312,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B113" s="9">
         <v>46161.58320657407</v>
@@ -8319,7 +8322,7 @@
         <v>46161.84576415509</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8346,13 +8349,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8362,7 +8365,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B114" s="5">
         <v>46161.58322151621</v>
@@ -8372,7 +8375,7 @@
         <v>46161.84576082176</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8399,13 +8402,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8415,7 +8418,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B115" s="9">
         <v>46161.58322717593</v>
@@ -8425,7 +8428,7 @@
         <v>46161.84575040509</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8452,13 +8455,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8468,7 +8471,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B116" s="5">
         <v>46161.58324248843</v>
@@ -8478,7 +8481,7 @@
         <v>46161.84574967592</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8505,13 +8508,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8521,7 +8524,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B117" s="9">
         <v>46161.58325402778</v>
@@ -8531,7 +8534,7 @@
         <v>46161.845748946755</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8558,13 +8561,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8574,7 +8577,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B118" s="5">
         <v>46161.58326291667</v>
@@ -8584,7 +8587,7 @@
         <v>46161.84574821759</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8611,13 +8614,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8627,7 +8630,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B119" s="9">
         <v>46161.58113928241</v>
@@ -8637,7 +8640,7 @@
         <v>46161.845971400464</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8664,13 +8667,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q119" s="9">
         <v>46296</v>
@@ -8690,7 +8693,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B120" s="5">
         <v>46161.58114282407</v>
@@ -8700,7 +8703,7 @@
         <v>46198.807521180555</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8727,13 +8730,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8743,7 +8746,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B121" s="9">
         <v>46161.585882430554</v>
@@ -8753,7 +8756,7 @@
         <v>46198.807499965274</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8780,13 +8783,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8796,7 +8799,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B122" s="5">
         <v>46161.58590298611</v>
@@ -8806,7 +8809,7 @@
         <v>46198.80750063657</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8833,13 +8836,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8849,7 +8852,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B123" s="9">
         <v>46161.585919861114</v>
@@ -8859,7 +8862,7 @@
         <v>46198.80750122685</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8886,13 +8889,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8902,7 +8905,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B124" s="5">
         <v>46161.585927175925</v>
@@ -8912,7 +8915,7 @@
         <v>46198.807501793985</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8939,13 +8942,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8955,7 +8958,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B125" s="9">
         <v>46161.58593310185</v>
@@ -8965,7 +8968,7 @@
         <v>46198.807502384254</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8992,13 +8995,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9008,7 +9011,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B126" s="5">
         <v>46161.58593739584</v>
@@ -9018,7 +9021,7 @@
         <v>46198.807502951386</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9045,13 +9048,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9061,7 +9064,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B127" s="9">
         <v>46161.58594590278</v>
@@ -9071,7 +9074,7 @@
         <v>46198.80750380787</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9098,13 +9101,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9114,7 +9117,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B128" s="5">
         <v>46161.5859562963</v>
@@ -9124,7 +9127,7 @@
         <v>46198.80750443287</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9151,13 +9154,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9167,7 +9170,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B129" s="9">
         <v>46161.58618912037</v>
@@ -9177,7 +9180,7 @@
         <v>46198.80750512732</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9204,13 +9207,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9220,7 +9223,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B130" s="5">
         <v>46161.58114761574</v>
@@ -9230,7 +9233,7 @@
         <v>46161.8461249074</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9257,13 +9260,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q130" s="5">
         <v>46300</v>
@@ -9283,7 +9286,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B131" s="9">
         <v>46161.58115116898</v>
@@ -9293,7 +9296,7 @@
         <v>46198.807510914354</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9320,13 +9323,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9336,7 +9339,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B132" s="5">
         <v>46161.58603712963</v>
@@ -9346,7 +9349,7 @@
         <v>46198.80750575232</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9373,13 +9376,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9389,7 +9392,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B133" s="9">
         <v>46161.586044930555</v>
@@ -9399,7 +9402,7 @@
         <v>46198.8075062037</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9426,13 +9429,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9442,7 +9445,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B134" s="5">
         <v>46161.58605891204</v>
@@ -9452,7 +9455,7 @@
         <v>46198.807506666664</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9479,13 +9482,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9495,7 +9498,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B135" s="9">
         <v>46161.58606768519</v>
@@ -9505,7 +9508,7 @@
         <v>46198.8075071412</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9532,13 +9535,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9548,7 +9551,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B136" s="5">
         <v>46161.58607575232</v>
@@ -9558,7 +9561,7 @@
         <v>46198.807507708334</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9585,13 +9588,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9601,7 +9604,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B137" s="9">
         <v>46161.586088854165</v>
@@ -9611,7 +9614,7 @@
         <v>46198.80750815972</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9638,13 +9641,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9654,7 +9657,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B138" s="5">
         <v>46161.58609570602</v>
@@ -9664,7 +9667,7 @@
         <v>46198.80750863426</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9691,13 +9694,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9707,7 +9710,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B139" s="9">
         <v>46161.586110578704</v>
@@ -9717,7 +9720,7 @@
         <v>46198.807509085644</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9744,13 +9747,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9760,7 +9763,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B140" s="5">
         <v>46161.58612255787</v>
@@ -9770,7 +9773,7 @@
         <v>46198.80750956018</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9797,13 +9800,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9813,7 +9816,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B141" s="9">
         <v>46161.58115643519</v>
@@ -9823,7 +9826,7 @@
         <v>46161.84629616898</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9850,13 +9853,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q141" s="9">
         <v>46303</v>
@@ -9876,7 +9879,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B142" s="5">
         <v>46161.58115993056</v>
@@ -9886,7 +9889,7 @@
         <v>46198.807521759256</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9913,13 +9916,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9929,7 +9932,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B143" s="9">
         <v>46161.58622641204</v>
@@ -9939,7 +9942,7 @@
         <v>46198.80750998843</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9966,13 +9969,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9982,7 +9985,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B144" s="5">
         <v>46161.586235995375</v>
@@ -9992,7 +9995,7 @@
         <v>46198.807510416664</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10019,13 +10022,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10035,7 +10038,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B145" s="9">
         <v>46161.586246770836</v>
@@ -10045,7 +10048,7 @@
         <v>46161.846280046295</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10072,13 +10075,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10088,7 +10091,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B146" s="5">
         <v>46161.586256435185</v>
@@ -10098,7 +10101,7 @@
         <v>46161.84627699074</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10125,13 +10128,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10141,7 +10144,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B147" s="9">
         <v>46161.586265833335</v>
@@ -10151,7 +10154,7 @@
         <v>46161.84627394676</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10178,13 +10181,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10194,7 +10197,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B148" s="5">
         <v>46161.586275671296</v>
@@ -10204,7 +10207,7 @@
         <v>46161.84627113426</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10231,13 +10234,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10247,7 +10250,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B149" s="9">
         <v>46161.58629186342</v>
@@ -10257,7 +10260,7 @@
         <v>46161.846268402776</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10284,13 +10287,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10300,7 +10303,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B150" s="5">
         <v>46161.58630879629</v>
@@ -10310,7 +10313,7 @@
         <v>46161.84626222222</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10337,13 +10340,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10353,7 +10356,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B151" s="9">
         <v>46161.58632163194</v>
@@ -10363,7 +10366,7 @@
         <v>46161.84626162037</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10390,13 +10393,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10406,7 +10409,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B152" s="5">
         <v>46161.5811646875</v>
@@ -10416,7 +10419,7 @@
         <v>46161.84643925926</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10443,13 +10446,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q152" s="5">
         <v>46307</v>
@@ -10469,7 +10472,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B153" s="9">
         <v>46161.58116828704</v>
@@ -10479,7 +10482,7 @@
         <v>46161.84644222222</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10504,13 +10507,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10520,7 +10523,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B154" s="5">
         <v>46161.63912622685</v>
@@ -10530,7 +10533,7 @@
         <v>46161.84643929398</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10555,10 +10558,10 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10571,7 +10574,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B155" s="9">
         <v>46161.63913737268</v>
@@ -10581,7 +10584,7 @@
         <v>46161.84643643518</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10606,10 +10609,10 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>26</v>
@@ -10622,7 +10625,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B156" s="5">
         <v>46161.63914719908</v>
@@ -10632,7 +10635,7 @@
         <v>46161.846433321756</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10657,10 +10660,10 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>26</v>
@@ -10673,7 +10676,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B157" s="9">
         <v>46161.639157557875</v>
@@ -10683,7 +10686,7 @@
         <v>46161.84643013889</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10708,10 +10711,10 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>26</v>
@@ -10724,7 +10727,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B158" s="5">
         <v>46161.6391721875</v>
@@ -10734,7 +10737,7 @@
         <v>46161.84642646991</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10759,10 +10762,10 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10775,7 +10778,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B159" s="9">
         <v>46161.639187395835</v>
@@ -10785,7 +10788,7 @@
         <v>46161.84642321759</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10810,10 +10813,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>26</v>
@@ -10826,7 +10829,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B160" s="5">
         <v>46161.639195289354</v>
@@ -10836,7 +10839,7 @@
         <v>46161.846420138885</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10861,10 +10864,10 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>26</v>
@@ -10877,7 +10880,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B161" s="9">
         <v>46161.63920550926</v>
@@ -10887,7 +10890,7 @@
         <v>46161.846413113424</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10912,10 +10915,10 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>26</v>
@@ -10928,7 +10931,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B162" s="5">
         <v>46161.63921432871</v>
@@ -10938,7 +10941,7 @@
         <v>46161.84641241898</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -10963,13 +10966,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10979,7 +10982,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B163" s="9">
         <v>46161.58117752315</v>
@@ -10989,7 +10992,7 @@
         <v>46161.84660503472</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11016,13 +11019,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q163" s="9">
         <v>46309</v>
@@ -11042,7 +11045,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B164" s="5">
         <v>46161.58118137732</v>
@@ -11052,7 +11055,7 @@
         <v>46161.84658016203</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11079,13 +11082,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11095,7 +11098,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B165" s="9">
         <v>46161.639253761576</v>
@@ -11105,7 +11108,7 @@
         <v>46161.846577187505</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11132,10 +11135,10 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P165" s="10" t="s">
         <v>26</v>
@@ -11148,7 +11151,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B166" s="5">
         <v>46161.63928710648</v>
@@ -11158,7 +11161,7 @@
         <v>46161.84657417824</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11185,10 +11188,10 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11201,7 +11204,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B167" s="9">
         <v>46161.63929736111</v>
@@ -11211,7 +11214,7 @@
         <v>46161.84657136574</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11238,10 +11241,10 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P167" s="10" t="s">
         <v>26</v>
@@ -11254,7 +11257,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B168" s="5">
         <v>46161.6393071412</v>
@@ -11264,7 +11267,7 @@
         <v>46161.84656841435</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11291,10 +11294,10 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>26</v>
@@ -11307,7 +11310,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B169" s="9">
         <v>46161.639315625</v>
@@ -11317,7 +11320,7 @@
         <v>46161.84656539352</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11344,10 +11347,10 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11360,7 +11363,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B170" s="5">
         <v>46161.63932686343</v>
@@ -11370,7 +11373,7 @@
         <v>46161.846562754625</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11397,10 +11400,10 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11413,7 +11416,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B171" s="9">
         <v>46161.63933708333</v>
@@ -11423,7 +11426,7 @@
         <v>46161.8465599537</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11450,10 +11453,10 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>26</v>
@@ -11466,7 +11469,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B172" s="5">
         <v>46161.63935484954</v>
@@ -11476,7 +11479,7 @@
         <v>46161.846553807874</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11503,10 +11506,10 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>26</v>
@@ -11519,7 +11522,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B173" s="9">
         <v>46161.63936453704</v>
@@ -11529,7 +11532,7 @@
         <v>46161.84655313657</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11556,13 +11559,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11572,7 +11575,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B174" s="5">
         <v>46161.5811852662</v>
@@ -11582,7 +11585,7 @@
         <v>46161.84092732639</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>25</v>
@@ -11606,7 +11609,7 @@
         <v>26</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>26</v>
@@ -11619,7 +11622,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B175" s="9">
         <v>46161.581188020835</v>
@@ -11629,16 +11632,16 @@
         <v>46161.84675815972</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I175" s="9">
         <v>46310</v>
@@ -11656,13 +11659,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q175" s="9">
         <v>46310</v>
@@ -11682,7 +11685,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B176" s="5">
         <v>46161.581192673606</v>
@@ -11692,16 +11695,16 @@
         <v>46161.846749351855</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I176" s="5">
         <v>46310</v>
@@ -11719,13 +11722,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11735,7 +11738,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B177" s="9">
         <v>46161.63982708333</v>
@@ -11745,16 +11748,16 @@
         <v>46161.84674655093</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I177" s="9">
         <v>46310</v>
@@ -11772,13 +11775,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11788,7 +11791,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B178" s="5">
         <v>46161.63983532407</v>
@@ -11798,16 +11801,16 @@
         <v>46161.846743981485</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I178" s="5">
         <v>46310</v>
@@ -11825,13 +11828,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11841,7 +11844,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B179" s="9">
         <v>46161.63984421296</v>
@@ -11851,16 +11854,16 @@
         <v>46161.84674143518</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I179" s="9">
         <v>46310</v>
@@ -11878,13 +11881,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11894,7 +11897,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B180" s="5">
         <v>46161.63985878472</v>
@@ -11904,16 +11907,16 @@
         <v>46161.846738541666</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I180" s="5">
         <v>46310</v>
@@ -11931,13 +11934,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11947,7 +11950,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B181" s="9">
         <v>46161.63986780093</v>
@@ -11957,16 +11960,16 @@
         <v>46161.84673559028</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I181" s="9">
         <v>46310</v>
@@ -11984,13 +11987,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -12000,7 +12003,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B182" s="5">
         <v>46161.639875</v>
@@ -12010,16 +12013,16 @@
         <v>46161.84673289352</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I182" s="5">
         <v>46310</v>
@@ -12037,13 +12040,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12053,7 +12056,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B183" s="9">
         <v>46161.63988342593</v>
@@ -12063,16 +12066,16 @@
         <v>46161.84672489583</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I183" s="9">
         <v>46310</v>
@@ -12090,13 +12093,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12106,7 +12109,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B184" s="5">
         <v>46161.63989143519</v>
@@ -12116,16 +12119,16 @@
         <v>46161.84672420139</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I184" s="5">
         <v>46310</v>
@@ -12143,13 +12146,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12159,7 +12162,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B185" s="9">
         <v>46161.639899340276</v>
@@ -12169,16 +12172,16 @@
         <v>46161.84672340278</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I185" s="9">
         <v>46310</v>
@@ -12196,13 +12199,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12212,7 +12215,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B186" s="5">
         <v>46161.5811965162</v>
@@ -12222,7 +12225,7 @@
         <v>46161.84690181713</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12249,13 +12252,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q186" s="5">
         <v>46311</v>
@@ -12275,7 +12278,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B187" s="9">
         <v>46161.58120002315</v>
@@ -12285,7 +12288,7 @@
         <v>46161.84690336806</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12312,13 +12315,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12328,7 +12331,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B188" s="5">
         <v>46161.63993424768</v>
@@ -12338,7 +12341,7 @@
         <v>46161.84690038195</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12365,13 +12368,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12381,7 +12384,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B189" s="9">
         <v>46161.6399947801</v>
@@ -12391,7 +12394,7 @@
         <v>46161.84689746528</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12418,13 +12421,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12434,7 +12437,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B190" s="5">
         <v>46161.640004444445</v>
@@ -12444,7 +12447,7 @@
         <v>46161.84689446759</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12471,13 +12474,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12487,7 +12490,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B191" s="9">
         <v>46161.64001501157</v>
@@ -12497,7 +12500,7 @@
         <v>46161.84689137731</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12524,13 +12527,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12540,7 +12543,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B192" s="5">
         <v>46161.640023831016</v>
@@ -12550,7 +12553,7 @@
         <v>46161.846888796295</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12577,13 +12580,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12593,7 +12596,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B193" s="9">
         <v>46161.640038310186</v>
@@ -12603,7 +12606,7 @@
         <v>46161.84688606481</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12630,13 +12633,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12646,7 +12649,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B194" s="5">
         <v>46161.64004747685</v>
@@ -12656,7 +12659,7 @@
         <v>46161.846882557875</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12683,13 +12686,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12699,7 +12702,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B195" s="9">
         <v>46161.64005649305</v>
@@ -12709,7 +12712,7 @@
         <v>46161.84687957176</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -12736,13 +12739,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12752,7 +12755,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B196" s="5">
         <v>46161.64006346065</v>
@@ -12762,7 +12765,7 @@
         <v>46161.846870243055</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12789,13 +12792,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12805,7 +12808,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B197" s="9">
         <v>46161.58120399306</v>
@@ -12815,16 +12818,16 @@
         <v>46161.84710645833</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H197" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I197" s="10"/>
       <c r="J197" s="9">
@@ -12840,13 +12843,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q197" s="9">
         <v>46316</v>
@@ -12866,7 +12869,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B198" s="5">
         <v>46161.58120755787</v>
@@ -12876,16 +12879,16 @@
         <v>46161.847077812505</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -12901,13 +12904,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12917,7 +12920,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B199" s="9">
         <v>46161.6401252662</v>
@@ -12927,16 +12930,16 @@
         <v>46161.84707505787</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -12952,13 +12955,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12968,7 +12971,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B200" s="5">
         <v>46161.64014137731</v>
@@ -12978,16 +12981,16 @@
         <v>46161.847072476856</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13003,13 +13006,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13019,7 +13022,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B201" s="9">
         <v>46161.64015293981</v>
@@ -13029,16 +13032,16 @@
         <v>46161.84706930556</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -13054,13 +13057,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13070,7 +13073,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B202" s="5">
         <v>46161.64016740741</v>
@@ -13080,16 +13083,16 @@
         <v>46161.847066608796</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13105,13 +13108,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13121,7 +13124,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B203" s="9">
         <v>46161.640203877316</v>
@@ -13131,16 +13134,16 @@
         <v>46161.84706402778</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -13156,13 +13159,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13172,7 +13175,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B204" s="5">
         <v>46161.64021510417</v>
@@ -13182,16 +13185,16 @@
         <v>46161.84706112268</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13207,13 +13210,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13223,7 +13226,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B205" s="9">
         <v>46161.64022702546</v>
@@ -13233,16 +13236,16 @@
         <v>46161.847053425925</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13258,13 +13261,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13274,7 +13277,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B206" s="5">
         <v>46161.64023784723</v>
@@ -13284,16 +13287,16 @@
         <v>46161.8470527662</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13309,13 +13312,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13325,7 +13328,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B207" s="9">
         <v>46161.64025311342</v>
@@ -13335,16 +13338,16 @@
         <v>46161.84705210648</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13360,13 +13363,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13376,7 +13379,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B208" s="5">
         <v>46161.58121466435</v>
@@ -13386,16 +13389,16 @@
         <v>46161.84730193287</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I208" s="5">
         <v>46317</v>
@@ -13413,13 +13416,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q208" s="5">
         <v>46317</v>
@@ -13439,7 +13442,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B209" s="9">
         <v>46161.58125732639</v>
@@ -13449,16 +13452,16 @@
         <v>46161.84728091436</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I209" s="10"/>
       <c r="J209" s="9">
@@ -13474,13 +13477,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13490,7 +13493,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B210" s="5">
         <v>46161.640307905094</v>
@@ -13500,16 +13503,16 @@
         <v>46161.84727769676</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13525,10 +13528,10 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>26</v>
@@ -13541,7 +13544,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B211" s="9">
         <v>46161.64031635417</v>
@@ -13551,16 +13554,16 @@
         <v>46161.84727525463</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I211" s="10"/>
       <c r="J211" s="9">
@@ -13576,10 +13579,10 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>26</v>
@@ -13592,7 +13595,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B212" s="5">
         <v>46161.64032832176</v>
@@ -13602,16 +13605,16 @@
         <v>46161.84727247685</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13627,10 +13630,10 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>26</v>
@@ -13643,7 +13646,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B213" s="9">
         <v>46161.640337986115</v>
@@ -13653,16 +13656,16 @@
         <v>46161.84726945602</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I213" s="10"/>
       <c r="J213" s="9">
@@ -13678,10 +13681,10 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>26</v>
@@ -13694,7 +13697,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B214" s="5">
         <v>46161.64035862268</v>
@@ -13704,16 +13707,16 @@
         <v>46161.84726638889</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13729,10 +13732,10 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13745,7 +13748,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B215" s="9">
         <v>46161.64036773148</v>
@@ -13755,16 +13758,16 @@
         <v>46161.84726359954</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I215" s="10"/>
       <c r="J215" s="9">
@@ -13780,10 +13783,10 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13796,7 +13799,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B216" s="5">
         <v>46161.64037657407</v>
@@ -13806,16 +13809,16 @@
         <v>46161.84726060185</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13831,10 +13834,10 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>26</v>
@@ -13847,7 +13850,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B217" s="9">
         <v>46161.64038473379</v>
@@ -13857,16 +13860,16 @@
         <v>46161.847254699074</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I217" s="10"/>
       <c r="J217" s="9">
@@ -13882,10 +13885,10 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>26</v>
@@ -13898,7 +13901,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B218" s="5">
         <v>46161.64039350694</v>
@@ -13908,16 +13911,16 @@
         <v>46161.8472540625</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -13933,10 +13936,10 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>26</v>
@@ -13949,7 +13952,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B219" s="9">
         <v>46161.581262824075</v>
@@ -13959,7 +13962,7 @@
         <v>46161.84801045139</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>25</v>
@@ -13983,7 +13986,7 @@
         <v>26</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>26</v>
@@ -13996,7 +13999,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B220" s="5">
         <v>46161.58126615741</v>
@@ -14006,16 +14009,16 @@
         <v>46161.84764756945</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I220" s="5">
         <v>46318</v>
@@ -14033,13 +14036,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q220" s="5">
         <v>46318</v>
@@ -14059,7 +14062,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B221" s="9">
         <v>46161.581270821756</v>
@@ -14069,7 +14072,7 @@
         <v>46198.80656221065</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -14096,13 +14099,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q221" s="9">
         <v>46318</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="453">
   <si>
     <t>50001555 - "ZITRON COLOMBIA ARIS MINING SEGOVIA"</t>
   </si>
@@ -119,6 +119,29 @@
   </si>
   <si>
     <t>Apertura pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buenas,
+Para el pedido 50001555, se tienen 10 ventiladores ZVN 1-10-110/2 para Zitrón Colombia (Airis Marmato):
+Alcance: TOBERA + REJILLA + FAR 100/100 + VENT + FAR 100/100 + TIPO A
+    Plano para fabricación:
+        Ventilador ZVN 1-10-110/2 con motor Weg o similar
+        Alcance Chile: TOBERA + REJILLA + FAR 100/100 + VENT + FAR 100/100 + TIPO A
+        Alcance Colombia: 2FAR 100/100 + TIPO A
+        Carpeta de Plano. hgutierrez@zitron.com por favor tu apoyo.
+    Definición Rodete ZVN 1-10:
+        Alabes s/plano 3073.01
+        Código 300003
+        Calaje y Consumo. hgutierrez@zitron.com por favor tu apoyo.
+    Datos eléctricos motor 110KW:
+        110 kW, 460 V, 60 Hz, 2 polos, IE3, IP-55; FS 1,15
+        Grasera automatica
+    Tratamiento superficial estándar Zitrón:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    Fecha de despacho a colombia: 23-08-2026
+</t>
   </si>
   <si>
     <t>1214937300987398</t>
@@ -2170,7 +2193,7 @@
         <v>46175.87848385416</v>
       </c>
       <c r="D6" s="5">
-        <v>46213.69304453704</v>
+        <v>46213.76529921296</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2192,7 +2215,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -2224,7 +2247,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="9">
         <v>46161.58075194445</v>
@@ -2236,7 +2259,7 @@
         <v>46175.878510497685</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>26</v>
@@ -2255,7 +2278,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>26</v>
@@ -2287,7 +2310,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5">
         <v>46161.58075466435</v>
@@ -2299,7 +2322,7 @@
         <v>46175.878510925926</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -2318,7 +2341,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -2330,7 +2353,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q8" s="5">
         <v>46153</v>
@@ -2350,7 +2373,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="9">
         <v>46161.5807578588</v>
@@ -2362,7 +2385,7 @@
         <v>46175.87851096065</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>26</v>
@@ -2381,7 +2404,7 @@
         <v>26</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>26</v>
@@ -2413,7 +2436,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46161.580639618056</v>
@@ -2423,7 +2446,7 @@
         <v>46198.80657155093</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>25</v>
@@ -2447,7 +2470,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2457,12 +2480,12 @@
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
       <c r="U10" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="9">
         <v>46161.580761307865</v>
@@ -2474,16 +2497,16 @@
         <v>46198.80656200231</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I11" s="9">
         <v>46154</v>
@@ -2495,19 +2518,19 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q11" s="9">
         <v>46154</v>
@@ -2527,7 +2550,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" s="5">
         <v>46161.580766307874</v>
@@ -2539,16 +2562,16 @@
         <v>46198.80656201389</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I12" s="5">
         <v>46154</v>
@@ -2560,19 +2583,19 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="5">
         <v>46154</v>
@@ -2581,7 +2604,7 @@
         <v>46162</v>
       </c>
       <c r="S12" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T12" s="6">
         <v>1</v>
@@ -2592,7 +2615,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="9">
         <v>46161.580771423614</v>
@@ -2604,16 +2627,16 @@
         <v>46198.80656199074</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I13" s="9">
         <v>46154</v>
@@ -2625,19 +2648,19 @@
         <v>26</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q13" s="9">
         <v>46154</v>
@@ -2646,7 +2669,7 @@
         <v>46162</v>
       </c>
       <c r="S13" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T13" s="10">
         <v>1</v>
@@ -2657,7 +2680,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" s="5">
         <v>46161.58064403935</v>
@@ -2669,7 +2692,7 @@
         <v>46209.56506746528</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2693,7 +2716,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2710,7 +2733,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="9">
         <v>46161.58078354166</v>
@@ -2722,16 +2745,16 @@
         <v>46198.8073902662</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I15" s="9">
         <v>46156</v>
@@ -2749,13 +2772,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q15" s="9">
         <v>46156</v>
@@ -2775,7 +2798,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="5">
         <v>46161.580788680556</v>
@@ -2787,16 +2810,16 @@
         <v>46209.565114375</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I16" s="5">
         <v>46164</v>
@@ -2814,13 +2837,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q16" s="5">
         <v>46164</v>
@@ -2829,7 +2852,7 @@
         <v>46167</v>
       </c>
       <c r="S16" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
@@ -2840,7 +2863,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" s="9">
         <v>46161.58079363426</v>
@@ -2852,16 +2875,16 @@
         <v>46197.675101863424</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I17" s="9">
         <v>46164</v>
@@ -2879,13 +2902,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q17" s="9">
         <v>46164</v>
@@ -2894,18 +2917,18 @@
         <v>46167</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T17" s="10">
         <v>1</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
         <v>46161.58079903935</v>
@@ -2917,16 +2940,16 @@
         <v>46206.560436921296</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I18" s="5">
         <v>46224</v>
@@ -2944,13 +2967,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2970,7 +2993,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B19" s="9">
         <v>46161.58080373843</v>
@@ -2982,16 +3005,16 @@
         <v>46206.560617662035</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I19" s="9">
         <v>46224</v>
@@ -3009,13 +3032,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="9">
         <v>46224</v>
@@ -3035,7 +3058,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46161.58080740741</v>
@@ -3047,16 +3070,16 @@
         <v>46206.56075704861</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I20" s="5">
         <v>46224</v>
@@ -3074,13 +3097,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -3100,7 +3123,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" s="9">
         <v>46161.580810740736</v>
@@ -3112,16 +3135,16 @@
         <v>46206.560877592594</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I21" s="9">
         <v>46224</v>
@@ -3139,13 +3162,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="9">
         <v>46224</v>
@@ -3165,7 +3188,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46161.58064796297</v>
@@ -3175,7 +3198,7 @@
         <v>46211.83005701389</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -3199,7 +3222,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -3212,7 +3235,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B23" s="9">
         <v>46161.58081472223</v>
@@ -3224,16 +3247,16 @@
         <v>46209.56551446759</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I23" s="9">
         <v>46168</v>
@@ -3251,13 +3274,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="9">
         <v>46168</v>
@@ -3277,7 +3300,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46161.580819016206</v>
@@ -3289,16 +3312,16 @@
         <v>46209.56543981482</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I24" s="5">
         <v>46168</v>
@@ -3316,13 +3339,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3333,12 +3356,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46161.58082350694</v>
@@ -3350,16 +3373,16 @@
         <v>46209.565488576394</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I25" s="9">
         <v>46170</v>
@@ -3377,13 +3400,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3394,12 +3417,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46161.58082824074</v>
@@ -3411,16 +3434,16 @@
         <v>46209.56600694444</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46168</v>
@@ -3438,13 +3461,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q26" s="5">
         <v>46168</v>
@@ -3453,7 +3476,7 @@
         <v>46171</v>
       </c>
       <c r="S26" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3464,7 +3487,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46161.5808325463</v>
@@ -3476,16 +3499,16 @@
         <v>46209.56565858796</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I27" s="9">
         <v>46168</v>
@@ -3503,13 +3526,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3520,12 +3543,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46161.580836967594</v>
@@ -3537,16 +3560,16 @@
         <v>46209.56570685185</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46170</v>
@@ -3564,13 +3587,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3581,12 +3604,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="9">
         <v>46161.58084165509</v>
@@ -3596,16 +3619,16 @@
         <v>46198.805784641205</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I29" s="9">
         <v>46156</v>
@@ -3623,13 +3646,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q29" s="9">
         <v>46156</v>
@@ -3644,12 +3667,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46161.58084603009</v>
@@ -3661,16 +3684,16 @@
         <v>46198.80572795139</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46156</v>
@@ -3688,13 +3711,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3705,12 +3728,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46161.580850439816</v>
@@ -3720,16 +3743,16 @@
         <v>46198.80573190972</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3747,13 +3770,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3764,12 +3787,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46161.58085503472</v>
@@ -3781,16 +3804,16 @@
         <v>46198.80577622685</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I32" s="5">
         <v>46176</v>
@@ -3808,13 +3831,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3825,12 +3848,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46161.58085940972</v>
@@ -3842,16 +3865,16 @@
         <v>46211.830060266206</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I33" s="9">
         <v>46226</v>
@@ -3869,13 +3892,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q33" s="9">
         <v>46226</v>
@@ -3895,7 +3918,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46161.58086364584</v>
@@ -3907,16 +3930,16 @@
         <v>46205.61008960648</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I34" s="5">
         <v>46226</v>
@@ -3934,13 +3957,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3951,12 +3974,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46161.58086832176</v>
@@ -3968,16 +3991,16 @@
         <v>46211.83003016203</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I35" s="9">
         <v>46230</v>
@@ -3995,13 +4018,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -4012,12 +4035,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46161.58087322916</v>
@@ -4029,16 +4052,16 @@
         <v>46209.804952569444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -4056,10 +4079,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -4082,7 +4105,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="9">
         <v>46161.580931018514</v>
@@ -4094,16 +4117,16 @@
         <v>46205.610248032404</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I37" s="9">
         <v>46226</v>
@@ -4121,13 +4144,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4137,7 +4160,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46161.58093646991</v>
@@ -4149,16 +4172,16 @@
         <v>46209.809419513884</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -4176,13 +4199,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4192,7 +4215,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46161.580941099535</v>
@@ -4204,16 +4227,16 @@
         <v>46209.62288859954</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I39" s="9">
         <v>46225</v>
@@ -4231,10 +4254,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4257,7 +4280,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46161.58094532407</v>
@@ -4269,16 +4292,16 @@
         <v>46209.622784444444</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I40" s="5">
         <v>46225</v>
@@ -4296,13 +4319,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4312,7 +4335,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46161.58094997685</v>
@@ -4324,16 +4347,16 @@
         <v>46209.62283091435</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I41" s="9">
         <v>46234</v>
@@ -4351,13 +4374,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4367,7 +4390,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46161.58095447917</v>
@@ -4377,16 +4400,16 @@
         <v>46209.62284077547</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I42" s="5">
         <v>46265</v>
@@ -4404,10 +4427,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4420,7 +4443,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>46161.58095743056</v>
@@ -4432,16 +4455,16 @@
         <v>46209.81259914352</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I43" s="9">
         <v>46226</v>
@@ -4459,10 +4482,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4485,7 +4508,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46161.58096091435</v>
@@ -4497,16 +4520,16 @@
         <v>46209.81220270833</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I44" s="5">
         <v>46226</v>
@@ -4524,13 +4547,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4540,7 +4563,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46161.580964988425</v>
@@ -4552,16 +4575,16 @@
         <v>46209.81257327546</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I45" s="9">
         <v>46230</v>
@@ -4579,13 +4602,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4595,7 +4618,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46161.58065239583</v>
@@ -4607,7 +4630,7 @@
         <v>46210.52870142361</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4631,7 +4654,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4648,7 +4671,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" s="9">
         <v>46161.580969780094</v>
@@ -4660,16 +4683,16 @@
         <v>46197.70504644676</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I47" s="9">
         <v>46164</v>
@@ -4687,13 +4710,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q47" s="9">
         <v>46164</v>
@@ -4702,7 +4725,7 @@
         <v>46170</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4713,7 +4736,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46161.580975069446</v>
@@ -4725,16 +4748,16 @@
         <v>46213.18419743056</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46216</v>
@@ -4752,13 +4775,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46216</v>
@@ -4767,7 +4790,7 @@
         <v>46220</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4778,7 +4801,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46161.58098100695</v>
@@ -4790,16 +4813,16 @@
         <v>46198.807511481486</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I49" s="9">
         <v>46223</v>
@@ -4817,13 +4840,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q49" s="9">
         <v>46223</v>
@@ -4843,7 +4866,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46161.58099116899</v>
@@ -4853,16 +4876,16 @@
         <v>46161.84476310185</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I50" s="5">
         <v>46308</v>
@@ -4880,10 +4903,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4901,12 +4924,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B51" s="9">
         <v>46161.58099418982</v>
@@ -4916,16 +4939,16 @@
         <v>46161.84476607639</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4941,13 +4964,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4957,7 +4980,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46161.63966489583</v>
@@ -4967,16 +4990,16 @@
         <v>46161.844763472225</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4992,13 +5015,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5008,7 +5031,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46161.63967261574</v>
@@ -5018,16 +5041,16 @@
         <v>46161.84476069444</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5043,13 +5066,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5059,7 +5082,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46161.63968388889</v>
@@ -5069,16 +5092,16 @@
         <v>46161.84475773148</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5094,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5110,7 +5133,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B55" s="9">
         <v>46161.63969275463</v>
@@ -5120,16 +5143,16 @@
         <v>46161.84475471065</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5145,13 +5168,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5161,7 +5184,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46161.639705208334</v>
@@ -5171,16 +5194,16 @@
         <v>46161.84475174769</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5196,13 +5219,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5212,7 +5235,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B57" s="9">
         <v>46161.639715474535</v>
@@ -5222,16 +5245,16 @@
         <v>46161.84474863426</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5247,13 +5270,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5263,7 +5286,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46161.63972679398</v>
@@ -5273,16 +5296,16 @@
         <v>46161.84474503472</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5298,13 +5321,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5314,7 +5337,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B59" s="9">
         <v>46161.63974304398</v>
@@ -5324,16 +5347,16 @@
         <v>46161.84473834491</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5349,13 +5372,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5365,7 +5388,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46161.63975269676</v>
@@ -5375,16 +5398,16 @@
         <v>46161.84473753472</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5400,13 +5423,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5416,7 +5439,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46161.58099818287</v>
@@ -5426,7 +5449,7 @@
         <v>46161.79647144676</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5450,7 +5473,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5463,7 +5486,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B62" s="5">
         <v>46161.58100145833</v>
@@ -5473,16 +5496,16 @@
         <v>46211.830047766205</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46239</v>
@@ -5500,13 +5523,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q62" s="5">
         <v>46239</v>
@@ -5521,12 +5544,12 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B63" s="9">
         <v>46161.58100614583</v>
@@ -5536,16 +5559,16 @@
         <v>46161.84491849537</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I63" s="9">
         <v>46241</v>
@@ -5563,13 +5586,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="9">
         <v>46241</v>
@@ -5584,12 +5607,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B64" s="5">
         <v>46161.58101638889</v>
@@ -5599,16 +5622,16 @@
         <v>46209.804944710646</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46239</v>
@@ -5626,13 +5649,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q64" s="5">
         <v>46239</v>
@@ -5647,12 +5670,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B65" s="9">
         <v>46161.58102099537</v>
@@ -5662,16 +5685,16 @@
         <v>46161.84491503472</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I65" s="9">
         <v>46241</v>
@@ -5689,13 +5712,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="9">
         <v>46241</v>
@@ -5710,12 +5733,12 @@
         <v>0</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B66" s="5">
         <v>46161.581024722225</v>
@@ -5725,16 +5748,16 @@
         <v>46209.81259190972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46239</v>
@@ -5752,13 +5775,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q66" s="5">
         <v>46239</v>
@@ -5773,12 +5796,12 @@
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B67" s="9">
         <v>46161.58102864583</v>
@@ -5788,16 +5811,16 @@
         <v>46161.844914270834</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I67" s="9">
         <v>46241</v>
@@ -5815,13 +5838,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q67" s="9">
         <v>46241</v>
@@ -5836,12 +5859,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B68" s="5">
         <v>46161.58103207176</v>
@@ -5851,7 +5874,7 @@
         <v>46161.797785821764</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5875,7 +5898,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5888,7 +5911,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B69" s="9">
         <v>46161.58103457176</v>
@@ -5898,16 +5921,16 @@
         <v>46161.845178449075</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I69" s="9">
         <v>46245</v>
@@ -5925,13 +5948,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q69" s="9">
         <v>46245</v>
@@ -5946,12 +5969,12 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46161.58103962963</v>
@@ -5961,16 +5984,16 @@
         <v>46161.845147071755</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I70" s="5">
         <v>46245</v>
@@ -5988,13 +6011,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6004,7 +6027,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46161.582011805556</v>
@@ -6014,16 +6037,16 @@
         <v>46161.84514348379</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I71" s="9">
         <v>46245</v>
@@ -6041,13 +6064,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6057,7 +6080,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46161.58202383102</v>
@@ -6067,16 +6090,16 @@
         <v>46161.845140324076</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I72" s="5">
         <v>46245</v>
@@ -6094,13 +6117,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6110,7 +6133,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B73" s="9">
         <v>46161.582662650464</v>
@@ -6120,16 +6143,16 @@
         <v>46161.845136655094</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I73" s="9">
         <v>46245</v>
@@ -6147,13 +6170,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6163,7 +6186,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46161.58267322917</v>
@@ -6173,16 +6196,16 @@
         <v>46161.845133518524</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I74" s="5">
         <v>46245</v>
@@ -6200,13 +6223,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6216,7 +6239,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46161.58270134259</v>
@@ -6226,16 +6249,16 @@
         <v>46161.84513074074</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I75" s="9">
         <v>46245</v>
@@ -6253,13 +6276,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6269,7 +6292,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46161.58271427083</v>
@@ -6279,16 +6302,16 @@
         <v>46161.84512803241</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I76" s="5">
         <v>46245</v>
@@ -6306,13 +6329,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6322,7 +6345,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46161.58272651621</v>
@@ -6332,16 +6355,16 @@
         <v>46161.84512407407</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I77" s="9">
         <v>46245</v>
@@ -6359,13 +6382,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6375,7 +6398,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
         <v>46161.58277962963</v>
@@ -6385,16 +6408,16 @@
         <v>46161.845117916666</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I78" s="5">
         <v>46245</v>
@@ -6412,13 +6435,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6428,7 +6451,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B79" s="9">
         <v>46161.58279046296</v>
@@ -6438,16 +6461,16 @@
         <v>46161.84511721064</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I79" s="9">
         <v>46245</v>
@@ -6465,13 +6488,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6481,7 +6504,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5">
         <v>46161.58104538194</v>
@@ -6491,16 +6514,16 @@
         <v>46161.845344814814</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I80" s="5">
         <v>46254</v>
@@ -6518,13 +6541,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q80" s="5">
         <v>46254</v>
@@ -6539,12 +6562,12 @@
         <v>0</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B81" s="9">
         <v>46161.58104903935</v>
@@ -6554,16 +6577,16 @@
         <v>46198.80752025463</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I81" s="9">
         <v>46254</v>
@@ -6581,13 +6604,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6597,7 +6620,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46161.582834120374</v>
@@ -6607,16 +6630,16 @@
         <v>46161.84533628472</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I82" s="5">
         <v>46254</v>
@@ -6634,13 +6657,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6650,7 +6673,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B83" s="9">
         <v>46161.58286459491</v>
@@ -6660,16 +6683,16 @@
         <v>46161.84533336805</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I83" s="9">
         <v>46254</v>
@@ -6687,13 +6710,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6703,7 +6726,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B84" s="5">
         <v>46161.58287381944</v>
@@ -6713,16 +6736,16 @@
         <v>46161.84533065972</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I84" s="5">
         <v>46254</v>
@@ -6740,13 +6763,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6756,7 +6779,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B85" s="9">
         <v>46161.58288365741</v>
@@ -6766,16 +6789,16 @@
         <v>46161.84532790509</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I85" s="9">
         <v>46254</v>
@@ -6793,13 +6816,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6809,7 +6832,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B86" s="5">
         <v>46161.58289255787</v>
@@ -6819,16 +6842,16 @@
         <v>46161.84532486111</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I86" s="5">
         <v>46254</v>
@@ -6846,13 +6869,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6862,7 +6885,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B87" s="9">
         <v>46161.58292542824</v>
@@ -6872,16 +6895,16 @@
         <v>46161.84532211805</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I87" s="9">
         <v>46254</v>
@@ -6899,13 +6922,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6915,7 +6938,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B88" s="5">
         <v>46161.58293696759</v>
@@ -6925,16 +6948,16 @@
         <v>46161.84531927083</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I88" s="5">
         <v>46254</v>
@@ -6952,13 +6975,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6968,7 +6991,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B89" s="9">
         <v>46161.58295282407</v>
@@ -6978,16 +7001,16 @@
         <v>46161.84531311343</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I89" s="9">
         <v>46254</v>
@@ -7005,13 +7028,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7021,7 +7044,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B90" s="5">
         <v>46161.58296773148</v>
@@ -7031,16 +7054,16 @@
         <v>46161.84531243055</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I90" s="5">
         <v>46254</v>
@@ -7058,13 +7081,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7074,7 +7097,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B91" s="9">
         <v>46161.581053761576</v>
@@ -7084,16 +7107,16 @@
         <v>46161.84552644676</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -7111,13 +7134,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q91" s="9">
         <v>46274</v>
@@ -7132,12 +7155,12 @@
         <v>0</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B92" s="5">
         <v>46161.58105741898</v>
@@ -7147,16 +7170,16 @@
         <v>46198.80752082176</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -7174,13 +7197,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7190,7 +7213,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B93" s="9">
         <v>46161.583039942125</v>
@@ -7200,16 +7223,16 @@
         <v>46161.84550880787</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I93" s="9">
         <v>46274</v>
@@ -7227,13 +7250,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7243,7 +7266,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B94" s="5">
         <v>46161.58305715278</v>
@@ -7253,16 +7276,16 @@
         <v>46161.845505324076</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I94" s="5">
         <v>46274</v>
@@ -7280,13 +7303,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7296,7 +7319,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B95" s="9">
         <v>46161.583076689814</v>
@@ -7306,16 +7329,16 @@
         <v>46161.84550258102</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I95" s="9">
         <v>46274</v>
@@ -7333,13 +7356,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7349,7 +7372,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B96" s="5">
         <v>46161.58308886574</v>
@@ -7359,16 +7382,16 @@
         <v>46161.84549928241</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I96" s="5">
         <v>46274</v>
@@ -7386,13 +7409,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7402,7 +7425,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B97" s="9">
         <v>46161.58310019676</v>
@@ -7412,16 +7435,16 @@
         <v>46161.84549533565</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I97" s="9">
         <v>46274</v>
@@ -7439,13 +7462,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7455,7 +7478,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B98" s="5">
         <v>46161.5831108912</v>
@@ -7465,16 +7488,16 @@
         <v>46161.84549206018</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I98" s="5">
         <v>46274</v>
@@ -7492,13 +7515,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7508,7 +7531,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B99" s="9">
         <v>46161.58312844907</v>
@@ -7518,16 +7541,16 @@
         <v>46161.84548887731</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I99" s="9">
         <v>46274</v>
@@ -7545,13 +7568,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7561,7 +7584,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B100" s="5">
         <v>46161.58300775463</v>
@@ -7571,16 +7594,16 @@
         <v>46161.84548230324</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I100" s="5">
         <v>46274</v>
@@ -7598,13 +7621,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7614,7 +7637,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B101" s="9">
         <v>46161.639501875004</v>
@@ -7624,16 +7647,16 @@
         <v>46161.845481620374</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I101" s="9">
         <v>46274</v>
@@ -7651,13 +7674,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7667,7 +7690,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B102" s="5">
         <v>46161.58110506945</v>
@@ -7677,7 +7700,7 @@
         <v>46161.80776861111</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7701,7 +7724,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7714,7 +7737,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B103" s="9">
         <v>46161.581108530096</v>
@@ -7724,16 +7747,16 @@
         <v>46209.56572255787</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I103" s="9">
         <v>46174</v>
@@ -7751,13 +7774,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q103" s="9">
         <v>46174</v>
@@ -7766,18 +7789,18 @@
         <v>46175</v>
       </c>
       <c r="S103" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T103" s="10">
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B104" s="5">
         <v>46161.58111370371</v>
@@ -7787,16 +7810,16 @@
         <v>46209.56550644676</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I104" s="5">
         <v>46282</v>
@@ -7814,13 +7837,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q104" s="5">
         <v>46282</v>
@@ -7835,12 +7858,12 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B105" s="9">
         <v>46161.581118449074</v>
@@ -7850,16 +7873,16 @@
         <v>46161.84560644676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I105" s="9">
         <v>46301</v>
@@ -7877,13 +7900,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q105" s="9">
         <v>46301</v>
@@ -7898,12 +7921,12 @@
         <v>0</v>
       </c>
       <c r="U105" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46161.58112311343</v>
@@ -7913,16 +7936,16 @@
         <v>46209.62284840278</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I106" s="5">
         <v>46237</v>
@@ -7940,13 +7963,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q106" s="5">
         <v>46237</v>
@@ -7961,12 +7984,12 @@
         <v>0</v>
       </c>
       <c r="U106" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B107" s="9">
         <v>46161.58112702546</v>
@@ -7976,7 +7999,7 @@
         <v>46161.83387362269</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -8000,7 +8023,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -8013,7 +8036,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B108" s="5">
         <v>46161.58112984954</v>
@@ -8023,16 +8046,16 @@
         <v>46161.84578230324</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I108" s="5">
         <v>46276</v>
@@ -8050,13 +8073,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q108" s="5">
         <v>46276</v>
@@ -8071,12 +8094,12 @@
         <v>0</v>
       </c>
       <c r="U108" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B109" s="9">
         <v>46161.581135555556</v>
@@ -8086,16 +8109,16 @@
         <v>46161.84577694444</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I109" s="9">
         <v>46276</v>
@@ -8113,13 +8136,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8129,7 +8152,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B110" s="5">
         <v>46161.58317730324</v>
@@ -8139,16 +8162,16 @@
         <v>46161.84577366898</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I110" s="5">
         <v>46276</v>
@@ -8166,13 +8189,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8182,7 +8205,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B111" s="9">
         <v>46161.58318758102</v>
@@ -8192,16 +8215,16 @@
         <v>46161.845770879634</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I111" s="9">
         <v>46276</v>
@@ -8219,13 +8242,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8235,7 +8258,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B112" s="5">
         <v>46161.5831975926</v>
@@ -8245,16 +8268,16 @@
         <v>46161.84576709491</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I112" s="5">
         <v>46276</v>
@@ -8272,13 +8295,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8288,7 +8311,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B113" s="9">
         <v>46161.58320657407</v>
@@ -8298,16 +8321,16 @@
         <v>46161.84576415509</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I113" s="9">
         <v>46276</v>
@@ -8325,13 +8348,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8341,7 +8364,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B114" s="5">
         <v>46161.58322151621</v>
@@ -8351,16 +8374,16 @@
         <v>46161.84576082176</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I114" s="5">
         <v>46276</v>
@@ -8378,13 +8401,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8394,7 +8417,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B115" s="9">
         <v>46161.58322717593</v>
@@ -8404,16 +8427,16 @@
         <v>46161.84575040509</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I115" s="9">
         <v>46276</v>
@@ -8431,13 +8454,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8447,7 +8470,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B116" s="5">
         <v>46161.58324248843</v>
@@ -8457,16 +8480,16 @@
         <v>46161.84574967592</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I116" s="5">
         <v>46276</v>
@@ -8484,13 +8507,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8500,7 +8523,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B117" s="9">
         <v>46161.58325402778</v>
@@ -8510,16 +8533,16 @@
         <v>46161.845748946755</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I117" s="9">
         <v>46276</v>
@@ -8537,13 +8560,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8553,7 +8576,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B118" s="5">
         <v>46161.58326291667</v>
@@ -8563,16 +8586,16 @@
         <v>46161.84574821759</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I118" s="5">
         <v>46276</v>
@@ -8590,13 +8613,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8606,7 +8629,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B119" s="9">
         <v>46161.58113928241</v>
@@ -8616,16 +8639,16 @@
         <v>46161.845971400464</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I119" s="9">
         <v>46296</v>
@@ -8643,13 +8666,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q119" s="9">
         <v>46296</v>
@@ -8664,12 +8687,12 @@
         <v>0</v>
       </c>
       <c r="U119" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B120" s="5">
         <v>46161.58114282407</v>
@@ -8679,16 +8702,16 @@
         <v>46198.807521180555</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I120" s="5">
         <v>46296</v>
@@ -8706,13 +8729,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8722,7 +8745,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B121" s="9">
         <v>46161.585882430554</v>
@@ -8732,16 +8755,16 @@
         <v>46198.807499965274</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I121" s="9">
         <v>46296</v>
@@ -8759,13 +8782,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8775,7 +8798,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B122" s="5">
         <v>46161.58590298611</v>
@@ -8785,16 +8808,16 @@
         <v>46198.80750063657</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I122" s="5">
         <v>46296</v>
@@ -8812,13 +8835,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8828,7 +8851,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B123" s="9">
         <v>46161.585919861114</v>
@@ -8838,16 +8861,16 @@
         <v>46198.80750122685</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I123" s="9">
         <v>46296</v>
@@ -8865,13 +8888,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8881,7 +8904,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B124" s="5">
         <v>46161.585927175925</v>
@@ -8891,16 +8914,16 @@
         <v>46198.807501793985</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I124" s="5">
         <v>46296</v>
@@ -8918,13 +8941,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8934,7 +8957,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B125" s="9">
         <v>46161.58593310185</v>
@@ -8944,16 +8967,16 @@
         <v>46198.807502384254</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I125" s="9">
         <v>46296</v>
@@ -8971,13 +8994,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8987,7 +9010,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B126" s="5">
         <v>46161.58593739584</v>
@@ -8997,16 +9020,16 @@
         <v>46198.807502951386</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I126" s="5">
         <v>46296</v>
@@ -9024,13 +9047,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9040,7 +9063,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B127" s="9">
         <v>46161.58594590278</v>
@@ -9050,16 +9073,16 @@
         <v>46198.80750380787</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I127" s="9">
         <v>46296</v>
@@ -9077,13 +9100,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9093,7 +9116,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B128" s="5">
         <v>46161.5859562963</v>
@@ -9103,16 +9126,16 @@
         <v>46198.80750443287</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I128" s="5">
         <v>46296</v>
@@ -9130,13 +9153,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9146,7 +9169,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B129" s="9">
         <v>46161.58618912037</v>
@@ -9156,16 +9179,16 @@
         <v>46198.80750512732</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I129" s="9">
         <v>46296</v>
@@ -9183,13 +9206,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9199,7 +9222,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B130" s="5">
         <v>46161.58114761574</v>
@@ -9209,16 +9232,16 @@
         <v>46161.8461249074</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I130" s="5">
         <v>46300</v>
@@ -9236,13 +9259,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q130" s="5">
         <v>46300</v>
@@ -9257,12 +9280,12 @@
         <v>0</v>
       </c>
       <c r="U130" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B131" s="9">
         <v>46161.58115116898</v>
@@ -9272,16 +9295,16 @@
         <v>46198.807510914354</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I131" s="9">
         <v>46300</v>
@@ -9299,13 +9322,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9315,7 +9338,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B132" s="5">
         <v>46161.58603712963</v>
@@ -9325,16 +9348,16 @@
         <v>46198.80750575232</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I132" s="5">
         <v>46300</v>
@@ -9352,13 +9375,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9368,7 +9391,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B133" s="9">
         <v>46161.586044930555</v>
@@ -9378,16 +9401,16 @@
         <v>46198.8075062037</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I133" s="9">
         <v>46300</v>
@@ -9405,13 +9428,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9421,7 +9444,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B134" s="5">
         <v>46161.58605891204</v>
@@ -9431,16 +9454,16 @@
         <v>46198.807506666664</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I134" s="5">
         <v>46300</v>
@@ -9458,13 +9481,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9474,7 +9497,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B135" s="9">
         <v>46161.58606768519</v>
@@ -9484,16 +9507,16 @@
         <v>46198.8075071412</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I135" s="9">
         <v>46300</v>
@@ -9511,13 +9534,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9527,7 +9550,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B136" s="5">
         <v>46161.58607575232</v>
@@ -9537,16 +9560,16 @@
         <v>46198.807507708334</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I136" s="5">
         <v>46300</v>
@@ -9564,13 +9587,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9580,7 +9603,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B137" s="9">
         <v>46161.586088854165</v>
@@ -9590,16 +9613,16 @@
         <v>46198.80750815972</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I137" s="9">
         <v>46300</v>
@@ -9617,13 +9640,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9633,7 +9656,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B138" s="5">
         <v>46161.58609570602</v>
@@ -9643,16 +9666,16 @@
         <v>46198.80750863426</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I138" s="5">
         <v>46300</v>
@@ -9670,13 +9693,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9686,7 +9709,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B139" s="9">
         <v>46161.586110578704</v>
@@ -9696,16 +9719,16 @@
         <v>46198.807509085644</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I139" s="9">
         <v>46300</v>
@@ -9723,13 +9746,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9739,7 +9762,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B140" s="5">
         <v>46161.58612255787</v>
@@ -9749,16 +9772,16 @@
         <v>46198.80750956018</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I140" s="5">
         <v>46300</v>
@@ -9776,13 +9799,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9792,7 +9815,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B141" s="9">
         <v>46161.58115643519</v>
@@ -9802,16 +9825,16 @@
         <v>46161.84629616898</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I141" s="9">
         <v>46303</v>
@@ -9829,13 +9852,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q141" s="9">
         <v>46303</v>
@@ -9850,12 +9873,12 @@
         <v>0</v>
       </c>
       <c r="U141" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B142" s="5">
         <v>46161.58115993056</v>
@@ -9865,16 +9888,16 @@
         <v>46198.807521759256</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I142" s="5">
         <v>46303</v>
@@ -9892,13 +9915,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9908,7 +9931,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B143" s="9">
         <v>46161.58622641204</v>
@@ -9918,16 +9941,16 @@
         <v>46198.80750998843</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I143" s="9">
         <v>46303</v>
@@ -9945,13 +9968,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9961,7 +9984,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B144" s="5">
         <v>46161.586235995375</v>
@@ -9971,16 +9994,16 @@
         <v>46198.807510416664</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I144" s="5">
         <v>46303</v>
@@ -9998,13 +10021,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10014,7 +10037,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B145" s="9">
         <v>46161.586246770836</v>
@@ -10024,16 +10047,16 @@
         <v>46161.846280046295</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I145" s="9">
         <v>46303</v>
@@ -10051,13 +10074,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10067,7 +10090,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B146" s="5">
         <v>46161.586256435185</v>
@@ -10077,16 +10100,16 @@
         <v>46161.84627699074</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I146" s="5">
         <v>46303</v>
@@ -10104,13 +10127,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10120,7 +10143,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B147" s="9">
         <v>46161.586265833335</v>
@@ -10130,16 +10153,16 @@
         <v>46161.84627394676</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I147" s="9">
         <v>46303</v>
@@ -10157,13 +10180,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10173,7 +10196,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B148" s="5">
         <v>46161.586275671296</v>
@@ -10183,16 +10206,16 @@
         <v>46161.84627113426</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I148" s="5">
         <v>46303</v>
@@ -10210,13 +10233,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10226,7 +10249,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B149" s="9">
         <v>46161.58629186342</v>
@@ -10236,16 +10259,16 @@
         <v>46161.846268402776</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I149" s="9">
         <v>46303</v>
@@ -10263,13 +10286,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10279,7 +10302,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B150" s="5">
         <v>46161.58630879629</v>
@@ -10289,16 +10312,16 @@
         <v>46161.84626222222</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I150" s="5">
         <v>46303</v>
@@ -10316,13 +10339,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10332,7 +10355,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B151" s="9">
         <v>46161.58632163194</v>
@@ -10342,16 +10365,16 @@
         <v>46161.84626162037</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I151" s="9">
         <v>46303</v>
@@ -10369,13 +10392,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10385,7 +10408,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B152" s="5">
         <v>46161.5811646875</v>
@@ -10395,16 +10418,16 @@
         <v>46161.84643925926</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I152" s="5">
         <v>46307</v>
@@ -10422,13 +10445,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q152" s="5">
         <v>46307</v>
@@ -10443,12 +10466,12 @@
         <v>0</v>
       </c>
       <c r="U152" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B153" s="9">
         <v>46161.58116828704</v>
@@ -10458,16 +10481,16 @@
         <v>46161.84644222222</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
@@ -10483,13 +10506,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10499,7 +10522,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B154" s="5">
         <v>46161.63912622685</v>
@@ -10509,16 +10532,16 @@
         <v>46161.84643929398</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I154" s="6"/>
       <c r="J154" s="5">
@@ -10534,10 +10557,10 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10550,7 +10573,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B155" s="9">
         <v>46161.63913737268</v>
@@ -10560,16 +10583,16 @@
         <v>46161.84643643518</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I155" s="10"/>
       <c r="J155" s="9">
@@ -10585,10 +10608,10 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>26</v>
@@ -10601,7 +10624,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B156" s="5">
         <v>46161.63914719908</v>
@@ -10611,16 +10634,16 @@
         <v>46161.846433321756</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I156" s="6"/>
       <c r="J156" s="5">
@@ -10636,10 +10659,10 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>26</v>
@@ -10652,7 +10675,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B157" s="9">
         <v>46161.639157557875</v>
@@ -10662,16 +10685,16 @@
         <v>46161.84643013889</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I157" s="10"/>
       <c r="J157" s="9">
@@ -10687,10 +10710,10 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>26</v>
@@ -10703,7 +10726,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B158" s="5">
         <v>46161.6391721875</v>
@@ -10713,16 +10736,16 @@
         <v>46161.84642646991</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I158" s="6"/>
       <c r="J158" s="5">
@@ -10738,10 +10761,10 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10754,7 +10777,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B159" s="9">
         <v>46161.639187395835</v>
@@ -10764,16 +10787,16 @@
         <v>46161.84642321759</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I159" s="10"/>
       <c r="J159" s="9">
@@ -10789,10 +10812,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>26</v>
@@ -10805,7 +10828,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B160" s="5">
         <v>46161.639195289354</v>
@@ -10815,16 +10838,16 @@
         <v>46161.846420138885</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I160" s="6"/>
       <c r="J160" s="5">
@@ -10840,10 +10863,10 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>26</v>
@@ -10856,7 +10879,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B161" s="9">
         <v>46161.63920550926</v>
@@ -10866,16 +10889,16 @@
         <v>46161.846413113424</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I161" s="10"/>
       <c r="J161" s="9">
@@ -10891,10 +10914,10 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>26</v>
@@ -10907,7 +10930,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B162" s="5">
         <v>46161.63921432871</v>
@@ -10917,16 +10940,16 @@
         <v>46161.84641241898</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I162" s="6"/>
       <c r="J162" s="5">
@@ -10942,13 +10965,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10958,7 +10981,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B163" s="9">
         <v>46161.58117752315</v>
@@ -10968,16 +10991,16 @@
         <v>46161.84660503472</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I163" s="9">
         <v>46309</v>
@@ -10995,13 +11018,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q163" s="9">
         <v>46309</v>
@@ -11016,12 +11039,12 @@
         <v>0</v>
       </c>
       <c r="U163" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B164" s="5">
         <v>46161.58118137732</v>
@@ -11031,16 +11054,16 @@
         <v>46161.84658016203</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I164" s="5">
         <v>46309</v>
@@ -11058,13 +11081,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11074,7 +11097,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B165" s="9">
         <v>46161.639253761576</v>
@@ -11084,16 +11107,16 @@
         <v>46161.846577187505</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I165" s="9">
         <v>46309</v>
@@ -11111,10 +11134,10 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P165" s="10" t="s">
         <v>26</v>
@@ -11127,7 +11150,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B166" s="5">
         <v>46161.63928710648</v>
@@ -11137,16 +11160,16 @@
         <v>46161.84657417824</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I166" s="5">
         <v>46309</v>
@@ -11164,10 +11187,10 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11180,7 +11203,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B167" s="9">
         <v>46161.63929736111</v>
@@ -11190,16 +11213,16 @@
         <v>46161.84657136574</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I167" s="9">
         <v>46309</v>
@@ -11217,10 +11240,10 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P167" s="10" t="s">
         <v>26</v>
@@ -11233,7 +11256,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B168" s="5">
         <v>46161.6393071412</v>
@@ -11243,16 +11266,16 @@
         <v>46161.84656841435</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I168" s="5">
         <v>46309</v>
@@ -11270,10 +11293,10 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>26</v>
@@ -11286,7 +11309,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B169" s="9">
         <v>46161.639315625</v>
@@ -11296,16 +11319,16 @@
         <v>46161.84656539352</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I169" s="9">
         <v>46309</v>
@@ -11323,10 +11346,10 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11339,7 +11362,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B170" s="5">
         <v>46161.63932686343</v>
@@ -11349,16 +11372,16 @@
         <v>46161.846562754625</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I170" s="5">
         <v>46309</v>
@@ -11376,10 +11399,10 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11392,7 +11415,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B171" s="9">
         <v>46161.63933708333</v>
@@ -11402,16 +11425,16 @@
         <v>46161.8465599537</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I171" s="9">
         <v>46309</v>
@@ -11429,10 +11452,10 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>26</v>
@@ -11445,7 +11468,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B172" s="5">
         <v>46161.63935484954</v>
@@ -11455,16 +11478,16 @@
         <v>46161.846553807874</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I172" s="5">
         <v>46309</v>
@@ -11482,10 +11505,10 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>26</v>
@@ -11498,7 +11521,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B173" s="9">
         <v>46161.63936453704</v>
@@ -11508,16 +11531,16 @@
         <v>46161.84655313657</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I173" s="9">
         <v>46309</v>
@@ -11535,13 +11558,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11551,7 +11574,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B174" s="5">
         <v>46161.5811852662</v>
@@ -11561,7 +11584,7 @@
         <v>46161.84092732639</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>25</v>
@@ -11585,7 +11608,7 @@
         <v>26</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>26</v>
@@ -11598,7 +11621,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B175" s="9">
         <v>46161.581188020835</v>
@@ -11608,16 +11631,16 @@
         <v>46161.84675815972</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I175" s="9">
         <v>46310</v>
@@ -11635,13 +11658,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q175" s="9">
         <v>46310</v>
@@ -11656,12 +11679,12 @@
         <v>0</v>
       </c>
       <c r="U175" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B176" s="5">
         <v>46161.581192673606</v>
@@ -11671,16 +11694,16 @@
         <v>46161.846749351855</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I176" s="5">
         <v>46310</v>
@@ -11698,13 +11721,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11714,7 +11737,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B177" s="9">
         <v>46161.63982708333</v>
@@ -11724,16 +11747,16 @@
         <v>46161.84674655093</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I177" s="9">
         <v>46310</v>
@@ -11751,13 +11774,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11767,7 +11790,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B178" s="5">
         <v>46161.63983532407</v>
@@ -11777,16 +11800,16 @@
         <v>46161.846743981485</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I178" s="5">
         <v>46310</v>
@@ -11804,13 +11827,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11820,7 +11843,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B179" s="9">
         <v>46161.63984421296</v>
@@ -11830,16 +11853,16 @@
         <v>46161.84674143518</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I179" s="9">
         <v>46310</v>
@@ -11857,13 +11880,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11873,7 +11896,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B180" s="5">
         <v>46161.63985878472</v>
@@ -11883,16 +11906,16 @@
         <v>46161.846738541666</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I180" s="5">
         <v>46310</v>
@@ -11910,13 +11933,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11926,7 +11949,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B181" s="9">
         <v>46161.63986780093</v>
@@ -11936,16 +11959,16 @@
         <v>46161.84673559028</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I181" s="9">
         <v>46310</v>
@@ -11963,13 +11986,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11979,7 +12002,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B182" s="5">
         <v>46161.639875</v>
@@ -11989,16 +12012,16 @@
         <v>46161.84673289352</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I182" s="5">
         <v>46310</v>
@@ -12016,13 +12039,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12032,7 +12055,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B183" s="9">
         <v>46161.63988342593</v>
@@ -12042,16 +12065,16 @@
         <v>46161.84672489583</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I183" s="9">
         <v>46310</v>
@@ -12069,13 +12092,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12085,7 +12108,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B184" s="5">
         <v>46161.63989143519</v>
@@ -12095,16 +12118,16 @@
         <v>46161.84672420139</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I184" s="5">
         <v>46310</v>
@@ -12122,13 +12145,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12138,7 +12161,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B185" s="9">
         <v>46161.639899340276</v>
@@ -12148,16 +12171,16 @@
         <v>46161.84672340278</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I185" s="9">
         <v>46310</v>
@@ -12175,13 +12198,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12191,7 +12214,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B186" s="5">
         <v>46161.5811965162</v>
@@ -12201,16 +12224,16 @@
         <v>46161.84690181713</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I186" s="5">
         <v>46311</v>
@@ -12228,13 +12251,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q186" s="5">
         <v>46311</v>
@@ -12249,12 +12272,12 @@
         <v>0</v>
       </c>
       <c r="U186" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B187" s="9">
         <v>46161.58120002315</v>
@@ -12264,16 +12287,16 @@
         <v>46161.84690336806</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H187" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I187" s="9">
         <v>46311</v>
@@ -12291,13 +12314,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12307,7 +12330,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B188" s="5">
         <v>46161.63993424768</v>
@@ -12317,16 +12340,16 @@
         <v>46161.84690038195</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I188" s="5">
         <v>46311</v>
@@ -12344,13 +12367,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12360,7 +12383,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B189" s="9">
         <v>46161.6399947801</v>
@@ -12370,16 +12393,16 @@
         <v>46161.84689746528</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H189" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I189" s="9">
         <v>46311</v>
@@ -12397,13 +12420,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12413,7 +12436,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B190" s="5">
         <v>46161.640004444445</v>
@@ -12423,16 +12446,16 @@
         <v>46161.84689446759</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I190" s="5">
         <v>46311</v>
@@ -12450,13 +12473,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12466,7 +12489,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B191" s="9">
         <v>46161.64001501157</v>
@@ -12476,16 +12499,16 @@
         <v>46161.84689137731</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H191" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I191" s="9">
         <v>46311</v>
@@ -12503,13 +12526,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12519,7 +12542,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B192" s="5">
         <v>46161.640023831016</v>
@@ -12529,16 +12552,16 @@
         <v>46161.846888796295</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I192" s="5">
         <v>46311</v>
@@ -12556,13 +12579,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12572,7 +12595,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B193" s="9">
         <v>46161.640038310186</v>
@@ -12582,16 +12605,16 @@
         <v>46161.84688606481</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H193" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I193" s="9">
         <v>46311</v>
@@ -12609,13 +12632,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12625,7 +12648,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B194" s="5">
         <v>46161.64004747685</v>
@@ -12635,16 +12658,16 @@
         <v>46161.846882557875</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I194" s="5">
         <v>46311</v>
@@ -12662,13 +12685,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12678,7 +12701,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B195" s="9">
         <v>46161.64005649305</v>
@@ -12688,16 +12711,16 @@
         <v>46161.84687957176</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H195" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I195" s="9">
         <v>46311</v>
@@ -12715,13 +12738,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12731,7 +12754,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B196" s="5">
         <v>46161.64006346065</v>
@@ -12741,16 +12764,16 @@
         <v>46161.846870243055</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I196" s="5">
         <v>46311</v>
@@ -12768,13 +12791,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12784,7 +12807,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B197" s="9">
         <v>46161.58120399306</v>
@@ -12794,16 +12817,16 @@
         <v>46161.84710645833</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H197" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I197" s="10"/>
       <c r="J197" s="9">
@@ -12819,13 +12842,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q197" s="9">
         <v>46316</v>
@@ -12840,12 +12863,12 @@
         <v>0</v>
       </c>
       <c r="U197" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B198" s="5">
         <v>46161.58120755787</v>
@@ -12855,16 +12878,16 @@
         <v>46161.847077812505</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -12880,13 +12903,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12896,7 +12919,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B199" s="9">
         <v>46161.6401252662</v>
@@ -12906,16 +12929,16 @@
         <v>46161.84707505787</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -12931,13 +12954,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12947,7 +12970,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B200" s="5">
         <v>46161.64014137731</v>
@@ -12957,16 +12980,16 @@
         <v>46161.847072476856</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -12982,13 +13005,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -12998,7 +13021,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B201" s="9">
         <v>46161.64015293981</v>
@@ -13008,16 +13031,16 @@
         <v>46161.84706930556</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -13033,13 +13056,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13049,7 +13072,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B202" s="5">
         <v>46161.64016740741</v>
@@ -13059,16 +13082,16 @@
         <v>46161.847066608796</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13084,13 +13107,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13100,7 +13123,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B203" s="9">
         <v>46161.640203877316</v>
@@ -13110,16 +13133,16 @@
         <v>46161.84706402778</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -13135,13 +13158,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13151,7 +13174,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B204" s="5">
         <v>46161.64021510417</v>
@@ -13161,16 +13184,16 @@
         <v>46161.84706112268</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13186,13 +13209,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13202,7 +13225,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B205" s="9">
         <v>46161.64022702546</v>
@@ -13212,16 +13235,16 @@
         <v>46161.847053425925</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13237,13 +13260,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13253,7 +13276,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B206" s="5">
         <v>46161.64023784723</v>
@@ -13263,16 +13286,16 @@
         <v>46161.8470527662</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13288,13 +13311,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13304,7 +13327,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B207" s="9">
         <v>46161.64025311342</v>
@@ -13314,16 +13337,16 @@
         <v>46161.84705210648</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13339,13 +13362,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13355,7 +13378,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B208" s="5">
         <v>46161.58121466435</v>
@@ -13365,16 +13388,16 @@
         <v>46161.84730193287</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I208" s="5">
         <v>46317</v>
@@ -13392,13 +13415,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q208" s="5">
         <v>46317</v>
@@ -13413,12 +13436,12 @@
         <v>0</v>
       </c>
       <c r="U208" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B209" s="9">
         <v>46161.58125732639</v>
@@ -13428,16 +13451,16 @@
         <v>46161.84728091436</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I209" s="10"/>
       <c r="J209" s="9">
@@ -13453,13 +13476,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13469,7 +13492,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B210" s="5">
         <v>46161.640307905094</v>
@@ -13479,16 +13502,16 @@
         <v>46161.84727769676</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13504,10 +13527,10 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>26</v>
@@ -13520,7 +13543,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B211" s="9">
         <v>46161.64031635417</v>
@@ -13530,16 +13553,16 @@
         <v>46161.84727525463</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I211" s="10"/>
       <c r="J211" s="9">
@@ -13555,10 +13578,10 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>26</v>
@@ -13571,7 +13594,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B212" s="5">
         <v>46161.64032832176</v>
@@ -13581,16 +13604,16 @@
         <v>46161.84727247685</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13606,10 +13629,10 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>26</v>
@@ -13622,7 +13645,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B213" s="9">
         <v>46161.640337986115</v>
@@ -13632,16 +13655,16 @@
         <v>46161.84726945602</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I213" s="10"/>
       <c r="J213" s="9">
@@ -13657,10 +13680,10 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>26</v>
@@ -13673,7 +13696,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B214" s="5">
         <v>46161.64035862268</v>
@@ -13683,16 +13706,16 @@
         <v>46161.84726638889</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13708,10 +13731,10 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13724,7 +13747,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B215" s="9">
         <v>46161.64036773148</v>
@@ -13734,16 +13757,16 @@
         <v>46161.84726359954</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I215" s="10"/>
       <c r="J215" s="9">
@@ -13759,10 +13782,10 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13775,7 +13798,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B216" s="5">
         <v>46161.64037657407</v>
@@ -13785,16 +13808,16 @@
         <v>46161.84726060185</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13810,10 +13833,10 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>26</v>
@@ -13826,7 +13849,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B217" s="9">
         <v>46161.64038473379</v>
@@ -13836,16 +13859,16 @@
         <v>46161.847254699074</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I217" s="10"/>
       <c r="J217" s="9">
@@ -13861,10 +13884,10 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>26</v>
@@ -13877,7 +13900,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B218" s="5">
         <v>46161.64039350694</v>
@@ -13887,16 +13910,16 @@
         <v>46161.8472540625</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -13912,10 +13935,10 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>26</v>
@@ -13928,7 +13951,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B219" s="9">
         <v>46161.581262824075</v>
@@ -13938,7 +13961,7 @@
         <v>46161.84801045139</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>25</v>
@@ -13962,7 +13985,7 @@
         <v>26</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>26</v>
@@ -13975,7 +13998,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B220" s="5">
         <v>46161.58126615741</v>
@@ -13985,16 +14008,16 @@
         <v>46161.84764756945</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I220" s="5">
         <v>46318</v>
@@ -14012,13 +14035,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q220" s="5">
         <v>46318</v>
@@ -14033,12 +14056,12 @@
         <v>0</v>
       </c>
       <c r="U220" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B221" s="9">
         <v>46161.581270821756</v>
@@ -14048,16 +14071,16 @@
         <v>46198.80656221065</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I221" s="9">
         <v>46318</v>
@@ -14075,13 +14098,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q221" s="9">
         <v>46318</v>
@@ -14096,7 +14119,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -4810,7 +4810,7 @@
         <v>46198.80749446759</v>
       </c>
       <c r="D49" s="9">
-        <v>46198.807511481486</v>
+        <v>46216.19023893519</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>82</v>
@@ -4854,8 +4854,8 @@
       <c r="R49" s="9">
         <v>46223</v>
       </c>
-      <c r="S49" s="7" t="s">
-        <v>33</v>
+      <c r="S49" s="11" t="s">
+        <v>182</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -5446,7 +5446,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.79647144676</v>
+        <v>46217.592142650465</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>205</v>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46211.830047766205</v>
+        <v>46217.59224327546</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>208</v>
@@ -5543,8 +5543,8 @@
       <c r="T62" s="6">
         <v>0</v>
       </c>
-      <c r="U62" s="11" t="s">
-        <v>49</v>
+      <c r="U62" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.84491849537</v>
+        <v>46217.59214284722</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>213</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -340,6 +340,9 @@
     <t>Generación OC materiales corte Laser ot 4332,Propuesta compras:</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214952151057796</t>
   </si>
   <si>
@@ -632,9 +635,6 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214937218721335</t>
@@ -2937,7 +2937,7 @@
         <v>46204.90066085648</v>
       </c>
       <c r="D18" s="5">
-        <v>46206.560436921296</v>
+        <v>46218.2038322338</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2981,8 +2981,8 @@
       <c r="R18" s="5">
         <v>46225</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>33</v>
+      <c r="S18" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2993,7 +2993,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B19" s="9">
         <v>46161.58080373843</v>
@@ -3002,10 +3002,10 @@
         <v>46204.90101555556</v>
       </c>
       <c r="D19" s="9">
-        <v>46206.560617662035</v>
+        <v>46218.2038325</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -3038,7 +3038,7 @@
         <v>82</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q19" s="9">
         <v>46224</v>
@@ -3046,8 +3046,8 @@
       <c r="R19" s="9">
         <v>46225</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>33</v>
+      <c r="S19" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" s="5">
         <v>46161.58080740741</v>
@@ -3067,10 +3067,10 @@
         <v>46204.90180252315</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.56075704861</v>
+        <v>46218.20383224537</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3103,7 +3103,7 @@
         <v>82</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -3111,8 +3111,8 @@
       <c r="R20" s="5">
         <v>46225</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>33</v>
+      <c r="S20" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B21" s="9">
         <v>46161.580810740736</v>
@@ -3132,10 +3132,10 @@
         <v>46204.90175329861</v>
       </c>
       <c r="D21" s="9">
-        <v>46206.560877592594</v>
+        <v>46218.20383224537</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -3168,7 +3168,7 @@
         <v>82</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="9">
         <v>46224</v>
@@ -3176,8 +3176,8 @@
       <c r="R21" s="9">
         <v>46225</v>
       </c>
-      <c r="S21" s="7" t="s">
-        <v>33</v>
+      <c r="S21" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B22" s="5">
         <v>46161.58064796297</v>
@@ -3198,7 +3198,7 @@
         <v>46211.83005701389</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -3222,7 +3222,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" s="9">
         <v>46161.58081472223</v>
@@ -3247,16 +3247,16 @@
         <v>46209.56551446759</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I23" s="9">
         <v>46168</v>
@@ -3274,13 +3274,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q23" s="9">
         <v>46168</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46161.580819016206</v>
@@ -3312,16 +3312,16 @@
         <v>46209.56543981482</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I24" s="5">
         <v>46168</v>
@@ -3339,13 +3339,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3356,12 +3356,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" s="9">
         <v>46161.58082350694</v>
@@ -3373,16 +3373,16 @@
         <v>46209.565488576394</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I25" s="9">
         <v>46170</v>
@@ -3400,13 +3400,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3417,12 +3417,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
         <v>46161.58082824074</v>
@@ -3434,16 +3434,16 @@
         <v>46209.56600694444</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I26" s="5">
         <v>46168</v>
@@ -3461,13 +3461,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q26" s="5">
         <v>46168</v>
@@ -3487,7 +3487,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B27" s="9">
         <v>46161.5808325463</v>
@@ -3499,16 +3499,16 @@
         <v>46209.56565858796</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I27" s="9">
         <v>46168</v>
@@ -3526,13 +3526,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3543,12 +3543,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5">
         <v>46161.580836967594</v>
@@ -3560,16 +3560,16 @@
         <v>46209.56570685185</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I28" s="5">
         <v>46170</v>
@@ -3587,13 +3587,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3604,12 +3604,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B29" s="9">
         <v>46161.58084165509</v>
@@ -3619,16 +3619,16 @@
         <v>46198.805784641205</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I29" s="9">
         <v>46156</v>
@@ -3646,13 +3646,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q29" s="9">
         <v>46156</v>
@@ -3667,12 +3667,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
         <v>46161.58084603009</v>
@@ -3684,16 +3684,16 @@
         <v>46198.80572795139</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I30" s="5">
         <v>46156</v>
@@ -3711,13 +3711,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3728,12 +3728,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="9">
         <v>46161.580850439816</v>
@@ -3743,16 +3743,16 @@
         <v>46198.80573190972</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3770,13 +3770,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3787,12 +3787,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B32" s="5">
         <v>46161.58085503472</v>
@@ -3804,16 +3804,16 @@
         <v>46198.80577622685</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I32" s="5">
         <v>46176</v>
@@ -3831,13 +3831,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3848,12 +3848,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46161.58085940972</v>
@@ -3865,16 +3865,16 @@
         <v>46211.830060266206</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I33" s="9">
         <v>46226</v>
@@ -3892,13 +3892,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q33" s="9">
         <v>46226</v>
@@ -3918,7 +3918,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46161.58086364584</v>
@@ -3930,16 +3930,16 @@
         <v>46205.61008960648</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I34" s="5">
         <v>46226</v>
@@ -3957,13 +3957,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3974,12 +3974,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B35" s="9">
         <v>46161.58086832176</v>
@@ -3991,16 +3991,16 @@
         <v>46211.83003016203</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I35" s="9">
         <v>46230</v>
@@ -4018,13 +4018,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -4035,12 +4035,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46161.58087322916</v>
@@ -4052,16 +4052,16 @@
         <v>46209.804952569444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -4079,10 +4079,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B37" s="9">
         <v>46161.580931018514</v>
@@ -4117,16 +4117,16 @@
         <v>46205.610248032404</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I37" s="9">
         <v>46226</v>
@@ -4144,13 +4144,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4160,7 +4160,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46161.58093646991</v>
@@ -4172,16 +4172,16 @@
         <v>46209.809419513884</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -4199,13 +4199,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4215,7 +4215,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46161.580941099535</v>
@@ -4227,16 +4227,16 @@
         <v>46209.62288859954</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I39" s="9">
         <v>46225</v>
@@ -4254,10 +4254,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46161.58094532407</v>
@@ -4292,16 +4292,16 @@
         <v>46209.622784444444</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I40" s="5">
         <v>46225</v>
@@ -4319,13 +4319,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46161.58094997685</v>
@@ -4347,16 +4347,16 @@
         <v>46209.62283091435</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I41" s="9">
         <v>46234</v>
@@ -4374,13 +4374,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4390,7 +4390,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46161.58095447917</v>
@@ -4400,16 +4400,16 @@
         <v>46209.62284077547</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I42" s="5">
         <v>46265</v>
@@ -4427,10 +4427,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4443,7 +4443,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B43" s="9">
         <v>46161.58095743056</v>
@@ -4455,16 +4455,16 @@
         <v>46209.81259914352</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I43" s="9">
         <v>46226</v>
@@ -4482,10 +4482,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4508,7 +4508,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
         <v>46161.58096091435</v>
@@ -4520,16 +4520,16 @@
         <v>46209.81220270833</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I44" s="5">
         <v>46226</v>
@@ -4547,13 +4547,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4563,7 +4563,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46161.580964988425</v>
@@ -4575,16 +4575,16 @@
         <v>46209.81257327546</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I45" s="9">
         <v>46230</v>
@@ -4602,13 +4602,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4618,7 +4618,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46161.58065239583</v>
@@ -4630,7 +4630,7 @@
         <v>46210.52870142361</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4654,7 +4654,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4671,7 +4671,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46161.580969780094</v>
@@ -4683,16 +4683,16 @@
         <v>46197.70504644676</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I47" s="9">
         <v>46164</v>
@@ -4710,13 +4710,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>62</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="9">
         <v>46164</v>
@@ -4736,7 +4736,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46161.580975069446</v>
@@ -4748,16 +4748,16 @@
         <v>46213.18419743056</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46216</v>
@@ -4775,13 +4775,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="5">
         <v>46216</v>
@@ -4790,7 +4790,7 @@
         <v>46220</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>182</v>
+        <v>84</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4840,10 +4840,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>186</v>
@@ -4855,7 +4855,7 @@
         <v>46223</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>182</v>
+        <v>84</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4903,7 +4903,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>191</v>
@@ -4924,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5526,7 +5526,7 @@
         <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>211</v>
@@ -5565,10 +5565,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I63" s="9">
         <v>46241</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5652,7 +5652,7 @@
         <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>218</v>
@@ -5691,10 +5691,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I65" s="9">
         <v>46241</v>
@@ -5733,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5778,7 +5778,7 @@
         <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>224</v>
@@ -5817,10 +5817,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I67" s="9">
         <v>46241</v>
@@ -5859,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5969,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -6562,7 +6562,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -7113,10 +7113,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -7155,7 +7155,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7176,10 +7176,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -7229,10 +7229,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I93" s="9">
         <v>46274</v>
@@ -7282,10 +7282,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I94" s="5">
         <v>46274</v>
@@ -7335,10 +7335,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I95" s="9">
         <v>46274</v>
@@ -7388,10 +7388,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I96" s="5">
         <v>46274</v>
@@ -7441,10 +7441,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I97" s="9">
         <v>46274</v>
@@ -7494,10 +7494,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I98" s="5">
         <v>46274</v>
@@ -7547,10 +7547,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I99" s="9">
         <v>46274</v>
@@ -7600,10 +7600,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I100" s="5">
         <v>46274</v>
@@ -7653,10 +7653,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I101" s="9">
         <v>46274</v>
@@ -7777,7 +7777,7 @@
         <v>205</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>282</v>
@@ -7840,7 +7840,7 @@
         <v>205</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>285</v>
@@ -7903,7 +7903,7 @@
         <v>205</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>288</v>
@@ -7921,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -7966,7 +7966,7 @@
         <v>205</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>291</v>
@@ -8094,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="U108" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="U119" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -9280,7 +9280,7 @@
         <v>0</v>
       </c>
       <c r="U130" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -9873,7 +9873,7 @@
         <v>0</v>
       </c>
       <c r="U141" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
@@ -10466,7 +10466,7 @@
         <v>0</v>
       </c>
       <c r="U152" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
@@ -11039,7 +11039,7 @@
         <v>0</v>
       </c>
       <c r="U163" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
@@ -11679,7 +11679,7 @@
         <v>0</v>
       </c>
       <c r="U175" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
@@ -12272,7 +12272,7 @@
         <v>0</v>
       </c>
       <c r="U186" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
@@ -12863,7 +12863,7 @@
         <v>0</v>
       </c>
       <c r="U197" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
@@ -13436,7 +13436,7 @@
         <v>0</v>
       </c>
       <c r="U208" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="U220" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
@@ -14119,7 +14119,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="450">
   <si>
     <t>50001555 - "ZITRON COLOMBIA ARIS MINING SEGOVIA"</t>
   </si>
@@ -316,9 +316,6 @@
     <t>propuesta nucleo rodete ot 4332</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Generación OC Rodete ot 4332,Propuesta compras:</t>
   </si>
   <si>
@@ -326,12 +323,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser ot 4332</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2881,11 +2872,9 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="10"/>
       <c r="I17" s="9">
         <v>46164</v>
       </c>
@@ -2908,7 +2897,7 @@
         <v>57</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="9">
         <v>46164</v>
@@ -2928,7 +2917,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5">
         <v>46161.58079903935</v>
@@ -2940,17 +2929,15 @@
         <v>46218.2038322338</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>81</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46224</v>
       </c>
@@ -2970,10 +2957,10 @@
         <v>66</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2982,7 +2969,7 @@
         <v>46225</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2993,7 +2980,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46161.58080373843</v>
@@ -3005,17 +2992,15 @@
         <v>46218.2038325</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>81</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="10"/>
       <c r="I19" s="9">
         <v>46224</v>
       </c>
@@ -3035,10 +3020,10 @@
         <v>66</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46224</v>
@@ -3047,7 +3032,7 @@
         <v>46225</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -3058,7 +3043,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46161.58080740741</v>
@@ -3070,17 +3055,15 @@
         <v>46218.20383224537</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>81</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="5">
         <v>46224</v>
       </c>
@@ -3100,10 +3083,10 @@
         <v>66</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -3112,7 +3095,7 @@
         <v>46225</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -3123,7 +3106,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
         <v>46161.580810740736</v>
@@ -3135,17 +3118,15 @@
         <v>46218.20383224537</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>81</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="10"/>
       <c r="I21" s="9">
         <v>46224</v>
       </c>
@@ -3165,10 +3146,10 @@
         <v>66</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="9">
         <v>46224</v>
@@ -3177,7 +3158,7 @@
         <v>46225</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -3188,7 +3169,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46161.58064796297</v>
@@ -3198,7 +3179,7 @@
         <v>46211.83005701389</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -3222,7 +3203,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -3235,7 +3216,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46161.58081472223</v>
@@ -3247,16 +3228,16 @@
         <v>46209.56551446759</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I23" s="9">
         <v>46168</v>
@@ -3274,13 +3255,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="9">
         <v>46168</v>
@@ -3300,7 +3281,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46161.580819016206</v>
@@ -3312,16 +3293,16 @@
         <v>46209.56543981482</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I24" s="5">
         <v>46168</v>
@@ -3339,13 +3320,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3356,12 +3337,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9">
         <v>46161.58082350694</v>
@@ -3373,16 +3354,16 @@
         <v>46209.565488576394</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I25" s="9">
         <v>46170</v>
@@ -3400,13 +3381,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3417,12 +3398,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46161.58082824074</v>
@@ -3434,16 +3415,16 @@
         <v>46209.56600694444</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I26" s="5">
         <v>46168</v>
@@ -3461,13 +3442,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Q26" s="5">
         <v>46168</v>
@@ -3487,7 +3468,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46161.5808325463</v>
@@ -3499,16 +3480,16 @@
         <v>46209.56565858796</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I27" s="9">
         <v>46168</v>
@@ -3526,13 +3507,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3543,12 +3524,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46161.580836967594</v>
@@ -3560,16 +3541,16 @@
         <v>46209.56570685185</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I28" s="5">
         <v>46170</v>
@@ -3587,13 +3568,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O28" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="O28" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="P28" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3604,12 +3585,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46161.58084165509</v>
@@ -3619,16 +3600,16 @@
         <v>46198.805784641205</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I29" s="9">
         <v>46156</v>
@@ -3646,13 +3627,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Q29" s="9">
         <v>46156</v>
@@ -3667,12 +3648,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46161.58084603009</v>
@@ -3684,16 +3665,16 @@
         <v>46198.80572795139</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I30" s="5">
         <v>46156</v>
@@ -3711,13 +3692,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3728,12 +3709,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46161.580850439816</v>
@@ -3743,16 +3724,16 @@
         <v>46198.80573190972</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3770,13 +3751,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="O31" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="O31" s="10" t="s">
-        <v>122</v>
-      </c>
       <c r="P31" s="10" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3787,12 +3768,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46161.58085503472</v>
@@ -3804,16 +3785,16 @@
         <v>46198.80577622685</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I32" s="5">
         <v>46176</v>
@@ -3831,13 +3812,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="O32" s="6" t="s">
-        <v>122</v>
-      </c>
       <c r="P32" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3848,12 +3829,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B33" s="9">
         <v>46161.58085940972</v>
@@ -3865,16 +3846,16 @@
         <v>46211.830060266206</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I33" s="9">
         <v>46226</v>
@@ -3892,13 +3873,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Q33" s="9">
         <v>46226</v>
@@ -3918,7 +3899,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46161.58086364584</v>
@@ -3930,16 +3911,16 @@
         <v>46205.61008960648</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46226</v>
@@ -3957,13 +3938,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3974,12 +3955,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46161.58086832176</v>
@@ -3991,16 +3972,16 @@
         <v>46211.83003016203</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46230</v>
@@ -4018,13 +3999,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -4035,12 +4016,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46161.58087322916</v>
@@ -4052,16 +4033,16 @@
         <v>46209.804952569444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -4079,10 +4060,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -4105,7 +4086,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46161.580931018514</v>
@@ -4117,16 +4098,16 @@
         <v>46205.610248032404</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46226</v>
@@ -4144,13 +4125,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="O37" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="P37" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>145</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4160,7 +4141,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46161.58093646991</v>
@@ -4172,16 +4153,16 @@
         <v>46209.809419513884</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -4199,13 +4180,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4215,7 +4196,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46161.580941099535</v>
@@ -4227,16 +4208,16 @@
         <v>46209.62288859954</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46225</v>
@@ -4254,10 +4235,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4280,7 +4261,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46161.58094532407</v>
@@ -4292,16 +4273,16 @@
         <v>46209.622784444444</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46225</v>
@@ -4319,13 +4300,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4335,7 +4316,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46161.58094997685</v>
@@ -4347,16 +4328,16 @@
         <v>46209.62283091435</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I41" s="9">
         <v>46234</v>
@@ -4374,13 +4355,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4390,7 +4371,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46161.58095447917</v>
@@ -4400,16 +4381,16 @@
         <v>46209.62284077547</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46265</v>
@@ -4427,10 +4408,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4443,7 +4424,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46161.58095743056</v>
@@ -4455,16 +4436,16 @@
         <v>46209.81259914352</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I43" s="9">
         <v>46226</v>
@@ -4482,10 +4463,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4508,7 +4489,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46161.58096091435</v>
@@ -4520,16 +4501,16 @@
         <v>46209.81220270833</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46226</v>
@@ -4547,13 +4528,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4563,7 +4544,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46161.580964988425</v>
@@ -4575,16 +4556,16 @@
         <v>46209.81257327546</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I45" s="9">
         <v>46230</v>
@@ -4602,13 +4583,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4618,7 +4599,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46161.58065239583</v>
@@ -4630,7 +4611,7 @@
         <v>46210.52870142361</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4654,7 +4635,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4671,7 +4652,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46161.580969780094</v>
@@ -4683,16 +4664,16 @@
         <v>46197.70504644676</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46164</v>
@@ -4710,13 +4691,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>62</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46164</v>
@@ -4736,7 +4717,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46161.580975069446</v>
@@ -4748,16 +4729,16 @@
         <v>46213.18419743056</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46216</v>
@@ -4775,13 +4756,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46216</v>
@@ -4790,7 +4771,7 @@
         <v>46220</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4801,7 +4782,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46161.58098100695</v>
@@ -4813,16 +4794,16 @@
         <v>46216.19023893519</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I49" s="9">
         <v>46223</v>
@@ -4840,13 +4821,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46223</v>
@@ -4855,7 +4836,7 @@
         <v>46223</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4866,7 +4847,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46161.58099116899</v>
@@ -4876,16 +4857,16 @@
         <v>46161.84476310185</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46308</v>
@@ -4903,10 +4884,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4924,12 +4905,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46161.58099418982</v>
@@ -4939,16 +4920,16 @@
         <v>46161.84476607639</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4964,13 +4945,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4980,7 +4961,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46161.63966489583</v>
@@ -4990,16 +4971,16 @@
         <v>46161.844763472225</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -5015,13 +4996,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5031,7 +5012,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46161.63967261574</v>
@@ -5041,16 +5022,16 @@
         <v>46161.84476069444</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5066,13 +5047,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5082,7 +5063,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46161.63968388889</v>
@@ -5092,16 +5073,16 @@
         <v>46161.84475773148</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5117,13 +5098,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5133,7 +5114,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B55" s="9">
         <v>46161.63969275463</v>
@@ -5143,16 +5124,16 @@
         <v>46161.84475471065</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5168,13 +5149,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5184,7 +5165,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46161.639705208334</v>
@@ -5194,16 +5175,16 @@
         <v>46161.84475174769</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5219,13 +5200,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5235,7 +5216,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B57" s="9">
         <v>46161.639715474535</v>
@@ -5245,16 +5226,16 @@
         <v>46161.84474863426</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5270,13 +5251,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5286,7 +5267,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B58" s="5">
         <v>46161.63972679398</v>
@@ -5296,16 +5277,16 @@
         <v>46161.84474503472</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5321,13 +5302,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5337,7 +5318,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46161.63974304398</v>
@@ -5347,16 +5328,16 @@
         <v>46161.84473834491</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5372,13 +5353,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5388,7 +5369,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B60" s="5">
         <v>46161.63975269676</v>
@@ -5398,16 +5379,16 @@
         <v>46161.84473753472</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5423,13 +5404,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5439,7 +5420,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B61" s="9">
         <v>46161.58099818287</v>
@@ -5449,7 +5430,7 @@
         <v>46217.592142650465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5473,7 +5454,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5486,7 +5467,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46161.58100145833</v>
@@ -5496,16 +5477,16 @@
         <v>46217.59224327546</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I62" s="5">
         <v>46239</v>
@@ -5523,13 +5504,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q62" s="5">
         <v>46239</v>
@@ -5549,7 +5530,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B63" s="9">
         <v>46161.58100614583</v>
@@ -5559,16 +5540,16 @@
         <v>46217.59214284722</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I63" s="9">
         <v>46241</v>
@@ -5586,13 +5567,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q63" s="9">
         <v>46241</v>
@@ -5607,12 +5588,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B64" s="5">
         <v>46161.58101638889</v>
@@ -5622,16 +5603,16 @@
         <v>46209.804944710646</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I64" s="5">
         <v>46239</v>
@@ -5649,13 +5630,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q64" s="5">
         <v>46239</v>
@@ -5675,7 +5656,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B65" s="9">
         <v>46161.58102099537</v>
@@ -5685,16 +5666,16 @@
         <v>46161.84491503472</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46241</v>
@@ -5712,13 +5693,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q65" s="9">
         <v>46241</v>
@@ -5733,12 +5714,12 @@
         <v>0</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B66" s="5">
         <v>46161.581024722225</v>
@@ -5748,16 +5729,16 @@
         <v>46209.81259190972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I66" s="5">
         <v>46239</v>
@@ -5775,13 +5756,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Q66" s="5">
         <v>46239</v>
@@ -5801,7 +5782,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B67" s="9">
         <v>46161.58102864583</v>
@@ -5811,16 +5792,16 @@
         <v>46161.844914270834</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I67" s="9">
         <v>46241</v>
@@ -5838,13 +5819,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O67" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="P67" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="Q67" s="9">
         <v>46241</v>
@@ -5859,12 +5840,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B68" s="5">
         <v>46161.58103207176</v>
@@ -5874,7 +5855,7 @@
         <v>46161.797785821764</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5898,7 +5879,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5911,7 +5892,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B69" s="9">
         <v>46161.58103457176</v>
@@ -5921,16 +5902,16 @@
         <v>46161.845178449075</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I69" s="9">
         <v>46245</v>
@@ -5948,13 +5929,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q69" s="9">
         <v>46245</v>
@@ -5969,12 +5950,12 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B70" s="5">
         <v>46161.58103962963</v>
@@ -5984,16 +5965,16 @@
         <v>46161.845147071755</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I70" s="5">
         <v>46245</v>
@@ -6011,13 +5992,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6027,7 +6008,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B71" s="9">
         <v>46161.582011805556</v>
@@ -6037,16 +6018,16 @@
         <v>46161.84514348379</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I71" s="9">
         <v>46245</v>
@@ -6064,13 +6045,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6080,7 +6061,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B72" s="5">
         <v>46161.58202383102</v>
@@ -6090,16 +6071,16 @@
         <v>46161.845140324076</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I72" s="5">
         <v>46245</v>
@@ -6117,13 +6098,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6133,7 +6114,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B73" s="9">
         <v>46161.582662650464</v>
@@ -6143,16 +6124,16 @@
         <v>46161.845136655094</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I73" s="9">
         <v>46245</v>
@@ -6170,13 +6151,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6186,7 +6167,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B74" s="5">
         <v>46161.58267322917</v>
@@ -6196,16 +6177,16 @@
         <v>46161.845133518524</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I74" s="5">
         <v>46245</v>
@@ -6223,13 +6204,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6239,7 +6220,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B75" s="9">
         <v>46161.58270134259</v>
@@ -6249,16 +6230,16 @@
         <v>46161.84513074074</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I75" s="9">
         <v>46245</v>
@@ -6276,13 +6257,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6292,7 +6273,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B76" s="5">
         <v>46161.58271427083</v>
@@ -6302,16 +6283,16 @@
         <v>46161.84512803241</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I76" s="5">
         <v>46245</v>
@@ -6329,13 +6310,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6345,7 +6326,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B77" s="9">
         <v>46161.58272651621</v>
@@ -6355,16 +6336,16 @@
         <v>46161.84512407407</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I77" s="9">
         <v>46245</v>
@@ -6382,13 +6363,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6398,7 +6379,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B78" s="5">
         <v>46161.58277962963</v>
@@ -6408,16 +6389,16 @@
         <v>46161.845117916666</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I78" s="5">
         <v>46245</v>
@@ -6435,13 +6416,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6451,7 +6432,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B79" s="9">
         <v>46161.58279046296</v>
@@ -6461,16 +6442,16 @@
         <v>46161.84511721064</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I79" s="9">
         <v>46245</v>
@@ -6488,13 +6469,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6504,7 +6485,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B80" s="5">
         <v>46161.58104538194</v>
@@ -6514,16 +6495,16 @@
         <v>46161.845344814814</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I80" s="5">
         <v>46254</v>
@@ -6541,13 +6522,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q80" s="5">
         <v>46254</v>
@@ -6562,12 +6543,12 @@
         <v>0</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B81" s="9">
         <v>46161.58104903935</v>
@@ -6577,16 +6558,16 @@
         <v>46198.80752025463</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I81" s="9">
         <v>46254</v>
@@ -6604,13 +6585,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="O81" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="P81" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="O81" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="P81" s="10" t="s">
-        <v>255</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6620,7 +6601,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B82" s="5">
         <v>46161.582834120374</v>
@@ -6630,16 +6611,16 @@
         <v>46161.84533628472</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I82" s="5">
         <v>46254</v>
@@ -6657,13 +6638,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6673,7 +6654,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B83" s="9">
         <v>46161.58286459491</v>
@@ -6683,16 +6664,16 @@
         <v>46161.84533336805</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I83" s="9">
         <v>46254</v>
@@ -6710,13 +6691,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6726,7 +6707,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B84" s="5">
         <v>46161.58287381944</v>
@@ -6736,16 +6717,16 @@
         <v>46161.84533065972</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I84" s="5">
         <v>46254</v>
@@ -6763,13 +6744,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6779,7 +6760,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B85" s="9">
         <v>46161.58288365741</v>
@@ -6789,16 +6770,16 @@
         <v>46161.84532790509</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I85" s="9">
         <v>46254</v>
@@ -6816,13 +6797,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6832,7 +6813,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B86" s="5">
         <v>46161.58289255787</v>
@@ -6842,16 +6823,16 @@
         <v>46161.84532486111</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I86" s="5">
         <v>46254</v>
@@ -6869,13 +6850,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6885,7 +6866,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B87" s="9">
         <v>46161.58292542824</v>
@@ -6895,16 +6876,16 @@
         <v>46161.84532211805</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I87" s="9">
         <v>46254</v>
@@ -6922,13 +6903,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6938,7 +6919,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B88" s="5">
         <v>46161.58293696759</v>
@@ -6948,16 +6929,16 @@
         <v>46161.84531927083</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I88" s="5">
         <v>46254</v>
@@ -6975,13 +6956,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6991,7 +6972,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B89" s="9">
         <v>46161.58295282407</v>
@@ -7001,16 +6982,16 @@
         <v>46161.84531311343</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I89" s="9">
         <v>46254</v>
@@ -7028,13 +7009,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7044,7 +7025,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B90" s="5">
         <v>46161.58296773148</v>
@@ -7054,16 +7035,16 @@
         <v>46161.84531243055</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I90" s="5">
         <v>46254</v>
@@ -7081,13 +7062,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7097,7 +7078,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B91" s="9">
         <v>46161.581053761576</v>
@@ -7107,16 +7088,16 @@
         <v>46161.84552644676</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -7134,13 +7115,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q91" s="9">
         <v>46274</v>
@@ -7155,12 +7136,12 @@
         <v>0</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B92" s="5">
         <v>46161.58105741898</v>
@@ -7170,16 +7151,16 @@
         <v>46198.80752082176</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -7197,13 +7178,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7213,7 +7194,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B93" s="9">
         <v>46161.583039942125</v>
@@ -7223,16 +7204,16 @@
         <v>46161.84550880787</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I93" s="9">
         <v>46274</v>
@@ -7250,13 +7231,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7266,7 +7247,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B94" s="5">
         <v>46161.58305715278</v>
@@ -7276,16 +7257,16 @@
         <v>46161.845505324076</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I94" s="5">
         <v>46274</v>
@@ -7303,13 +7284,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7319,7 +7300,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B95" s="9">
         <v>46161.583076689814</v>
@@ -7329,16 +7310,16 @@
         <v>46161.84550258102</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I95" s="9">
         <v>46274</v>
@@ -7356,13 +7337,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7372,7 +7353,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B96" s="5">
         <v>46161.58308886574</v>
@@ -7382,16 +7363,16 @@
         <v>46161.84549928241</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I96" s="5">
         <v>46274</v>
@@ -7409,13 +7390,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7425,7 +7406,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B97" s="9">
         <v>46161.58310019676</v>
@@ -7435,16 +7416,16 @@
         <v>46161.84549533565</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I97" s="9">
         <v>46274</v>
@@ -7462,13 +7443,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7478,7 +7459,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B98" s="5">
         <v>46161.5831108912</v>
@@ -7488,16 +7469,16 @@
         <v>46161.84549206018</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I98" s="5">
         <v>46274</v>
@@ -7515,13 +7496,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7531,7 +7512,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B99" s="9">
         <v>46161.58312844907</v>
@@ -7541,16 +7522,16 @@
         <v>46161.84548887731</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I99" s="9">
         <v>46274</v>
@@ -7568,13 +7549,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7584,7 +7565,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B100" s="5">
         <v>46161.58300775463</v>
@@ -7594,16 +7575,16 @@
         <v>46161.84548230324</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I100" s="5">
         <v>46274</v>
@@ -7621,13 +7602,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7637,7 +7618,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B101" s="9">
         <v>46161.639501875004</v>
@@ -7647,16 +7628,16 @@
         <v>46161.845481620374</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I101" s="9">
         <v>46274</v>
@@ -7674,13 +7655,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7690,7 +7671,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B102" s="5">
         <v>46161.58110506945</v>
@@ -7700,7 +7681,7 @@
         <v>46161.80776861111</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7724,7 +7705,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7737,7 +7718,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B103" s="9">
         <v>46161.581108530096</v>
@@ -7747,16 +7728,16 @@
         <v>46209.56572255787</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I103" s="9">
         <v>46174</v>
@@ -7774,13 +7755,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q103" s="9">
         <v>46174</v>
@@ -7800,7 +7781,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B104" s="5">
         <v>46161.58111370371</v>
@@ -7810,16 +7791,16 @@
         <v>46209.56550644676</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I104" s="5">
         <v>46282</v>
@@ -7837,13 +7818,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Q104" s="5">
         <v>46282</v>
@@ -7863,7 +7844,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B105" s="9">
         <v>46161.581118449074</v>
@@ -7873,16 +7854,16 @@
         <v>46161.84560644676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I105" s="9">
         <v>46301</v>
@@ -7900,13 +7881,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Q105" s="9">
         <v>46301</v>
@@ -7921,12 +7902,12 @@
         <v>0</v>
       </c>
       <c r="U105" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B106" s="5">
         <v>46161.58112311343</v>
@@ -7936,16 +7917,16 @@
         <v>46209.62284840278</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I106" s="5">
         <v>46237</v>
@@ -7963,13 +7944,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="Q106" s="5">
         <v>46237</v>
@@ -7989,7 +7970,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B107" s="9">
         <v>46161.58112702546</v>
@@ -7999,7 +7980,7 @@
         <v>46161.83387362269</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -8023,7 +8004,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -8036,7 +8017,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B108" s="5">
         <v>46161.58112984954</v>
@@ -8046,17 +8027,15 @@
         <v>46161.84578230324</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H108" s="6"/>
       <c r="I108" s="5">
         <v>46276</v>
       </c>
@@ -8073,13 +8052,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q108" s="5">
         <v>46276</v>
@@ -8094,12 +8073,12 @@
         <v>0</v>
       </c>
       <c r="U108" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B109" s="9">
         <v>46161.581135555556</v>
@@ -8109,17 +8088,15 @@
         <v>46161.84577694444</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H109" s="10"/>
       <c r="I109" s="9">
         <v>46276</v>
       </c>
@@ -8136,13 +8113,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8152,7 +8129,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B110" s="5">
         <v>46161.58317730324</v>
@@ -8162,17 +8139,15 @@
         <v>46161.84577366898</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H110" s="6"/>
       <c r="I110" s="5">
         <v>46276</v>
       </c>
@@ -8189,13 +8164,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8205,7 +8180,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B111" s="9">
         <v>46161.58318758102</v>
@@ -8215,17 +8190,15 @@
         <v>46161.845770879634</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H111" s="10"/>
       <c r="I111" s="9">
         <v>46276</v>
       </c>
@@ -8242,13 +8215,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8258,7 +8231,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B112" s="5">
         <v>46161.5831975926</v>
@@ -8268,17 +8241,15 @@
         <v>46161.84576709491</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H112" s="6"/>
       <c r="I112" s="5">
         <v>46276</v>
       </c>
@@ -8295,13 +8266,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8311,7 +8282,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B113" s="9">
         <v>46161.58320657407</v>
@@ -8321,17 +8292,15 @@
         <v>46161.84576415509</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H113" s="10"/>
       <c r="I113" s="9">
         <v>46276</v>
       </c>
@@ -8348,13 +8317,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8364,7 +8333,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B114" s="5">
         <v>46161.58322151621</v>
@@ -8374,17 +8343,15 @@
         <v>46161.84576082176</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H114" s="6"/>
       <c r="I114" s="5">
         <v>46276</v>
       </c>
@@ -8401,13 +8368,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8417,7 +8384,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B115" s="9">
         <v>46161.58322717593</v>
@@ -8427,17 +8394,15 @@
         <v>46161.84575040509</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H115" s="10"/>
       <c r="I115" s="9">
         <v>46276</v>
       </c>
@@ -8454,13 +8419,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8470,7 +8435,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B116" s="5">
         <v>46161.58324248843</v>
@@ -8480,17 +8445,15 @@
         <v>46161.84574967592</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H116" s="6"/>
       <c r="I116" s="5">
         <v>46276</v>
       </c>
@@ -8507,13 +8470,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8523,7 +8486,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B117" s="9">
         <v>46161.58325402778</v>
@@ -8533,17 +8496,15 @@
         <v>46161.845748946755</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H117" s="10"/>
       <c r="I117" s="9">
         <v>46276</v>
       </c>
@@ -8560,13 +8521,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8576,7 +8537,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B118" s="5">
         <v>46161.58326291667</v>
@@ -8586,17 +8547,15 @@
         <v>46161.84574821759</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H118" s="6"/>
       <c r="I118" s="5">
         <v>46276</v>
       </c>
@@ -8613,13 +8572,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8629,7 +8588,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B119" s="9">
         <v>46161.58113928241</v>
@@ -8639,17 +8598,15 @@
         <v>46161.845971400464</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H119" s="10"/>
       <c r="I119" s="9">
         <v>46296</v>
       </c>
@@ -8666,13 +8623,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q119" s="9">
         <v>46296</v>
@@ -8687,12 +8644,12 @@
         <v>0</v>
       </c>
       <c r="U119" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B120" s="5">
         <v>46161.58114282407</v>
@@ -8702,17 +8659,15 @@
         <v>46198.807521180555</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H120" s="6"/>
       <c r="I120" s="5">
         <v>46296</v>
       </c>
@@ -8729,13 +8684,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="O120" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="P120" s="6" t="s">
         <v>310</v>
-      </c>
-      <c r="O120" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="P120" s="6" t="s">
-        <v>313</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8745,7 +8700,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B121" s="9">
         <v>46161.585882430554</v>
@@ -8755,17 +8710,15 @@
         <v>46198.807499965274</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H121" s="10"/>
       <c r="I121" s="9">
         <v>46296</v>
       </c>
@@ -8782,13 +8735,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8798,7 +8751,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B122" s="5">
         <v>46161.58590298611</v>
@@ -8808,17 +8761,15 @@
         <v>46198.80750063657</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H122" s="6"/>
       <c r="I122" s="5">
         <v>46296</v>
       </c>
@@ -8835,13 +8786,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8851,7 +8802,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B123" s="9">
         <v>46161.585919861114</v>
@@ -8861,17 +8812,15 @@
         <v>46198.80750122685</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="10"/>
       <c r="I123" s="9">
         <v>46296</v>
       </c>
@@ -8888,13 +8837,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8904,7 +8853,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B124" s="5">
         <v>46161.585927175925</v>
@@ -8914,17 +8863,15 @@
         <v>46198.807501793985</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H124" s="6"/>
       <c r="I124" s="5">
         <v>46296</v>
       </c>
@@ -8941,13 +8888,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8957,7 +8904,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B125" s="9">
         <v>46161.58593310185</v>
@@ -8967,17 +8914,15 @@
         <v>46198.807502384254</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H125" s="10"/>
       <c r="I125" s="9">
         <v>46296</v>
       </c>
@@ -8994,13 +8939,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9010,7 +8955,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B126" s="5">
         <v>46161.58593739584</v>
@@ -9020,17 +8965,15 @@
         <v>46198.807502951386</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H126" s="6"/>
       <c r="I126" s="5">
         <v>46296</v>
       </c>
@@ -9047,13 +8990,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9063,7 +9006,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B127" s="9">
         <v>46161.58594590278</v>
@@ -9073,17 +9016,15 @@
         <v>46198.80750380787</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H127" s="10"/>
       <c r="I127" s="9">
         <v>46296</v>
       </c>
@@ -9100,13 +9041,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9116,7 +9057,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B128" s="5">
         <v>46161.5859562963</v>
@@ -9126,17 +9067,15 @@
         <v>46198.80750443287</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H128" s="6"/>
       <c r="I128" s="5">
         <v>46296</v>
       </c>
@@ -9153,13 +9092,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9169,7 +9108,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B129" s="9">
         <v>46161.58618912037</v>
@@ -9179,17 +9118,15 @@
         <v>46198.80750512732</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H129" s="10"/>
       <c r="I129" s="9">
         <v>46296</v>
       </c>
@@ -9206,13 +9143,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9222,7 +9159,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B130" s="5">
         <v>46161.58114761574</v>
@@ -9232,17 +9169,15 @@
         <v>46161.8461249074</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H130" s="6"/>
       <c r="I130" s="5">
         <v>46300</v>
       </c>
@@ -9259,13 +9194,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q130" s="5">
         <v>46300</v>
@@ -9280,12 +9215,12 @@
         <v>0</v>
       </c>
       <c r="U130" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B131" s="9">
         <v>46161.58115116898</v>
@@ -9295,17 +9230,15 @@
         <v>46198.807510914354</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H131" s="10"/>
       <c r="I131" s="9">
         <v>46300</v>
       </c>
@@ -9322,13 +9255,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="O131" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="P131" s="10" t="s">
         <v>328</v>
-      </c>
-      <c r="O131" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="P131" s="10" t="s">
-        <v>331</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9338,7 +9271,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B132" s="5">
         <v>46161.58603712963</v>
@@ -9348,17 +9281,15 @@
         <v>46198.80750575232</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H132" s="6"/>
       <c r="I132" s="5">
         <v>46300</v>
       </c>
@@ -9375,13 +9306,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9391,7 +9322,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B133" s="9">
         <v>46161.586044930555</v>
@@ -9401,17 +9332,15 @@
         <v>46198.8075062037</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H133" s="10"/>
       <c r="I133" s="9">
         <v>46300</v>
       </c>
@@ -9428,13 +9357,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9444,7 +9373,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B134" s="5">
         <v>46161.58605891204</v>
@@ -9454,17 +9383,15 @@
         <v>46198.807506666664</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H134" s="6"/>
       <c r="I134" s="5">
         <v>46300</v>
       </c>
@@ -9481,13 +9408,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9497,7 +9424,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B135" s="9">
         <v>46161.58606768519</v>
@@ -9507,17 +9434,15 @@
         <v>46198.8075071412</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H135" s="10"/>
       <c r="I135" s="9">
         <v>46300</v>
       </c>
@@ -9534,13 +9459,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9550,7 +9475,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B136" s="5">
         <v>46161.58607575232</v>
@@ -9560,17 +9485,15 @@
         <v>46198.807507708334</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H136" s="6"/>
       <c r="I136" s="5">
         <v>46300</v>
       </c>
@@ -9587,13 +9510,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9603,7 +9526,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B137" s="9">
         <v>46161.586088854165</v>
@@ -9613,17 +9536,15 @@
         <v>46198.80750815972</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H137" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H137" s="10"/>
       <c r="I137" s="9">
         <v>46300</v>
       </c>
@@ -9640,13 +9561,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9656,7 +9577,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B138" s="5">
         <v>46161.58609570602</v>
@@ -9666,17 +9587,15 @@
         <v>46198.80750863426</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H138" s="6"/>
       <c r="I138" s="5">
         <v>46300</v>
       </c>
@@ -9693,13 +9612,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9709,7 +9628,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B139" s="9">
         <v>46161.586110578704</v>
@@ -9719,17 +9638,15 @@
         <v>46198.807509085644</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H139" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H139" s="10"/>
       <c r="I139" s="9">
         <v>46300</v>
       </c>
@@ -9746,13 +9663,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9762,7 +9679,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B140" s="5">
         <v>46161.58612255787</v>
@@ -9772,17 +9689,15 @@
         <v>46198.80750956018</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H140" s="6"/>
       <c r="I140" s="5">
         <v>46300</v>
       </c>
@@ -9799,13 +9714,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9815,7 +9730,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B141" s="9">
         <v>46161.58115643519</v>
@@ -9825,17 +9740,15 @@
         <v>46161.84629616898</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H141" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H141" s="10"/>
       <c r="I141" s="9">
         <v>46303</v>
       </c>
@@ -9852,13 +9765,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q141" s="9">
         <v>46303</v>
@@ -9873,12 +9786,12 @@
         <v>0</v>
       </c>
       <c r="U141" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B142" s="5">
         <v>46161.58115993056</v>
@@ -9888,17 +9801,15 @@
         <v>46198.807521759256</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H142" s="6"/>
       <c r="I142" s="5">
         <v>46303</v>
       </c>
@@ -9915,13 +9826,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="O142" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="P142" s="6" t="s">
         <v>345</v>
-      </c>
-      <c r="O142" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="P142" s="6" t="s">
-        <v>348</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9931,7 +9842,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B143" s="9">
         <v>46161.58622641204</v>
@@ -9941,17 +9852,15 @@
         <v>46198.80750998843</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H143" s="10"/>
       <c r="I143" s="9">
         <v>46303</v>
       </c>
@@ -9968,13 +9877,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9984,7 +9893,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B144" s="5">
         <v>46161.586235995375</v>
@@ -9994,17 +9903,15 @@
         <v>46198.807510416664</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H144" s="6"/>
       <c r="I144" s="5">
         <v>46303</v>
       </c>
@@ -10021,13 +9928,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10037,7 +9944,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B145" s="9">
         <v>46161.586246770836</v>
@@ -10047,17 +9954,15 @@
         <v>46161.846280046295</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H145" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H145" s="10"/>
       <c r="I145" s="9">
         <v>46303</v>
       </c>
@@ -10074,13 +9979,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10090,7 +9995,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B146" s="5">
         <v>46161.586256435185</v>
@@ -10100,17 +10005,15 @@
         <v>46161.84627699074</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H146" s="6"/>
       <c r="I146" s="5">
         <v>46303</v>
       </c>
@@ -10127,13 +10030,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10143,7 +10046,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B147" s="9">
         <v>46161.586265833335</v>
@@ -10153,17 +10056,15 @@
         <v>46161.84627394676</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H147" s="10"/>
       <c r="I147" s="9">
         <v>46303</v>
       </c>
@@ -10180,13 +10081,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10196,7 +10097,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B148" s="5">
         <v>46161.586275671296</v>
@@ -10206,17 +10107,15 @@
         <v>46161.84627113426</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H148" s="6"/>
       <c r="I148" s="5">
         <v>46303</v>
       </c>
@@ -10233,13 +10132,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10249,7 +10148,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B149" s="9">
         <v>46161.58629186342</v>
@@ -10259,17 +10158,15 @@
         <v>46161.846268402776</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H149" s="10"/>
       <c r="I149" s="9">
         <v>46303</v>
       </c>
@@ -10286,13 +10183,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10302,7 +10199,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B150" s="5">
         <v>46161.58630879629</v>
@@ -10312,17 +10209,15 @@
         <v>46161.84626222222</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H150" s="6"/>
       <c r="I150" s="5">
         <v>46303</v>
       </c>
@@ -10339,13 +10234,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10355,7 +10250,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B151" s="9">
         <v>46161.58632163194</v>
@@ -10365,17 +10260,15 @@
         <v>46161.84626162037</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H151" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H151" s="10"/>
       <c r="I151" s="9">
         <v>46303</v>
       </c>
@@ -10392,13 +10285,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10408,7 +10301,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B152" s="5">
         <v>46161.5811646875</v>
@@ -10418,17 +10311,15 @@
         <v>46161.84643925926</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H152" s="6"/>
       <c r="I152" s="5">
         <v>46307</v>
       </c>
@@ -10445,13 +10336,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q152" s="5">
         <v>46307</v>
@@ -10466,12 +10357,12 @@
         <v>0</v>
       </c>
       <c r="U152" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B153" s="9">
         <v>46161.58116828704</v>
@@ -10481,17 +10372,15 @@
         <v>46161.84644222222</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H153" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H153" s="10"/>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
         <v>46307</v>
@@ -10506,13 +10395,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10522,7 +10411,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B154" s="5">
         <v>46161.63912622685</v>
@@ -10532,17 +10421,15 @@
         <v>46161.84643929398</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H154" s="6"/>
       <c r="I154" s="6"/>
       <c r="J154" s="5">
         <v>46307</v>
@@ -10557,10 +10444,10 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10573,7 +10460,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B155" s="9">
         <v>46161.63913737268</v>
@@ -10583,17 +10470,15 @@
         <v>46161.84643643518</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H155" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H155" s="10"/>
       <c r="I155" s="10"/>
       <c r="J155" s="9">
         <v>46307</v>
@@ -10608,10 +10493,10 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>26</v>
@@ -10624,7 +10509,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B156" s="5">
         <v>46161.63914719908</v>
@@ -10634,17 +10519,15 @@
         <v>46161.846433321756</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H156" s="6"/>
       <c r="I156" s="6"/>
       <c r="J156" s="5">
         <v>46307</v>
@@ -10659,10 +10542,10 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>26</v>
@@ -10675,7 +10558,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B157" s="9">
         <v>46161.639157557875</v>
@@ -10685,17 +10568,15 @@
         <v>46161.84643013889</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H157" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H157" s="10"/>
       <c r="I157" s="10"/>
       <c r="J157" s="9">
         <v>46307</v>
@@ -10710,10 +10591,10 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>26</v>
@@ -10726,7 +10607,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B158" s="5">
         <v>46161.6391721875</v>
@@ -10736,17 +10617,15 @@
         <v>46161.84642646991</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H158" s="6"/>
       <c r="I158" s="6"/>
       <c r="J158" s="5">
         <v>46307</v>
@@ -10761,10 +10640,10 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10777,7 +10656,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B159" s="9">
         <v>46161.639187395835</v>
@@ -10787,17 +10666,15 @@
         <v>46161.84642321759</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H159" s="10"/>
       <c r="I159" s="10"/>
       <c r="J159" s="9">
         <v>46307</v>
@@ -10812,10 +10689,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>26</v>
@@ -10828,7 +10705,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B160" s="5">
         <v>46161.639195289354</v>
@@ -10838,17 +10715,15 @@
         <v>46161.846420138885</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H160" s="6"/>
       <c r="I160" s="6"/>
       <c r="J160" s="5">
         <v>46307</v>
@@ -10863,10 +10738,10 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>26</v>
@@ -10879,7 +10754,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B161" s="9">
         <v>46161.63920550926</v>
@@ -10889,17 +10764,15 @@
         <v>46161.846413113424</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H161" s="10"/>
       <c r="I161" s="10"/>
       <c r="J161" s="9">
         <v>46307</v>
@@ -10914,10 +10787,10 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>26</v>
@@ -10930,7 +10803,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B162" s="5">
         <v>46161.63921432871</v>
@@ -10940,17 +10813,15 @@
         <v>46161.84641241898</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H162" s="6"/>
       <c r="I162" s="6"/>
       <c r="J162" s="5">
         <v>46307</v>
@@ -10965,13 +10836,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10981,7 +10852,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B163" s="9">
         <v>46161.58117752315</v>
@@ -10991,17 +10862,15 @@
         <v>46161.84660503472</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H163" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H163" s="10"/>
       <c r="I163" s="9">
         <v>46309</v>
       </c>
@@ -11018,13 +10887,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="Q163" s="9">
         <v>46309</v>
@@ -11039,12 +10908,12 @@
         <v>0</v>
       </c>
       <c r="U163" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B164" s="5">
         <v>46161.58118137732</v>
@@ -11054,17 +10923,15 @@
         <v>46161.84658016203</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H164" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H164" s="6"/>
       <c r="I164" s="5">
         <v>46309</v>
       </c>
@@ -11081,13 +10948,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="O164" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P164" s="6" t="s">
         <v>374</v>
-      </c>
-      <c r="O164" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="P164" s="6" t="s">
-        <v>377</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11097,7 +10964,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B165" s="9">
         <v>46161.639253761576</v>
@@ -11107,17 +10974,15 @@
         <v>46161.846577187505</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H165" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H165" s="10"/>
       <c r="I165" s="9">
         <v>46309</v>
       </c>
@@ -11134,10 +10999,10 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P165" s="10" t="s">
         <v>26</v>
@@ -11150,7 +11015,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B166" s="5">
         <v>46161.63928710648</v>
@@ -11160,17 +11025,15 @@
         <v>46161.84657417824</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H166" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H166" s="6"/>
       <c r="I166" s="5">
         <v>46309</v>
       </c>
@@ -11187,10 +11050,10 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11203,7 +11066,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B167" s="9">
         <v>46161.63929736111</v>
@@ -11213,17 +11076,15 @@
         <v>46161.84657136574</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H167" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H167" s="10"/>
       <c r="I167" s="9">
         <v>46309</v>
       </c>
@@ -11240,10 +11101,10 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P167" s="10" t="s">
         <v>26</v>
@@ -11256,7 +11117,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B168" s="5">
         <v>46161.6393071412</v>
@@ -11266,17 +11127,15 @@
         <v>46161.84656841435</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H168" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H168" s="6"/>
       <c r="I168" s="5">
         <v>46309</v>
       </c>
@@ -11293,10 +11152,10 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>26</v>
@@ -11309,7 +11168,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B169" s="9">
         <v>46161.639315625</v>
@@ -11319,17 +11178,15 @@
         <v>46161.84656539352</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H169" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H169" s="10"/>
       <c r="I169" s="9">
         <v>46309</v>
       </c>
@@ -11346,10 +11203,10 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11362,7 +11219,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B170" s="5">
         <v>46161.63932686343</v>
@@ -11372,17 +11229,15 @@
         <v>46161.846562754625</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H170" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H170" s="6"/>
       <c r="I170" s="5">
         <v>46309</v>
       </c>
@@ -11399,10 +11254,10 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11415,7 +11270,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B171" s="9">
         <v>46161.63933708333</v>
@@ -11425,17 +11280,15 @@
         <v>46161.8465599537</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H171" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H171" s="10"/>
       <c r="I171" s="9">
         <v>46309</v>
       </c>
@@ -11452,10 +11305,10 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>26</v>
@@ -11468,7 +11321,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B172" s="5">
         <v>46161.63935484954</v>
@@ -11478,17 +11331,15 @@
         <v>46161.846553807874</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H172" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H172" s="6"/>
       <c r="I172" s="5">
         <v>46309</v>
       </c>
@@ -11505,10 +11356,10 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>26</v>
@@ -11521,7 +11372,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B173" s="9">
         <v>46161.63936453704</v>
@@ -11531,17 +11382,15 @@
         <v>46161.84655313657</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H173" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H173" s="10"/>
       <c r="I173" s="9">
         <v>46309</v>
       </c>
@@ -11558,13 +11407,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11574,7 +11423,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B174" s="5">
         <v>46161.5811852662</v>
@@ -11584,7 +11433,7 @@
         <v>46161.84092732639</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>25</v>
@@ -11608,7 +11457,7 @@
         <v>26</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>26</v>
@@ -11621,7 +11470,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B175" s="9">
         <v>46161.581188020835</v>
@@ -11631,16 +11480,16 @@
         <v>46161.84675815972</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I175" s="9">
         <v>46310</v>
@@ -11658,13 +11507,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="Q175" s="9">
         <v>46310</v>
@@ -11679,12 +11528,12 @@
         <v>0</v>
       </c>
       <c r="U175" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B176" s="5">
         <v>46161.581192673606</v>
@@ -11694,16 +11543,16 @@
         <v>46161.846749351855</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I176" s="5">
         <v>46310</v>
@@ -11721,13 +11570,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11737,7 +11586,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B177" s="9">
         <v>46161.63982708333</v>
@@ -11747,16 +11596,16 @@
         <v>46161.84674655093</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I177" s="9">
         <v>46310</v>
@@ -11774,13 +11623,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11790,7 +11639,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B178" s="5">
         <v>46161.63983532407</v>
@@ -11800,16 +11649,16 @@
         <v>46161.846743981485</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I178" s="5">
         <v>46310</v>
@@ -11827,13 +11676,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11843,7 +11692,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B179" s="9">
         <v>46161.63984421296</v>
@@ -11853,16 +11702,16 @@
         <v>46161.84674143518</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I179" s="9">
         <v>46310</v>
@@ -11880,13 +11729,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11896,7 +11745,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B180" s="5">
         <v>46161.63985878472</v>
@@ -11906,16 +11755,16 @@
         <v>46161.846738541666</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I180" s="5">
         <v>46310</v>
@@ -11933,13 +11782,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11949,7 +11798,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B181" s="9">
         <v>46161.63986780093</v>
@@ -11959,16 +11808,16 @@
         <v>46161.84673559028</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I181" s="9">
         <v>46310</v>
@@ -11986,13 +11835,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -12002,7 +11851,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B182" s="5">
         <v>46161.639875</v>
@@ -12012,16 +11861,16 @@
         <v>46161.84673289352</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I182" s="5">
         <v>46310</v>
@@ -12039,13 +11888,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12055,7 +11904,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B183" s="9">
         <v>46161.63988342593</v>
@@ -12065,16 +11914,16 @@
         <v>46161.84672489583</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I183" s="9">
         <v>46310</v>
@@ -12092,13 +11941,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12108,7 +11957,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B184" s="5">
         <v>46161.63989143519</v>
@@ -12118,16 +11967,16 @@
         <v>46161.84672420139</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I184" s="5">
         <v>46310</v>
@@ -12145,13 +11994,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12161,7 +12010,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B185" s="9">
         <v>46161.639899340276</v>
@@ -12171,16 +12020,16 @@
         <v>46161.84672340278</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I185" s="9">
         <v>46310</v>
@@ -12198,13 +12047,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12214,7 +12063,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B186" s="5">
         <v>46161.5811965162</v>
@@ -12224,17 +12073,15 @@
         <v>46161.84690181713</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H186" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H186" s="6"/>
       <c r="I186" s="5">
         <v>46311</v>
       </c>
@@ -12251,13 +12098,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="Q186" s="5">
         <v>46311</v>
@@ -12272,12 +12119,12 @@
         <v>0</v>
       </c>
       <c r="U186" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B187" s="9">
         <v>46161.58120002315</v>
@@ -12287,17 +12134,15 @@
         <v>46161.84690336806</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H187" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H187" s="10"/>
       <c r="I187" s="9">
         <v>46311</v>
       </c>
@@ -12314,13 +12159,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12330,7 +12175,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B188" s="5">
         <v>46161.63993424768</v>
@@ -12340,17 +12185,15 @@
         <v>46161.84690038195</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H188" s="6"/>
       <c r="I188" s="5">
         <v>46311</v>
       </c>
@@ -12367,13 +12210,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12383,7 +12226,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B189" s="9">
         <v>46161.6399947801</v>
@@ -12393,17 +12236,15 @@
         <v>46161.84689746528</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H189" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H189" s="10"/>
       <c r="I189" s="9">
         <v>46311</v>
       </c>
@@ -12420,13 +12261,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12436,7 +12277,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B190" s="5">
         <v>46161.640004444445</v>
@@ -12446,17 +12287,15 @@
         <v>46161.84689446759</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H190" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H190" s="6"/>
       <c r="I190" s="5">
         <v>46311</v>
       </c>
@@ -12473,13 +12312,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12489,7 +12328,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B191" s="9">
         <v>46161.64001501157</v>
@@ -12499,17 +12338,15 @@
         <v>46161.84689137731</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H191" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H191" s="10"/>
       <c r="I191" s="9">
         <v>46311</v>
       </c>
@@ -12526,13 +12363,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12542,7 +12379,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B192" s="5">
         <v>46161.640023831016</v>
@@ -12552,17 +12389,15 @@
         <v>46161.846888796295</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H192" s="6"/>
       <c r="I192" s="5">
         <v>46311</v>
       </c>
@@ -12579,13 +12414,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12595,7 +12430,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B193" s="9">
         <v>46161.640038310186</v>
@@ -12605,17 +12440,15 @@
         <v>46161.84688606481</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H193" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H193" s="10"/>
       <c r="I193" s="9">
         <v>46311</v>
       </c>
@@ -12632,13 +12465,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12648,7 +12481,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B194" s="5">
         <v>46161.64004747685</v>
@@ -12658,17 +12491,15 @@
         <v>46161.846882557875</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H194" s="6"/>
       <c r="I194" s="5">
         <v>46311</v>
       </c>
@@ -12685,13 +12516,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12701,7 +12532,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B195" s="9">
         <v>46161.64005649305</v>
@@ -12711,17 +12542,15 @@
         <v>46161.84687957176</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H195" s="10" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H195" s="10"/>
       <c r="I195" s="9">
         <v>46311</v>
       </c>
@@ -12738,13 +12567,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12754,7 +12583,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B196" s="5">
         <v>46161.64006346065</v>
@@ -12764,17 +12593,15 @@
         <v>46161.846870243055</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H196" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H196" s="6"/>
       <c r="I196" s="5">
         <v>46311</v>
       </c>
@@ -12791,13 +12618,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12807,7 +12634,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B197" s="9">
         <v>46161.58120399306</v>
@@ -12817,16 +12644,16 @@
         <v>46161.84710645833</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H197" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I197" s="10"/>
       <c r="J197" s="9">
@@ -12842,13 +12669,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="Q197" s="9">
         <v>46316</v>
@@ -12863,12 +12690,12 @@
         <v>0</v>
       </c>
       <c r="U197" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B198" s="5">
         <v>46161.58120755787</v>
@@ -12878,16 +12705,16 @@
         <v>46161.847077812505</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -12903,13 +12730,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12919,7 +12746,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B199" s="9">
         <v>46161.6401252662</v>
@@ -12929,16 +12756,16 @@
         <v>46161.84707505787</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -12954,13 +12781,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12970,7 +12797,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B200" s="5">
         <v>46161.64014137731</v>
@@ -12980,16 +12807,16 @@
         <v>46161.847072476856</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13005,13 +12832,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13021,7 +12848,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B201" s="9">
         <v>46161.64015293981</v>
@@ -13031,16 +12858,16 @@
         <v>46161.84706930556</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -13056,13 +12883,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13072,7 +12899,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B202" s="5">
         <v>46161.64016740741</v>
@@ -13082,16 +12909,16 @@
         <v>46161.847066608796</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13107,13 +12934,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13123,7 +12950,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B203" s="9">
         <v>46161.640203877316</v>
@@ -13133,16 +12960,16 @@
         <v>46161.84706402778</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -13158,13 +12985,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13174,7 +13001,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B204" s="5">
         <v>46161.64021510417</v>
@@ -13184,16 +13011,16 @@
         <v>46161.84706112268</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13209,13 +13036,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13225,7 +13052,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B205" s="9">
         <v>46161.64022702546</v>
@@ -13235,16 +13062,16 @@
         <v>46161.847053425925</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13260,13 +13087,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13276,7 +13103,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B206" s="5">
         <v>46161.64023784723</v>
@@ -13286,16 +13113,16 @@
         <v>46161.8470527662</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13311,13 +13138,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13327,7 +13154,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B207" s="9">
         <v>46161.64025311342</v>
@@ -13337,16 +13164,16 @@
         <v>46161.84705210648</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13362,13 +13189,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13378,7 +13205,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B208" s="5">
         <v>46161.58121466435</v>
@@ -13388,16 +13215,16 @@
         <v>46161.84730193287</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I208" s="5">
         <v>46317</v>
@@ -13415,13 +13242,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="Q208" s="5">
         <v>46317</v>
@@ -13436,12 +13263,12 @@
         <v>0</v>
       </c>
       <c r="U208" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B209" s="9">
         <v>46161.58125732639</v>
@@ -13451,16 +13278,16 @@
         <v>46161.84728091436</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I209" s="10"/>
       <c r="J209" s="9">
@@ -13476,13 +13303,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13492,7 +13319,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B210" s="5">
         <v>46161.640307905094</v>
@@ -13502,16 +13329,16 @@
         <v>46161.84727769676</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13527,10 +13354,10 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>26</v>
@@ -13543,7 +13370,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B211" s="9">
         <v>46161.64031635417</v>
@@ -13553,16 +13380,16 @@
         <v>46161.84727525463</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I211" s="10"/>
       <c r="J211" s="9">
@@ -13578,10 +13405,10 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>26</v>
@@ -13594,7 +13421,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B212" s="5">
         <v>46161.64032832176</v>
@@ -13604,16 +13431,16 @@
         <v>46161.84727247685</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13629,10 +13456,10 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>26</v>
@@ -13645,7 +13472,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B213" s="9">
         <v>46161.640337986115</v>
@@ -13655,16 +13482,16 @@
         <v>46161.84726945602</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I213" s="10"/>
       <c r="J213" s="9">
@@ -13680,10 +13507,10 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>26</v>
@@ -13696,7 +13523,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B214" s="5">
         <v>46161.64035862268</v>
@@ -13706,16 +13533,16 @@
         <v>46161.84726638889</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13731,10 +13558,10 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13747,7 +13574,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B215" s="9">
         <v>46161.64036773148</v>
@@ -13757,16 +13584,16 @@
         <v>46161.84726359954</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I215" s="10"/>
       <c r="J215" s="9">
@@ -13782,10 +13609,10 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13798,7 +13625,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B216" s="5">
         <v>46161.64037657407</v>
@@ -13808,16 +13635,16 @@
         <v>46161.84726060185</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13833,10 +13660,10 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>26</v>
@@ -13849,7 +13676,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B217" s="9">
         <v>46161.64038473379</v>
@@ -13859,16 +13686,16 @@
         <v>46161.847254699074</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I217" s="10"/>
       <c r="J217" s="9">
@@ -13884,10 +13711,10 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>26</v>
@@ -13900,7 +13727,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B218" s="5">
         <v>46161.64039350694</v>
@@ -13910,16 +13737,16 @@
         <v>46161.8472540625</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -13935,10 +13762,10 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>26</v>
@@ -13951,7 +13778,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B219" s="9">
         <v>46161.581262824075</v>
@@ -13961,7 +13788,7 @@
         <v>46161.84801045139</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>25</v>
@@ -13985,7 +13812,7 @@
         <v>26</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>26</v>
@@ -13998,7 +13825,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B220" s="5">
         <v>46161.58126615741</v>
@@ -14008,16 +13835,16 @@
         <v>46161.84764756945</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I220" s="5">
         <v>46318</v>
@@ -14035,13 +13862,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="Q220" s="5">
         <v>46318</v>
@@ -14056,12 +13883,12 @@
         <v>0</v>
       </c>
       <c r="U220" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B221" s="9">
         <v>46161.581270821756</v>
@@ -14071,7 +13898,7 @@
         <v>46198.80656221065</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -14098,13 +13925,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="Q221" s="9">
         <v>46318</v>
@@ -14119,7 +13946,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -4726,7 +4726,7 @@
         <v>46198.8074493287</v>
       </c>
       <c r="D48" s="5">
-        <v>46213.18419743056</v>
+        <v>46221.17370061342</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4770,8 +4770,8 @@
       <c r="R48" s="5">
         <v>46220</v>
       </c>
-      <c r="S48" s="11" t="s">
-        <v>81</v>
+      <c r="S48" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="451">
   <si>
     <t>50001555 - "ZITRON COLOMBIA ARIS MINING SEGOVIA"</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete ot 4332</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Generación OC Rodete ot 4332,Propuesta compras:</t>
@@ -2863,7 +2866,7 @@
         <v>46197.58859138889</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.675101863424</v>
+        <v>46223.58333574074</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2872,9 +2875,11 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I17" s="9">
         <v>46164</v>
       </c>
@@ -2897,7 +2902,7 @@
         <v>57</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q17" s="9">
         <v>46164</v>
@@ -2917,7 +2922,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
         <v>46161.58079903935</v>
@@ -2926,18 +2931,20 @@
         <v>46204.90066085648</v>
       </c>
       <c r="D18" s="5">
-        <v>46218.2038322338</v>
+        <v>46223.58333158564</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I18" s="5">
         <v>46224</v>
       </c>
@@ -2957,10 +2964,10 @@
         <v>66</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2969,7 +2976,7 @@
         <v>46225</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2980,7 +2987,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9">
         <v>46161.58080373843</v>
@@ -2989,18 +2996,20 @@
         <v>46204.90101555556</v>
       </c>
       <c r="D19" s="9">
-        <v>46218.2038325</v>
+        <v>46223.58332738426</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I19" s="9">
         <v>46224</v>
       </c>
@@ -3020,10 +3029,10 @@
         <v>66</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="9">
         <v>46224</v>
@@ -3032,7 +3041,7 @@
         <v>46225</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -3043,7 +3052,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46161.58080740741</v>
@@ -3052,18 +3061,20 @@
         <v>46204.90180252315</v>
       </c>
       <c r="D20" s="5">
-        <v>46218.20383224537</v>
+        <v>46223.5833241088</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I20" s="5">
         <v>46224</v>
       </c>
@@ -3083,10 +3094,10 @@
         <v>66</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -3095,7 +3106,7 @@
         <v>46225</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -3106,7 +3117,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9">
         <v>46161.580810740736</v>
@@ -3115,18 +3126,20 @@
         <v>46204.90175329861</v>
       </c>
       <c r="D21" s="9">
-        <v>46218.20383224537</v>
+        <v>46223.58331811342</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I21" s="9">
         <v>46224</v>
       </c>
@@ -3146,10 +3159,10 @@
         <v>66</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="9">
         <v>46224</v>
@@ -3158,7 +3171,7 @@
         <v>46225</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -3169,7 +3182,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46161.58064796297</v>
@@ -3179,7 +3192,7 @@
         <v>46211.83005701389</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -3203,7 +3216,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -3216,7 +3229,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B23" s="9">
         <v>46161.58081472223</v>
@@ -3228,16 +3241,16 @@
         <v>46209.56551446759</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I23" s="9">
         <v>46168</v>
@@ -3255,13 +3268,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="9">
         <v>46168</v>
@@ -3281,7 +3294,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46161.580819016206</v>
@@ -3293,16 +3306,16 @@
         <v>46209.56543981482</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I24" s="5">
         <v>46168</v>
@@ -3320,13 +3333,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3337,12 +3350,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
         <v>46161.58082350694</v>
@@ -3354,16 +3367,16 @@
         <v>46209.565488576394</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I25" s="9">
         <v>46170</v>
@@ -3381,13 +3394,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3398,12 +3411,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46161.58082824074</v>
@@ -3415,16 +3428,16 @@
         <v>46209.56600694444</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I26" s="5">
         <v>46168</v>
@@ -3442,13 +3455,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q26" s="5">
         <v>46168</v>
@@ -3468,7 +3481,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46161.5808325463</v>
@@ -3480,16 +3493,16 @@
         <v>46209.56565858796</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I27" s="9">
         <v>46168</v>
@@ -3507,13 +3520,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3524,12 +3537,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46161.580836967594</v>
@@ -3541,16 +3554,16 @@
         <v>46209.56570685185</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I28" s="5">
         <v>46170</v>
@@ -3568,13 +3581,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3585,12 +3598,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46161.58084165509</v>
@@ -3600,16 +3613,16 @@
         <v>46198.805784641205</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I29" s="9">
         <v>46156</v>
@@ -3627,13 +3640,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q29" s="9">
         <v>46156</v>
@@ -3648,12 +3661,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46161.58084603009</v>
@@ -3665,16 +3678,16 @@
         <v>46198.80572795139</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I30" s="5">
         <v>46156</v>
@@ -3692,13 +3705,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3709,12 +3722,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46161.580850439816</v>
@@ -3724,16 +3737,16 @@
         <v>46198.80573190972</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3751,13 +3764,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3768,12 +3781,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46161.58085503472</v>
@@ -3785,16 +3798,16 @@
         <v>46198.80577622685</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I32" s="5">
         <v>46176</v>
@@ -3812,13 +3825,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3829,12 +3842,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>46161.58085940972</v>
@@ -3846,16 +3859,16 @@
         <v>46211.830060266206</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I33" s="9">
         <v>46226</v>
@@ -3873,13 +3886,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q33" s="9">
         <v>46226</v>
@@ -3899,7 +3912,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
         <v>46161.58086364584</v>
@@ -3911,16 +3924,16 @@
         <v>46205.61008960648</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I34" s="5">
         <v>46226</v>
@@ -3938,13 +3951,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3955,12 +3968,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
         <v>46161.58086832176</v>
@@ -3972,16 +3985,16 @@
         <v>46211.83003016203</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I35" s="9">
         <v>46230</v>
@@ -3999,13 +4012,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -4016,12 +4029,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46161.58087322916</v>
@@ -4033,16 +4046,16 @@
         <v>46209.804952569444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -4060,10 +4073,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -4086,7 +4099,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46161.580931018514</v>
@@ -4098,16 +4111,16 @@
         <v>46205.610248032404</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I37" s="9">
         <v>46226</v>
@@ -4125,13 +4138,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4141,7 +4154,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46161.58093646991</v>
@@ -4153,16 +4166,16 @@
         <v>46209.809419513884</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -4180,13 +4193,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4196,7 +4209,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
         <v>46161.580941099535</v>
@@ -4208,16 +4221,16 @@
         <v>46209.62288859954</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I39" s="9">
         <v>46225</v>
@@ -4235,10 +4248,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4261,7 +4274,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46161.58094532407</v>
@@ -4273,16 +4286,16 @@
         <v>46209.622784444444</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46225</v>
@@ -4300,13 +4313,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4316,7 +4329,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46161.58094997685</v>
@@ -4328,16 +4341,16 @@
         <v>46209.62283091435</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" s="9">
         <v>46234</v>
@@ -4355,13 +4368,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4371,7 +4384,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46161.58095447917</v>
@@ -4381,16 +4394,16 @@
         <v>46209.62284077547</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46265</v>
@@ -4408,10 +4421,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4424,7 +4437,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46161.58095743056</v>
@@ -4436,16 +4449,16 @@
         <v>46209.81259914352</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I43" s="9">
         <v>46226</v>
@@ -4463,10 +4476,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4489,7 +4502,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46161.58096091435</v>
@@ -4501,16 +4514,16 @@
         <v>46209.81220270833</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I44" s="5">
         <v>46226</v>
@@ -4528,13 +4541,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4544,7 +4557,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46161.580964988425</v>
@@ -4556,16 +4569,16 @@
         <v>46209.81257327546</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I45" s="9">
         <v>46230</v>
@@ -4583,13 +4596,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4599,7 +4612,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46161.58065239583</v>
@@ -4611,7 +4624,7 @@
         <v>46210.52870142361</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4635,7 +4648,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4652,7 +4665,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46161.580969780094</v>
@@ -4664,16 +4677,16 @@
         <v>46197.70504644676</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46164</v>
@@ -4691,13 +4704,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>62</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46164</v>
@@ -4717,7 +4730,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46161.580975069446</v>
@@ -4729,16 +4742,16 @@
         <v>46221.17370061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46216</v>
@@ -4756,13 +4769,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46216</v>
@@ -4782,7 +4795,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46161.58098100695</v>
@@ -4794,16 +4807,16 @@
         <v>46216.19023893519</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I49" s="9">
         <v>46223</v>
@@ -4821,13 +4834,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46223</v>
@@ -4836,7 +4849,7 @@
         <v>46223</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4847,7 +4860,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46161.58099116899</v>
@@ -4857,16 +4870,16 @@
         <v>46161.84476310185</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46308</v>
@@ -4884,10 +4897,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4905,12 +4918,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46161.58099418982</v>
@@ -4920,16 +4933,16 @@
         <v>46161.84476607639</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4945,13 +4958,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4961,7 +4974,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46161.63966489583</v>
@@ -4971,16 +4984,16 @@
         <v>46161.844763472225</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4996,13 +5009,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5012,7 +5025,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46161.63967261574</v>
@@ -5022,16 +5035,16 @@
         <v>46161.84476069444</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5047,13 +5060,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5063,7 +5076,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46161.63968388889</v>
@@ -5073,16 +5086,16 @@
         <v>46161.84475773148</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5098,13 +5111,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5114,7 +5127,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
         <v>46161.63969275463</v>
@@ -5124,16 +5137,16 @@
         <v>46161.84475471065</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5149,13 +5162,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5165,7 +5178,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46161.639705208334</v>
@@ -5175,16 +5188,16 @@
         <v>46161.84475174769</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5200,13 +5213,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5216,7 +5229,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="9">
         <v>46161.639715474535</v>
@@ -5226,16 +5239,16 @@
         <v>46161.84474863426</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5251,13 +5264,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5267,7 +5280,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46161.63972679398</v>
@@ -5277,16 +5290,16 @@
         <v>46161.84474503472</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5302,13 +5315,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5318,7 +5331,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" s="9">
         <v>46161.63974304398</v>
@@ -5328,16 +5341,16 @@
         <v>46161.84473834491</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5353,13 +5366,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5369,7 +5382,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46161.63975269676</v>
@@ -5379,16 +5392,16 @@
         <v>46161.84473753472</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5404,13 +5417,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5420,7 +5433,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B61" s="9">
         <v>46161.58099818287</v>
@@ -5430,7 +5443,7 @@
         <v>46217.592142650465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5454,7 +5467,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5467,7 +5480,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46161.58100145833</v>
@@ -5477,16 +5490,16 @@
         <v>46217.59224327546</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46239</v>
@@ -5504,13 +5517,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q62" s="5">
         <v>46239</v>
@@ -5530,7 +5543,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B63" s="9">
         <v>46161.58100614583</v>
@@ -5540,16 +5553,16 @@
         <v>46217.59214284722</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I63" s="9">
         <v>46241</v>
@@ -5567,13 +5580,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q63" s="9">
         <v>46241</v>
@@ -5588,12 +5601,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B64" s="5">
         <v>46161.58101638889</v>
@@ -5603,16 +5616,16 @@
         <v>46209.804944710646</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I64" s="5">
         <v>46239</v>
@@ -5630,13 +5643,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q64" s="5">
         <v>46239</v>
@@ -5656,7 +5669,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B65" s="9">
         <v>46161.58102099537</v>
@@ -5666,16 +5679,16 @@
         <v>46161.84491503472</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I65" s="9">
         <v>46241</v>
@@ -5693,13 +5706,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q65" s="9">
         <v>46241</v>
@@ -5714,12 +5727,12 @@
         <v>0</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B66" s="5">
         <v>46161.581024722225</v>
@@ -5729,16 +5742,16 @@
         <v>46209.81259190972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I66" s="5">
         <v>46239</v>
@@ -5756,13 +5769,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q66" s="5">
         <v>46239</v>
@@ -5782,7 +5795,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B67" s="9">
         <v>46161.58102864583</v>
@@ -5792,16 +5805,16 @@
         <v>46161.844914270834</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I67" s="9">
         <v>46241</v>
@@ -5819,13 +5832,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q67" s="9">
         <v>46241</v>
@@ -5840,12 +5853,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B68" s="5">
         <v>46161.58103207176</v>
@@ -5855,7 +5868,7 @@
         <v>46161.797785821764</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5879,7 +5892,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5892,7 +5905,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B69" s="9">
         <v>46161.58103457176</v>
@@ -5902,16 +5915,16 @@
         <v>46161.845178449075</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I69" s="9">
         <v>46245</v>
@@ -5929,13 +5942,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q69" s="9">
         <v>46245</v>
@@ -5950,12 +5963,12 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B70" s="5">
         <v>46161.58103962963</v>
@@ -5965,16 +5978,16 @@
         <v>46161.845147071755</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I70" s="5">
         <v>46245</v>
@@ -5992,13 +6005,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6008,7 +6021,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B71" s="9">
         <v>46161.582011805556</v>
@@ -6018,16 +6031,16 @@
         <v>46161.84514348379</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I71" s="9">
         <v>46245</v>
@@ -6045,13 +6058,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6061,7 +6074,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5">
         <v>46161.58202383102</v>
@@ -6071,16 +6084,16 @@
         <v>46161.845140324076</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I72" s="5">
         <v>46245</v>
@@ -6098,13 +6111,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6114,7 +6127,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B73" s="9">
         <v>46161.582662650464</v>
@@ -6124,16 +6137,16 @@
         <v>46161.845136655094</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I73" s="9">
         <v>46245</v>
@@ -6151,13 +6164,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6167,7 +6180,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5">
         <v>46161.58267322917</v>
@@ -6177,16 +6190,16 @@
         <v>46161.845133518524</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I74" s="5">
         <v>46245</v>
@@ -6204,13 +6217,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6220,7 +6233,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B75" s="9">
         <v>46161.58270134259</v>
@@ -6230,16 +6243,16 @@
         <v>46161.84513074074</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I75" s="9">
         <v>46245</v>
@@ -6257,13 +6270,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6273,7 +6286,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
         <v>46161.58271427083</v>
@@ -6283,16 +6296,16 @@
         <v>46161.84512803241</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I76" s="5">
         <v>46245</v>
@@ -6310,13 +6323,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6326,7 +6339,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B77" s="9">
         <v>46161.58272651621</v>
@@ -6336,16 +6349,16 @@
         <v>46161.84512407407</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I77" s="9">
         <v>46245</v>
@@ -6363,13 +6376,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6379,7 +6392,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B78" s="5">
         <v>46161.58277962963</v>
@@ -6389,16 +6402,16 @@
         <v>46161.845117916666</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I78" s="5">
         <v>46245</v>
@@ -6416,13 +6429,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6432,7 +6445,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B79" s="9">
         <v>46161.58279046296</v>
@@ -6442,16 +6455,16 @@
         <v>46161.84511721064</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I79" s="9">
         <v>46245</v>
@@ -6469,13 +6482,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6485,7 +6498,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B80" s="5">
         <v>46161.58104538194</v>
@@ -6495,16 +6508,16 @@
         <v>46161.845344814814</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I80" s="5">
         <v>46254</v>
@@ -6522,13 +6535,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q80" s="5">
         <v>46254</v>
@@ -6543,12 +6556,12 @@
         <v>0</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B81" s="9">
         <v>46161.58104903935</v>
@@ -6558,16 +6571,16 @@
         <v>46198.80752025463</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I81" s="9">
         <v>46254</v>
@@ -6585,13 +6598,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6601,7 +6614,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46161.582834120374</v>
@@ -6611,16 +6624,16 @@
         <v>46161.84533628472</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I82" s="5">
         <v>46254</v>
@@ -6638,13 +6651,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6654,7 +6667,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B83" s="9">
         <v>46161.58286459491</v>
@@ -6664,16 +6677,16 @@
         <v>46161.84533336805</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I83" s="9">
         <v>46254</v>
@@ -6691,13 +6704,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6707,7 +6720,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B84" s="5">
         <v>46161.58287381944</v>
@@ -6717,16 +6730,16 @@
         <v>46161.84533065972</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I84" s="5">
         <v>46254</v>
@@ -6744,13 +6757,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6760,7 +6773,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B85" s="9">
         <v>46161.58288365741</v>
@@ -6770,16 +6783,16 @@
         <v>46161.84532790509</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I85" s="9">
         <v>46254</v>
@@ -6797,13 +6810,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6813,7 +6826,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B86" s="5">
         <v>46161.58289255787</v>
@@ -6823,16 +6836,16 @@
         <v>46161.84532486111</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I86" s="5">
         <v>46254</v>
@@ -6850,13 +6863,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6866,7 +6879,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B87" s="9">
         <v>46161.58292542824</v>
@@ -6876,16 +6889,16 @@
         <v>46161.84532211805</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I87" s="9">
         <v>46254</v>
@@ -6903,13 +6916,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6919,7 +6932,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B88" s="5">
         <v>46161.58293696759</v>
@@ -6929,16 +6942,16 @@
         <v>46161.84531927083</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I88" s="5">
         <v>46254</v>
@@ -6956,13 +6969,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6972,7 +6985,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B89" s="9">
         <v>46161.58295282407</v>
@@ -6982,16 +6995,16 @@
         <v>46161.84531311343</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I89" s="9">
         <v>46254</v>
@@ -7009,13 +7022,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7025,7 +7038,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B90" s="5">
         <v>46161.58296773148</v>
@@ -7035,16 +7048,16 @@
         <v>46161.84531243055</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I90" s="5">
         <v>46254</v>
@@ -7062,13 +7075,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7078,7 +7091,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B91" s="9">
         <v>46161.581053761576</v>
@@ -7088,16 +7101,16 @@
         <v>46161.84552644676</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -7115,13 +7128,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q91" s="9">
         <v>46274</v>
@@ -7136,12 +7149,12 @@
         <v>0</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B92" s="5">
         <v>46161.58105741898</v>
@@ -7151,16 +7164,16 @@
         <v>46198.80752082176</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -7178,13 +7191,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7194,7 +7207,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B93" s="9">
         <v>46161.583039942125</v>
@@ -7204,16 +7217,16 @@
         <v>46161.84550880787</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I93" s="9">
         <v>46274</v>
@@ -7231,13 +7244,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7247,7 +7260,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B94" s="5">
         <v>46161.58305715278</v>
@@ -7257,16 +7270,16 @@
         <v>46161.845505324076</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I94" s="5">
         <v>46274</v>
@@ -7284,13 +7297,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7300,7 +7313,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B95" s="9">
         <v>46161.583076689814</v>
@@ -7310,16 +7323,16 @@
         <v>46161.84550258102</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I95" s="9">
         <v>46274</v>
@@ -7337,13 +7350,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7353,7 +7366,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B96" s="5">
         <v>46161.58308886574</v>
@@ -7363,16 +7376,16 @@
         <v>46161.84549928241</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I96" s="5">
         <v>46274</v>
@@ -7390,13 +7403,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7406,7 +7419,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B97" s="9">
         <v>46161.58310019676</v>
@@ -7416,16 +7429,16 @@
         <v>46161.84549533565</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I97" s="9">
         <v>46274</v>
@@ -7443,13 +7456,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7459,7 +7472,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B98" s="5">
         <v>46161.5831108912</v>
@@ -7469,16 +7482,16 @@
         <v>46161.84549206018</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I98" s="5">
         <v>46274</v>
@@ -7496,13 +7509,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7512,7 +7525,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B99" s="9">
         <v>46161.58312844907</v>
@@ -7522,16 +7535,16 @@
         <v>46161.84548887731</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I99" s="9">
         <v>46274</v>
@@ -7549,13 +7562,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7565,7 +7578,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B100" s="5">
         <v>46161.58300775463</v>
@@ -7575,16 +7588,16 @@
         <v>46161.84548230324</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I100" s="5">
         <v>46274</v>
@@ -7602,13 +7615,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7618,7 +7631,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B101" s="9">
         <v>46161.639501875004</v>
@@ -7628,16 +7641,16 @@
         <v>46161.845481620374</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I101" s="9">
         <v>46274</v>
@@ -7655,13 +7668,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7671,7 +7684,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B102" s="5">
         <v>46161.58110506945</v>
@@ -7681,7 +7694,7 @@
         <v>46161.80776861111</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7705,7 +7718,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7718,7 +7731,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B103" s="9">
         <v>46161.581108530096</v>
@@ -7728,16 +7741,16 @@
         <v>46209.56572255787</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I103" s="9">
         <v>46174</v>
@@ -7755,13 +7768,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q103" s="9">
         <v>46174</v>
@@ -7781,7 +7794,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B104" s="5">
         <v>46161.58111370371</v>
@@ -7791,16 +7804,16 @@
         <v>46209.56550644676</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I104" s="5">
         <v>46282</v>
@@ -7818,13 +7831,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q104" s="5">
         <v>46282</v>
@@ -7844,7 +7857,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B105" s="9">
         <v>46161.581118449074</v>
@@ -7854,16 +7867,16 @@
         <v>46161.84560644676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I105" s="9">
         <v>46301</v>
@@ -7881,13 +7894,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q105" s="9">
         <v>46301</v>
@@ -7902,12 +7915,12 @@
         <v>0</v>
       </c>
       <c r="U105" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B106" s="5">
         <v>46161.58112311343</v>
@@ -7917,16 +7930,16 @@
         <v>46209.62284840278</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I106" s="5">
         <v>46237</v>
@@ -7944,13 +7957,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q106" s="5">
         <v>46237</v>
@@ -7970,7 +7983,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B107" s="9">
         <v>46161.58112702546</v>
@@ -7980,7 +7993,7 @@
         <v>46161.83387362269</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -8004,7 +8017,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -8017,25 +8030,27 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B108" s="5">
         <v>46161.58112984954</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46161.84578230324</v>
+        <v>46223.58492069444</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I108" s="5">
         <v>46276</v>
       </c>
@@ -8052,13 +8067,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q108" s="5">
         <v>46276</v>
@@ -8073,30 +8088,32 @@
         <v>0</v>
       </c>
       <c r="U108" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B109" s="9">
         <v>46161.581135555556</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46161.84577694444</v>
+        <v>46223.58354871528</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I109" s="9">
         <v>46276</v>
       </c>
@@ -8113,13 +8130,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8129,25 +8146,27 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B110" s="5">
         <v>46161.58317730324</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46161.84577366898</v>
+        <v>46223.58354810185</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I110" s="5">
         <v>46276</v>
       </c>
@@ -8164,13 +8183,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8180,25 +8199,27 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B111" s="9">
         <v>46161.58318758102</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46161.845770879634</v>
+        <v>46223.58354731482</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I111" s="9">
         <v>46276</v>
       </c>
@@ -8215,13 +8236,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8231,25 +8252,27 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B112" s="5">
         <v>46161.5831975926</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46161.84576709491</v>
+        <v>46223.583546678245</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I112" s="5">
         <v>46276</v>
       </c>
@@ -8266,13 +8289,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8282,25 +8305,27 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B113" s="9">
         <v>46161.58320657407</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46161.84576415509</v>
+        <v>46223.58354601852</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I113" s="9">
         <v>46276</v>
       </c>
@@ -8317,13 +8342,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8333,25 +8358,27 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B114" s="5">
         <v>46161.58322151621</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46161.84576082176</v>
+        <v>46223.583545381945</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I114" s="5">
         <v>46276</v>
       </c>
@@ -8368,13 +8395,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8384,25 +8411,27 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B115" s="9">
         <v>46161.58322717593</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46161.84575040509</v>
+        <v>46223.583544733796</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H115" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I115" s="9">
         <v>46276</v>
       </c>
@@ -8419,13 +8448,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8435,25 +8464,27 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B116" s="5">
         <v>46161.58324248843</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46161.84574967592</v>
+        <v>46223.583544050925</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H116" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I116" s="5">
         <v>46276</v>
       </c>
@@ -8470,13 +8501,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8486,25 +8517,27 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B117" s="9">
         <v>46161.58325402778</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46161.845748946755</v>
+        <v>46223.58354342592</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H117" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I117" s="9">
         <v>46276</v>
       </c>
@@ -8521,13 +8554,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8537,25 +8570,27 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B118" s="5">
         <v>46161.58326291667</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46161.84574821759</v>
+        <v>46223.5835428125</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H118" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I118" s="5">
         <v>46276</v>
       </c>
@@ -8572,13 +8607,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8588,25 +8623,27 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B119" s="9">
         <v>46161.58113928241</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46161.845971400464</v>
+        <v>46223.58491987269</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I119" s="9">
         <v>46296</v>
       </c>
@@ -8623,13 +8660,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q119" s="9">
         <v>46296</v>
@@ -8644,30 +8681,32 @@
         <v>0</v>
       </c>
       <c r="U119" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B120" s="5">
         <v>46161.58114282407</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46198.807521180555</v>
+        <v>46223.583707557875</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I120" s="5">
         <v>46296</v>
       </c>
@@ -8684,13 +8723,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8700,25 +8739,27 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B121" s="9">
         <v>46161.585882430554</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46198.807499965274</v>
+        <v>46223.58370696759</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I121" s="9">
         <v>46296</v>
       </c>
@@ -8735,13 +8776,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8751,25 +8792,27 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B122" s="5">
         <v>46161.58590298611</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46198.80750063657</v>
+        <v>46223.58370635417</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H122" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I122" s="5">
         <v>46296</v>
       </c>
@@ -8786,13 +8829,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8802,25 +8845,27 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B123" s="9">
         <v>46161.585919861114</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46198.80750122685</v>
+        <v>46223.583705717596</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I123" s="9">
         <v>46296</v>
       </c>
@@ -8837,13 +8882,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8853,25 +8898,27 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B124" s="5">
         <v>46161.585927175925</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46198.807501793985</v>
+        <v>46223.58370516203</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I124" s="5">
         <v>46296</v>
       </c>
@@ -8888,13 +8935,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8904,25 +8951,27 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B125" s="9">
         <v>46161.58593310185</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46198.807502384254</v>
+        <v>46223.583704375</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H125" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I125" s="9">
         <v>46296</v>
       </c>
@@ -8939,13 +8988,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8955,25 +9004,27 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B126" s="5">
         <v>46161.58593739584</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46198.807502951386</v>
+        <v>46223.58370383102</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I126" s="5">
         <v>46296</v>
       </c>
@@ -8990,13 +9041,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9006,25 +9057,27 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B127" s="9">
         <v>46161.58594590278</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46198.80750380787</v>
+        <v>46223.58370325231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H127" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I127" s="9">
         <v>46296</v>
       </c>
@@ -9041,13 +9094,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9057,25 +9110,27 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B128" s="5">
         <v>46161.5859562963</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46198.80750443287</v>
+        <v>46223.58370267361</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H128" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I128" s="5">
         <v>46296</v>
       </c>
@@ -9092,13 +9147,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9108,25 +9163,27 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B129" s="9">
         <v>46161.58618912037</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46198.80750512732</v>
+        <v>46223.583702083335</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H129" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H129" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I129" s="9">
         <v>46296</v>
       </c>
@@ -9143,13 +9200,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9159,25 +9216,27 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B130" s="5">
         <v>46161.58114761574</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46161.8461249074</v>
+        <v>46223.58491914352</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H130" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I130" s="5">
         <v>46300</v>
       </c>
@@ -9194,13 +9253,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q130" s="5">
         <v>46300</v>
@@ -9215,30 +9274,32 @@
         <v>0</v>
       </c>
       <c r="U130" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B131" s="9">
         <v>46161.58115116898</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46198.807510914354</v>
+        <v>46223.58385747686</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H131" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H131" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I131" s="9">
         <v>46300</v>
       </c>
@@ -9255,13 +9316,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9271,25 +9332,27 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B132" s="5">
         <v>46161.58603712963</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46198.80750575232</v>
+        <v>46223.58385686342</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H132" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I132" s="5">
         <v>46300</v>
       </c>
@@ -9306,13 +9369,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9322,25 +9385,27 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B133" s="9">
         <v>46161.586044930555</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46198.8075062037</v>
+        <v>46223.58385618056</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H133" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H133" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I133" s="9">
         <v>46300</v>
       </c>
@@ -9357,13 +9422,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9373,25 +9438,27 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B134" s="5">
         <v>46161.58605891204</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46198.807506666664</v>
+        <v>46223.583855543984</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H134" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I134" s="5">
         <v>46300</v>
       </c>
@@ -9408,13 +9475,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9424,25 +9491,27 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B135" s="9">
         <v>46161.58606768519</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46198.8075071412</v>
+        <v>46223.5838549537</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H135" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H135" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I135" s="9">
         <v>46300</v>
       </c>
@@ -9459,13 +9528,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9475,25 +9544,27 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B136" s="5">
         <v>46161.58607575232</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46198.807507708334</v>
+        <v>46223.58385431713</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H136" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I136" s="5">
         <v>46300</v>
       </c>
@@ -9510,13 +9581,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9526,25 +9597,27 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B137" s="9">
         <v>46161.586088854165</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46198.80750815972</v>
+        <v>46223.583853715274</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H137" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I137" s="9">
         <v>46300</v>
       </c>
@@ -9561,13 +9634,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9577,25 +9650,27 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B138" s="5">
         <v>46161.58609570602</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46198.80750863426</v>
+        <v>46223.58385304398</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H138" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I138" s="5">
         <v>46300</v>
       </c>
@@ -9612,13 +9687,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9628,25 +9703,27 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B139" s="9">
         <v>46161.586110578704</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46198.807509085644</v>
+        <v>46223.58385228009</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H139" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I139" s="9">
         <v>46300</v>
       </c>
@@ -9663,13 +9740,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9679,25 +9756,27 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B140" s="5">
         <v>46161.58612255787</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46198.80750956018</v>
+        <v>46223.58385163195</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H140" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I140" s="5">
         <v>46300</v>
       </c>
@@ -9714,13 +9793,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9730,25 +9809,27 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B141" s="9">
         <v>46161.58115643519</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46161.84629616898</v>
+        <v>46223.58491846065</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H141" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H141" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I141" s="9">
         <v>46303</v>
       </c>
@@ -9765,13 +9846,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q141" s="9">
         <v>46303</v>
@@ -9786,30 +9867,32 @@
         <v>0</v>
       </c>
       <c r="U141" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B142" s="5">
         <v>46161.58115993056</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46198.807521759256</v>
+        <v>46223.583971608794</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H142" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I142" s="5">
         <v>46303</v>
       </c>
@@ -9826,13 +9909,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9842,25 +9925,27 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B143" s="9">
         <v>46161.58622641204</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46198.80750998843</v>
+        <v>46223.583970949076</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H143" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I143" s="9">
         <v>46303</v>
       </c>
@@ -9877,13 +9962,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9893,25 +9978,27 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B144" s="5">
         <v>46161.586235995375</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46198.807510416664</v>
+        <v>46223.583970277774</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H144" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I144" s="5">
         <v>46303</v>
       </c>
@@ -9928,13 +10015,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9944,25 +10031,27 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B145" s="9">
         <v>46161.586246770836</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46161.846280046295</v>
+        <v>46223.583969479165</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H145" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H145" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I145" s="9">
         <v>46303</v>
       </c>
@@ -9979,13 +10068,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9995,25 +10084,27 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B146" s="5">
         <v>46161.586256435185</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46161.84627699074</v>
+        <v>46223.58396876157</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H146" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I146" s="5">
         <v>46303</v>
       </c>
@@ -10030,13 +10121,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10046,25 +10137,27 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B147" s="9">
         <v>46161.586265833335</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46161.84627394676</v>
+        <v>46223.5839677662</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H147" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H147" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I147" s="9">
         <v>46303</v>
       </c>
@@ -10081,13 +10174,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10097,25 +10190,27 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B148" s="5">
         <v>46161.586275671296</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46161.84627113426</v>
+        <v>46223.58396645833</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H148" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I148" s="5">
         <v>46303</v>
       </c>
@@ -10132,13 +10227,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10148,25 +10243,27 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B149" s="9">
         <v>46161.58629186342</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46161.846268402776</v>
+        <v>46223.58396577546</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H149" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I149" s="9">
         <v>46303</v>
       </c>
@@ -10183,13 +10280,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10199,25 +10296,27 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B150" s="5">
         <v>46161.58630879629</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46161.84626222222</v>
+        <v>46223.58396513889</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H150" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I150" s="5">
         <v>46303</v>
       </c>
@@ -10234,13 +10333,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10250,25 +10349,27 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B151" s="9">
         <v>46161.58632163194</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46161.84626162037</v>
+        <v>46223.583964537036</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H151" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H151" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I151" s="9">
         <v>46303</v>
       </c>
@@ -10285,13 +10386,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10301,25 +10402,27 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B152" s="5">
         <v>46161.5811646875</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46161.84643925926</v>
+        <v>46223.5849177662</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H152" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I152" s="5">
         <v>46307</v>
       </c>
@@ -10336,13 +10439,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q152" s="5">
         <v>46307</v>
@@ -10357,30 +10460,32 @@
         <v>0</v>
       </c>
       <c r="U152" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B153" s="9">
         <v>46161.58116828704</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46161.84644222222</v>
+        <v>46223.584198055556</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H153" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H153" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
         <v>46307</v>
@@ -10395,13 +10500,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10411,25 +10516,27 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B154" s="5">
         <v>46161.63912622685</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46161.84643929398</v>
+        <v>46223.5841919213</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H154" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I154" s="6"/>
       <c r="J154" s="5">
         <v>46307</v>
@@ -10444,10 +10551,10 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10460,25 +10567,27 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B155" s="9">
         <v>46161.63913737268</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46161.84643643518</v>
+        <v>46223.5841909375</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H155" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H155" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I155" s="10"/>
       <c r="J155" s="9">
         <v>46307</v>
@@ -10493,10 +10602,10 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>26</v>
@@ -10509,25 +10618,27 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B156" s="5">
         <v>46161.63914719908</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46161.846433321756</v>
+        <v>46223.58419032407</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H156" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I156" s="6"/>
       <c r="J156" s="5">
         <v>46307</v>
@@ -10542,10 +10653,10 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>26</v>
@@ -10558,25 +10669,27 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B157" s="9">
         <v>46161.639157557875</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46161.84643013889</v>
+        <v>46223.584189699075</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H157" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H157" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I157" s="10"/>
       <c r="J157" s="9">
         <v>46307</v>
@@ -10591,10 +10704,10 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>26</v>
@@ -10607,25 +10720,27 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B158" s="5">
         <v>46161.6391721875</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46161.84642646991</v>
+        <v>46223.58418898148</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H158" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H158" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I158" s="6"/>
       <c r="J158" s="5">
         <v>46307</v>
@@ -10640,10 +10755,10 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10656,25 +10771,27 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B159" s="9">
         <v>46161.639187395835</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46161.84642321759</v>
+        <v>46223.58418828704</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H159" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H159" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I159" s="10"/>
       <c r="J159" s="9">
         <v>46307</v>
@@ -10689,10 +10806,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>26</v>
@@ -10705,25 +10822,27 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B160" s="5">
         <v>46161.639195289354</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46161.846420138885</v>
+        <v>46223.584187650464</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H160" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I160" s="6"/>
       <c r="J160" s="5">
         <v>46307</v>
@@ -10738,10 +10857,10 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>26</v>
@@ -10754,25 +10873,27 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B161" s="9">
         <v>46161.63920550926</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46161.846413113424</v>
+        <v>46223.58418706019</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H161" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H161" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I161" s="10"/>
       <c r="J161" s="9">
         <v>46307</v>
@@ -10787,10 +10908,10 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>26</v>
@@ -10803,25 +10924,27 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B162" s="5">
         <v>46161.63921432871</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46161.84641241898</v>
+        <v>46223.58418637731</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H162" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I162" s="6"/>
       <c r="J162" s="5">
         <v>46307</v>
@@ -10836,13 +10959,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10852,25 +10975,27 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B163" s="9">
         <v>46161.58117752315</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46161.84660503472</v>
+        <v>46223.58491697916</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H163" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H163" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I163" s="9">
         <v>46309</v>
       </c>
@@ -10887,13 +11012,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q163" s="9">
         <v>46309</v>
@@ -10908,30 +11033,32 @@
         <v>0</v>
       </c>
       <c r="U163" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B164" s="5">
         <v>46161.58118137732</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46161.84658016203</v>
+        <v>46223.584646874995</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H164" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H164" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I164" s="5">
         <v>46309</v>
       </c>
@@ -10948,13 +11075,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -10964,25 +11091,27 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B165" s="9">
         <v>46161.639253761576</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46161.846577187505</v>
+        <v>46223.584646261574</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H165" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H165" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I165" s="9">
         <v>46309</v>
       </c>
@@ -10999,10 +11128,10 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P165" s="10" t="s">
         <v>26</v>
@@ -11015,25 +11144,27 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B166" s="5">
         <v>46161.63928710648</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46161.84657417824</v>
+        <v>46223.5846455787</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H166" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H166" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I166" s="5">
         <v>46309</v>
       </c>
@@ -11050,10 +11181,10 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11066,25 +11197,27 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B167" s="9">
         <v>46161.63929736111</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46161.84657136574</v>
+        <v>46223.58464490741</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H167" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H167" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I167" s="9">
         <v>46309</v>
       </c>
@@ -11101,10 +11234,10 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P167" s="10" t="s">
         <v>26</v>
@@ -11117,25 +11250,27 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B168" s="5">
         <v>46161.6393071412</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46161.84656841435</v>
+        <v>46223.58464418982</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H168" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H168" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I168" s="5">
         <v>46309</v>
       </c>
@@ -11152,10 +11287,10 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>26</v>
@@ -11168,25 +11303,27 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B169" s="9">
         <v>46161.639315625</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46161.84656539352</v>
+        <v>46223.58464350694</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H169" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H169" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I169" s="9">
         <v>46309</v>
       </c>
@@ -11203,10 +11340,10 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11219,25 +11356,27 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B170" s="5">
         <v>46161.63932686343</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46161.846562754625</v>
+        <v>46223.58464282408</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H170" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H170" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I170" s="5">
         <v>46309</v>
       </c>
@@ -11254,10 +11393,10 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11270,25 +11409,27 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B171" s="9">
         <v>46161.63933708333</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46161.8465599537</v>
+        <v>46223.584642118054</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H171" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H171" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I171" s="9">
         <v>46309</v>
       </c>
@@ -11305,10 +11446,10 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>26</v>
@@ -11321,25 +11462,27 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B172" s="5">
         <v>46161.63935484954</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46161.846553807874</v>
+        <v>46223.58464141204</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H172" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H172" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I172" s="5">
         <v>46309</v>
       </c>
@@ -11356,10 +11499,10 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>26</v>
@@ -11372,25 +11515,27 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B173" s="9">
         <v>46161.63936453704</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46161.84655313657</v>
+        <v>46223.58464068287</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H173" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H173" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I173" s="9">
         <v>46309</v>
       </c>
@@ -11407,13 +11552,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11423,7 +11568,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B174" s="5">
         <v>46161.5811852662</v>
@@ -11433,7 +11578,7 @@
         <v>46161.84092732639</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>25</v>
@@ -11457,7 +11602,7 @@
         <v>26</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>26</v>
@@ -11470,7 +11615,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B175" s="9">
         <v>46161.581188020835</v>
@@ -11480,16 +11625,16 @@
         <v>46161.84675815972</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I175" s="9">
         <v>46310</v>
@@ -11507,13 +11652,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q175" s="9">
         <v>46310</v>
@@ -11528,12 +11673,12 @@
         <v>0</v>
       </c>
       <c r="U175" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B176" s="5">
         <v>46161.581192673606</v>
@@ -11543,16 +11688,16 @@
         <v>46161.846749351855</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I176" s="5">
         <v>46310</v>
@@ -11570,13 +11715,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11586,7 +11731,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B177" s="9">
         <v>46161.63982708333</v>
@@ -11596,16 +11741,16 @@
         <v>46161.84674655093</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I177" s="9">
         <v>46310</v>
@@ -11623,13 +11768,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11639,7 +11784,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B178" s="5">
         <v>46161.63983532407</v>
@@ -11649,16 +11794,16 @@
         <v>46161.846743981485</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I178" s="5">
         <v>46310</v>
@@ -11676,13 +11821,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11692,7 +11837,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B179" s="9">
         <v>46161.63984421296</v>
@@ -11702,16 +11847,16 @@
         <v>46161.84674143518</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I179" s="9">
         <v>46310</v>
@@ -11729,13 +11874,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11745,7 +11890,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B180" s="5">
         <v>46161.63985878472</v>
@@ -11755,16 +11900,16 @@
         <v>46161.846738541666</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I180" s="5">
         <v>46310</v>
@@ -11782,13 +11927,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11798,7 +11943,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B181" s="9">
         <v>46161.63986780093</v>
@@ -11808,16 +11953,16 @@
         <v>46161.84673559028</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I181" s="9">
         <v>46310</v>
@@ -11835,13 +11980,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11851,7 +11996,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B182" s="5">
         <v>46161.639875</v>
@@ -11861,16 +12006,16 @@
         <v>46161.84673289352</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I182" s="5">
         <v>46310</v>
@@ -11888,13 +12033,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -11904,7 +12049,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B183" s="9">
         <v>46161.63988342593</v>
@@ -11914,16 +12059,16 @@
         <v>46161.84672489583</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I183" s="9">
         <v>46310</v>
@@ -11941,13 +12086,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -11957,7 +12102,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B184" s="5">
         <v>46161.63989143519</v>
@@ -11967,16 +12112,16 @@
         <v>46161.84672420139</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I184" s="5">
         <v>46310</v>
@@ -11994,13 +12139,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12010,7 +12155,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B185" s="9">
         <v>46161.639899340276</v>
@@ -12020,16 +12165,16 @@
         <v>46161.84672340278</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I185" s="9">
         <v>46310</v>
@@ -12047,13 +12192,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12063,25 +12208,27 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B186" s="5">
         <v>46161.5811965162</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46161.84690181713</v>
+        <v>46223.585025</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H186" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I186" s="5">
         <v>46311</v>
       </c>
@@ -12098,13 +12245,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q186" s="5">
         <v>46311</v>
@@ -12119,30 +12266,32 @@
         <v>0</v>
       </c>
       <c r="U186" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B187" s="9">
         <v>46161.58120002315</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46161.84690336806</v>
+        <v>46223.58481888889</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H187" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H187" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I187" s="9">
         <v>46311</v>
       </c>
@@ -12159,13 +12308,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12175,25 +12324,27 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B188" s="5">
         <v>46161.63993424768</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46161.84690038195</v>
+        <v>46223.58481829861</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H188" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H188" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I188" s="5">
         <v>46311</v>
       </c>
@@ -12210,13 +12361,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12226,25 +12377,27 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B189" s="9">
         <v>46161.6399947801</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46161.84689746528</v>
+        <v>46223.584817662035</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H189" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H189" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I189" s="9">
         <v>46311</v>
       </c>
@@ -12261,13 +12414,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12277,25 +12430,27 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B190" s="5">
         <v>46161.640004444445</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46161.84689446759</v>
+        <v>46223.584817083334</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H190" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H190" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I190" s="5">
         <v>46311</v>
       </c>
@@ -12312,13 +12467,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12328,25 +12483,27 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B191" s="9">
         <v>46161.64001501157</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46161.84689137731</v>
+        <v>46223.58481644676</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H191" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H191" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I191" s="9">
         <v>46311</v>
       </c>
@@ -12363,13 +12520,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12379,25 +12536,27 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B192" s="5">
         <v>46161.640023831016</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46161.846888796295</v>
+        <v>46223.58481584491</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H192" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I192" s="5">
         <v>46311</v>
       </c>
@@ -12414,13 +12573,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12430,25 +12589,27 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B193" s="9">
         <v>46161.640038310186</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46161.84688606481</v>
+        <v>46223.58481525463</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H193" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H193" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I193" s="9">
         <v>46311</v>
       </c>
@@ -12465,13 +12626,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12481,25 +12642,27 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B194" s="5">
         <v>46161.64004747685</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46161.846882557875</v>
+        <v>46223.58481465278</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H194" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H194" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I194" s="5">
         <v>46311</v>
       </c>
@@ -12516,13 +12679,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12532,25 +12695,27 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B195" s="9">
         <v>46161.64005649305</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46161.84687957176</v>
+        <v>46223.5848140625</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H195" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="H195" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I195" s="9">
         <v>46311</v>
       </c>
@@ -12567,13 +12732,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12583,25 +12748,27 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B196" s="5">
         <v>46161.64006346065</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46161.846870243055</v>
+        <v>46223.58481342593</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H196" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H196" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="I196" s="5">
         <v>46311</v>
       </c>
@@ -12618,13 +12785,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12634,7 +12801,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B197" s="9">
         <v>46161.58120399306</v>
@@ -12644,16 +12811,16 @@
         <v>46161.84710645833</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H197" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I197" s="10"/>
       <c r="J197" s="9">
@@ -12669,13 +12836,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q197" s="9">
         <v>46316</v>
@@ -12690,12 +12857,12 @@
         <v>0</v>
       </c>
       <c r="U197" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B198" s="5">
         <v>46161.58120755787</v>
@@ -12705,16 +12872,16 @@
         <v>46161.847077812505</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -12730,13 +12897,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12746,7 +12913,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B199" s="9">
         <v>46161.6401252662</v>
@@ -12756,16 +12923,16 @@
         <v>46161.84707505787</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -12781,13 +12948,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12797,7 +12964,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B200" s="5">
         <v>46161.64014137731</v>
@@ -12807,16 +12974,16 @@
         <v>46161.847072476856</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -12832,13 +12999,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -12848,7 +13015,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B201" s="9">
         <v>46161.64015293981</v>
@@ -12858,16 +13025,16 @@
         <v>46161.84706930556</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -12883,13 +13050,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -12899,7 +13066,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B202" s="5">
         <v>46161.64016740741</v>
@@ -12909,16 +13076,16 @@
         <v>46161.847066608796</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -12934,13 +13101,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -12950,7 +13117,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B203" s="9">
         <v>46161.640203877316</v>
@@ -12960,16 +13127,16 @@
         <v>46161.84706402778</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -12985,13 +13152,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13001,7 +13168,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B204" s="5">
         <v>46161.64021510417</v>
@@ -13011,16 +13178,16 @@
         <v>46161.84706112268</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13036,13 +13203,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13052,7 +13219,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B205" s="9">
         <v>46161.64022702546</v>
@@ -13062,16 +13229,16 @@
         <v>46161.847053425925</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13087,13 +13254,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13103,7 +13270,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B206" s="5">
         <v>46161.64023784723</v>
@@ -13113,16 +13280,16 @@
         <v>46161.8470527662</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13138,13 +13305,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13154,7 +13321,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B207" s="9">
         <v>46161.64025311342</v>
@@ -13164,16 +13331,16 @@
         <v>46161.84705210648</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13189,13 +13356,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13205,7 +13372,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B208" s="5">
         <v>46161.58121466435</v>
@@ -13215,16 +13382,16 @@
         <v>46161.84730193287</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I208" s="5">
         <v>46317</v>
@@ -13242,13 +13409,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q208" s="5">
         <v>46317</v>
@@ -13263,12 +13430,12 @@
         <v>0</v>
       </c>
       <c r="U208" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B209" s="9">
         <v>46161.58125732639</v>
@@ -13278,16 +13445,16 @@
         <v>46161.84728091436</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I209" s="10"/>
       <c r="J209" s="9">
@@ -13303,13 +13470,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13319,7 +13486,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B210" s="5">
         <v>46161.640307905094</v>
@@ -13329,16 +13496,16 @@
         <v>46161.84727769676</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13354,10 +13521,10 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>26</v>
@@ -13370,7 +13537,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B211" s="9">
         <v>46161.64031635417</v>
@@ -13380,16 +13547,16 @@
         <v>46161.84727525463</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I211" s="10"/>
       <c r="J211" s="9">
@@ -13405,10 +13572,10 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>26</v>
@@ -13421,7 +13588,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B212" s="5">
         <v>46161.64032832176</v>
@@ -13431,16 +13598,16 @@
         <v>46161.84727247685</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13456,10 +13623,10 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>26</v>
@@ -13472,7 +13639,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B213" s="9">
         <v>46161.640337986115</v>
@@ -13482,16 +13649,16 @@
         <v>46161.84726945602</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I213" s="10"/>
       <c r="J213" s="9">
@@ -13507,10 +13674,10 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>26</v>
@@ -13523,7 +13690,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B214" s="5">
         <v>46161.64035862268</v>
@@ -13533,16 +13700,16 @@
         <v>46161.84726638889</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13558,10 +13725,10 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13574,7 +13741,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B215" s="9">
         <v>46161.64036773148</v>
@@ -13584,16 +13751,16 @@
         <v>46161.84726359954</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I215" s="10"/>
       <c r="J215" s="9">
@@ -13609,10 +13776,10 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13625,7 +13792,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B216" s="5">
         <v>46161.64037657407</v>
@@ -13635,16 +13802,16 @@
         <v>46161.84726060185</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13660,10 +13827,10 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>26</v>
@@ -13676,7 +13843,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B217" s="9">
         <v>46161.64038473379</v>
@@ -13686,16 +13853,16 @@
         <v>46161.847254699074</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I217" s="10"/>
       <c r="J217" s="9">
@@ -13711,10 +13878,10 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>26</v>
@@ -13727,7 +13894,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B218" s="5">
         <v>46161.64039350694</v>
@@ -13737,16 +13904,16 @@
         <v>46161.8472540625</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -13762,10 +13929,10 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>26</v>
@@ -13778,7 +13945,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B219" s="9">
         <v>46161.581262824075</v>
@@ -13788,7 +13955,7 @@
         <v>46161.84801045139</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>25</v>
@@ -13812,7 +13979,7 @@
         <v>26</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>26</v>
@@ -13825,7 +13992,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B220" s="5">
         <v>46161.58126615741</v>
@@ -13835,16 +14002,16 @@
         <v>46161.84764756945</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="I220" s="5">
         <v>46318</v>
@@ -13862,13 +14029,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q220" s="5">
         <v>46318</v>
@@ -13883,12 +14050,12 @@
         <v>0</v>
       </c>
       <c r="U220" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B221" s="9">
         <v>46161.581270821756</v>
@@ -13898,7 +14065,7 @@
         <v>46198.80656221065</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -13925,13 +14092,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q221" s="9">
         <v>46318</v>
@@ -13946,7 +14113,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -4804,7 +4804,7 @@
         <v>46198.80749446759</v>
       </c>
       <c r="D49" s="9">
-        <v>46216.19023893519</v>
+        <v>46224.182198888884</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>80</v>
@@ -4848,8 +4848,8 @@
       <c r="R49" s="9">
         <v>46223</v>
       </c>
-      <c r="S49" s="11" t="s">
-        <v>82</v>
+      <c r="S49" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -784,7 +784,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 </t>
+    <t>OT 4332 -  ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214937509401251</t>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46161.845178449075</v>
+        <v>46224.87838555555</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>229</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -784,7 +784,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4332 -  ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4332 -  ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1214937509401251</t>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46224.87838555555</v>
+        <v>46225.00961248843</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>229</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -784,7 +784,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4332 -  ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1214937509401251</t>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46225.00961248843</v>
+        <v>46225.58945407407</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>229</v>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="452">
   <si>
     <t>50001555 - "ZITRON COLOMBIA ARIS MINING SEGOVIA"</t>
   </si>
@@ -316,6 +316,9 @@
     <t>propuesta nucleo rodete ot 4332</t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
     <t>nespinoza@zitron.com</t>
   </si>
   <si>
@@ -784,7 +787,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4332 -  ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+    <t>OT 4332 -  ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214937509401251</t>
@@ -2878,7 +2881,7 @@
         <v>76</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I17" s="9">
         <v>46164</v>
@@ -2902,7 +2905,7 @@
         <v>57</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="9">
         <v>46164</v>
@@ -2922,7 +2925,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" s="5">
         <v>46161.58079903935</v>
@@ -2934,7 +2937,7 @@
         <v>46223.58333158564</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2943,7 +2946,7 @@
         <v>76</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I18" s="5">
         <v>46224</v>
@@ -2964,10 +2967,10 @@
         <v>66</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2976,7 +2979,7 @@
         <v>46225</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2987,7 +2990,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B19" s="9">
         <v>46161.58080373843</v>
@@ -2999,7 +3002,7 @@
         <v>46223.58332738426</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -3008,7 +3011,7 @@
         <v>76</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I19" s="9">
         <v>46224</v>
@@ -3029,10 +3032,10 @@
         <v>66</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="9">
         <v>46224</v>
@@ -3041,7 +3044,7 @@
         <v>46225</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -3052,7 +3055,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46161.58080740741</v>
@@ -3064,7 +3067,7 @@
         <v>46223.5833241088</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3073,7 +3076,7 @@
         <v>76</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I20" s="5">
         <v>46224</v>
@@ -3094,10 +3097,10 @@
         <v>66</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -3106,7 +3109,7 @@
         <v>46225</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -3117,7 +3120,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" s="9">
         <v>46161.580810740736</v>
@@ -3129,7 +3132,7 @@
         <v>46223.58331811342</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -3138,7 +3141,7 @@
         <v>76</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I21" s="9">
         <v>46224</v>
@@ -3159,10 +3162,10 @@
         <v>66</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="9">
         <v>46224</v>
@@ -3171,7 +3174,7 @@
         <v>46225</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -3182,7 +3185,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46161.58064796297</v>
@@ -3192,7 +3195,7 @@
         <v>46211.83005701389</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -3216,7 +3219,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -3229,7 +3232,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B23" s="9">
         <v>46161.58081472223</v>
@@ -3241,16 +3244,16 @@
         <v>46209.56551446759</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I23" s="9">
         <v>46168</v>
@@ -3268,13 +3271,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="9">
         <v>46168</v>
@@ -3294,7 +3297,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46161.580819016206</v>
@@ -3306,16 +3309,16 @@
         <v>46209.56543981482</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I24" s="5">
         <v>46168</v>
@@ -3333,13 +3336,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3350,12 +3353,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46161.58082350694</v>
@@ -3367,16 +3370,16 @@
         <v>46209.565488576394</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I25" s="9">
         <v>46170</v>
@@ -3394,13 +3397,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3411,12 +3414,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46161.58082824074</v>
@@ -3428,16 +3431,16 @@
         <v>46209.56600694444</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46168</v>
@@ -3455,13 +3458,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q26" s="5">
         <v>46168</v>
@@ -3481,7 +3484,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46161.5808325463</v>
@@ -3493,16 +3496,16 @@
         <v>46209.56565858796</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I27" s="9">
         <v>46168</v>
@@ -3520,13 +3523,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3537,12 +3540,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46161.580836967594</v>
@@ -3554,16 +3557,16 @@
         <v>46209.56570685185</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46170</v>
@@ -3581,13 +3584,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3598,12 +3601,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="9">
         <v>46161.58084165509</v>
@@ -3613,16 +3616,16 @@
         <v>46198.805784641205</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I29" s="9">
         <v>46156</v>
@@ -3640,13 +3643,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q29" s="9">
         <v>46156</v>
@@ -3661,12 +3664,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46161.58084603009</v>
@@ -3678,16 +3681,16 @@
         <v>46198.80572795139</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46156</v>
@@ -3705,13 +3708,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3722,12 +3725,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46161.580850439816</v>
@@ -3737,16 +3740,16 @@
         <v>46198.80573190972</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3764,13 +3767,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3781,12 +3784,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46161.58085503472</v>
@@ -3798,16 +3801,16 @@
         <v>46198.80577622685</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I32" s="5">
         <v>46176</v>
@@ -3825,13 +3828,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3842,12 +3845,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46161.58085940972</v>
@@ -3859,16 +3862,16 @@
         <v>46211.830060266206</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I33" s="9">
         <v>46226</v>
@@ -3886,13 +3889,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q33" s="9">
         <v>46226</v>
@@ -3912,7 +3915,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46161.58086364584</v>
@@ -3924,16 +3927,16 @@
         <v>46205.61008960648</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I34" s="5">
         <v>46226</v>
@@ -3951,13 +3954,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3968,12 +3971,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46161.58086832176</v>
@@ -3985,16 +3988,16 @@
         <v>46211.83003016203</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I35" s="9">
         <v>46230</v>
@@ -4012,13 +4015,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -4029,12 +4032,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46161.58087322916</v>
@@ -4046,16 +4049,16 @@
         <v>46209.804952569444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -4073,10 +4076,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -4099,7 +4102,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="9">
         <v>46161.580931018514</v>
@@ -4111,16 +4114,16 @@
         <v>46205.610248032404</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I37" s="9">
         <v>46226</v>
@@ -4138,13 +4141,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4154,7 +4157,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46161.58093646991</v>
@@ -4166,16 +4169,16 @@
         <v>46209.809419513884</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -4193,13 +4196,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4209,7 +4212,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46161.580941099535</v>
@@ -4221,16 +4224,16 @@
         <v>46209.62288859954</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I39" s="9">
         <v>46225</v>
@@ -4248,10 +4251,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4274,7 +4277,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46161.58094532407</v>
@@ -4286,16 +4289,16 @@
         <v>46209.622784444444</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I40" s="5">
         <v>46225</v>
@@ -4313,13 +4316,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4329,7 +4332,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46161.58094997685</v>
@@ -4341,16 +4344,16 @@
         <v>46209.62283091435</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I41" s="9">
         <v>46234</v>
@@ -4368,13 +4371,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4384,7 +4387,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46161.58095447917</v>
@@ -4394,16 +4397,16 @@
         <v>46209.62284077547</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I42" s="5">
         <v>46265</v>
@@ -4421,10 +4424,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4437,7 +4440,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>46161.58095743056</v>
@@ -4449,16 +4452,16 @@
         <v>46209.81259914352</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I43" s="9">
         <v>46226</v>
@@ -4476,10 +4479,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4502,7 +4505,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46161.58096091435</v>
@@ -4514,16 +4517,16 @@
         <v>46209.81220270833</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I44" s="5">
         <v>46226</v>
@@ -4541,13 +4544,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4557,7 +4560,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46161.580964988425</v>
@@ -4569,16 +4572,16 @@
         <v>46209.81257327546</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I45" s="9">
         <v>46230</v>
@@ -4596,13 +4599,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4612,7 +4615,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46161.58065239583</v>
@@ -4624,7 +4627,7 @@
         <v>46210.52870142361</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4648,7 +4651,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4665,7 +4668,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" s="9">
         <v>46161.580969780094</v>
@@ -4677,16 +4680,16 @@
         <v>46197.70504644676</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I47" s="9">
         <v>46164</v>
@@ -4704,13 +4707,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>62</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q47" s="9">
         <v>46164</v>
@@ -4730,7 +4733,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46161.580975069446</v>
@@ -4742,16 +4745,16 @@
         <v>46221.17370061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46216</v>
@@ -4769,13 +4772,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46216</v>
@@ -4795,7 +4798,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46161.58098100695</v>
@@ -4807,16 +4810,16 @@
         <v>46224.182198888884</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I49" s="9">
         <v>46223</v>
@@ -4834,13 +4837,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q49" s="9">
         <v>46223</v>
@@ -4860,7 +4863,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46161.58099116899</v>
@@ -4870,16 +4873,16 @@
         <v>46161.84476310185</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I50" s="5">
         <v>46308</v>
@@ -4897,10 +4900,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4918,12 +4921,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46161.58099418982</v>
@@ -4933,16 +4936,16 @@
         <v>46161.84476607639</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4958,13 +4961,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4974,7 +4977,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46161.63966489583</v>
@@ -4984,16 +4987,16 @@
         <v>46161.844763472225</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -5009,13 +5012,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5025,7 +5028,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46161.63967261574</v>
@@ -5035,16 +5038,16 @@
         <v>46161.84476069444</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5060,13 +5063,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5076,7 +5079,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46161.63968388889</v>
@@ -5086,16 +5089,16 @@
         <v>46161.84475773148</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5111,13 +5114,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5127,7 +5130,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="9">
         <v>46161.63969275463</v>
@@ -5137,16 +5140,16 @@
         <v>46161.84475471065</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5162,13 +5165,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5178,7 +5181,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46161.639705208334</v>
@@ -5188,16 +5191,16 @@
         <v>46161.84475174769</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5213,13 +5216,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5229,7 +5232,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B57" s="9">
         <v>46161.639715474535</v>
@@ -5239,16 +5242,16 @@
         <v>46161.84474863426</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5264,13 +5267,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5280,7 +5283,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46161.63972679398</v>
@@ -5290,16 +5293,16 @@
         <v>46161.84474503472</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5315,13 +5318,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5331,7 +5334,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B59" s="9">
         <v>46161.63974304398</v>
@@ -5341,16 +5344,16 @@
         <v>46161.84473834491</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5366,13 +5369,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5382,7 +5385,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46161.63975269676</v>
@@ -5392,16 +5395,16 @@
         <v>46161.84473753472</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5417,13 +5420,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5433,7 +5436,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B61" s="9">
         <v>46161.58099818287</v>
@@ -5443,7 +5446,7 @@
         <v>46217.592142650465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5467,7 +5470,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5480,7 +5483,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B62" s="5">
         <v>46161.58100145833</v>
@@ -5490,16 +5493,16 @@
         <v>46217.59224327546</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46239</v>
@@ -5517,13 +5520,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q62" s="5">
         <v>46239</v>
@@ -5543,7 +5546,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B63" s="9">
         <v>46161.58100614583</v>
@@ -5553,16 +5556,16 @@
         <v>46217.59214284722</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I63" s="9">
         <v>46241</v>
@@ -5580,13 +5583,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="9">
         <v>46241</v>
@@ -5601,12 +5604,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B64" s="5">
         <v>46161.58101638889</v>
@@ -5616,16 +5619,16 @@
         <v>46209.804944710646</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I64" s="5">
         <v>46239</v>
@@ -5643,13 +5646,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q64" s="5">
         <v>46239</v>
@@ -5669,7 +5672,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B65" s="9">
         <v>46161.58102099537</v>
@@ -5679,16 +5682,16 @@
         <v>46161.84491503472</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I65" s="9">
         <v>46241</v>
@@ -5706,13 +5709,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q65" s="9">
         <v>46241</v>
@@ -5727,12 +5730,12 @@
         <v>0</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B66" s="5">
         <v>46161.581024722225</v>
@@ -5742,16 +5745,16 @@
         <v>46209.81259190972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>46239</v>
@@ -5769,13 +5772,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q66" s="5">
         <v>46239</v>
@@ -5795,7 +5798,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B67" s="9">
         <v>46161.58102864583</v>
@@ -5805,16 +5808,16 @@
         <v>46161.844914270834</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I67" s="9">
         <v>46241</v>
@@ -5832,13 +5835,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q67" s="9">
         <v>46241</v>
@@ -5853,12 +5856,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B68" s="5">
         <v>46161.58103207176</v>
@@ -5868,7 +5871,7 @@
         <v>46161.797785821764</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5892,7 +5895,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5905,26 +5908,26 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B69" s="9">
         <v>46161.58103457176</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46225.58945407407</v>
+        <v>46225.86189390047</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I69" s="9">
         <v>46245</v>
@@ -5942,13 +5945,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q69" s="9">
         <v>46245</v>
@@ -5963,12 +5966,12 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
         <v>46161.58103962963</v>
@@ -5978,16 +5981,16 @@
         <v>46161.845147071755</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I70" s="5">
         <v>46245</v>
@@ -6005,13 +6008,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6021,7 +6024,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
         <v>46161.582011805556</v>
@@ -6031,16 +6034,16 @@
         <v>46161.84514348379</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I71" s="9">
         <v>46245</v>
@@ -6058,13 +6061,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6074,7 +6077,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46161.58202383102</v>
@@ -6084,16 +6087,16 @@
         <v>46161.845140324076</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I72" s="5">
         <v>46245</v>
@@ -6111,13 +6114,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6127,7 +6130,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
         <v>46161.582662650464</v>
@@ -6137,16 +6140,16 @@
         <v>46161.845136655094</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I73" s="9">
         <v>46245</v>
@@ -6164,13 +6167,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6180,7 +6183,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46161.58267322917</v>
@@ -6190,16 +6193,16 @@
         <v>46161.845133518524</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I74" s="5">
         <v>46245</v>
@@ -6217,13 +6220,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6233,7 +6236,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B75" s="9">
         <v>46161.58270134259</v>
@@ -6243,16 +6246,16 @@
         <v>46161.84513074074</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I75" s="9">
         <v>46245</v>
@@ -6270,13 +6273,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6286,7 +6289,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5">
         <v>46161.58271427083</v>
@@ -6296,16 +6299,16 @@
         <v>46161.84512803241</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I76" s="5">
         <v>46245</v>
@@ -6323,13 +6326,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6339,7 +6342,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
         <v>46161.58272651621</v>
@@ -6349,16 +6352,16 @@
         <v>46161.84512407407</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I77" s="9">
         <v>46245</v>
@@ -6376,13 +6379,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6392,7 +6395,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B78" s="5">
         <v>46161.58277962963</v>
@@ -6402,16 +6405,16 @@
         <v>46161.845117916666</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I78" s="5">
         <v>46245</v>
@@ -6429,13 +6432,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6445,7 +6448,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B79" s="9">
         <v>46161.58279046296</v>
@@ -6455,16 +6458,16 @@
         <v>46161.84511721064</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I79" s="9">
         <v>46245</v>
@@ -6482,13 +6485,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6498,7 +6501,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B80" s="5">
         <v>46161.58104538194</v>
@@ -6508,16 +6511,16 @@
         <v>46161.845344814814</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I80" s="5">
         <v>46254</v>
@@ -6535,13 +6538,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q80" s="5">
         <v>46254</v>
@@ -6556,12 +6559,12 @@
         <v>0</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B81" s="9">
         <v>46161.58104903935</v>
@@ -6571,16 +6574,16 @@
         <v>46198.80752025463</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I81" s="9">
         <v>46254</v>
@@ -6598,13 +6601,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6614,7 +6617,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B82" s="5">
         <v>46161.582834120374</v>
@@ -6624,16 +6627,16 @@
         <v>46161.84533628472</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I82" s="5">
         <v>46254</v>
@@ -6651,13 +6654,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6667,7 +6670,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B83" s="9">
         <v>46161.58286459491</v>
@@ -6677,16 +6680,16 @@
         <v>46161.84533336805</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I83" s="9">
         <v>46254</v>
@@ -6704,13 +6707,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6720,7 +6723,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B84" s="5">
         <v>46161.58287381944</v>
@@ -6730,16 +6733,16 @@
         <v>46161.84533065972</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I84" s="5">
         <v>46254</v>
@@ -6757,13 +6760,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6773,7 +6776,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B85" s="9">
         <v>46161.58288365741</v>
@@ -6783,16 +6786,16 @@
         <v>46161.84532790509</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I85" s="9">
         <v>46254</v>
@@ -6810,13 +6813,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6826,7 +6829,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B86" s="5">
         <v>46161.58289255787</v>
@@ -6836,16 +6839,16 @@
         <v>46161.84532486111</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I86" s="5">
         <v>46254</v>
@@ -6863,13 +6866,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6879,7 +6882,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B87" s="9">
         <v>46161.58292542824</v>
@@ -6889,16 +6892,16 @@
         <v>46161.84532211805</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I87" s="9">
         <v>46254</v>
@@ -6916,13 +6919,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6932,7 +6935,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B88" s="5">
         <v>46161.58293696759</v>
@@ -6942,16 +6945,16 @@
         <v>46161.84531927083</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I88" s="5">
         <v>46254</v>
@@ -6969,13 +6972,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6985,7 +6988,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B89" s="9">
         <v>46161.58295282407</v>
@@ -6995,16 +6998,16 @@
         <v>46161.84531311343</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I89" s="9">
         <v>46254</v>
@@ -7022,13 +7025,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7038,7 +7041,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B90" s="5">
         <v>46161.58296773148</v>
@@ -7048,16 +7051,16 @@
         <v>46161.84531243055</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I90" s="5">
         <v>46254</v>
@@ -7075,13 +7078,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7091,7 +7094,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B91" s="9">
         <v>46161.581053761576</v>
@@ -7101,16 +7104,16 @@
         <v>46161.84552644676</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -7128,13 +7131,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q91" s="9">
         <v>46274</v>
@@ -7149,12 +7152,12 @@
         <v>0</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B92" s="5">
         <v>46161.58105741898</v>
@@ -7164,16 +7167,16 @@
         <v>46198.80752082176</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -7191,13 +7194,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7207,7 +7210,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B93" s="9">
         <v>46161.583039942125</v>
@@ -7217,16 +7220,16 @@
         <v>46161.84550880787</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I93" s="9">
         <v>46274</v>
@@ -7244,13 +7247,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7260,7 +7263,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B94" s="5">
         <v>46161.58305715278</v>
@@ -7270,16 +7273,16 @@
         <v>46161.845505324076</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I94" s="5">
         <v>46274</v>
@@ -7297,13 +7300,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7313,7 +7316,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B95" s="9">
         <v>46161.583076689814</v>
@@ -7323,16 +7326,16 @@
         <v>46161.84550258102</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I95" s="9">
         <v>46274</v>
@@ -7350,13 +7353,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7366,7 +7369,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B96" s="5">
         <v>46161.58308886574</v>
@@ -7376,16 +7379,16 @@
         <v>46161.84549928241</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I96" s="5">
         <v>46274</v>
@@ -7403,13 +7406,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7419,7 +7422,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B97" s="9">
         <v>46161.58310019676</v>
@@ -7429,16 +7432,16 @@
         <v>46161.84549533565</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I97" s="9">
         <v>46274</v>
@@ -7456,13 +7459,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7472,7 +7475,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B98" s="5">
         <v>46161.5831108912</v>
@@ -7482,16 +7485,16 @@
         <v>46161.84549206018</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I98" s="5">
         <v>46274</v>
@@ -7509,13 +7512,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7525,7 +7528,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B99" s="9">
         <v>46161.58312844907</v>
@@ -7535,16 +7538,16 @@
         <v>46161.84548887731</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I99" s="9">
         <v>46274</v>
@@ -7562,13 +7565,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7578,7 +7581,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B100" s="5">
         <v>46161.58300775463</v>
@@ -7588,16 +7591,16 @@
         <v>46161.84548230324</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I100" s="5">
         <v>46274</v>
@@ -7615,13 +7618,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7631,7 +7634,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B101" s="9">
         <v>46161.639501875004</v>
@@ -7641,16 +7644,16 @@
         <v>46161.845481620374</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I101" s="9">
         <v>46274</v>
@@ -7668,13 +7671,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7684,7 +7687,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B102" s="5">
         <v>46161.58110506945</v>
@@ -7694,7 +7697,7 @@
         <v>46161.80776861111</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7718,7 +7721,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7731,7 +7734,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B103" s="9">
         <v>46161.581108530096</v>
@@ -7741,16 +7744,16 @@
         <v>46209.56572255787</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I103" s="9">
         <v>46174</v>
@@ -7768,13 +7771,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q103" s="9">
         <v>46174</v>
@@ -7794,7 +7797,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B104" s="5">
         <v>46161.58111370371</v>
@@ -7804,16 +7807,16 @@
         <v>46209.56550644676</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I104" s="5">
         <v>46282</v>
@@ -7831,13 +7834,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q104" s="5">
         <v>46282</v>
@@ -7857,7 +7860,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B105" s="9">
         <v>46161.581118449074</v>
@@ -7867,16 +7870,16 @@
         <v>46161.84560644676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I105" s="9">
         <v>46301</v>
@@ -7894,13 +7897,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q105" s="9">
         <v>46301</v>
@@ -7915,12 +7918,12 @@
         <v>0</v>
       </c>
       <c r="U105" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B106" s="5">
         <v>46161.58112311343</v>
@@ -7930,16 +7933,16 @@
         <v>46209.62284840278</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I106" s="5">
         <v>46237</v>
@@ -7957,13 +7960,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q106" s="5">
         <v>46237</v>
@@ -7983,7 +7986,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B107" s="9">
         <v>46161.58112702546</v>
@@ -7993,7 +7996,7 @@
         <v>46161.83387362269</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -8017,7 +8020,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -8030,7 +8033,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B108" s="5">
         <v>46161.58112984954</v>
@@ -8040,7 +8043,7 @@
         <v>46223.58492069444</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8049,7 +8052,7 @@
         <v>76</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I108" s="5">
         <v>46276</v>
@@ -8067,13 +8070,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q108" s="5">
         <v>46276</v>
@@ -8088,12 +8091,12 @@
         <v>0</v>
       </c>
       <c r="U108" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B109" s="9">
         <v>46161.581135555556</v>
@@ -8103,7 +8106,7 @@
         <v>46223.58354871528</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8112,7 +8115,7 @@
         <v>76</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I109" s="9">
         <v>46276</v>
@@ -8130,13 +8133,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8146,7 +8149,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B110" s="5">
         <v>46161.58317730324</v>
@@ -8156,7 +8159,7 @@
         <v>46223.58354810185</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8165,7 +8168,7 @@
         <v>76</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I110" s="5">
         <v>46276</v>
@@ -8183,13 +8186,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8199,7 +8202,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B111" s="9">
         <v>46161.58318758102</v>
@@ -8209,7 +8212,7 @@
         <v>46223.58354731482</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8218,7 +8221,7 @@
         <v>76</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I111" s="9">
         <v>46276</v>
@@ -8236,13 +8239,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8252,7 +8255,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B112" s="5">
         <v>46161.5831975926</v>
@@ -8262,7 +8265,7 @@
         <v>46223.583546678245</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8271,7 +8274,7 @@
         <v>76</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I112" s="5">
         <v>46276</v>
@@ -8289,13 +8292,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8305,7 +8308,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B113" s="9">
         <v>46161.58320657407</v>
@@ -8315,7 +8318,7 @@
         <v>46223.58354601852</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8324,7 +8327,7 @@
         <v>76</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I113" s="9">
         <v>46276</v>
@@ -8342,13 +8345,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8358,7 +8361,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B114" s="5">
         <v>46161.58322151621</v>
@@ -8368,7 +8371,7 @@
         <v>46223.583545381945</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8377,7 +8380,7 @@
         <v>76</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I114" s="5">
         <v>46276</v>
@@ -8395,13 +8398,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8411,7 +8414,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B115" s="9">
         <v>46161.58322717593</v>
@@ -8421,7 +8424,7 @@
         <v>46223.583544733796</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8430,7 +8433,7 @@
         <v>76</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I115" s="9">
         <v>46276</v>
@@ -8448,13 +8451,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8464,7 +8467,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B116" s="5">
         <v>46161.58324248843</v>
@@ -8474,7 +8477,7 @@
         <v>46223.583544050925</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8483,7 +8486,7 @@
         <v>76</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I116" s="5">
         <v>46276</v>
@@ -8501,13 +8504,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8517,7 +8520,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B117" s="9">
         <v>46161.58325402778</v>
@@ -8527,7 +8530,7 @@
         <v>46223.58354342592</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8536,7 +8539,7 @@
         <v>76</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I117" s="9">
         <v>46276</v>
@@ -8554,13 +8557,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8570,7 +8573,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B118" s="5">
         <v>46161.58326291667</v>
@@ -8580,7 +8583,7 @@
         <v>46223.5835428125</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8589,7 +8592,7 @@
         <v>76</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I118" s="5">
         <v>46276</v>
@@ -8607,13 +8610,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8623,7 +8626,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B119" s="9">
         <v>46161.58113928241</v>
@@ -8633,7 +8636,7 @@
         <v>46223.58491987269</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8642,7 +8645,7 @@
         <v>76</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I119" s="9">
         <v>46296</v>
@@ -8660,13 +8663,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q119" s="9">
         <v>46296</v>
@@ -8681,12 +8684,12 @@
         <v>0</v>
       </c>
       <c r="U119" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B120" s="5">
         <v>46161.58114282407</v>
@@ -8696,7 +8699,7 @@
         <v>46223.583707557875</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8705,7 +8708,7 @@
         <v>76</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I120" s="5">
         <v>46296</v>
@@ -8723,13 +8726,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8739,7 +8742,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B121" s="9">
         <v>46161.585882430554</v>
@@ -8749,7 +8752,7 @@
         <v>46223.58370696759</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8758,7 +8761,7 @@
         <v>76</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I121" s="9">
         <v>46296</v>
@@ -8776,13 +8779,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8792,7 +8795,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B122" s="5">
         <v>46161.58590298611</v>
@@ -8802,7 +8805,7 @@
         <v>46223.58370635417</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8811,7 +8814,7 @@
         <v>76</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I122" s="5">
         <v>46296</v>
@@ -8829,13 +8832,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8845,7 +8848,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B123" s="9">
         <v>46161.585919861114</v>
@@ -8855,7 +8858,7 @@
         <v>46223.583705717596</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8864,7 +8867,7 @@
         <v>76</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I123" s="9">
         <v>46296</v>
@@ -8882,13 +8885,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8898,7 +8901,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B124" s="5">
         <v>46161.585927175925</v>
@@ -8908,7 +8911,7 @@
         <v>46223.58370516203</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8917,7 +8920,7 @@
         <v>76</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I124" s="5">
         <v>46296</v>
@@ -8935,13 +8938,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8951,7 +8954,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B125" s="9">
         <v>46161.58593310185</v>
@@ -8961,7 +8964,7 @@
         <v>46223.583704375</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8970,7 +8973,7 @@
         <v>76</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I125" s="9">
         <v>46296</v>
@@ -8988,13 +8991,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9004,7 +9007,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B126" s="5">
         <v>46161.58593739584</v>
@@ -9014,7 +9017,7 @@
         <v>46223.58370383102</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9023,7 +9026,7 @@
         <v>76</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I126" s="5">
         <v>46296</v>
@@ -9041,13 +9044,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9057,7 +9060,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B127" s="9">
         <v>46161.58594590278</v>
@@ -9067,7 +9070,7 @@
         <v>46223.58370325231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9076,7 +9079,7 @@
         <v>76</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I127" s="9">
         <v>46296</v>
@@ -9094,13 +9097,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9110,7 +9113,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B128" s="5">
         <v>46161.5859562963</v>
@@ -9120,7 +9123,7 @@
         <v>46223.58370267361</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9129,7 +9132,7 @@
         <v>76</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I128" s="5">
         <v>46296</v>
@@ -9147,13 +9150,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9163,7 +9166,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B129" s="9">
         <v>46161.58618912037</v>
@@ -9173,7 +9176,7 @@
         <v>46223.583702083335</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9182,7 +9185,7 @@
         <v>76</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I129" s="9">
         <v>46296</v>
@@ -9200,13 +9203,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9216,7 +9219,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B130" s="5">
         <v>46161.58114761574</v>
@@ -9226,7 +9229,7 @@
         <v>46223.58491914352</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9235,7 +9238,7 @@
         <v>76</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I130" s="5">
         <v>46300</v>
@@ -9253,13 +9256,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q130" s="5">
         <v>46300</v>
@@ -9274,12 +9277,12 @@
         <v>0</v>
       </c>
       <c r="U130" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B131" s="9">
         <v>46161.58115116898</v>
@@ -9289,7 +9292,7 @@
         <v>46223.58385747686</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9298,7 +9301,7 @@
         <v>76</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I131" s="9">
         <v>46300</v>
@@ -9316,13 +9319,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9332,7 +9335,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B132" s="5">
         <v>46161.58603712963</v>
@@ -9342,7 +9345,7 @@
         <v>46223.58385686342</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9351,7 +9354,7 @@
         <v>76</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I132" s="5">
         <v>46300</v>
@@ -9369,13 +9372,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9385,7 +9388,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B133" s="9">
         <v>46161.586044930555</v>
@@ -9395,7 +9398,7 @@
         <v>46223.58385618056</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9404,7 +9407,7 @@
         <v>76</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I133" s="9">
         <v>46300</v>
@@ -9422,13 +9425,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9438,7 +9441,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B134" s="5">
         <v>46161.58605891204</v>
@@ -9448,7 +9451,7 @@
         <v>46223.583855543984</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9457,7 +9460,7 @@
         <v>76</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I134" s="5">
         <v>46300</v>
@@ -9475,13 +9478,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9491,7 +9494,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B135" s="9">
         <v>46161.58606768519</v>
@@ -9501,7 +9504,7 @@
         <v>46223.5838549537</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9510,7 +9513,7 @@
         <v>76</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I135" s="9">
         <v>46300</v>
@@ -9528,13 +9531,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9544,7 +9547,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B136" s="5">
         <v>46161.58607575232</v>
@@ -9554,7 +9557,7 @@
         <v>46223.58385431713</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9563,7 +9566,7 @@
         <v>76</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I136" s="5">
         <v>46300</v>
@@ -9581,13 +9584,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9597,7 +9600,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B137" s="9">
         <v>46161.586088854165</v>
@@ -9607,7 +9610,7 @@
         <v>46223.583853715274</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9616,7 +9619,7 @@
         <v>76</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I137" s="9">
         <v>46300</v>
@@ -9634,13 +9637,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9650,7 +9653,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B138" s="5">
         <v>46161.58609570602</v>
@@ -9660,7 +9663,7 @@
         <v>46223.58385304398</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9669,7 +9672,7 @@
         <v>76</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I138" s="5">
         <v>46300</v>
@@ -9687,13 +9690,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9703,7 +9706,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B139" s="9">
         <v>46161.586110578704</v>
@@ -9713,7 +9716,7 @@
         <v>46223.58385228009</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9722,7 +9725,7 @@
         <v>76</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I139" s="9">
         <v>46300</v>
@@ -9740,13 +9743,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9756,7 +9759,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B140" s="5">
         <v>46161.58612255787</v>
@@ -9766,7 +9769,7 @@
         <v>46223.58385163195</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9775,7 +9778,7 @@
         <v>76</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I140" s="5">
         <v>46300</v>
@@ -9793,13 +9796,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9809,7 +9812,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B141" s="9">
         <v>46161.58115643519</v>
@@ -9819,7 +9822,7 @@
         <v>46223.58491846065</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9828,7 +9831,7 @@
         <v>76</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I141" s="9">
         <v>46303</v>
@@ -9846,13 +9849,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q141" s="9">
         <v>46303</v>
@@ -9867,12 +9870,12 @@
         <v>0</v>
       </c>
       <c r="U141" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B142" s="5">
         <v>46161.58115993056</v>
@@ -9882,7 +9885,7 @@
         <v>46223.583971608794</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9891,7 +9894,7 @@
         <v>76</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I142" s="5">
         <v>46303</v>
@@ -9909,13 +9912,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9925,7 +9928,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B143" s="9">
         <v>46161.58622641204</v>
@@ -9935,7 +9938,7 @@
         <v>46223.583970949076</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9944,7 +9947,7 @@
         <v>76</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I143" s="9">
         <v>46303</v>
@@ -9962,13 +9965,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9978,7 +9981,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B144" s="5">
         <v>46161.586235995375</v>
@@ -9988,7 +9991,7 @@
         <v>46223.583970277774</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9997,7 +10000,7 @@
         <v>76</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I144" s="5">
         <v>46303</v>
@@ -10015,13 +10018,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10031,7 +10034,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B145" s="9">
         <v>46161.586246770836</v>
@@ -10041,7 +10044,7 @@
         <v>46223.583969479165</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10050,7 +10053,7 @@
         <v>76</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I145" s="9">
         <v>46303</v>
@@ -10068,13 +10071,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10084,7 +10087,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B146" s="5">
         <v>46161.586256435185</v>
@@ -10094,7 +10097,7 @@
         <v>46223.58396876157</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10103,7 +10106,7 @@
         <v>76</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I146" s="5">
         <v>46303</v>
@@ -10121,13 +10124,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10137,7 +10140,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B147" s="9">
         <v>46161.586265833335</v>
@@ -10147,7 +10150,7 @@
         <v>46223.5839677662</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10156,7 +10159,7 @@
         <v>76</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I147" s="9">
         <v>46303</v>
@@ -10174,13 +10177,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10190,7 +10193,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B148" s="5">
         <v>46161.586275671296</v>
@@ -10200,7 +10203,7 @@
         <v>46223.58396645833</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10209,7 +10212,7 @@
         <v>76</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I148" s="5">
         <v>46303</v>
@@ -10227,13 +10230,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10243,7 +10246,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B149" s="9">
         <v>46161.58629186342</v>
@@ -10253,7 +10256,7 @@
         <v>46223.58396577546</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10262,7 +10265,7 @@
         <v>76</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I149" s="9">
         <v>46303</v>
@@ -10280,13 +10283,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10296,7 +10299,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B150" s="5">
         <v>46161.58630879629</v>
@@ -10306,7 +10309,7 @@
         <v>46223.58396513889</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10315,7 +10318,7 @@
         <v>76</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I150" s="5">
         <v>46303</v>
@@ -10333,13 +10336,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10349,7 +10352,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B151" s="9">
         <v>46161.58632163194</v>
@@ -10359,7 +10362,7 @@
         <v>46223.583964537036</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10368,7 +10371,7 @@
         <v>76</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I151" s="9">
         <v>46303</v>
@@ -10386,13 +10389,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10402,7 +10405,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B152" s="5">
         <v>46161.5811646875</v>
@@ -10412,7 +10415,7 @@
         <v>46223.5849177662</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10421,7 +10424,7 @@
         <v>76</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I152" s="5">
         <v>46307</v>
@@ -10439,13 +10442,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q152" s="5">
         <v>46307</v>
@@ -10460,12 +10463,12 @@
         <v>0</v>
       </c>
       <c r="U152" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B153" s="9">
         <v>46161.58116828704</v>
@@ -10475,7 +10478,7 @@
         <v>46223.584198055556</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10484,7 +10487,7 @@
         <v>76</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
@@ -10500,13 +10503,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10516,7 +10519,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B154" s="5">
         <v>46161.63912622685</v>
@@ -10526,7 +10529,7 @@
         <v>46223.5841919213</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10535,7 +10538,7 @@
         <v>76</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I154" s="6"/>
       <c r="J154" s="5">
@@ -10551,10 +10554,10 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10567,7 +10570,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B155" s="9">
         <v>46161.63913737268</v>
@@ -10577,7 +10580,7 @@
         <v>46223.5841909375</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10586,7 +10589,7 @@
         <v>76</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I155" s="10"/>
       <c r="J155" s="9">
@@ -10602,10 +10605,10 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>26</v>
@@ -10618,7 +10621,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B156" s="5">
         <v>46161.63914719908</v>
@@ -10628,7 +10631,7 @@
         <v>46223.58419032407</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10637,7 +10640,7 @@
         <v>76</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I156" s="6"/>
       <c r="J156" s="5">
@@ -10653,10 +10656,10 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>26</v>
@@ -10669,7 +10672,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B157" s="9">
         <v>46161.639157557875</v>
@@ -10679,7 +10682,7 @@
         <v>46223.584189699075</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10688,7 +10691,7 @@
         <v>76</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I157" s="10"/>
       <c r="J157" s="9">
@@ -10704,10 +10707,10 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>26</v>
@@ -10720,7 +10723,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B158" s="5">
         <v>46161.6391721875</v>
@@ -10730,7 +10733,7 @@
         <v>46223.58418898148</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10739,7 +10742,7 @@
         <v>76</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I158" s="6"/>
       <c r="J158" s="5">
@@ -10755,10 +10758,10 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10771,7 +10774,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B159" s="9">
         <v>46161.639187395835</v>
@@ -10781,7 +10784,7 @@
         <v>46223.58418828704</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10790,7 +10793,7 @@
         <v>76</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I159" s="10"/>
       <c r="J159" s="9">
@@ -10806,10 +10809,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>26</v>
@@ -10822,7 +10825,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B160" s="5">
         <v>46161.639195289354</v>
@@ -10832,7 +10835,7 @@
         <v>46223.584187650464</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10841,7 +10844,7 @@
         <v>76</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I160" s="6"/>
       <c r="J160" s="5">
@@ -10857,10 +10860,10 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>26</v>
@@ -10873,7 +10876,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B161" s="9">
         <v>46161.63920550926</v>
@@ -10883,7 +10886,7 @@
         <v>46223.58418706019</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10892,7 +10895,7 @@
         <v>76</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I161" s="10"/>
       <c r="J161" s="9">
@@ -10908,10 +10911,10 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>26</v>
@@ -10924,7 +10927,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B162" s="5">
         <v>46161.63921432871</v>
@@ -10934,7 +10937,7 @@
         <v>46223.58418637731</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -10943,7 +10946,7 @@
         <v>76</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I162" s="6"/>
       <c r="J162" s="5">
@@ -10959,13 +10962,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10975,7 +10978,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B163" s="9">
         <v>46161.58117752315</v>
@@ -10985,7 +10988,7 @@
         <v>46223.58491697916</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -10994,7 +10997,7 @@
         <v>76</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I163" s="9">
         <v>46309</v>
@@ -11012,13 +11015,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q163" s="9">
         <v>46309</v>
@@ -11033,12 +11036,12 @@
         <v>0</v>
       </c>
       <c r="U163" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B164" s="5">
         <v>46161.58118137732</v>
@@ -11048,7 +11051,7 @@
         <v>46223.584646874995</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11057,7 +11060,7 @@
         <v>76</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I164" s="5">
         <v>46309</v>
@@ -11075,13 +11078,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11091,7 +11094,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B165" s="9">
         <v>46161.639253761576</v>
@@ -11101,7 +11104,7 @@
         <v>46223.584646261574</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11110,7 +11113,7 @@
         <v>76</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I165" s="9">
         <v>46309</v>
@@ -11128,10 +11131,10 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P165" s="10" t="s">
         <v>26</v>
@@ -11144,7 +11147,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B166" s="5">
         <v>46161.63928710648</v>
@@ -11154,7 +11157,7 @@
         <v>46223.5846455787</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11163,7 +11166,7 @@
         <v>76</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I166" s="5">
         <v>46309</v>
@@ -11181,10 +11184,10 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11197,7 +11200,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B167" s="9">
         <v>46161.63929736111</v>
@@ -11207,7 +11210,7 @@
         <v>46223.58464490741</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11216,7 +11219,7 @@
         <v>76</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I167" s="9">
         <v>46309</v>
@@ -11234,10 +11237,10 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P167" s="10" t="s">
         <v>26</v>
@@ -11250,7 +11253,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B168" s="5">
         <v>46161.6393071412</v>
@@ -11260,7 +11263,7 @@
         <v>46223.58464418982</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11269,7 +11272,7 @@
         <v>76</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I168" s="5">
         <v>46309</v>
@@ -11287,10 +11290,10 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>26</v>
@@ -11303,7 +11306,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B169" s="9">
         <v>46161.639315625</v>
@@ -11313,7 +11316,7 @@
         <v>46223.58464350694</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11322,7 +11325,7 @@
         <v>76</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I169" s="9">
         <v>46309</v>
@@ -11340,10 +11343,10 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11356,7 +11359,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B170" s="5">
         <v>46161.63932686343</v>
@@ -11366,7 +11369,7 @@
         <v>46223.58464282408</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11375,7 +11378,7 @@
         <v>76</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I170" s="5">
         <v>46309</v>
@@ -11393,10 +11396,10 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11409,7 +11412,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B171" s="9">
         <v>46161.63933708333</v>
@@ -11419,7 +11422,7 @@
         <v>46223.584642118054</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11428,7 +11431,7 @@
         <v>76</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I171" s="9">
         <v>46309</v>
@@ -11446,10 +11449,10 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>26</v>
@@ -11462,7 +11465,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B172" s="5">
         <v>46161.63935484954</v>
@@ -11472,7 +11475,7 @@
         <v>46223.58464141204</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11481,7 +11484,7 @@
         <v>76</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I172" s="5">
         <v>46309</v>
@@ -11499,10 +11502,10 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>26</v>
@@ -11515,7 +11518,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B173" s="9">
         <v>46161.63936453704</v>
@@ -11525,7 +11528,7 @@
         <v>46223.58464068287</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11534,7 +11537,7 @@
         <v>76</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I173" s="9">
         <v>46309</v>
@@ -11552,13 +11555,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11568,7 +11571,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B174" s="5">
         <v>46161.5811852662</v>
@@ -11578,7 +11581,7 @@
         <v>46161.84092732639</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>25</v>
@@ -11602,7 +11605,7 @@
         <v>26</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>26</v>
@@ -11615,7 +11618,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B175" s="9">
         <v>46161.581188020835</v>
@@ -11625,16 +11628,16 @@
         <v>46161.84675815972</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I175" s="9">
         <v>46310</v>
@@ -11652,13 +11655,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q175" s="9">
         <v>46310</v>
@@ -11673,12 +11676,12 @@
         <v>0</v>
       </c>
       <c r="U175" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B176" s="5">
         <v>46161.581192673606</v>
@@ -11688,16 +11691,16 @@
         <v>46161.846749351855</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I176" s="5">
         <v>46310</v>
@@ -11715,13 +11718,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11731,7 +11734,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B177" s="9">
         <v>46161.63982708333</v>
@@ -11741,16 +11744,16 @@
         <v>46161.84674655093</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I177" s="9">
         <v>46310</v>
@@ -11768,13 +11771,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11784,7 +11787,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B178" s="5">
         <v>46161.63983532407</v>
@@ -11794,16 +11797,16 @@
         <v>46161.846743981485</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I178" s="5">
         <v>46310</v>
@@ -11821,13 +11824,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11837,7 +11840,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B179" s="9">
         <v>46161.63984421296</v>
@@ -11847,16 +11850,16 @@
         <v>46161.84674143518</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I179" s="9">
         <v>46310</v>
@@ -11874,13 +11877,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11890,7 +11893,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B180" s="5">
         <v>46161.63985878472</v>
@@ -11900,16 +11903,16 @@
         <v>46161.846738541666</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I180" s="5">
         <v>46310</v>
@@ -11927,13 +11930,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11943,7 +11946,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B181" s="9">
         <v>46161.63986780093</v>
@@ -11953,16 +11956,16 @@
         <v>46161.84673559028</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I181" s="9">
         <v>46310</v>
@@ -11980,13 +11983,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11996,7 +11999,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B182" s="5">
         <v>46161.639875</v>
@@ -12006,16 +12009,16 @@
         <v>46161.84673289352</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I182" s="5">
         <v>46310</v>
@@ -12033,13 +12036,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12049,7 +12052,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B183" s="9">
         <v>46161.63988342593</v>
@@ -12059,16 +12062,16 @@
         <v>46161.84672489583</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I183" s="9">
         <v>46310</v>
@@ -12086,13 +12089,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12102,7 +12105,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B184" s="5">
         <v>46161.63989143519</v>
@@ -12112,16 +12115,16 @@
         <v>46161.84672420139</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I184" s="5">
         <v>46310</v>
@@ -12139,13 +12142,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12155,7 +12158,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B185" s="9">
         <v>46161.639899340276</v>
@@ -12165,16 +12168,16 @@
         <v>46161.84672340278</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I185" s="9">
         <v>46310</v>
@@ -12192,13 +12195,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12208,7 +12211,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B186" s="5">
         <v>46161.5811965162</v>
@@ -12218,7 +12221,7 @@
         <v>46223.585025</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12227,7 +12230,7 @@
         <v>76</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I186" s="5">
         <v>46311</v>
@@ -12245,13 +12248,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q186" s="5">
         <v>46311</v>
@@ -12266,12 +12269,12 @@
         <v>0</v>
       </c>
       <c r="U186" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B187" s="9">
         <v>46161.58120002315</v>
@@ -12281,7 +12284,7 @@
         <v>46223.58481888889</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12290,7 +12293,7 @@
         <v>76</v>
       </c>
       <c r="H187" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I187" s="9">
         <v>46311</v>
@@ -12308,13 +12311,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12324,7 +12327,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B188" s="5">
         <v>46161.63993424768</v>
@@ -12334,7 +12337,7 @@
         <v>46223.58481829861</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12343,7 +12346,7 @@
         <v>76</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I188" s="5">
         <v>46311</v>
@@ -12361,13 +12364,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12377,7 +12380,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B189" s="9">
         <v>46161.6399947801</v>
@@ -12387,7 +12390,7 @@
         <v>46223.584817662035</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12396,7 +12399,7 @@
         <v>76</v>
       </c>
       <c r="H189" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I189" s="9">
         <v>46311</v>
@@ -12414,13 +12417,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12430,7 +12433,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B190" s="5">
         <v>46161.640004444445</v>
@@ -12440,7 +12443,7 @@
         <v>46223.584817083334</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12449,7 +12452,7 @@
         <v>76</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I190" s="5">
         <v>46311</v>
@@ -12467,13 +12470,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12483,7 +12486,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B191" s="9">
         <v>46161.64001501157</v>
@@ -12493,7 +12496,7 @@
         <v>46223.58481644676</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12502,7 +12505,7 @@
         <v>76</v>
       </c>
       <c r="H191" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I191" s="9">
         <v>46311</v>
@@ -12520,13 +12523,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12536,7 +12539,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B192" s="5">
         <v>46161.640023831016</v>
@@ -12546,7 +12549,7 @@
         <v>46223.58481584491</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12555,7 +12558,7 @@
         <v>76</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I192" s="5">
         <v>46311</v>
@@ -12573,13 +12576,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12589,7 +12592,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B193" s="9">
         <v>46161.640038310186</v>
@@ -12599,7 +12602,7 @@
         <v>46223.58481525463</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12608,7 +12611,7 @@
         <v>76</v>
       </c>
       <c r="H193" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I193" s="9">
         <v>46311</v>
@@ -12626,13 +12629,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12642,7 +12645,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B194" s="5">
         <v>46161.64004747685</v>
@@ -12652,7 +12655,7 @@
         <v>46223.58481465278</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12661,7 +12664,7 @@
         <v>76</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I194" s="5">
         <v>46311</v>
@@ -12679,13 +12682,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12695,7 +12698,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B195" s="9">
         <v>46161.64005649305</v>
@@ -12705,7 +12708,7 @@
         <v>46223.5848140625</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -12714,7 +12717,7 @@
         <v>76</v>
       </c>
       <c r="H195" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I195" s="9">
         <v>46311</v>
@@ -12732,13 +12735,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12748,7 +12751,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B196" s="5">
         <v>46161.64006346065</v>
@@ -12758,7 +12761,7 @@
         <v>46223.58481342593</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12767,7 +12770,7 @@
         <v>76</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I196" s="5">
         <v>46311</v>
@@ -12785,13 +12788,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12801,7 +12804,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B197" s="9">
         <v>46161.58120399306</v>
@@ -12811,16 +12814,16 @@
         <v>46161.84710645833</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H197" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I197" s="10"/>
       <c r="J197" s="9">
@@ -12836,13 +12839,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q197" s="9">
         <v>46316</v>
@@ -12857,12 +12860,12 @@
         <v>0</v>
       </c>
       <c r="U197" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B198" s="5">
         <v>46161.58120755787</v>
@@ -12872,16 +12875,16 @@
         <v>46161.847077812505</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -12897,13 +12900,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12913,7 +12916,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B199" s="9">
         <v>46161.6401252662</v>
@@ -12923,16 +12926,16 @@
         <v>46161.84707505787</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -12948,13 +12951,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12964,7 +12967,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B200" s="5">
         <v>46161.64014137731</v>
@@ -12974,16 +12977,16 @@
         <v>46161.847072476856</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -12999,13 +13002,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13015,7 +13018,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B201" s="9">
         <v>46161.64015293981</v>
@@ -13025,16 +13028,16 @@
         <v>46161.84706930556</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -13050,13 +13053,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13066,7 +13069,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B202" s="5">
         <v>46161.64016740741</v>
@@ -13076,16 +13079,16 @@
         <v>46161.847066608796</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13101,13 +13104,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13117,7 +13120,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B203" s="9">
         <v>46161.640203877316</v>
@@ -13127,16 +13130,16 @@
         <v>46161.84706402778</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -13152,13 +13155,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13168,7 +13171,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B204" s="5">
         <v>46161.64021510417</v>
@@ -13178,16 +13181,16 @@
         <v>46161.84706112268</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13203,13 +13206,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13219,7 +13222,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B205" s="9">
         <v>46161.64022702546</v>
@@ -13229,16 +13232,16 @@
         <v>46161.847053425925</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13254,13 +13257,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13270,7 +13273,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B206" s="5">
         <v>46161.64023784723</v>
@@ -13280,16 +13283,16 @@
         <v>46161.8470527662</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13305,13 +13308,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13321,7 +13324,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B207" s="9">
         <v>46161.64025311342</v>
@@ -13331,16 +13334,16 @@
         <v>46161.84705210648</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13356,13 +13359,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13372,7 +13375,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B208" s="5">
         <v>46161.58121466435</v>
@@ -13382,16 +13385,16 @@
         <v>46161.84730193287</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I208" s="5">
         <v>46317</v>
@@ -13409,13 +13412,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q208" s="5">
         <v>46317</v>
@@ -13430,12 +13433,12 @@
         <v>0</v>
       </c>
       <c r="U208" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B209" s="9">
         <v>46161.58125732639</v>
@@ -13445,16 +13448,16 @@
         <v>46161.84728091436</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I209" s="10"/>
       <c r="J209" s="9">
@@ -13470,13 +13473,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13486,7 +13489,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B210" s="5">
         <v>46161.640307905094</v>
@@ -13496,16 +13499,16 @@
         <v>46161.84727769676</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13521,10 +13524,10 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>26</v>
@@ -13537,7 +13540,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B211" s="9">
         <v>46161.64031635417</v>
@@ -13547,16 +13550,16 @@
         <v>46161.84727525463</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I211" s="10"/>
       <c r="J211" s="9">
@@ -13572,10 +13575,10 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>26</v>
@@ -13588,7 +13591,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B212" s="5">
         <v>46161.64032832176</v>
@@ -13598,16 +13601,16 @@
         <v>46161.84727247685</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13623,10 +13626,10 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>26</v>
@@ -13639,7 +13642,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B213" s="9">
         <v>46161.640337986115</v>
@@ -13649,16 +13652,16 @@
         <v>46161.84726945602</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I213" s="10"/>
       <c r="J213" s="9">
@@ -13674,10 +13677,10 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>26</v>
@@ -13690,7 +13693,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B214" s="5">
         <v>46161.64035862268</v>
@@ -13700,16 +13703,16 @@
         <v>46161.84726638889</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13725,10 +13728,10 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13741,7 +13744,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B215" s="9">
         <v>46161.64036773148</v>
@@ -13751,16 +13754,16 @@
         <v>46161.84726359954</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I215" s="10"/>
       <c r="J215" s="9">
@@ -13776,10 +13779,10 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13792,7 +13795,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B216" s="5">
         <v>46161.64037657407</v>
@@ -13802,16 +13805,16 @@
         <v>46161.84726060185</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13827,10 +13830,10 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>26</v>
@@ -13843,7 +13846,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B217" s="9">
         <v>46161.64038473379</v>
@@ -13853,16 +13856,16 @@
         <v>46161.847254699074</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I217" s="10"/>
       <c r="J217" s="9">
@@ -13878,10 +13881,10 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>26</v>
@@ -13894,7 +13897,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B218" s="5">
         <v>46161.64039350694</v>
@@ -13904,16 +13907,16 @@
         <v>46161.8472540625</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -13929,10 +13932,10 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>26</v>
@@ -13945,7 +13948,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B219" s="9">
         <v>46161.581262824075</v>
@@ -13955,7 +13958,7 @@
         <v>46161.84801045139</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>25</v>
@@ -13979,7 +13982,7 @@
         <v>26</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>26</v>
@@ -13992,7 +13995,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B220" s="5">
         <v>46161.58126615741</v>
@@ -14002,16 +14005,16 @@
         <v>46161.84764756945</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I220" s="5">
         <v>46318</v>
@@ -14029,13 +14032,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q220" s="5">
         <v>46318</v>
@@ -14050,12 +14053,12 @@
         <v>0</v>
       </c>
       <c r="U220" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B221" s="9">
         <v>46161.581270821756</v>
@@ -14065,7 +14068,7 @@
         <v>46198.80656221065</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -14092,13 +14095,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q221" s="9">
         <v>46318</v>
@@ -14113,7 +14116,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
+++ b/data/50001555 - ZITRON COLOMBIA ARIS MINING SEGOVIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="451">
   <si>
     <t>50001555 - "ZITRON COLOMBIA ARIS MINING SEGOVIA"</t>
   </si>
@@ -335,9 +335,6 @@
   </si>
   <si>
     <t>Generación OC materiales corte Laser ot 4332,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214952151057796</t>
@@ -2934,7 +2931,7 @@
         <v>46204.90066085648</v>
       </c>
       <c r="D18" s="5">
-        <v>46223.58333158564</v>
+        <v>46226.17802471065</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2978,8 +2975,8 @@
       <c r="R18" s="5">
         <v>46225</v>
       </c>
-      <c r="S18" s="11" t="s">
-        <v>83</v>
+      <c r="S18" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2990,7 +2987,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9">
         <v>46161.58080373843</v>
@@ -2999,10 +2996,10 @@
         <v>46204.90101555556</v>
       </c>
       <c r="D19" s="9">
-        <v>46223.58332738426</v>
+        <v>46226.17802467593</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -3035,7 +3032,7 @@
         <v>81</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="9">
         <v>46224</v>
@@ -3043,8 +3040,8 @@
       <c r="R19" s="9">
         <v>46225</v>
       </c>
-      <c r="S19" s="11" t="s">
-        <v>83</v>
+      <c r="S19" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -3055,7 +3052,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46161.58080740741</v>
@@ -3064,10 +3061,10 @@
         <v>46204.90180252315</v>
       </c>
       <c r="D20" s="5">
-        <v>46223.5833241088</v>
+        <v>46226.17802466435</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3100,7 +3097,7 @@
         <v>81</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -3108,8 +3105,8 @@
       <c r="R20" s="5">
         <v>46225</v>
       </c>
-      <c r="S20" s="11" t="s">
-        <v>83</v>
+      <c r="S20" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -3120,7 +3117,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9">
         <v>46161.580810740736</v>
@@ -3129,10 +3126,10 @@
         <v>46204.90175329861</v>
       </c>
       <c r="D21" s="9">
-        <v>46223.58331811342</v>
+        <v>46226.17802467593</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -3165,7 +3162,7 @@
         <v>81</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="9">
         <v>46224</v>
@@ -3173,8 +3170,8 @@
       <c r="R21" s="9">
         <v>46225</v>
       </c>
-      <c r="S21" s="11" t="s">
-        <v>83</v>
+      <c r="S21" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -3185,7 +3182,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46161.58064796297</v>
@@ -3195,7 +3192,7 @@
         <v>46211.83005701389</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -3219,7 +3216,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -3232,7 +3229,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" s="9">
         <v>46161.58081472223</v>
@@ -3244,16 +3241,16 @@
         <v>46209.56551446759</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I23" s="9">
         <v>46168</v>
@@ -3271,13 +3268,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="9">
         <v>46168</v>
@@ -3297,7 +3294,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46161.580819